--- a/key検討用/ppxkey.xlsx
+++ b/key検討用/ppxkey.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gocho\Desktop\ppx_cust20251217(Wed)\ppx_cust\key検討用\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B57BD6-33C8-44AD-BF55-ECB98CC51218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F06A61F-B467-4AAE-9809-9FCBEB5609A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19080" yWindow="5355" windowWidth="24240" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="1431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="1430">
   <si>
     <t>キー</t>
   </si>
@@ -1410,6 +1410,9 @@
     <t>[Ctrl+Shift+G]</t>
   </si>
   <si>
+    <t>エントリパスを補完リストに登録</t>
+  </si>
+  <si>
     <t>%k"^\G"</t>
   </si>
   <si>
@@ -3537,782 +3540,854 @@
     <t>参考URL</t>
   </si>
   <si>
+    <t>Qalculate!</t>
+  </si>
+  <si>
+    <t>単位変換・為替・物理定数などに対応した多機能な高度計算機</t>
+  </si>
+  <si>
+    <t>UMIOCR</t>
+  </si>
+  <si>
+    <t>画像ファイルのOCRテキスト一括出力・画像ファイル検索（日本語OCR対応）</t>
+  </si>
+  <si>
     <t>allrename</t>
   </si>
   <si>
     <t>正規表現なしのリネーム　テキストエディタでリネーム</t>
   </si>
   <si>
+    <t>aria2</t>
+  </si>
+  <si>
+    <t>ダウンローダ</t>
+  </si>
+  <si>
+    <t>autohotkey</t>
+  </si>
+  <si>
+    <t>Windows自動化</t>
+  </si>
+  <si>
+    <t>azurecui</t>
+  </si>
+  <si>
+    <t>JPEG無劣化回転・自動回転</t>
+  </si>
+  <si>
+    <t>browserie</t>
+  </si>
+  <si>
+    <t>IEエンジンのブラウザ</t>
+  </si>
+  <si>
+    <t>bulkfilechanger</t>
+  </si>
+  <si>
+    <t>ファイルの属性・タイムスタンプ一括変更</t>
+  </si>
+  <si>
+    <t>busybox</t>
+  </si>
+  <si>
+    <t>Unixコマンド Unicode版あり。</t>
+  </si>
+  <si>
+    <t>claunch</t>
+  </si>
+  <si>
+    <t>マウスで操作するランチャ</t>
+  </si>
+  <si>
+    <t>clsclose</t>
+  </si>
+  <si>
+    <t>マウスクリックで窓を強制終了</t>
+  </si>
+  <si>
+    <t>ct</t>
+  </si>
+  <si>
+    <t>タイムスタンプのコピー</t>
+  </si>
+  <si>
+    <t>dialoghandler</t>
+  </si>
+  <si>
+    <t>ダイアログにエントリのパスを送る</t>
+  </si>
+  <si>
+    <t>dibas32</t>
+  </si>
+  <si>
+    <t>画像編集ソフト</t>
+  </si>
+  <si>
+    <t>dockshow</t>
+  </si>
+  <si>
+    <t>メディアプレーヤー</t>
+  </si>
+  <si>
+    <t>dre</t>
+  </si>
+  <si>
+    <t>重複画像削除</t>
+  </si>
+  <si>
+    <t>duplicatecleaner</t>
+  </si>
+  <si>
+    <t>重複ファイル/重複画像削除(free版あり）</t>
+  </si>
+  <si>
+    <t>ebook-convert</t>
+  </si>
+  <si>
+    <t>電子書籍のテキスト一括変換（Calibreに同梱）</t>
+  </si>
+  <si>
+    <t>ebook-viewer</t>
+  </si>
+  <si>
+    <t>電子書籍ビューア（Calibreに同梱）</t>
+  </si>
+  <si>
+    <t>emeditor</t>
+  </si>
+  <si>
+    <t>高速なエディタ</t>
+  </si>
+  <si>
+    <t>es</t>
+  </si>
+  <si>
+    <t>Everythingをコマンドラインで操作</t>
+  </si>
+  <si>
+    <t>everything</t>
+  </si>
+  <si>
+    <t>ファイルを超高速検索・重複ファイル抽出</t>
+  </si>
+  <si>
+    <t>exiftool</t>
+  </si>
+  <si>
+    <t>EXIF情報閲覧・デジカメのリネーム</t>
+  </si>
+  <si>
+    <t>fastcopy</t>
+  </si>
+  <si>
+    <t>高速ファイルコピー・移動・削除</t>
+  </si>
+  <si>
+    <t>fenrirscan</t>
+  </si>
+  <si>
+    <t>ディレクトリパスリスト生成（[Shift+G]用）</t>
+  </si>
+  <si>
+    <t>ffmpeg</t>
+  </si>
+  <si>
+    <t>動画形式変換</t>
+  </si>
+  <si>
+    <t>filediver</t>
+  </si>
+  <si>
+    <t>Officeファイル・圧縮ファイルのGrep</t>
+  </si>
+  <si>
+    <t>filesum</t>
+  </si>
+  <si>
+    <t>フォルダサイズ分析</t>
+  </si>
+  <si>
+    <t>filetypesman</t>
+  </si>
+  <si>
+    <t>ファイルの関連づけ編集</t>
+  </si>
+  <si>
+    <t>fittle</t>
+  </si>
+  <si>
+    <t>音楽ファイル再生</t>
+  </si>
+  <si>
+    <t>fitwin</t>
+  </si>
+  <si>
+    <t>ウィンドウを並べる</t>
+  </si>
+  <si>
+    <t>flaxc</t>
+  </si>
+  <si>
+    <t>画像の減色</t>
+  </si>
+  <si>
+    <t>foldertimeupdate</t>
+  </si>
+  <si>
+    <t>フォルダのタイムスタンプをフォルダ内の最新ファイルに合わせる</t>
+  </si>
+  <si>
+    <t>gb</t>
+  </si>
+  <si>
+    <t>コマンドラインで動くごみ箱</t>
+  </si>
+  <si>
+    <t>irfanview</t>
+  </si>
+  <si>
+    <t>簡易画像エディタ・サムネイル画像生成</t>
+  </si>
+  <si>
+    <t>ish</t>
+  </si>
+  <si>
+    <t>バイナリファイルのテキスト化</t>
+  </si>
+  <si>
+    <t>ls2lf</t>
+  </si>
+  <si>
+    <t>ファイルリストをPPxのリストファイルへ変換（aux path sampleに同梱）</t>
+  </si>
+  <si>
+    <t>magick</t>
+  </si>
+  <si>
+    <t>画像変換</t>
+  </si>
+  <si>
+    <t>mediainfo(CLI版)</t>
+  </si>
+  <si>
+    <t>音楽・動画ファイル情報取得</t>
+  </si>
+  <si>
+    <t>mery</t>
+  </si>
+  <si>
+    <t>テキストエディタ</t>
+  </si>
+  <si>
+    <t>mp3tag</t>
+  </si>
+  <si>
+    <t>MP3タグエディタ（GUI操作向け）</t>
+  </si>
+  <si>
+    <t>msdos</t>
+  </si>
+  <si>
+    <t>古いDOSアプリを64bitで動かす</t>
+  </si>
+  <si>
+    <t>multiwallpaper</t>
+  </si>
+  <si>
+    <t>マルチモニタ環境でモニタ毎に別々の壁紙を貼る</t>
+  </si>
+  <si>
+    <t>musicbranz picard</t>
+  </si>
+  <si>
+    <t>MP3タグエディタ（MusicBrainzデータベース連携）</t>
+  </si>
+  <si>
+    <t>neeview</t>
+  </si>
+  <si>
+    <t>書庫内画像ビューア</t>
+  </si>
+  <si>
+    <t>nircmd</t>
+  </si>
+  <si>
+    <t>キーボードで音量調整など</t>
+  </si>
+  <si>
+    <t>nkf</t>
+  </si>
+  <si>
+    <t>文字コード変換</t>
+  </si>
+  <si>
+    <t>omegachart</t>
+  </si>
+  <si>
+    <t>株チャート</t>
+  </si>
+  <si>
+    <t>optiopenxml</t>
+  </si>
+  <si>
+    <t>Officeファイル最適化（NXPowerlite相当）</t>
+  </si>
+  <si>
+    <t>oscdimg</t>
+  </si>
+  <si>
+    <t>ISOファイル作成</t>
+  </si>
+  <si>
+    <t>otvdm</t>
+  </si>
+  <si>
+    <t>古いWindows16bitアプリを64bitで動かす</t>
+  </si>
+  <si>
+    <t>pandoc</t>
+  </si>
+  <si>
+    <t>ドキュメント形式変換（md/docx/html等）</t>
+  </si>
+  <si>
+    <t>pathstore</t>
+  </si>
+  <si>
+    <t>パスを記録してあとで一気に使う</t>
+  </si>
+  <si>
+    <t>pathtoclip</t>
+  </si>
+  <si>
+    <t>パスをクリップボードへコピー</t>
+  </si>
+  <si>
+    <t>pdfcpu</t>
+  </si>
+  <si>
+    <t>PDFファイルの操作</t>
+  </si>
+  <si>
+    <t>photoshop</t>
+  </si>
+  <si>
+    <t>写真編集(5.0のセットアップはIS3ENGINEを使う)</t>
+  </si>
+  <si>
+    <t>picturefan</t>
+  </si>
+  <si>
+    <t>画像サムネイル＋簡易編集</t>
+  </si>
+  <si>
+    <t>rapidee</t>
+  </si>
+  <si>
+    <t>環境変数の編集</t>
+  </si>
+  <si>
+    <t>rapture</t>
+  </si>
+  <si>
+    <t>デスクトップキャプチャ</t>
+  </si>
+  <si>
+    <t>rar</t>
+  </si>
+  <si>
+    <t>RAR,ZIPファイルの圧縮・解凍（コンソール版）</t>
+  </si>
+  <si>
+    <t>realesrgan</t>
+  </si>
+  <si>
+    <t>画像の超解像処理</t>
+  </si>
+  <si>
+    <t>rg</t>
+  </si>
+  <si>
+    <t>テキストファイルの高速なGrep</t>
+  </si>
+  <si>
+    <t>rrpatch</t>
+  </si>
+  <si>
+    <t>バイナリパッチ適用ツール</t>
+  </si>
+  <si>
+    <t>sakura</t>
+  </si>
+  <si>
+    <t>派生版sakuraVzが高速</t>
+  </si>
+  <si>
+    <t>scrdbg</t>
+  </si>
+  <si>
+    <t>VBScriptのデバッガ</t>
+  </si>
+  <si>
+    <t>shellexview</t>
+  </si>
+  <si>
+    <t>シェルエクステンション一覧表示</t>
+  </si>
+  <si>
+    <t>shellmenuview</t>
+  </si>
+  <si>
+    <t>コンテキストメニューの項目一覧表示</t>
+  </si>
+  <si>
+    <t>shukusen</t>
+  </si>
+  <si>
+    <t>画像サイズを一括で縮小</t>
+  </si>
+  <si>
+    <t>simplemount</t>
+  </si>
+  <si>
+    <t>ISOファイルへのドライブの割り当て</t>
+  </si>
+  <si>
+    <t>soyokaze</t>
+  </si>
+  <si>
+    <t>BlueWind風ランチャ</t>
+  </si>
+  <si>
+    <t>step</t>
+  </si>
+  <si>
+    <t>MP3タグエディタ（軽量・シンプル操作向け）</t>
+  </si>
+  <si>
+    <t>tresgrep</t>
+  </si>
+  <si>
+    <t>OfficeファイルのWz風Grep</t>
+  </si>
+  <si>
+    <t>undup</t>
+  </si>
+  <si>
+    <t>重複ファイル削除</t>
+  </si>
+  <si>
+    <t>uniextract</t>
+  </si>
+  <si>
+    <t>通常では解凍できない形式を解凍</t>
+  </si>
+  <si>
+    <t>vant</t>
+  </si>
+  <si>
+    <t>メモソフト</t>
+  </si>
+  <si>
+    <t>videoLAN</t>
+  </si>
+  <si>
+    <t>VLC：コーデック内蔵動画プレーヤ</t>
+  </si>
+  <si>
+    <t>vscode</t>
+  </si>
+  <si>
+    <t>プログラムエディタ</t>
+  </si>
+  <si>
+    <t>windowspy</t>
+  </si>
+  <si>
+    <t>ウィンドウハンドルを調べる(Autohotkeyに付属)</t>
+  </si>
+  <si>
+    <t>winexchange</t>
+  </si>
+  <si>
+    <t>ファイルタイプを判別して正しい拡張子をつける</t>
+  </si>
+  <si>
+    <t>winmerge</t>
+  </si>
+  <si>
+    <t>ファイル比較</t>
+  </si>
+  <si>
+    <t>winrar</t>
+  </si>
+  <si>
+    <t>RAR,ZIPファイルの圧縮・解凍</t>
+  </si>
+  <si>
+    <t>wiztree</t>
+  </si>
+  <si>
+    <t>xdoc2txt</t>
+  </si>
+  <si>
+    <t>OfficeファイルやPDFをテキスト化</t>
+  </si>
+  <si>
+    <t>zoxide</t>
+  </si>
+  <si>
+    <t>使用頻度に基づくディレクトリジャンプ補完</t>
+  </si>
+  <si>
+    <t>エクスプローラ拡張</t>
+  </si>
+  <si>
+    <t>ifilter4archives</t>
+  </si>
+  <si>
+    <t>ifilter対応ビューアで書庫の中身を見る</t>
+  </si>
+  <si>
+    <t>https://github.com/Meitinger/iFilter4Archives</t>
+  </si>
+  <si>
+    <t>DarkThumbs</t>
+  </si>
+  <si>
+    <t>書庫ファイルや電子書籍にサムネイル付加</t>
+  </si>
+  <si>
+    <t>https://github.com/fire-eggs/DarkThumbs</t>
+  </si>
+  <si>
+    <t>cleanflash</t>
+  </si>
+  <si>
+    <t>今でもインストールできるFlash</t>
+  </si>
+  <si>
+    <t>https://github.com/darktohka/clean-flash-builds</t>
+  </si>
+  <si>
+    <t>https://www.haijin-boys.com/wiki/%E3%83%A1%E3%82%A4%E3%83%B3%E3%83%9A%E3%83%BC%E3%82%B8</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>https://beefway.sakura.ne.jp/dl-allrename.html</t>
-  </si>
-  <si>
-    <t>aria2</t>
-  </si>
-  <si>
-    <t>ダウンローダ</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://aria2.github.io</t>
-  </si>
-  <si>
-    <t>autohotkey</t>
-  </si>
-  <si>
-    <t>Windows自動化</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.autohotkey.com</t>
-  </si>
-  <si>
-    <t>azurecui</t>
-  </si>
-  <si>
-    <t>JPEG無劣化回転・自動回転</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.vector.co.jp/soft/winnt/art/se490883.html</t>
-  </si>
-  <si>
-    <t>browserie</t>
-  </si>
-  <si>
-    <t>IEエンジンのブラウザ</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.vector.co.jp/soft/win95/net/se305050.html</t>
-  </si>
-  <si>
-    <t>bulkfilechanger</t>
-  </si>
-  <si>
-    <t>ファイルの属性・タイムスタンプ一括変更</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.nirsoft.net/utils/bulk_file_changer.html</t>
-  </si>
-  <si>
-    <t>busybox</t>
-  </si>
-  <si>
-    <t>Unixコマンド Unicode版あり。</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://frippery.org/busybox/</t>
-  </si>
-  <si>
-    <t>calmemo</t>
-  </si>
-  <si>
-    <t>メモ帳付き電卓</t>
-  </si>
-  <si>
-    <t>https://web.archive.org/web/20130114222225/http://www.ric.hi-ho.ne.jp/many/many/calmemo.html
-https://web.archive.org/web/20130116072040/http://www.ric.hi-ho.ne.jp/many/many/lzh/calmemo.lzh</t>
-  </si>
-  <si>
-    <t>claunch</t>
-  </si>
-  <si>
-    <t>マウスで操作するランチャ</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>http://hp.vector.co.jp/authors/VA018351/</t>
-  </si>
-  <si>
-    <t>clsclose</t>
-  </si>
-  <si>
-    <t>マウスクリックで窓を強制終了</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://softkomono.chips.jp/ClsClose.html</t>
-  </si>
-  <si>
-    <t>ct</t>
-  </si>
-  <si>
-    <t>タイムスタンプのコピー</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>http://toro.d.dooo.jp/slwin4.html#ct</t>
-  </si>
-  <si>
-    <t>dialoghandler</t>
-  </si>
-  <si>
-    <t>ダイアログにエントリのパスを送る</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://frozenlib.net/dialog_handler/</t>
-  </si>
-  <si>
-    <t>dibas32</t>
-  </si>
-  <si>
-    <t>画像編集ソフト</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>http://knoa.jp/jiko/pc/dibas/
 http://knoa.jp/jiko/pc/dibas/dbs32104.lzh
 http://knoa.jp/jiko/pc/dibas/dbssusho.lzh</t>
-  </si>
-  <si>
-    <t>dockshow</t>
-  </si>
-  <si>
-    <t>メディアプレーヤー</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>http://toro.d.dooo.jp/slppx.html#ppxdockshow</t>
-  </si>
-  <si>
-    <t>dre</t>
-  </si>
-  <si>
-    <t>重複画像削除</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>http://www.windproject.sakura.ne.jp/thisnor/dre/</t>
-  </si>
-  <si>
-    <t>duplicatecleaner</t>
-  </si>
-  <si>
-    <t>重複ファイル/重複画像削除(free版あり）</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.digitalvolcano.co.uk/dcdownloads.html
 https://www.digitalvolcano.co.uk/dcdownload_versions.html
 https://maukameadows.net/duplicatecleaner/</t>
-  </si>
-  <si>
-    <t>ebook-convert</t>
-  </si>
-  <si>
-    <t>電子書籍のテキスト一括変換（Calibreに同梱）</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://calibre-ebook.com/ja/download_windows</t>
-  </si>
-  <si>
-    <t>ebook-viewer</t>
-  </si>
-  <si>
-    <t>電子書籍ビューア（Calibreに同梱）</t>
-  </si>
-  <si>
-    <t>emeditor</t>
-  </si>
-  <si>
-    <t>高速なエディタ</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://jp.emeditor.com/</t>
-  </si>
-  <si>
-    <t>es</t>
-  </si>
-  <si>
-    <t>Everythingをコマンドラインで操作</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.voidtools.com/support/everything/command_line_interface/</t>
-  </si>
-  <si>
-    <t>everything</t>
-  </si>
-  <si>
-    <t>ファイルを超高速検索・重複ファイル抽出</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.voidtools.com/downloads/</t>
-  </si>
-  <si>
-    <t>exiftool</t>
-  </si>
-  <si>
-    <t>EXIF情報閲覧・デジカメのリネーム</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://exiftool.org</t>
-  </si>
-  <si>
-    <t>fastcopy</t>
-  </si>
-  <si>
-    <t>高速ファイルコピー・移動・削除</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://fastcopy.jp</t>
-  </si>
-  <si>
-    <t>fenrirscan</t>
-  </si>
-  <si>
-    <t>ディレクトリパスリスト生成（[Shift+G]用）</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>http://hp.vector.co.jp/authors/VA026310/soft2.htm</t>
-  </si>
-  <si>
-    <t>ffmpeg</t>
-  </si>
-  <si>
-    <t>動画形式変換</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>http://ffmpeg.org/download.html</t>
-  </si>
-  <si>
-    <t>filediver</t>
-  </si>
-  <si>
-    <t>Officeファイル・圧縮ファイルのGrep</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>http://www.vector.co.jp/soft/winnt/util/se482619.html</t>
-  </si>
-  <si>
-    <t>filesum</t>
-  </si>
-  <si>
-    <t>フォルダサイズ分析</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.net3-tv.net/~m-tsuchy/tsuchy/filesum.htm</t>
-  </si>
-  <si>
-    <t>filetypesman</t>
-  </si>
-  <si>
-    <t>ファイルの関連づけ編集</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.nirsoft.net/utils/file_types_manager.html</t>
-  </si>
-  <si>
-    <t>fittle</t>
-  </si>
-  <si>
-    <t>音楽ファイル再生</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://w.atwiki.jp/fittle/pages/30.html</t>
-  </si>
-  <si>
-    <t>fitwin</t>
-  </si>
-  <si>
-    <t>ウィンドウを並べる</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://hakomo.github.io/fitwin/</t>
-  </si>
-  <si>
-    <t>flaxc</t>
-  </si>
-  <si>
-    <t>画像の減色</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://aoriika.exout.net</t>
-  </si>
-  <si>
-    <t>foldertimeupdate</t>
-  </si>
-  <si>
-    <t>フォルダのタイムスタンプをフォルダ内の最新ファイルに合わせる</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>http://www.nirsoft.net/utils/folder_time_update.html</t>
-  </si>
-  <si>
-    <t>gb</t>
-  </si>
-  <si>
-    <t>コマンドラインで動くごみ箱</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.comona.co.jp/gb.html</t>
-  </si>
-  <si>
-    <t>hidemaru</t>
-  </si>
-  <si>
-    <t>テキストエディタ</t>
-  </si>
-  <si>
-    <t>https://hide.maruo.co.jp/software/hidemaru.html</t>
-  </si>
-  <si>
-    <t>irfanview</t>
-  </si>
-  <si>
-    <t>簡易画像エディタ・サムネイル画像生成</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.irfanview.com</t>
-  </si>
-  <si>
-    <t>ish</t>
-  </si>
-  <si>
-    <t>バイナリファイルのテキスト化</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.vector.co.jp/soft/unix/util/se499536.html</t>
-  </si>
-  <si>
-    <t>ls2lf</t>
-  </si>
-  <si>
-    <t>ファイルリストをPPxのリストファイルへ変換（aux path sampleに同梱）</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>http://toro.d.dooo.jp/slppx.html#ppxaux</t>
-  </si>
-  <si>
-    <t>magick</t>
-  </si>
-  <si>
-    <t>画像変換</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://imagemagick.org/script/download.php</t>
-  </si>
-  <si>
-    <t>mediainfo(CLI版)</t>
-  </si>
-  <si>
-    <t>音楽・動画ファイル情報取得</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://mediaarea.net/en/MediaInfo/Download/Windows</t>
-  </si>
-  <si>
-    <t>mp3tag</t>
-  </si>
-  <si>
-    <t>MP3タグエディタ（GUI操作向け）</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.mp3tag.de/en/download.html</t>
-  </si>
-  <si>
-    <t>msdos</t>
-  </si>
-  <si>
-    <t>古いDOSアプリを64bitで動かす</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>http://takeda-toshiya.my.coocan.jp/msdos/</t>
-  </si>
-  <si>
-    <t>multiwallpaper</t>
-  </si>
-  <si>
-    <t>マルチモニタ環境でモニタ毎に別々の壁紙を貼る</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.vector.co.jp/soft/winnt/amuse/se388334.html</t>
-  </si>
-  <si>
-    <t>musicbranz picard</t>
-  </si>
-  <si>
-    <t>MP3タグエディタ（MusicBrainzデータベース連携）</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://picard.musicbrainz.org/</t>
-  </si>
-  <si>
-    <t>neeview</t>
-  </si>
-  <si>
-    <t>書庫内画像ビューア</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://github.com/neelabo/NeeView</t>
-  </si>
-  <si>
-    <t>nircmd</t>
-  </si>
-  <si>
-    <t>キーボードで音量調整など</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.nirsoft.net/utils/nircmd.html</t>
-  </si>
-  <si>
-    <t>nkf</t>
-  </si>
-  <si>
-    <t>文字コード変換</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.vector.co.jp/soft/win95/util/se295331.html</t>
-  </si>
-  <si>
-    <t>omegachart</t>
-  </si>
-  <si>
-    <t>株チャート</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://sourceforge.net/projects/omegachart/</t>
-  </si>
-  <si>
-    <t>optiopenxml</t>
-  </si>
-  <si>
-    <t>Officeファイル最適化（NXPowerlite相当）</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.vector.co.jp/soft/winnt/business/se510221.html</t>
-  </si>
-  <si>
-    <t>oscdimg</t>
-  </si>
-  <si>
-    <t>ISOファイル作成</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://learn.microsoft.com/ja-jp/windows-hardware/manufacture/desktop/oscdimg-command-line-options?view=windows-11</t>
-  </si>
-  <si>
-    <t>otvdm</t>
-  </si>
-  <si>
-    <t>古いWindows16bitアプリを64bitで動かす</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://github.com/otya128/OTVDM</t>
-  </si>
-  <si>
-    <t>pandoc</t>
-  </si>
-  <si>
-    <t>ドキュメント形式変換（md/docx/html等）</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://github.com/jgm/pandoc</t>
-  </si>
-  <si>
-    <t>pathstore</t>
-  </si>
-  <si>
-    <t>パスを記録してあとで一気に使う</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>http://moewe.xrea.jp/down/pathstore.html</t>
-  </si>
-  <si>
-    <t>pathtoclip</t>
-  </si>
-  <si>
-    <t>パスをクリップボードへコピー</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://github.com/hymkor/PathToClip</t>
-  </si>
-  <si>
-    <t>pdfcpu</t>
-  </si>
-  <si>
-    <t>PDFファイルの操作</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://github.com/pdfcpu/pdfcpu</t>
-  </si>
-  <si>
-    <t>photoshop</t>
-  </si>
-  <si>
-    <t>写真編集(5.0のセットアップはIS3ENGINEを使う)</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.adobe.com/jp/products/photoshop.html
 http://toastytech.com/files/setup.html</t>
-  </si>
-  <si>
-    <t>picturefan</t>
-  </si>
-  <si>
-    <t>画像サムネイル＋簡易編集</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://iooiau.net/picturefan.html</t>
-  </si>
-  <si>
-    <t>rapidee</t>
-  </si>
-  <si>
-    <t>環境変数の編集</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://qalculate.github.io/</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.rapidee.com/ja/about</t>
-  </si>
-  <si>
-    <t>rapture</t>
-  </si>
-  <si>
-    <t>デスクトップキャプチャ</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.vector.co.jp/soft/win95/art/se386376.html</t>
-  </si>
-  <si>
-    <t>rar</t>
-  </si>
-  <si>
-    <t>RAR,ZIPファイルの圧縮・解凍（コンソール版）</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.rarlab.com</t>
-  </si>
-  <si>
-    <t>realesrgan</t>
-  </si>
-  <si>
-    <t>画像の超解像処理</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://github.com/xinntao/Real-ESRGAN</t>
-  </si>
-  <si>
-    <t>rg</t>
-  </si>
-  <si>
-    <t>テキストファイルの高速なGrep</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://github.com/BurntSushi/ripgrep</t>
-  </si>
-  <si>
-    <t>rrpatch</t>
-  </si>
-  <si>
-    <t>バイナリパッチ適用ツール</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://nstjp.com/soft/77.html</t>
-  </si>
-  <si>
-    <t>sakura</t>
-  </si>
-  <si>
-    <t>派生版sakuraVzが高速</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://github.com/yoshinrt/SakuraVz</t>
-  </si>
-  <si>
-    <t>scrdbg</t>
-  </si>
-  <si>
-    <t>VBScriptのデバッガ</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>http://pc-labo.seesaa.net/article/413882845.html</t>
-  </si>
-  <si>
-    <t>shellexview</t>
-  </si>
-  <si>
-    <t>シェルエクステンション一覧表示</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.nirsoft.net/utils/shexview.html</t>
-  </si>
-  <si>
-    <t>shellmenuview</t>
-  </si>
-  <si>
-    <t>コンテキストメニューの項目一覧表示</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.nirsoft.net/utils/shell_menu_view.html</t>
-  </si>
-  <si>
-    <t>shukusen</t>
-  </si>
-  <si>
-    <t>画像サイズを一括で縮小</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://i-section.net/software/shukusen/</t>
-  </si>
-  <si>
-    <t>simplemount</t>
-  </si>
-  <si>
-    <t>ISOファイルへのドライブの割り当て</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://main-sssoftware.ssl-lolipop.jp/simple_mount/usage.html</t>
-  </si>
-  <si>
-    <t>soyokaze</t>
-  </si>
-  <si>
-    <t>BlueWind風ランチャ</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://github.com/ampmmn/Soyokaze</t>
-  </si>
-  <si>
-    <t>step</t>
-  </si>
-  <si>
-    <t>MP3タグエディタ（軽量・シンプル操作向け）</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://github.com/jarupxx/STEP_J</t>
-  </si>
-  <si>
-    <t>tresgrep</t>
-  </si>
-  <si>
-    <t>OfficeファイルのWz風Grep</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>http://hp.vector.co.jp/authors/VA055804/TresGrep/</t>
-  </si>
-  <si>
-    <t>UMIOCR</t>
-  </si>
-  <si>
-    <t>画像ファイルのOCRテキスト一括出力・画像ファイル検索（日本語OCR対応）</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://github.com/hiroi-sora/Umi-OCR</t>
-  </si>
-  <si>
-    <t>undup</t>
-  </si>
-  <si>
-    <t>重複ファイル削除</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.vector.co.jp/soft/win95/util/se257656.html</t>
-  </si>
-  <si>
-    <t>uniextract</t>
-  </si>
-  <si>
-    <t>通常では解凍できない形式を解凍</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://github.com/Bioruebe/UniExtract2</t>
-  </si>
-  <si>
-    <t>vant</t>
-  </si>
-  <si>
-    <t>メモソフト</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://forestail.com/vant-top/</t>
-  </si>
-  <si>
-    <t>videoLAN</t>
-  </si>
-  <si>
-    <t>VLC：コーデック内蔵動画プレーヤ</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.videolan.org/</t>
-  </si>
-  <si>
-    <t>vscode</t>
-  </si>
-  <si>
-    <t>プログラムエディタ</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://code.visualstudio.com/</t>
-  </si>
-  <si>
-    <t>windowspy</t>
-  </si>
-  <si>
-    <t>ウィンドウハンドルを調べる(Autohotkeyに付属)</t>
-  </si>
-  <si>
-    <t>winexchange</t>
-  </si>
-  <si>
-    <t>ファイルタイプを判別して正しい拡張子をつける</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.vector.co.jp/soft/win95/util/se139464.html</t>
-  </si>
-  <si>
-    <t>winmerge</t>
-  </si>
-  <si>
-    <t>ファイル比較</t>
-  </si>
-  <si>
-    <t>winrar</t>
-  </si>
-  <si>
-    <t>RAR,ZIPファイルの圧縮・解凍</t>
-  </si>
-  <si>
-    <t>wiztree</t>
-  </si>
-  <si>
-    <t>xdoc2txt</t>
-  </si>
-  <si>
-    <t>OfficeファイルやPDFをテキスト化</t>
-  </si>
-  <si>
-    <t>zoxide</t>
-  </si>
-  <si>
-    <t>使用頻度に基づくディレクトリジャンプ補完</t>
-  </si>
-  <si>
-    <t>エクスプローラ拡張</t>
-  </si>
-  <si>
-    <t>ifilter4archives</t>
-  </si>
-  <si>
-    <t>ifilter対応ビューアで書庫の中身を見る</t>
-  </si>
-  <si>
-    <t>https://github.com/Meitinger/iFilter4Archives</t>
-  </si>
-  <si>
-    <t>DarkThumbs</t>
-  </si>
-  <si>
-    <t>書庫ファイルや電子書籍にサムネイル付加</t>
-  </si>
-  <si>
-    <t>https://github.com/fire-eggs/DarkThumbs</t>
-  </si>
-  <si>
-    <t>cleanflash</t>
-  </si>
-  <si>
-    <t>今でもインストールできるFlash</t>
-  </si>
-  <si>
-    <t>https://github.com/darktohka/clean-flash-builds</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://winmergejp.bitbucket.io</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>https://www.rarlab.com</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>https://www.diskanalyzer.com/</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -4322,10 +4397,6 @@
   </si>
   <si>
     <t>https://github.com/ajeetdsouza/zoxide</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>エントリパスを補完リストに登録</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4431,7 +4502,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -4440,12 +4511,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4465,10 +4530,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -4790,4062 +4855,4062 @@
   <dimension ref="A1:AE91"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="14.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="75.1640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="90.33203125" style="12" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="93.6640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.83203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.1640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="67" style="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.83203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="29.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="70.83203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18" style="12" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="27.1640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="53" style="12" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="18" style="12" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="26" style="12" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="55.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="18" style="12" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="29.83203125" style="12" customWidth="1"/>
-    <col min="30" max="30" width="37.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="19.1640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="75.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="90.33203125" style="9" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="93.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="67" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="29.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="70.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="53" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18" style="9" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="26" style="9" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="55.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="18" style="9" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="29.83203125" style="9" customWidth="1"/>
+    <col min="30" max="30" width="37.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="19.1640625" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="O1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="10" t="s">
+      <c r="Q1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="R1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="S1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="U1" s="10" t="s">
+      <c r="U1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="V1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="W1" s="10" t="s">
+      <c r="W1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="Y1" s="10" t="s">
+      <c r="Y1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="Z1" s="10" t="s">
+      <c r="Z1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="AA1" s="10" t="s">
+      <c r="AA1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="AC1" s="10" t="s">
+      <c r="AC1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="AD1" s="10" t="s">
+      <c r="AD1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="AE1" s="10" t="s">
+      <c r="AE1" s="8" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="N2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="10" t="s">
+      <c r="Q2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10" t="s">
+      <c r="R2" s="8"/>
+      <c r="S2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="U2" s="10" t="s">
+      <c r="U2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="V2" s="10"/>
-      <c r="W2" s="10" t="s">
+      <c r="V2" s="8"/>
+      <c r="W2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="Y2" s="10" t="s">
+      <c r="Y2" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="Z2" s="10"/>
-      <c r="AA2" s="10" t="s">
+      <c r="Z2" s="8"/>
+      <c r="AA2" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="AC2" s="10" t="s">
+      <c r="AC2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="AD2" s="10"/>
-      <c r="AE2" s="10" t="s">
+      <c r="AD2" s="8"/>
+      <c r="AE2" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="M3" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10" t="s">
+      <c r="N3" s="8"/>
+      <c r="O3" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="Q3" s="10" t="s">
+      <c r="Q3" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="R3" s="10"/>
-      <c r="S3" s="10" t="s">
+      <c r="R3" s="8"/>
+      <c r="S3" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U3" s="10" t="s">
+      <c r="U3" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="V3" s="10"/>
-      <c r="W3" s="10" t="s">
+      <c r="V3" s="8"/>
+      <c r="W3" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="Y3" s="10" t="s">
+      <c r="Y3" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="Z3" s="10"/>
-      <c r="AA3" s="10" t="s">
+      <c r="Z3" s="8"/>
+      <c r="AA3" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="AC3" s="10" t="s">
+      <c r="AC3" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="AD3" s="10"/>
-      <c r="AE3" s="10" t="s">
+      <c r="AD3" s="8"/>
+      <c r="AE3" s="8" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="M4" s="10" t="s">
+      <c r="M4" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="N4" s="10" t="s">
+      <c r="N4" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="O4" s="10" t="s">
+      <c r="O4" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="Q4" s="10" t="s">
+      <c r="Q4" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="R4" s="10"/>
-      <c r="S4" s="10" t="s">
+      <c r="R4" s="8"/>
+      <c r="S4" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="U4" s="10" t="s">
+      <c r="U4" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="V4" s="10" t="s">
+      <c r="V4" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="W4" s="10" t="s">
+      <c r="W4" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="Y4" s="10" t="s">
+      <c r="Y4" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="Z4" s="10"/>
-      <c r="AA4" s="10" t="s">
+      <c r="Z4" s="8"/>
+      <c r="AA4" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="AC4" s="10" t="s">
+      <c r="AC4" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="AD4" s="10"/>
-      <c r="AE4" s="10" t="s">
+      <c r="AD4" s="8"/>
+      <c r="AE4" s="8" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10" t="s">
+      <c r="J5" s="8"/>
+      <c r="K5" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="M5" s="10" t="s">
+      <c r="M5" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10" t="s">
+      <c r="N5" s="8"/>
+      <c r="O5" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="Q5" s="10" t="s">
+      <c r="Q5" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="R5" s="10"/>
-      <c r="S5" s="10" t="s">
+      <c r="R5" s="8"/>
+      <c r="S5" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="U5" s="10" t="s">
+      <c r="U5" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="V5" s="10"/>
-      <c r="W5" s="10" t="s">
+      <c r="V5" s="8"/>
+      <c r="W5" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="Y5" s="10" t="s">
+      <c r="Y5" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="Z5" s="10"/>
-      <c r="AA5" s="10" t="s">
+      <c r="Z5" s="8"/>
+      <c r="AA5" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="AC5" s="10" t="s">
+      <c r="AC5" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="AD5" s="10"/>
-      <c r="AE5" s="10" t="s">
+      <c r="AD5" s="8"/>
+      <c r="AE5" s="8" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10" t="s">
+      <c r="B6" s="8"/>
+      <c r="C6" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10" t="s">
+      <c r="F6" s="8"/>
+      <c r="G6" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="I6" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10" t="s">
+      <c r="J6" s="8"/>
+      <c r="K6" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="M6" s="10" t="s">
+      <c r="M6" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10" t="s">
+      <c r="N6" s="8"/>
+      <c r="O6" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="Q6" s="10" t="s">
+      <c r="Q6" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="R6" s="10"/>
-      <c r="S6" s="10" t="s">
+      <c r="R6" s="8"/>
+      <c r="S6" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="U6" s="10" t="s">
+      <c r="U6" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="V6" s="10"/>
-      <c r="W6" s="10" t="s">
+      <c r="V6" s="8"/>
+      <c r="W6" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="Y6" s="10" t="s">
+      <c r="Y6" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="Z6" s="10"/>
-      <c r="AA6" s="10" t="s">
+      <c r="Z6" s="8"/>
+      <c r="AA6" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="AC6" s="10" t="s">
+      <c r="AC6" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="AD6" s="10"/>
-      <c r="AE6" s="10" t="s">
+      <c r="AD6" s="8"/>
+      <c r="AE6" s="8" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10" t="s">
+      <c r="J7" s="8"/>
+      <c r="K7" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="M7" s="10" t="s">
+      <c r="M7" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10" t="s">
+      <c r="N7" s="8"/>
+      <c r="O7" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="Q7" s="10" t="s">
+      <c r="Q7" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="R7" s="10"/>
-      <c r="S7" s="10" t="s">
+      <c r="R7" s="8"/>
+      <c r="S7" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="U7" s="10" t="s">
+      <c r="U7" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="V7" s="10"/>
-      <c r="W7" s="10" t="s">
+      <c r="V7" s="8"/>
+      <c r="W7" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="Y7" s="10" t="s">
+      <c r="Y7" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="Z7" s="10"/>
-      <c r="AA7" s="10" t="s">
+      <c r="Z7" s="8"/>
+      <c r="AA7" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="AC7" s="10" t="s">
+      <c r="AC7" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="AD7" s="10"/>
-      <c r="AE7" s="10" t="s">
+      <c r="AD7" s="8"/>
+      <c r="AE7" s="8" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="M8" s="10" t="s">
+      <c r="M8" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10" t="s">
+      <c r="N8" s="8"/>
+      <c r="O8" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="Q8" s="10" t="s">
+      <c r="Q8" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="R8" s="10"/>
-      <c r="S8" s="10" t="s">
+      <c r="R8" s="8"/>
+      <c r="S8" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="U8" s="10" t="s">
+      <c r="U8" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="V8" s="10"/>
-      <c r="W8" s="10" t="s">
+      <c r="V8" s="8"/>
+      <c r="W8" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="Y8" s="10" t="s">
+      <c r="Y8" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="Z8" s="10"/>
-      <c r="AA8" s="10" t="s">
+      <c r="Z8" s="8"/>
+      <c r="AA8" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="AC8" s="10" t="s">
+      <c r="AC8" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="AD8" s="10"/>
-      <c r="AE8" s="10" t="s">
+      <c r="AD8" s="8"/>
+      <c r="AE8" s="8" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10" t="s">
+      <c r="F9" s="8"/>
+      <c r="G9" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10" t="s">
+      <c r="J9" s="8"/>
+      <c r="K9" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="M9" s="10" t="s">
+      <c r="M9" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10" t="s">
+      <c r="N9" s="8"/>
+      <c r="O9" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="Q9" s="10" t="s">
+      <c r="Q9" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="R9" s="10"/>
-      <c r="S9" s="10" t="s">
+      <c r="R9" s="8"/>
+      <c r="S9" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="U9" s="10" t="s">
+      <c r="U9" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="V9" s="10"/>
-      <c r="W9" s="10" t="s">
+      <c r="V9" s="8"/>
+      <c r="W9" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="Y9" s="10" t="s">
+      <c r="Y9" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="Z9" s="10"/>
-      <c r="AA9" s="10" t="s">
+      <c r="Z9" s="8"/>
+      <c r="AA9" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="AC9" s="10" t="s">
+      <c r="AC9" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="AD9" s="10"/>
-      <c r="AE9" s="10" t="s">
+      <c r="AD9" s="8"/>
+      <c r="AE9" s="8" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10" t="s">
+      <c r="F10" s="8"/>
+      <c r="G10" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="I10" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10" t="s">
+      <c r="J10" s="8"/>
+      <c r="K10" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="M10" s="10" t="s">
+      <c r="M10" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10" t="s">
+      <c r="N10" s="8"/>
+      <c r="O10" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="Q10" s="10" t="s">
+      <c r="Q10" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="R10" s="10"/>
-      <c r="S10" s="10" t="s">
+      <c r="R10" s="8"/>
+      <c r="S10" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="U10" s="10" t="s">
+      <c r="U10" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="V10" s="10"/>
-      <c r="W10" s="10" t="s">
+      <c r="V10" s="8"/>
+      <c r="W10" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="Y10" s="10" t="s">
+      <c r="Y10" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="Z10" s="10"/>
-      <c r="AA10" s="10" t="s">
+      <c r="Z10" s="8"/>
+      <c r="AA10" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="AC10" s="10" t="s">
+      <c r="AC10" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="AD10" s="10"/>
-      <c r="AE10" s="10" t="s">
+      <c r="AD10" s="8"/>
+      <c r="AE10" s="8" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10" t="s">
+      <c r="F11" s="8"/>
+      <c r="G11" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10" t="s">
+      <c r="J11" s="8"/>
+      <c r="K11" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="M11" s="10" t="s">
+      <c r="M11" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10" t="s">
+      <c r="N11" s="8"/>
+      <c r="O11" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="Q11" s="10" t="s">
+      <c r="Q11" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="R11" s="10"/>
-      <c r="S11" s="10" t="s">
+      <c r="R11" s="8"/>
+      <c r="S11" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="U11" s="10" t="s">
+      <c r="U11" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="V11" s="10"/>
-      <c r="W11" s="10" t="s">
+      <c r="V11" s="8"/>
+      <c r="W11" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="Y11" s="10" t="s">
+      <c r="Y11" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="Z11" s="10"/>
-      <c r="AA11" s="10" t="s">
+      <c r="Z11" s="8"/>
+      <c r="AA11" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="AC11" s="10" t="s">
+      <c r="AC11" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="AD11" s="10"/>
-      <c r="AE11" s="10" t="s">
+      <c r="AD11" s="8"/>
+      <c r="AE11" s="8" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10" t="s">
+      <c r="F12" s="8"/>
+      <c r="G12" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="I12" s="10" t="s">
+      <c r="I12" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10" t="s">
+      <c r="J12" s="8"/>
+      <c r="K12" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="M12" s="7" t="s">
+      <c r="M12" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="N12" s="7" t="s">
+      <c r="N12" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="O12" s="7" t="s">
+      <c r="O12" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="Q12" s="10" t="s">
+      <c r="Q12" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="R12" s="10"/>
-      <c r="S12" s="10" t="s">
+      <c r="R12" s="8"/>
+      <c r="S12" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="U12" s="10" t="s">
+      <c r="U12" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="V12" s="10"/>
-      <c r="W12" s="10" t="s">
+      <c r="V12" s="8"/>
+      <c r="W12" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="Y12" s="10" t="s">
+      <c r="Y12" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="Z12" s="10"/>
-      <c r="AA12" s="10" t="s">
+      <c r="Z12" s="8"/>
+      <c r="AA12" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="AC12" s="10" t="s">
+      <c r="AC12" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="AD12" s="10"/>
-      <c r="AE12" s="10" t="s">
+      <c r="AD12" s="8"/>
+      <c r="AE12" s="8" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="I13" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="J13" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="K13" s="7" t="s">
+      <c r="K13" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="M13" s="7" t="s">
+      <c r="M13" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="N13" s="7" t="s">
+      <c r="N13" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="O13" s="7" t="s">
+      <c r="O13" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="Q13" s="10" t="s">
+      <c r="Q13" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="R13" s="10" t="s">
+      <c r="R13" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="S13" s="10" t="s">
+      <c r="S13" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="U13" s="10" t="s">
+      <c r="U13" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="V13" s="10"/>
-      <c r="W13" s="10" t="s">
+      <c r="V13" s="8"/>
+      <c r="W13" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="Y13" s="10" t="s">
+      <c r="Y13" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="Z13" s="10"/>
-      <c r="AA13" s="10" t="s">
+      <c r="Z13" s="8"/>
+      <c r="AA13" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="AC13" s="10" t="s">
+      <c r="AC13" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="AD13" s="10"/>
-      <c r="AE13" s="10" t="s">
+      <c r="AD13" s="8"/>
+      <c r="AE13" s="8" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="G14" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="I14" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="J14" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="K14" s="7" t="s">
+      <c r="K14" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="M14" s="7" t="s">
+      <c r="M14" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="N14" s="7" t="s">
+      <c r="N14" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="O14" s="7" t="s">
+      <c r="O14" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="Q14" s="7" t="s">
+      <c r="Q14" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="R14" s="7" t="s">
+      <c r="R14" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="S14" s="7" t="s">
+      <c r="S14" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="U14" s="10" t="s">
+      <c r="U14" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="V14" s="10"/>
-      <c r="W14" s="10" t="s">
+      <c r="V14" s="8"/>
+      <c r="W14" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="Y14" s="10" t="s">
+      <c r="Y14" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="Z14" s="10"/>
-      <c r="AA14" s="10" t="s">
+      <c r="Z14" s="8"/>
+      <c r="AA14" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="AC14" s="10" t="s">
+      <c r="AC14" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="AD14" s="10"/>
-      <c r="AE14" s="10" t="s">
+      <c r="AD14" s="8"/>
+      <c r="AE14" s="8" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="I15" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="J15" s="7" t="s">
+      <c r="J15" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="K15" s="7" t="s">
+      <c r="K15" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="M15" s="7" t="s">
+      <c r="M15" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="N15" s="7" t="s">
+      <c r="N15" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="O15" s="7" t="s">
+      <c r="O15" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="Q15" s="10" t="s">
+      <c r="Q15" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="R15" s="10"/>
-      <c r="S15" s="10" t="s">
+      <c r="R15" s="8"/>
+      <c r="S15" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="U15" s="10" t="s">
+      <c r="U15" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="V15" s="10"/>
-      <c r="W15" s="10" t="s">
+      <c r="V15" s="8"/>
+      <c r="W15" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="Y15" s="10" t="s">
+      <c r="Y15" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="Z15" s="10"/>
-      <c r="AA15" s="10" t="s">
+      <c r="Z15" s="8"/>
+      <c r="AA15" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="AC15" s="10" t="s">
+      <c r="AC15" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="AD15" s="10"/>
-      <c r="AE15" s="10" t="s">
+      <c r="AD15" s="8"/>
+      <c r="AE15" s="8" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="G16" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="I16" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="J16" s="7" t="s">
+      <c r="J16" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="K16" s="7" t="s">
+      <c r="K16" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="M16" s="7" t="s">
+      <c r="M16" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="N16" s="7" t="s">
+      <c r="N16" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="O16" s="7" t="s">
+      <c r="O16" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="Q16" s="7" t="s">
+      <c r="Q16" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="R16" s="7" t="s">
+      <c r="R16" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="S16" s="7" t="s">
+      <c r="S16" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="U16" s="10" t="s">
+      <c r="U16" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="V16" s="10"/>
-      <c r="W16" s="10" t="s">
+      <c r="V16" s="8"/>
+      <c r="W16" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="Y16" s="10" t="s">
+      <c r="Y16" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="Z16" s="10"/>
-      <c r="AA16" s="10" t="s">
+      <c r="Z16" s="8"/>
+      <c r="AA16" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="AC16" s="10" t="s">
+      <c r="AC16" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="AD16" s="10"/>
-      <c r="AE16" s="10" t="s">
+      <c r="AD16" s="8"/>
+      <c r="AE16" s="8" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="G17" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="I17" s="10" t="s">
+      <c r="I17" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="J17" s="10" t="s">
+      <c r="J17" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="K17" s="10" t="s">
+      <c r="K17" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="M17" s="10" t="s">
+      <c r="M17" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10" t="s">
+      <c r="N17" s="8"/>
+      <c r="O17" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="Q17" s="10" t="s">
+      <c r="Q17" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="R17" s="10"/>
-      <c r="S17" s="10" t="s">
+      <c r="R17" s="8"/>
+      <c r="S17" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="U17" s="10" t="s">
+      <c r="U17" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="V17" s="10"/>
-      <c r="W17" s="10" t="s">
+      <c r="V17" s="8"/>
+      <c r="W17" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="Y17" s="10" t="s">
+      <c r="Y17" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="Z17" s="10"/>
-      <c r="AA17" s="10" t="s">
+      <c r="Z17" s="8"/>
+      <c r="AA17" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="AC17" s="10" t="s">
+      <c r="AC17" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="AD17" s="10"/>
-      <c r="AE17" s="10" t="s">
+      <c r="AD17" s="8"/>
+      <c r="AE17" s="8" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G18" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="I18" s="10" t="s">
+      <c r="I18" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="J18" s="10" t="s">
+      <c r="J18" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="K18" s="10" t="s">
+      <c r="K18" s="8" t="s">
         <v>313</v>
       </c>
-      <c r="M18" s="10" t="s">
+      <c r="M18" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="N18" s="10"/>
-      <c r="O18" s="10" t="s">
+      <c r="N18" s="8"/>
+      <c r="O18" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="Q18" s="10" t="s">
+      <c r="Q18" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="R18" s="10"/>
-      <c r="S18" s="10" t="s">
+      <c r="R18" s="8"/>
+      <c r="S18" s="8" t="s">
         <v>317</v>
       </c>
-      <c r="U18" s="10" t="s">
+      <c r="U18" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="V18" s="10"/>
-      <c r="W18" s="10" t="s">
+      <c r="V18" s="8"/>
+      <c r="W18" s="8" t="s">
         <v>319</v>
       </c>
-      <c r="Y18" s="10" t="s">
+      <c r="Y18" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="Z18" s="10"/>
-      <c r="AA18" s="10" t="s">
+      <c r="Z18" s="8"/>
+      <c r="AA18" s="8" t="s">
         <v>321</v>
       </c>
-      <c r="AC18" s="10" t="s">
+      <c r="AC18" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="AD18" s="10"/>
-      <c r="AE18" s="10" t="s">
+      <c r="AD18" s="8"/>
+      <c r="AE18" s="8" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="8" t="s">
         <v>327</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="I19" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="J19" s="5" t="s">
+      <c r="J19" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="K19" s="5" t="s">
+      <c r="K19" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="M19" s="10" t="s">
+      <c r="M19" s="8" t="s">
         <v>333</v>
       </c>
-      <c r="N19" s="10"/>
-      <c r="O19" s="10" t="s">
+      <c r="N19" s="8"/>
+      <c r="O19" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="Q19" s="10" t="s">
+      <c r="Q19" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="R19" s="10" t="s">
+      <c r="R19" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="S19" s="10" t="s">
+      <c r="S19" s="8" t="s">
         <v>337</v>
       </c>
-      <c r="U19" s="10" t="s">
+      <c r="U19" s="8" t="s">
         <v>338</v>
       </c>
-      <c r="V19" s="10"/>
-      <c r="W19" s="10" t="s">
+      <c r="V19" s="8"/>
+      <c r="W19" s="8" t="s">
         <v>339</v>
       </c>
-      <c r="Y19" s="10" t="s">
+      <c r="Y19" s="8" t="s">
         <v>340</v>
       </c>
-      <c r="Z19" s="10"/>
-      <c r="AA19" s="10" t="s">
+      <c r="Z19" s="8"/>
+      <c r="AA19" s="8" t="s">
         <v>341</v>
       </c>
-      <c r="AC19" s="10" t="s">
+      <c r="AC19" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="AD19" s="10"/>
-      <c r="AE19" s="10" t="s">
+      <c r="AD19" s="8"/>
+      <c r="AE19" s="8" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="8" t="s">
         <v>347</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F20" s="8" t="s">
         <v>348</v>
       </c>
-      <c r="G20" s="10" t="s">
+      <c r="G20" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="I20" s="10" t="s">
+      <c r="I20" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="J20" s="10" t="s">
+      <c r="J20" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="K20" s="10" t="s">
+      <c r="K20" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="M20" s="10" t="s">
+      <c r="M20" s="8" t="s">
         <v>353</v>
       </c>
-      <c r="N20" s="10"/>
-      <c r="O20" s="10" t="s">
+      <c r="N20" s="8"/>
+      <c r="O20" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="Q20" s="10" t="s">
+      <c r="Q20" s="8" t="s">
         <v>355</v>
       </c>
-      <c r="R20" s="10"/>
-      <c r="S20" s="10" t="s">
+      <c r="R20" s="8"/>
+      <c r="S20" s="8" t="s">
         <v>356</v>
       </c>
-      <c r="U20" s="10" t="s">
+      <c r="U20" s="8" t="s">
         <v>357</v>
       </c>
-      <c r="V20" s="10"/>
-      <c r="W20" s="10" t="s">
+      <c r="V20" s="8"/>
+      <c r="W20" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="Y20" s="10" t="s">
+      <c r="Y20" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="Z20" s="10"/>
-      <c r="AA20" s="10" t="s">
+      <c r="Z20" s="8"/>
+      <c r="AA20" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="AC20" s="10" t="s">
+      <c r="AC20" s="8" t="s">
         <v>361</v>
       </c>
-      <c r="AD20" s="10"/>
-      <c r="AE20" s="10" t="s">
+      <c r="AD20" s="8"/>
+      <c r="AE20" s="8" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="I21" s="5" t="s">
+      <c r="I21" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="J21" s="5" t="s">
+      <c r="J21" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="K21" s="5" t="s">
+      <c r="K21" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="M21" s="10" t="s">
+      <c r="M21" s="8" t="s">
         <v>372</v>
       </c>
-      <c r="N21" s="10" t="s">
+      <c r="N21" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="O21" s="10" t="s">
+      <c r="O21" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="Q21" s="10" t="s">
+      <c r="Q21" s="8" t="s">
         <v>375</v>
       </c>
-      <c r="R21" s="10" t="s">
+      <c r="R21" s="8" t="s">
         <v>376</v>
       </c>
-      <c r="S21" s="10" t="s">
+      <c r="S21" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="U21" s="10" t="s">
+      <c r="U21" s="8" t="s">
         <v>378</v>
       </c>
-      <c r="V21" s="10"/>
-      <c r="W21" s="10" t="s">
+      <c r="V21" s="8"/>
+      <c r="W21" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="Y21" s="10" t="s">
+      <c r="Y21" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="Z21" s="10"/>
-      <c r="AA21" s="10" t="s">
+      <c r="Z21" s="8"/>
+      <c r="AA21" s="8" t="s">
         <v>381</v>
       </c>
-      <c r="AC21" s="10" t="s">
+      <c r="AC21" s="8" t="s">
         <v>382</v>
       </c>
-      <c r="AD21" s="10" t="s">
+      <c r="AD21" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="AE21" s="10" t="s">
+      <c r="AE21" s="8" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="5" t="s">
         <v>388</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="5" t="s">
         <v>389</v>
       </c>
-      <c r="G22" s="7" t="s">
+      <c r="G22" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="I22" s="7" t="s">
+      <c r="I22" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="J22" s="7" t="s">
+      <c r="J22" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="K22" s="7" t="s">
+      <c r="K22" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="M22" s="10" t="s">
+      <c r="M22" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="N22" s="10" t="s">
+      <c r="N22" s="8" t="s">
         <v>395</v>
       </c>
-      <c r="O22" s="10" t="s">
+      <c r="O22" s="8" t="s">
         <v>396</v>
       </c>
-      <c r="Q22" s="10" t="s">
+      <c r="Q22" s="8" t="s">
         <v>397</v>
       </c>
-      <c r="R22" s="10" t="s">
+      <c r="R22" s="8" t="s">
         <v>398</v>
       </c>
-      <c r="S22" s="10" t="s">
+      <c r="S22" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="U22" s="7" t="s">
+      <c r="U22" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="V22" s="7" t="s">
+      <c r="V22" s="5" t="s">
         <v>401</v>
       </c>
-      <c r="W22" s="7" t="s">
+      <c r="W22" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="Y22" s="7" t="s">
+      <c r="Y22" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="Z22" s="7" t="s">
+      <c r="Z22" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="AA22" s="7" t="s">
+      <c r="AA22" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="AC22" s="10" t="s">
+      <c r="AC22" s="8" t="s">
         <v>406</v>
       </c>
-      <c r="AD22" s="10" t="s">
+      <c r="AD22" s="8" t="s">
         <v>407</v>
       </c>
-      <c r="AE22" s="10" t="s">
+      <c r="AE22" s="8" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="5" t="s">
         <v>412</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="G23" s="7" t="s">
+      <c r="G23" s="5" t="s">
         <v>414</v>
       </c>
-      <c r="I23" s="7" t="s">
+      <c r="I23" s="5" t="s">
         <v>415</v>
       </c>
-      <c r="J23" s="7" t="s">
+      <c r="J23" s="5" t="s">
         <v>416</v>
       </c>
-      <c r="K23" s="7" t="s">
+      <c r="K23" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="M23" s="10" t="s">
+      <c r="M23" s="8" t="s">
         <v>418</v>
       </c>
-      <c r="N23" s="10" t="s">
+      <c r="N23" s="8" t="s">
         <v>419</v>
       </c>
-      <c r="O23" s="10" t="s">
+      <c r="O23" s="8" t="s">
         <v>420</v>
       </c>
-      <c r="Q23" s="10" t="s">
+      <c r="Q23" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="R23" s="10" t="s">
+      <c r="R23" s="8" t="s">
         <v>422</v>
       </c>
-      <c r="S23" s="10" t="s">
+      <c r="S23" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="U23" s="10" t="s">
+      <c r="U23" s="8" t="s">
         <v>424</v>
       </c>
-      <c r="V23" s="10"/>
-      <c r="W23" s="10" t="s">
+      <c r="V23" s="8"/>
+      <c r="W23" s="8" t="s">
         <v>425</v>
       </c>
-      <c r="Y23" s="10" t="s">
+      <c r="Y23" s="8" t="s">
         <v>426</v>
       </c>
-      <c r="Z23" s="10"/>
-      <c r="AA23" s="10" t="s">
+      <c r="Z23" s="8"/>
+      <c r="AA23" s="8" t="s">
         <v>427</v>
       </c>
-      <c r="AC23" s="10" t="s">
+      <c r="AC23" s="8" t="s">
         <v>428</v>
       </c>
-      <c r="AD23" s="10"/>
-      <c r="AE23" s="10" t="s">
+      <c r="AD23" s="8"/>
+      <c r="AE23" s="8" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E24" s="8" t="s">
         <v>433</v>
       </c>
-      <c r="F24" s="10" t="s">
+      <c r="F24" s="8" t="s">
         <v>434</v>
       </c>
-      <c r="G24" s="10" t="s">
+      <c r="G24" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="I24" s="7" t="s">
+      <c r="I24" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="J24" s="7" t="s">
+      <c r="J24" s="5" t="s">
         <v>437</v>
       </c>
-      <c r="K24" s="7" t="s">
+      <c r="K24" s="5" t="s">
         <v>438</v>
       </c>
-      <c r="M24" s="10" t="s">
+      <c r="M24" s="8" t="s">
         <v>439</v>
       </c>
-      <c r="N24" s="10" t="s">
+      <c r="N24" s="8" t="s">
         <v>440</v>
       </c>
-      <c r="O24" s="10" t="s">
+      <c r="O24" s="8" t="s">
         <v>441</v>
       </c>
-      <c r="Q24" s="10" t="s">
+      <c r="Q24" s="8" t="s">
         <v>442</v>
       </c>
-      <c r="R24" s="10" t="s">
+      <c r="R24" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="S24" s="10" t="s">
+      <c r="S24" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="U24" s="10" t="s">
+      <c r="U24" s="8" t="s">
         <v>445</v>
       </c>
-      <c r="V24" s="10"/>
-      <c r="W24" s="10" t="s">
+      <c r="V24" s="8"/>
+      <c r="W24" s="8" t="s">
         <v>446</v>
       </c>
-      <c r="Y24" s="10" t="s">
+      <c r="Y24" s="8" t="s">
         <v>447</v>
       </c>
-      <c r="Z24" s="10"/>
-      <c r="AA24" s="10" t="s">
+      <c r="Z24" s="8"/>
+      <c r="AA24" s="8" t="s">
         <v>448</v>
       </c>
-      <c r="AC24" s="10" t="s">
+      <c r="AC24" s="8" t="s">
         <v>449</v>
       </c>
-      <c r="AD24" s="10"/>
-      <c r="AE24" s="10" t="s">
+      <c r="AD24" s="8"/>
+      <c r="AE24" s="8" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="5" t="s">
         <v>451</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="E25" s="8" t="s">
         <v>454</v>
       </c>
-      <c r="F25" s="10" t="s">
+      <c r="F25" s="8" t="s">
         <v>455</v>
       </c>
-      <c r="G25" s="10" t="s">
+      <c r="G25" s="8" t="s">
         <v>456</v>
       </c>
-      <c r="I25" s="10" t="s">
+      <c r="I25" s="8" t="s">
         <v>457</v>
       </c>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10" t="s">
+      <c r="J25" s="8"/>
+      <c r="K25" s="8" t="s">
         <v>458</v>
       </c>
-      <c r="M25" s="10" t="s">
+      <c r="M25" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="N25" s="10"/>
-      <c r="O25" s="10" t="s">
+      <c r="N25" s="8"/>
+      <c r="O25" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="Q25" s="10" t="s">
+      <c r="Q25" s="8" t="s">
         <v>461</v>
       </c>
-      <c r="R25" s="10" t="s">
-        <v>1430</v>
-      </c>
-      <c r="S25" s="10" t="s">
+      <c r="R25" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="U25" s="10" t="s">
+      <c r="S25" s="8" t="s">
         <v>463</v>
       </c>
-      <c r="V25" s="10"/>
-      <c r="W25" s="10" t="s">
+      <c r="U25" s="8" t="s">
         <v>464</v>
       </c>
-      <c r="Y25" s="10" t="s">
+      <c r="V25" s="8"/>
+      <c r="W25" s="8" t="s">
         <v>465</v>
       </c>
-      <c r="Z25" s="10"/>
-      <c r="AA25" s="10" t="s">
+      <c r="Y25" s="8" t="s">
         <v>466</v>
       </c>
-      <c r="AC25" s="10" t="s">
+      <c r="Z25" s="8"/>
+      <c r="AA25" s="8" t="s">
         <v>467</v>
       </c>
-      <c r="AD25" s="10"/>
-      <c r="AE25" s="10" t="s">
+      <c r="AC25" s="8" t="s">
         <v>468</v>
       </c>
+      <c r="AD25" s="8"/>
+      <c r="AE25" s="8" t="s">
+        <v>469</v>
+      </c>
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A26" s="5" t="s">
-        <v>469</v>
-      </c>
-      <c r="B26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="C26" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="E26" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="F26" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="I26" s="10" t="s">
+      <c r="G26" s="3" t="s">
         <v>475</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>476</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="K26" s="10" t="s">
-        <v>476</v>
-      </c>
-      <c r="M26" s="10" t="s">
+      <c r="K26" s="8" t="s">
         <v>477</v>
       </c>
-      <c r="N26" s="10" t="s">
+      <c r="M26" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="O26" s="10" t="s">
+      <c r="N26" s="8" t="s">
         <v>479</v>
       </c>
-      <c r="Q26" s="10" t="s">
+      <c r="O26" s="8" t="s">
         <v>480</v>
       </c>
-      <c r="R26" s="10" t="s">
+      <c r="Q26" s="8" t="s">
         <v>481</v>
       </c>
-      <c r="S26" s="10" t="s">
+      <c r="R26" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="U26" s="10" t="s">
+      <c r="S26" s="8" t="s">
         <v>483</v>
       </c>
-      <c r="V26" s="10"/>
-      <c r="W26" s="10" t="s">
+      <c r="U26" s="8" t="s">
         <v>484</v>
       </c>
-      <c r="Y26" s="10" t="s">
+      <c r="V26" s="8"/>
+      <c r="W26" s="8" t="s">
         <v>485</v>
       </c>
-      <c r="Z26" s="10"/>
-      <c r="AA26" s="10" t="s">
+      <c r="Y26" s="8" t="s">
         <v>486</v>
       </c>
-      <c r="AC26" s="10" t="s">
+      <c r="Z26" s="8"/>
+      <c r="AA26" s="8" t="s">
         <v>487</v>
       </c>
-      <c r="AD26" s="10"/>
-      <c r="AE26" s="10" t="s">
+      <c r="AC26" s="8" t="s">
         <v>488</v>
       </c>
+      <c r="AD26" s="8"/>
+      <c r="AE26" s="8" t="s">
+        <v>489</v>
+      </c>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A27" s="10" t="s">
-        <v>489</v>
-      </c>
-      <c r="B27" s="10" t="s">
+      <c r="A27" s="8" t="s">
         <v>490</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="B27" s="8" t="s">
         <v>491</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="C27" s="8" t="s">
         <v>492</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="E27" s="8" t="s">
         <v>493</v>
       </c>
-      <c r="G27" s="10" t="s">
+      <c r="F27" s="8" t="s">
         <v>494</v>
       </c>
-      <c r="I27" s="10" t="s">
+      <c r="G27" s="8" t="s">
         <v>495</v>
       </c>
-      <c r="J27" s="10" t="s">
+      <c r="I27" s="8" t="s">
         <v>496</v>
       </c>
-      <c r="K27" s="10" t="s">
+      <c r="J27" s="8" t="s">
         <v>497</v>
       </c>
-      <c r="M27" s="10" t="s">
+      <c r="K27" s="8" t="s">
         <v>498</v>
       </c>
-      <c r="N27" s="10" t="s">
+      <c r="M27" s="8" t="s">
         <v>499</v>
       </c>
-      <c r="O27" s="10" t="s">
+      <c r="N27" s="8" t="s">
         <v>500</v>
       </c>
-      <c r="Q27" s="10" t="s">
+      <c r="O27" s="8" t="s">
         <v>501</v>
       </c>
-      <c r="R27" s="10" t="s">
+      <c r="Q27" s="8" t="s">
         <v>502</v>
       </c>
-      <c r="S27" s="10" t="s">
+      <c r="R27" s="8" t="s">
         <v>503</v>
       </c>
-      <c r="U27" s="10" t="s">
+      <c r="S27" s="8" t="s">
         <v>504</v>
       </c>
-      <c r="V27" s="10"/>
-      <c r="W27" s="10" t="s">
+      <c r="U27" s="8" t="s">
         <v>505</v>
       </c>
-      <c r="Y27" s="10" t="s">
+      <c r="V27" s="8"/>
+      <c r="W27" s="8" t="s">
         <v>506</v>
       </c>
-      <c r="Z27" s="10"/>
-      <c r="AA27" s="10" t="s">
+      <c r="Y27" s="8" t="s">
         <v>507</v>
       </c>
-      <c r="AC27" s="10" t="s">
+      <c r="Z27" s="8"/>
+      <c r="AA27" s="8" t="s">
         <v>508</v>
       </c>
-      <c r="AD27" s="10"/>
-      <c r="AE27" s="10" t="s">
+      <c r="AC27" s="8" t="s">
         <v>509</v>
       </c>
+      <c r="AD27" s="8"/>
+      <c r="AE27" s="8" t="s">
+        <v>510</v>
+      </c>
     </row>
     <row r="28" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A28" s="7" t="s">
-        <v>510</v>
-      </c>
-      <c r="B28" s="7" t="s">
+      <c r="A28" s="5" t="s">
         <v>511</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="B28" s="5" t="s">
         <v>512</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="C28" s="5" t="s">
         <v>513</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="E28" s="5" t="s">
         <v>514</v>
       </c>
-      <c r="G28" s="7" t="s">
+      <c r="F28" s="5" t="s">
         <v>515</v>
       </c>
-      <c r="I28" s="10" t="s">
+      <c r="G28" s="5" t="s">
         <v>516</v>
       </c>
-      <c r="J28" s="10" t="s">
+      <c r="I28" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="J28" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="K28" s="10" t="s">
-        <v>517</v>
-      </c>
-      <c r="M28" s="10" t="s">
+      <c r="K28" s="8" t="s">
         <v>518</v>
       </c>
-      <c r="N28" s="10"/>
-      <c r="O28" s="10" t="s">
+      <c r="M28" s="8" t="s">
         <v>519</v>
       </c>
-      <c r="Q28" s="10" t="s">
+      <c r="N28" s="8"/>
+      <c r="O28" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="R28" s="10"/>
-      <c r="S28" s="10" t="s">
+      <c r="Q28" s="8" t="s">
         <v>521</v>
       </c>
-      <c r="U28" s="10" t="s">
+      <c r="R28" s="8"/>
+      <c r="S28" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="V28" s="10"/>
-      <c r="W28" s="10" t="s">
+      <c r="U28" s="8" t="s">
         <v>523</v>
       </c>
-      <c r="Y28" s="10" t="s">
+      <c r="V28" s="8"/>
+      <c r="W28" s="8" t="s">
         <v>524</v>
       </c>
-      <c r="Z28" s="10"/>
-      <c r="AA28" s="10" t="s">
+      <c r="Y28" s="8" t="s">
         <v>525</v>
       </c>
-      <c r="AC28" s="10" t="s">
+      <c r="Z28" s="8"/>
+      <c r="AA28" s="8" t="s">
         <v>526</v>
       </c>
-      <c r="AD28" s="10"/>
-      <c r="AE28" s="10" t="s">
+      <c r="AC28" s="8" t="s">
         <v>527</v>
       </c>
+      <c r="AD28" s="8"/>
+      <c r="AE28" s="8" t="s">
+        <v>528</v>
+      </c>
     </row>
     <row r="29" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A29" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="B29" s="5" t="s">
+      <c r="A29" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="C29" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="E29" s="5" t="s">
         <v>532</v>
       </c>
-      <c r="G29" s="7" t="s">
+      <c r="F29" s="5" t="s">
         <v>533</v>
       </c>
-      <c r="I29" s="10" t="s">
+      <c r="G29" s="5" t="s">
         <v>534</v>
       </c>
-      <c r="J29" s="10" t="s">
+      <c r="I29" s="8" t="s">
+        <v>535</v>
+      </c>
+      <c r="J29" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="K29" s="10" t="s">
-        <v>535</v>
-      </c>
-      <c r="M29" s="10" t="s">
+      <c r="K29" s="8" t="s">
         <v>536</v>
       </c>
-      <c r="N29" s="10"/>
-      <c r="O29" s="10" t="s">
+      <c r="M29" s="8" t="s">
         <v>537</v>
       </c>
-      <c r="Q29" s="10" t="s">
+      <c r="N29" s="8"/>
+      <c r="O29" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="R29" s="10"/>
-      <c r="S29" s="10" t="s">
+      <c r="Q29" s="8" t="s">
         <v>539</v>
       </c>
-      <c r="U29" s="10" t="s">
+      <c r="R29" s="8"/>
+      <c r="S29" s="8" t="s">
         <v>540</v>
       </c>
-      <c r="V29" s="10"/>
-      <c r="W29" s="10" t="s">
+      <c r="U29" s="8" t="s">
         <v>541</v>
       </c>
-      <c r="Y29" s="10" t="s">
+      <c r="V29" s="8"/>
+      <c r="W29" s="8" t="s">
         <v>542</v>
       </c>
-      <c r="Z29" s="10"/>
-      <c r="AA29" s="10" t="s">
+      <c r="Y29" s="8" t="s">
         <v>543</v>
       </c>
-      <c r="AC29" s="10" t="s">
+      <c r="Z29" s="8"/>
+      <c r="AA29" s="8" t="s">
         <v>544</v>
       </c>
-      <c r="AD29" s="10"/>
-      <c r="AE29" s="10" t="s">
+      <c r="AC29" s="8" t="s">
         <v>545</v>
       </c>
+      <c r="AD29" s="8"/>
+      <c r="AE29" s="8" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A30" s="5" t="s">
-        <v>546</v>
-      </c>
-      <c r="B30" s="5" t="s">
+      <c r="A30" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="C30" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="E30" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="G30" s="5" t="s">
+      <c r="F30" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="I30" s="10" t="s">
+      <c r="G30" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="J30" s="10" t="s">
+      <c r="I30" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="J30" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="K30" s="10" t="s">
-        <v>553</v>
-      </c>
-      <c r="M30" s="10" t="s">
+      <c r="K30" s="8" t="s">
         <v>554</v>
       </c>
-      <c r="N30" s="10" t="s">
+      <c r="M30" s="8" t="s">
         <v>555</v>
       </c>
-      <c r="O30" s="10" t="s">
+      <c r="N30" s="8" t="s">
         <v>556</v>
       </c>
-      <c r="Q30" s="10" t="s">
+      <c r="O30" s="8" t="s">
         <v>557</v>
       </c>
-      <c r="R30" s="10" t="s">
+      <c r="Q30" s="8" t="s">
         <v>558</v>
       </c>
-      <c r="S30" s="10" t="s">
+      <c r="R30" s="8" t="s">
         <v>559</v>
       </c>
-      <c r="U30" s="10" t="s">
+      <c r="S30" s="8" t="s">
         <v>560</v>
       </c>
-      <c r="V30" s="10"/>
-      <c r="W30" s="10" t="s">
+      <c r="U30" s="8" t="s">
         <v>561</v>
       </c>
-      <c r="Y30" s="10" t="s">
+      <c r="V30" s="8"/>
+      <c r="W30" s="8" t="s">
         <v>562</v>
       </c>
-      <c r="Z30" s="10"/>
-      <c r="AA30" s="10" t="s">
+      <c r="Y30" s="8" t="s">
         <v>563</v>
       </c>
-      <c r="AC30" s="10" t="s">
+      <c r="Z30" s="8"/>
+      <c r="AA30" s="8" t="s">
         <v>564</v>
       </c>
-      <c r="AD30" s="10"/>
-      <c r="AE30" s="10" t="s">
+      <c r="AC30" s="8" t="s">
         <v>565</v>
       </c>
+      <c r="AD30" s="8"/>
+      <c r="AE30" s="8" t="s">
+        <v>566</v>
+      </c>
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A31" s="5" t="s">
-        <v>566</v>
-      </c>
-      <c r="B31" s="5" t="s">
+      <c r="A31" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="B31" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="C31" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="E31" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="G31" s="5" t="s">
+      <c r="F31" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="I31" s="10" t="s">
+      <c r="G31" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="J31" s="10" t="s">
+      <c r="I31" s="8" t="s">
         <v>573</v>
       </c>
-      <c r="K31" s="10" t="s">
+      <c r="J31" s="8" t="s">
         <v>574</v>
       </c>
-      <c r="M31" s="10" t="s">
+      <c r="K31" s="8" t="s">
         <v>575</v>
       </c>
-      <c r="N31" s="10" t="s">
+      <c r="M31" s="8" t="s">
         <v>576</v>
       </c>
-      <c r="O31" s="10" t="s">
+      <c r="N31" s="8" t="s">
         <v>577</v>
       </c>
-      <c r="Q31" s="10" t="s">
+      <c r="O31" s="8" t="s">
         <v>578</v>
       </c>
-      <c r="R31" s="10" t="s">
+      <c r="Q31" s="8" t="s">
         <v>579</v>
       </c>
-      <c r="S31" s="10" t="s">
+      <c r="R31" s="8" t="s">
         <v>580</v>
       </c>
-      <c r="U31" s="10" t="s">
+      <c r="S31" s="8" t="s">
         <v>581</v>
       </c>
-      <c r="V31" s="10"/>
-      <c r="W31" s="10" t="s">
+      <c r="U31" s="8" t="s">
         <v>582</v>
       </c>
-      <c r="Y31" s="10" t="s">
+      <c r="V31" s="8"/>
+      <c r="W31" s="8" t="s">
         <v>583</v>
       </c>
-      <c r="Z31" s="10"/>
-      <c r="AA31" s="10" t="s">
+      <c r="Y31" s="8" t="s">
         <v>584</v>
       </c>
-      <c r="AC31" s="10" t="s">
+      <c r="Z31" s="8"/>
+      <c r="AA31" s="8" t="s">
         <v>585</v>
       </c>
-      <c r="AD31" s="10" t="s">
+      <c r="AC31" s="8" t="s">
         <v>586</v>
       </c>
-      <c r="AE31" s="10" t="s">
+      <c r="AD31" s="8" t="s">
         <v>587</v>
       </c>
+      <c r="AE31" s="8" t="s">
+        <v>588</v>
+      </c>
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A32" s="10" t="s">
-        <v>588</v>
-      </c>
-      <c r="B32" s="10" t="s">
+      <c r="A32" s="8" t="s">
         <v>589</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="B32" s="8" t="s">
         <v>590</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="C32" s="8" t="s">
         <v>591</v>
       </c>
-      <c r="F32" s="10" t="s">
+      <c r="E32" s="8" t="s">
         <v>592</v>
       </c>
-      <c r="G32" s="10" t="s">
+      <c r="F32" s="8" t="s">
         <v>593</v>
       </c>
-      <c r="I32" s="10" t="s">
+      <c r="G32" s="8" t="s">
         <v>594</v>
       </c>
-      <c r="J32" s="10" t="s">
+      <c r="I32" s="8" t="s">
+        <v>595</v>
+      </c>
+      <c r="J32" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="K32" s="10" t="s">
-        <v>595</v>
-      </c>
-      <c r="M32" s="10" t="s">
+      <c r="K32" s="8" t="s">
         <v>596</v>
       </c>
-      <c r="N32" s="10"/>
-      <c r="O32" s="10" t="s">
+      <c r="M32" s="8" t="s">
         <v>597</v>
       </c>
-      <c r="Q32" s="10" t="s">
+      <c r="N32" s="8"/>
+      <c r="O32" s="8" t="s">
         <v>598</v>
       </c>
-      <c r="R32" s="10"/>
-      <c r="S32" s="10" t="s">
+      <c r="Q32" s="8" t="s">
         <v>599</v>
       </c>
-      <c r="U32" s="10" t="s">
+      <c r="R32" s="8"/>
+      <c r="S32" s="8" t="s">
         <v>600</v>
       </c>
-      <c r="V32" s="10"/>
-      <c r="W32" s="10" t="s">
+      <c r="U32" s="8" t="s">
         <v>601</v>
       </c>
-      <c r="Y32" s="10" t="s">
+      <c r="V32" s="8"/>
+      <c r="W32" s="8" t="s">
         <v>602</v>
       </c>
-      <c r="Z32" s="10"/>
-      <c r="AA32" s="10" t="s">
+      <c r="Y32" s="8" t="s">
         <v>603</v>
       </c>
-      <c r="AC32" s="10" t="s">
+      <c r="Z32" s="8"/>
+      <c r="AA32" s="8" t="s">
         <v>604</v>
       </c>
-      <c r="AD32" s="10"/>
-      <c r="AE32" s="10" t="s">
+      <c r="AC32" s="8" t="s">
         <v>605</v>
       </c>
+      <c r="AD32" s="8"/>
+      <c r="AE32" s="8" t="s">
+        <v>606</v>
+      </c>
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A33" s="7" t="s">
-        <v>606</v>
-      </c>
-      <c r="B33" s="7" t="s">
+      <c r="A33" s="5" t="s">
         <v>607</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="B33" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="E33" s="10" t="s">
+      <c r="C33" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="F33" s="10" t="s">
+      <c r="E33" s="8" t="s">
         <v>610</v>
       </c>
-      <c r="G33" s="10" t="s">
+      <c r="F33" s="8" t="s">
         <v>611</v>
       </c>
-      <c r="I33" s="10" t="s">
+      <c r="G33" s="8" t="s">
         <v>612</v>
       </c>
-      <c r="J33" s="10"/>
-      <c r="K33" s="10" t="s">
+      <c r="I33" s="8" t="s">
         <v>613</v>
       </c>
-      <c r="M33" s="10" t="s">
+      <c r="J33" s="8"/>
+      <c r="K33" s="8" t="s">
         <v>614</v>
       </c>
-      <c r="N33" s="10" t="s">
+      <c r="M33" s="8" t="s">
         <v>615</v>
       </c>
-      <c r="O33" s="10" t="s">
+      <c r="N33" s="8" t="s">
         <v>616</v>
       </c>
-      <c r="Q33" s="10" t="s">
+      <c r="O33" s="8" t="s">
         <v>617</v>
       </c>
-      <c r="R33" s="10"/>
-      <c r="S33" s="10" t="s">
+      <c r="Q33" s="8" t="s">
         <v>618</v>
       </c>
-      <c r="U33" s="10" t="s">
+      <c r="R33" s="8"/>
+      <c r="S33" s="8" t="s">
         <v>619</v>
       </c>
-      <c r="V33" s="10"/>
-      <c r="W33" s="10" t="s">
+      <c r="U33" s="8" t="s">
         <v>620</v>
       </c>
-      <c r="Y33" s="10" t="s">
+      <c r="V33" s="8"/>
+      <c r="W33" s="8" t="s">
         <v>621</v>
       </c>
-      <c r="Z33" s="10"/>
-      <c r="AA33" s="10" t="s">
+      <c r="Y33" s="8" t="s">
         <v>622</v>
       </c>
-      <c r="AC33" s="10" t="s">
+      <c r="Z33" s="8"/>
+      <c r="AA33" s="8" t="s">
         <v>623</v>
       </c>
-      <c r="AD33" s="10"/>
-      <c r="AE33" s="10" t="s">
+      <c r="AC33" s="8" t="s">
         <v>624</v>
       </c>
+      <c r="AD33" s="8"/>
+      <c r="AE33" s="8" t="s">
+        <v>625</v>
+      </c>
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A34" s="5" t="s">
-        <v>625</v>
-      </c>
-      <c r="B34" s="5" t="s">
+      <c r="A34" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="B34" s="3" t="s">
         <v>627</v>
       </c>
-      <c r="E34" s="10" t="s">
+      <c r="C34" s="3" t="s">
         <v>628</v>
       </c>
-      <c r="F34" s="10" t="s">
+      <c r="E34" s="8" t="s">
         <v>629</v>
       </c>
-      <c r="G34" s="10" t="s">
+      <c r="F34" s="8" t="s">
         <v>630</v>
       </c>
-      <c r="I34" s="10" t="s">
+      <c r="G34" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="J34" s="10" t="s">
+      <c r="I34" s="8" t="s">
         <v>632</v>
       </c>
-      <c r="K34" s="10" t="s">
+      <c r="J34" s="8" t="s">
         <v>633</v>
       </c>
-      <c r="M34" s="10" t="s">
+      <c r="K34" s="8" t="s">
         <v>634</v>
       </c>
-      <c r="N34" s="10"/>
-      <c r="O34" s="10" t="s">
+      <c r="M34" s="8" t="s">
         <v>635</v>
       </c>
-      <c r="Q34" s="10" t="s">
+      <c r="N34" s="8"/>
+      <c r="O34" s="8" t="s">
         <v>636</v>
       </c>
-      <c r="R34" s="10"/>
-      <c r="S34" s="10" t="s">
+      <c r="Q34" s="8" t="s">
         <v>637</v>
       </c>
-      <c r="U34" s="10" t="s">
+      <c r="R34" s="8"/>
+      <c r="S34" s="8" t="s">
         <v>638</v>
       </c>
-      <c r="V34" s="10"/>
-      <c r="W34" s="10" t="s">
+      <c r="U34" s="8" t="s">
         <v>639</v>
       </c>
-      <c r="Y34" s="10" t="s">
+      <c r="V34" s="8"/>
+      <c r="W34" s="8" t="s">
         <v>640</v>
       </c>
-      <c r="Z34" s="10"/>
-      <c r="AA34" s="10" t="s">
+      <c r="Y34" s="8" t="s">
         <v>641</v>
       </c>
-      <c r="AC34" s="10" t="s">
+      <c r="Z34" s="8"/>
+      <c r="AA34" s="8" t="s">
         <v>642</v>
       </c>
-      <c r="AD34" s="10"/>
-      <c r="AE34" s="10" t="s">
+      <c r="AC34" s="8" t="s">
         <v>643</v>
       </c>
+      <c r="AD34" s="8"/>
+      <c r="AE34" s="8" t="s">
+        <v>644</v>
+      </c>
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A35" s="10" t="s">
-        <v>644</v>
-      </c>
-      <c r="B35" s="10" t="s">
+      <c r="A35" s="8" t="s">
         <v>645</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="B35" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="E35" s="10" t="s">
+      <c r="C35" s="8" t="s">
         <v>647</v>
       </c>
-      <c r="F35" s="10" t="s">
+      <c r="E35" s="8" t="s">
         <v>648</v>
       </c>
-      <c r="G35" s="10" t="s">
+      <c r="F35" s="8" t="s">
         <v>649</v>
       </c>
-      <c r="I35" s="10" t="s">
+      <c r="G35" s="8" t="s">
         <v>650</v>
       </c>
-      <c r="J35" s="10"/>
-      <c r="K35" s="10" t="s">
+      <c r="I35" s="8" t="s">
         <v>651</v>
       </c>
-      <c r="M35" s="5" t="s">
+      <c r="J35" s="8"/>
+      <c r="K35" s="8" t="s">
         <v>652</v>
       </c>
-      <c r="N35" s="5" t="s">
+      <c r="M35" s="3" t="s">
         <v>653</v>
       </c>
-      <c r="O35" s="5" t="s">
+      <c r="N35" s="3" t="s">
         <v>654</v>
       </c>
-      <c r="Q35" s="10" t="s">
+      <c r="O35" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="R35" s="10" t="s">
+      <c r="Q35" s="8" t="s">
         <v>656</v>
       </c>
-      <c r="S35" s="10" t="s">
+      <c r="R35" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="U35" s="10" t="s">
+      <c r="S35" s="8" t="s">
         <v>658</v>
       </c>
-      <c r="V35" s="10"/>
-      <c r="W35" s="10" t="s">
+      <c r="U35" s="8" t="s">
         <v>659</v>
       </c>
-      <c r="Y35" s="10" t="s">
+      <c r="V35" s="8"/>
+      <c r="W35" s="8" t="s">
         <v>660</v>
       </c>
-      <c r="Z35" s="10"/>
-      <c r="AA35" s="10" t="s">
+      <c r="Y35" s="8" t="s">
         <v>661</v>
       </c>
-      <c r="AC35" s="10" t="s">
+      <c r="Z35" s="8"/>
+      <c r="AA35" s="8" t="s">
         <v>662</v>
       </c>
-      <c r="AD35" s="10"/>
-      <c r="AE35" s="10" t="s">
+      <c r="AC35" s="8" t="s">
         <v>663</v>
       </c>
+      <c r="AD35" s="8"/>
+      <c r="AE35" s="8" t="s">
+        <v>664</v>
+      </c>
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A36" s="5" t="s">
-        <v>664</v>
-      </c>
-      <c r="B36" s="5" t="s">
+      <c r="A36" s="3" t="s">
         <v>665</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="B36" s="3" t="s">
         <v>666</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="C36" s="3" t="s">
         <v>667</v>
       </c>
-      <c r="F36" s="7" t="s">
+      <c r="E36" s="5" t="s">
         <v>668</v>
       </c>
-      <c r="G36" s="7" t="s">
+      <c r="F36" s="5" t="s">
         <v>669</v>
       </c>
-      <c r="I36" s="10" t="s">
+      <c r="G36" s="5" t="s">
         <v>670</v>
       </c>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10" t="s">
+      <c r="I36" s="8" t="s">
         <v>671</v>
       </c>
-      <c r="M36" s="10" t="s">
+      <c r="J36" s="8"/>
+      <c r="K36" s="8" t="s">
         <v>672</v>
       </c>
-      <c r="N36" s="10" t="s">
+      <c r="M36" s="8" t="s">
         <v>673</v>
       </c>
-      <c r="O36" s="10" t="s">
+      <c r="N36" s="8" t="s">
         <v>674</v>
       </c>
-      <c r="Q36" s="10" t="s">
+      <c r="O36" s="8" t="s">
         <v>675</v>
       </c>
-      <c r="R36" s="10"/>
-      <c r="S36" s="10" t="s">
+      <c r="Q36" s="8" t="s">
         <v>676</v>
       </c>
-      <c r="U36" s="10" t="s">
+      <c r="R36" s="8"/>
+      <c r="S36" s="8" t="s">
         <v>677</v>
       </c>
-      <c r="V36" s="10"/>
-      <c r="W36" s="10" t="s">
+      <c r="U36" s="8" t="s">
         <v>678</v>
       </c>
-      <c r="Y36" s="10" t="s">
+      <c r="V36" s="8"/>
+      <c r="W36" s="8" t="s">
         <v>679</v>
       </c>
-      <c r="Z36" s="10"/>
-      <c r="AA36" s="10" t="s">
+      <c r="Y36" s="8" t="s">
         <v>680</v>
       </c>
-      <c r="AC36" s="10" t="s">
+      <c r="Z36" s="8"/>
+      <c r="AA36" s="8" t="s">
         <v>681</v>
       </c>
-      <c r="AD36" s="10"/>
-      <c r="AE36" s="10" t="s">
+      <c r="AC36" s="8" t="s">
         <v>682</v>
       </c>
+      <c r="AD36" s="8"/>
+      <c r="AE36" s="8" t="s">
+        <v>683</v>
+      </c>
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A37" s="9" t="s">
-        <v>683</v>
-      </c>
-      <c r="B37" s="9" t="s">
+      <c r="A37" s="7" t="s">
         <v>684</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="B37" s="7" t="s">
         <v>685</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="C37" s="7" t="s">
         <v>686</v>
       </c>
-      <c r="F37" s="10" t="s">
+      <c r="E37" s="8" t="s">
         <v>687</v>
       </c>
-      <c r="G37" s="10" t="s">
+      <c r="F37" s="8" t="s">
         <v>688</v>
       </c>
-      <c r="I37" s="10" t="s">
+      <c r="G37" s="8" t="s">
         <v>689</v>
       </c>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10" t="s">
+      <c r="I37" s="8" t="s">
         <v>690</v>
       </c>
-      <c r="M37" s="10" t="s">
+      <c r="J37" s="8"/>
+      <c r="K37" s="8" t="s">
         <v>691</v>
       </c>
-      <c r="N37" s="10"/>
-      <c r="O37" s="10" t="s">
+      <c r="M37" s="8" t="s">
         <v>692</v>
       </c>
-      <c r="Q37" s="10" t="s">
+      <c r="N37" s="8"/>
+      <c r="O37" s="8" t="s">
         <v>693</v>
       </c>
-      <c r="R37" s="10"/>
-      <c r="S37" s="10" t="s">
+      <c r="Q37" s="8" t="s">
         <v>694</v>
       </c>
-      <c r="U37" s="10" t="s">
+      <c r="R37" s="8"/>
+      <c r="S37" s="8" t="s">
         <v>695</v>
       </c>
-      <c r="V37" s="10"/>
-      <c r="W37" s="10" t="s">
+      <c r="U37" s="8" t="s">
         <v>696</v>
       </c>
-      <c r="Y37" s="7" t="s">
+      <c r="V37" s="8"/>
+      <c r="W37" s="8" t="s">
         <v>697</v>
       </c>
-      <c r="Z37" s="7" t="s">
+      <c r="Y37" s="5" t="s">
         <v>698</v>
       </c>
-      <c r="AA37" s="7" t="s">
+      <c r="Z37" s="5" t="s">
         <v>699</v>
       </c>
-      <c r="AC37" s="10" t="s">
+      <c r="AA37" s="5" t="s">
         <v>700</v>
       </c>
-      <c r="AD37" s="10"/>
-      <c r="AE37" s="10" t="s">
+      <c r="AC37" s="8" t="s">
         <v>701</v>
       </c>
+      <c r="AD37" s="8"/>
+      <c r="AE37" s="8" t="s">
+        <v>702</v>
+      </c>
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A38" s="10" t="s">
-        <v>702</v>
-      </c>
-      <c r="B38" s="10" t="s">
+      <c r="A38" s="8" t="s">
         <v>703</v>
       </c>
-      <c r="C38" s="10" t="s">
+      <c r="B38" s="8" t="s">
         <v>704</v>
       </c>
-      <c r="E38" s="10" t="s">
+      <c r="C38" s="8" t="s">
         <v>705</v>
       </c>
-      <c r="F38" s="10" t="s">
+      <c r="E38" s="8" t="s">
         <v>706</v>
       </c>
-      <c r="G38" s="10" t="s">
+      <c r="F38" s="8" t="s">
         <v>707</v>
       </c>
-      <c r="I38" s="10" t="s">
+      <c r="G38" s="8" t="s">
         <v>708</v>
       </c>
-      <c r="J38" s="10" t="s">
+      <c r="I38" s="8" t="s">
         <v>709</v>
       </c>
-      <c r="K38" s="10" t="s">
+      <c r="J38" s="8" t="s">
         <v>710</v>
       </c>
-      <c r="M38" s="10" t="s">
+      <c r="K38" s="8" t="s">
         <v>711</v>
       </c>
-      <c r="N38" s="10" t="s">
+      <c r="M38" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="O38" s="10" t="s">
+      <c r="N38" s="8" t="s">
         <v>713</v>
       </c>
-      <c r="Q38" s="10" t="s">
+      <c r="O38" s="8" t="s">
         <v>714</v>
       </c>
-      <c r="R38" s="10"/>
-      <c r="S38" s="10" t="s">
+      <c r="Q38" s="8" t="s">
         <v>715</v>
       </c>
-      <c r="U38" s="10" t="s">
+      <c r="R38" s="8"/>
+      <c r="S38" s="8" t="s">
         <v>716</v>
       </c>
-      <c r="V38" s="10"/>
-      <c r="W38" s="10" t="s">
+      <c r="U38" s="8" t="s">
         <v>717</v>
       </c>
-      <c r="Y38" s="10" t="s">
+      <c r="V38" s="8"/>
+      <c r="W38" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="Z38" s="10"/>
-      <c r="AA38" s="10" t="s">
+      <c r="Y38" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="AC38" s="10" t="s">
+      <c r="Z38" s="8"/>
+      <c r="AA38" s="8" t="s">
         <v>720</v>
       </c>
-      <c r="AD38" s="10"/>
-      <c r="AE38" s="10" t="s">
+      <c r="AC38" s="8" t="s">
         <v>721</v>
       </c>
+      <c r="AD38" s="8"/>
+      <c r="AE38" s="8" t="s">
+        <v>722</v>
+      </c>
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A39" s="5" t="s">
-        <v>722</v>
-      </c>
-      <c r="B39" s="5" t="s">
+      <c r="A39" s="3" t="s">
         <v>723</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="B39" s="3" t="s">
         <v>724</v>
       </c>
-      <c r="E39" s="7" t="s">
+      <c r="C39" s="3" t="s">
         <v>725</v>
       </c>
-      <c r="F39" s="7" t="s">
+      <c r="E39" s="5" t="s">
         <v>726</v>
       </c>
-      <c r="G39" s="7" t="s">
+      <c r="F39" s="5" t="s">
         <v>727</v>
       </c>
-      <c r="I39" s="10" t="s">
+      <c r="G39" s="5" t="s">
         <v>728</v>
       </c>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10" t="s">
+      <c r="I39" s="8" t="s">
         <v>729</v>
       </c>
-      <c r="M39" s="10" t="s">
+      <c r="J39" s="8"/>
+      <c r="K39" s="8" t="s">
         <v>730</v>
       </c>
-      <c r="N39" s="10"/>
-      <c r="O39" s="10" t="s">
+      <c r="M39" s="8" t="s">
         <v>731</v>
       </c>
-      <c r="Q39" s="10" t="s">
+      <c r="N39" s="8"/>
+      <c r="O39" s="8" t="s">
         <v>732</v>
       </c>
-      <c r="R39" s="10"/>
-      <c r="S39" s="10" t="s">
+      <c r="Q39" s="8" t="s">
         <v>733</v>
       </c>
-      <c r="U39" s="10" t="s">
+      <c r="R39" s="8"/>
+      <c r="S39" s="8" t="s">
         <v>734</v>
       </c>
-      <c r="V39" s="10"/>
-      <c r="W39" s="10" t="s">
+      <c r="U39" s="8" t="s">
         <v>735</v>
       </c>
-      <c r="Y39" s="10" t="s">
+      <c r="V39" s="8"/>
+      <c r="W39" s="8" t="s">
         <v>736</v>
       </c>
-      <c r="Z39" s="10"/>
-      <c r="AA39" s="10" t="s">
+      <c r="Y39" s="8" t="s">
         <v>737</v>
       </c>
-      <c r="AC39" s="10" t="s">
+      <c r="Z39" s="8"/>
+      <c r="AA39" s="8" t="s">
         <v>738</v>
       </c>
-      <c r="AD39" s="10"/>
-      <c r="AE39" s="10" t="s">
+      <c r="AC39" s="8" t="s">
         <v>739</v>
       </c>
+      <c r="AD39" s="8"/>
+      <c r="AE39" s="8" t="s">
+        <v>740</v>
+      </c>
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A40" s="5" t="s">
-        <v>740</v>
-      </c>
-      <c r="B40" s="5" t="s">
+      <c r="A40" s="3" t="s">
         <v>741</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="B40" s="3" t="s">
         <v>742</v>
       </c>
-      <c r="E40" s="10" t="s">
+      <c r="C40" s="3" t="s">
         <v>743</v>
       </c>
-      <c r="F40" s="10" t="s">
+      <c r="E40" s="8" t="s">
         <v>744</v>
       </c>
-      <c r="G40" s="10" t="s">
+      <c r="F40" s="8" t="s">
         <v>745</v>
       </c>
-      <c r="I40" s="5" t="s">
+      <c r="G40" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="J40" s="5" t="s">
+      <c r="I40" s="3" t="s">
         <v>747</v>
       </c>
-      <c r="K40" s="5" t="s">
+      <c r="J40" s="3" t="s">
         <v>748</v>
       </c>
-      <c r="M40" s="10" t="s">
+      <c r="K40" s="3" t="s">
         <v>749</v>
       </c>
-      <c r="N40" s="10" t="s">
+      <c r="M40" s="8" t="s">
         <v>750</v>
       </c>
-      <c r="O40" s="10" t="s">
+      <c r="N40" s="8" t="s">
         <v>751</v>
       </c>
-      <c r="Q40" s="10" t="s">
+      <c r="O40" s="8" t="s">
         <v>752</v>
       </c>
-      <c r="R40" s="10" t="s">
+      <c r="Q40" s="8" t="s">
         <v>753</v>
       </c>
-      <c r="S40" s="10" t="s">
+      <c r="R40" s="8" t="s">
         <v>754</v>
       </c>
-      <c r="U40" s="10" t="s">
+      <c r="S40" s="8" t="s">
         <v>755</v>
       </c>
-      <c r="V40" s="10"/>
-      <c r="W40" s="10" t="s">
+      <c r="U40" s="8" t="s">
         <v>756</v>
       </c>
-      <c r="Y40" s="10" t="s">
+      <c r="V40" s="8"/>
+      <c r="W40" s="8" t="s">
         <v>757</v>
       </c>
-      <c r="Z40" s="10"/>
-      <c r="AA40" s="10" t="s">
+      <c r="Y40" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="AC40" s="10" t="s">
+      <c r="Z40" s="8"/>
+      <c r="AA40" s="8" t="s">
         <v>759</v>
       </c>
-      <c r="AD40" s="10"/>
-      <c r="AE40" s="10" t="s">
+      <c r="AC40" s="8" t="s">
         <v>760</v>
       </c>
+      <c r="AD40" s="8"/>
+      <c r="AE40" s="8" t="s">
+        <v>761</v>
+      </c>
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A41" s="5" t="s">
-        <v>761</v>
-      </c>
-      <c r="B41" s="5" t="s">
+      <c r="A41" s="3" t="s">
         <v>762</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="B41" s="3" t="s">
         <v>763</v>
       </c>
-      <c r="E41" s="10" t="s">
+      <c r="C41" s="3" t="s">
         <v>764</v>
       </c>
-      <c r="F41" s="10" t="s">
+      <c r="E41" s="8" t="s">
         <v>765</v>
       </c>
-      <c r="G41" s="10" t="s">
+      <c r="F41" s="8" t="s">
         <v>766</v>
       </c>
-      <c r="I41" s="10" t="s">
+      <c r="G41" s="8" t="s">
         <v>767</v>
       </c>
-      <c r="J41" s="10" t="s">
+      <c r="I41" s="8" t="s">
         <v>768</v>
       </c>
-      <c r="K41" s="10" t="s">
+      <c r="J41" s="8" t="s">
         <v>769</v>
       </c>
-      <c r="M41" s="10" t="s">
+      <c r="K41" s="8" t="s">
         <v>770</v>
       </c>
-      <c r="N41" s="10" t="s">
+      <c r="M41" s="8" t="s">
         <v>771</v>
       </c>
-      <c r="O41" s="10" t="s">
+      <c r="N41" s="8" t="s">
         <v>772</v>
       </c>
-      <c r="Q41" s="10" t="s">
+      <c r="O41" s="8" t="s">
         <v>773</v>
       </c>
-      <c r="R41" s="10" t="s">
+      <c r="Q41" s="8" t="s">
         <v>774</v>
       </c>
-      <c r="S41" s="10" t="s">
+      <c r="R41" s="8" t="s">
         <v>775</v>
       </c>
-      <c r="U41" s="10" t="s">
+      <c r="S41" s="8" t="s">
         <v>776</v>
       </c>
-      <c r="V41" s="10"/>
-      <c r="W41" s="10" t="s">
+      <c r="U41" s="8" t="s">
         <v>777</v>
       </c>
-      <c r="Y41" s="10" t="s">
+      <c r="V41" s="8"/>
+      <c r="W41" s="8" t="s">
         <v>778</v>
       </c>
-      <c r="Z41" s="10"/>
-      <c r="AA41" s="10" t="s">
+      <c r="Y41" s="8" t="s">
         <v>779</v>
       </c>
-      <c r="AC41" s="10" t="s">
+      <c r="Z41" s="8"/>
+      <c r="AA41" s="8" t="s">
         <v>780</v>
       </c>
-      <c r="AD41" s="10"/>
-      <c r="AE41" s="10" t="s">
+      <c r="AC41" s="8" t="s">
         <v>781</v>
       </c>
+      <c r="AD41" s="8"/>
+      <c r="AE41" s="8" t="s">
+        <v>782</v>
+      </c>
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A42" s="10" t="s">
-        <v>782</v>
-      </c>
-      <c r="B42" s="10" t="s">
+      <c r="A42" s="8" t="s">
         <v>783</v>
       </c>
-      <c r="C42" s="10" t="s">
+      <c r="B42" s="8" t="s">
         <v>784</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="C42" s="8" t="s">
         <v>785</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="E42" s="3" t="s">
         <v>786</v>
       </c>
-      <c r="G42" s="5" t="s">
+      <c r="F42" s="3" t="s">
         <v>787</v>
       </c>
-      <c r="I42" s="5" t="s">
+      <c r="G42" s="3" t="s">
         <v>788</v>
       </c>
-      <c r="J42" s="5" t="s">
+      <c r="I42" s="3" t="s">
         <v>789</v>
       </c>
-      <c r="K42" s="5" t="s">
+      <c r="J42" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="M42" s="10" t="s">
+      <c r="K42" s="3" t="s">
         <v>791</v>
       </c>
-      <c r="N42" s="10"/>
-      <c r="O42" s="10" t="s">
+      <c r="M42" s="8" t="s">
         <v>792</v>
       </c>
-      <c r="Q42" s="10" t="s">
+      <c r="N42" s="8"/>
+      <c r="O42" s="8" t="s">
         <v>793</v>
       </c>
-      <c r="R42" s="10" t="s">
+      <c r="Q42" s="8" t="s">
         <v>794</v>
       </c>
-      <c r="S42" s="10" t="s">
+      <c r="R42" s="8" t="s">
         <v>795</v>
       </c>
-      <c r="U42" s="10" t="s">
+      <c r="S42" s="8" t="s">
         <v>796</v>
       </c>
-      <c r="V42" s="10"/>
-      <c r="W42" s="10" t="s">
+      <c r="U42" s="8" t="s">
         <v>797</v>
       </c>
-      <c r="Y42" s="10" t="s">
+      <c r="V42" s="8"/>
+      <c r="W42" s="8" t="s">
         <v>798</v>
       </c>
-      <c r="Z42" s="10"/>
-      <c r="AA42" s="10" t="s">
+      <c r="Y42" s="8" t="s">
         <v>799</v>
       </c>
-      <c r="AC42" s="10" t="s">
+      <c r="Z42" s="8"/>
+      <c r="AA42" s="8" t="s">
         <v>800</v>
       </c>
-      <c r="AD42" s="10"/>
-      <c r="AE42" s="10" t="s">
+      <c r="AC42" s="8" t="s">
         <v>801</v>
       </c>
+      <c r="AD42" s="8"/>
+      <c r="AE42" s="8" t="s">
+        <v>802</v>
+      </c>
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A43" s="7" t="s">
-        <v>802</v>
-      </c>
-      <c r="B43" s="7" t="s">
+      <c r="A43" s="5" t="s">
         <v>803</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="B43" s="5" t="s">
         <v>804</v>
       </c>
-      <c r="E43" s="7" t="s">
+      <c r="C43" s="5" t="s">
         <v>805</v>
       </c>
-      <c r="F43" s="7" t="s">
+      <c r="E43" s="5" t="s">
         <v>806</v>
       </c>
-      <c r="G43" s="7" t="s">
+      <c r="F43" s="5" t="s">
         <v>807</v>
       </c>
-      <c r="I43" s="10" t="s">
+      <c r="G43" s="5" t="s">
         <v>808</v>
       </c>
-      <c r="J43" s="10" t="s">
+      <c r="I43" s="8" t="s">
         <v>809</v>
       </c>
-      <c r="K43" s="10" t="s">
+      <c r="J43" s="8" t="s">
         <v>810</v>
       </c>
-      <c r="M43" s="10" t="s">
+      <c r="K43" s="8" t="s">
         <v>811</v>
       </c>
-      <c r="N43" s="10"/>
-      <c r="O43" s="10" t="s">
+      <c r="M43" s="8" t="s">
         <v>812</v>
       </c>
-      <c r="Q43" s="10" t="s">
+      <c r="N43" s="8"/>
+      <c r="O43" s="8" t="s">
         <v>813</v>
       </c>
-      <c r="R43" s="10"/>
-      <c r="S43" s="10" t="s">
+      <c r="Q43" s="8" t="s">
         <v>814</v>
       </c>
-      <c r="U43" s="10" t="s">
+      <c r="R43" s="8"/>
+      <c r="S43" s="8" t="s">
         <v>815</v>
       </c>
-      <c r="V43" s="10"/>
-      <c r="W43" s="10" t="s">
+      <c r="U43" s="8" t="s">
         <v>816</v>
       </c>
-      <c r="Y43" s="10" t="s">
+      <c r="V43" s="8"/>
+      <c r="W43" s="8" t="s">
         <v>817</v>
       </c>
-      <c r="Z43" s="10"/>
-      <c r="AA43" s="10" t="s">
+      <c r="Y43" s="8" t="s">
         <v>818</v>
       </c>
-      <c r="AC43" s="10" t="s">
+      <c r="Z43" s="8"/>
+      <c r="AA43" s="8" t="s">
         <v>819</v>
       </c>
-      <c r="AD43" s="10"/>
-      <c r="AE43" s="10" t="s">
+      <c r="AC43" s="8" t="s">
         <v>820</v>
       </c>
+      <c r="AD43" s="8"/>
+      <c r="AE43" s="8" t="s">
+        <v>821</v>
+      </c>
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A44" s="5" t="s">
-        <v>821</v>
-      </c>
-      <c r="B44" s="5" t="s">
+      <c r="A44" s="3" t="s">
         <v>822</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="B44" s="3" t="s">
         <v>823</v>
       </c>
-      <c r="E44" s="7" t="s">
+      <c r="C44" s="3" t="s">
         <v>824</v>
       </c>
-      <c r="F44" s="7" t="s">
+      <c r="E44" s="5" t="s">
         <v>825</v>
       </c>
-      <c r="G44" s="7" t="s">
+      <c r="F44" s="5" t="s">
         <v>826</v>
       </c>
-      <c r="I44" s="10" t="s">
+      <c r="G44" s="5" t="s">
         <v>827</v>
       </c>
-      <c r="J44" s="10" t="s">
+      <c r="I44" s="8" t="s">
         <v>828</v>
       </c>
-      <c r="K44" s="10" t="s">
+      <c r="J44" s="8" t="s">
         <v>829</v>
       </c>
-      <c r="M44" s="10" t="s">
+      <c r="K44" s="8" t="s">
         <v>830</v>
       </c>
-      <c r="N44" s="10" t="s">
+      <c r="M44" s="8" t="s">
         <v>831</v>
       </c>
-      <c r="O44" s="10" t="s">
+      <c r="N44" s="8" t="s">
         <v>832</v>
       </c>
-      <c r="Q44" s="10" t="s">
+      <c r="O44" s="8" t="s">
         <v>833</v>
       </c>
-      <c r="R44" s="10"/>
-      <c r="S44" s="10" t="s">
+      <c r="Q44" s="8" t="s">
         <v>834</v>
       </c>
-      <c r="U44" s="10" t="s">
+      <c r="R44" s="8"/>
+      <c r="S44" s="8" t="s">
         <v>835</v>
       </c>
-      <c r="V44" s="10"/>
-      <c r="W44" s="10" t="s">
+      <c r="U44" s="8" t="s">
         <v>836</v>
       </c>
-      <c r="Y44" s="10" t="s">
+      <c r="V44" s="8"/>
+      <c r="W44" s="8" t="s">
         <v>837</v>
       </c>
-      <c r="Z44" s="10"/>
-      <c r="AA44" s="10" t="s">
+      <c r="Y44" s="8" t="s">
         <v>838</v>
       </c>
-      <c r="AC44" s="10" t="s">
+      <c r="Z44" s="8"/>
+      <c r="AA44" s="8" t="s">
         <v>839</v>
       </c>
-      <c r="AD44" s="10"/>
-      <c r="AE44" s="10" t="s">
+      <c r="AC44" s="8" t="s">
         <v>840</v>
       </c>
+      <c r="AD44" s="8"/>
+      <c r="AE44" s="8" t="s">
+        <v>841</v>
+      </c>
     </row>
     <row r="45" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A45" s="10" t="s">
-        <v>841</v>
-      </c>
-      <c r="B45" s="10" t="s">
+      <c r="A45" s="8" t="s">
         <v>842</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="B45" s="8" t="s">
         <v>843</v>
       </c>
-      <c r="E45" s="7" t="s">
+      <c r="C45" s="8" t="s">
         <v>844</v>
       </c>
-      <c r="F45" s="7" t="s">
+      <c r="E45" s="5" t="s">
         <v>845</v>
       </c>
-      <c r="G45" s="7" t="s">
+      <c r="F45" s="5" t="s">
         <v>846</v>
       </c>
-      <c r="I45" s="10" t="s">
+      <c r="G45" s="5" t="s">
         <v>847</v>
       </c>
-      <c r="J45" s="10" t="s">
+      <c r="I45" s="8" t="s">
         <v>848</v>
       </c>
-      <c r="K45" s="10" t="s">
+      <c r="J45" s="8" t="s">
         <v>849</v>
       </c>
-      <c r="M45" s="10" t="s">
+      <c r="K45" s="8" t="s">
         <v>850</v>
       </c>
-      <c r="N45" s="10"/>
-      <c r="O45" s="10" t="s">
+      <c r="M45" s="8" t="s">
         <v>851</v>
       </c>
-      <c r="Q45" s="10" t="s">
+      <c r="N45" s="8"/>
+      <c r="O45" s="8" t="s">
         <v>852</v>
       </c>
-      <c r="R45" s="10"/>
-      <c r="S45" s="10" t="s">
+      <c r="Q45" s="8" t="s">
         <v>853</v>
       </c>
-      <c r="U45" s="10" t="s">
+      <c r="R45" s="8"/>
+      <c r="S45" s="8" t="s">
         <v>854</v>
       </c>
-      <c r="V45" s="10"/>
-      <c r="W45" s="10" t="s">
+      <c r="U45" s="8" t="s">
         <v>855</v>
       </c>
-      <c r="Y45" s="10" t="s">
+      <c r="V45" s="8"/>
+      <c r="W45" s="8" t="s">
         <v>856</v>
       </c>
-      <c r="Z45" s="10"/>
-      <c r="AA45" s="10" t="s">
+      <c r="Y45" s="8" t="s">
         <v>857</v>
       </c>
-      <c r="AC45" s="10" t="s">
+      <c r="Z45" s="8"/>
+      <c r="AA45" s="8" t="s">
         <v>858</v>
       </c>
-      <c r="AD45" s="10"/>
-      <c r="AE45" s="10" t="s">
+      <c r="AC45" s="8" t="s">
         <v>859</v>
       </c>
+      <c r="AD45" s="8"/>
+      <c r="AE45" s="8" t="s">
+        <v>860</v>
+      </c>
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A46" s="5" t="s">
-        <v>860</v>
-      </c>
-      <c r="B46" s="5" t="s">
+      <c r="A46" s="3" t="s">
         <v>861</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="B46" s="3" t="s">
         <v>862</v>
       </c>
-      <c r="E46" s="10" t="s">
+      <c r="C46" s="3" t="s">
         <v>863</v>
       </c>
-      <c r="F46" s="10" t="s">
+      <c r="E46" s="8" t="s">
         <v>864</v>
       </c>
-      <c r="G46" s="10" t="s">
+      <c r="F46" s="8" t="s">
         <v>865</v>
       </c>
-      <c r="I46" s="10" t="s">
+      <c r="G46" s="8" t="s">
         <v>866</v>
       </c>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10" t="s">
+      <c r="I46" s="8" t="s">
         <v>867</v>
       </c>
-      <c r="M46" s="10" t="s">
+      <c r="J46" s="8"/>
+      <c r="K46" s="8" t="s">
         <v>868</v>
       </c>
-      <c r="N46" s="10"/>
-      <c r="O46" s="10" t="s">
+      <c r="M46" s="8" t="s">
         <v>869</v>
       </c>
-      <c r="Q46" s="10" t="s">
+      <c r="N46" s="8"/>
+      <c r="O46" s="8" t="s">
         <v>870</v>
       </c>
-      <c r="R46" s="10"/>
-      <c r="S46" s="10" t="s">
+      <c r="Q46" s="8" t="s">
         <v>871</v>
       </c>
-      <c r="U46" s="10" t="s">
+      <c r="R46" s="8"/>
+      <c r="S46" s="8" t="s">
         <v>872</v>
       </c>
-      <c r="V46" s="10"/>
-      <c r="W46" s="10" t="s">
+      <c r="U46" s="8" t="s">
         <v>873</v>
       </c>
-      <c r="Y46" s="10" t="s">
+      <c r="V46" s="8"/>
+      <c r="W46" s="8" t="s">
         <v>874</v>
       </c>
-      <c r="Z46" s="10"/>
-      <c r="AA46" s="10" t="s">
+      <c r="Y46" s="8" t="s">
         <v>875</v>
       </c>
-      <c r="AC46" s="10" t="s">
+      <c r="Z46" s="8"/>
+      <c r="AA46" s="8" t="s">
         <v>876</v>
       </c>
-      <c r="AD46" s="10"/>
-      <c r="AE46" s="10" t="s">
+      <c r="AC46" s="8" t="s">
         <v>877</v>
       </c>
+      <c r="AD46" s="8"/>
+      <c r="AE46" s="8" t="s">
+        <v>878</v>
+      </c>
     </row>
     <row r="47" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A47" s="10" t="s">
-        <v>878</v>
-      </c>
-      <c r="B47" s="10" t="s">
+      <c r="A47" s="8" t="s">
         <v>879</v>
       </c>
-      <c r="C47" s="10" t="s">
+      <c r="B47" s="8" t="s">
         <v>880</v>
       </c>
-      <c r="E47" s="10" t="s">
+      <c r="C47" s="8" t="s">
         <v>881</v>
       </c>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10" t="s">
+      <c r="E47" s="8" t="s">
         <v>882</v>
       </c>
-      <c r="I47" s="10" t="s">
+      <c r="F47" s="8"/>
+      <c r="G47" s="8" t="s">
         <v>883</v>
       </c>
-      <c r="J47" s="10"/>
-      <c r="K47" s="10" t="s">
+      <c r="I47" s="8" t="s">
         <v>884</v>
       </c>
-      <c r="M47" s="10" t="s">
+      <c r="J47" s="8"/>
+      <c r="K47" s="8" t="s">
         <v>885</v>
       </c>
-      <c r="N47" s="10"/>
-      <c r="O47" s="10" t="s">
+      <c r="M47" s="8" t="s">
         <v>886</v>
       </c>
-      <c r="Q47" s="10" t="s">
+      <c r="N47" s="8"/>
+      <c r="O47" s="8" t="s">
         <v>887</v>
       </c>
-      <c r="R47" s="10"/>
-      <c r="S47" s="10" t="s">
+      <c r="Q47" s="8" t="s">
         <v>888</v>
       </c>
-      <c r="U47" s="10" t="s">
+      <c r="R47" s="8"/>
+      <c r="S47" s="8" t="s">
         <v>889</v>
       </c>
-      <c r="V47" s="10"/>
-      <c r="W47" s="10" t="s">
+      <c r="U47" s="8" t="s">
         <v>890</v>
       </c>
-      <c r="Y47" s="10" t="s">
+      <c r="V47" s="8"/>
+      <c r="W47" s="8" t="s">
         <v>891</v>
       </c>
-      <c r="Z47" s="10"/>
-      <c r="AA47" s="10" t="s">
+      <c r="Y47" s="8" t="s">
         <v>892</v>
       </c>
-      <c r="AC47" s="10" t="s">
+      <c r="Z47" s="8"/>
+      <c r="AA47" s="8" t="s">
         <v>893</v>
       </c>
-      <c r="AD47" s="10"/>
-      <c r="AE47" s="10" t="s">
+      <c r="AC47" s="8" t="s">
         <v>894</v>
       </c>
+      <c r="AD47" s="8"/>
+      <c r="AE47" s="8" t="s">
+        <v>895</v>
+      </c>
     </row>
     <row r="48" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A48" s="10" t="s">
-        <v>895</v>
-      </c>
-      <c r="B48" s="10" t="s">
+      <c r="A48" s="8" t="s">
         <v>896</v>
       </c>
-      <c r="C48" s="10" t="s">
+      <c r="B48" s="8" t="s">
         <v>897</v>
       </c>
-      <c r="E48" s="7" t="s">
+      <c r="C48" s="8" t="s">
         <v>898</v>
       </c>
-      <c r="F48" s="7" t="s">
+      <c r="E48" s="5" t="s">
+        <v>899</v>
+      </c>
+      <c r="F48" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="G48" s="7" t="s">
-        <v>899</v>
-      </c>
-      <c r="I48" s="10" t="s">
+      <c r="G48" s="5" t="s">
         <v>900</v>
       </c>
-      <c r="J48" s="10" t="s">
-        <v>768</v>
-      </c>
-      <c r="K48" s="10" t="s">
+      <c r="I48" s="8" t="s">
         <v>901</v>
       </c>
-      <c r="M48" s="10" t="s">
+      <c r="J48" s="8" t="s">
+        <v>769</v>
+      </c>
+      <c r="K48" s="8" t="s">
         <v>902</v>
       </c>
-      <c r="N48" s="10"/>
-      <c r="O48" s="10" t="s">
+      <c r="M48" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="Q48" s="10" t="s">
+      <c r="N48" s="8"/>
+      <c r="O48" s="8" t="s">
         <v>904</v>
       </c>
-      <c r="R48" s="10"/>
-      <c r="S48" s="10" t="s">
+      <c r="Q48" s="8" t="s">
         <v>905</v>
       </c>
-      <c r="U48" s="10" t="s">
+      <c r="R48" s="8"/>
+      <c r="S48" s="8" t="s">
         <v>906</v>
       </c>
-      <c r="V48" s="10"/>
-      <c r="W48" s="10" t="s">
+      <c r="U48" s="8" t="s">
         <v>907</v>
       </c>
-      <c r="Y48" s="10" t="s">
+      <c r="V48" s="8"/>
+      <c r="W48" s="8" t="s">
         <v>908</v>
       </c>
-      <c r="Z48" s="10"/>
-      <c r="AA48" s="10" t="s">
+      <c r="Y48" s="8" t="s">
         <v>909</v>
       </c>
-      <c r="AC48" s="10" t="s">
+      <c r="Z48" s="8"/>
+      <c r="AA48" s="8" t="s">
         <v>910</v>
       </c>
-      <c r="AD48" s="10"/>
-      <c r="AE48" s="10" t="s">
+      <c r="AC48" s="8" t="s">
         <v>911</v>
       </c>
+      <c r="AD48" s="8"/>
+      <c r="AE48" s="8" t="s">
+        <v>912</v>
+      </c>
     </row>
     <row r="49" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A49" s="10" t="s">
-        <v>912</v>
-      </c>
-      <c r="B49" s="10" t="s">
+      <c r="A49" s="8" t="s">
         <v>913</v>
       </c>
-      <c r="C49" s="10" t="s">
+      <c r="B49" s="8" t="s">
         <v>914</v>
       </c>
-      <c r="E49" s="10" t="s">
+      <c r="C49" s="8" t="s">
         <v>915</v>
       </c>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10" t="s">
+      <c r="E49" s="8" t="s">
         <v>916</v>
       </c>
-      <c r="I49" s="10" t="s">
+      <c r="F49" s="8"/>
+      <c r="G49" s="8" t="s">
         <v>917</v>
       </c>
-      <c r="J49" s="10" t="s">
+      <c r="I49" s="8" t="s">
         <v>918</v>
       </c>
-      <c r="K49" s="10" t="s">
+      <c r="J49" s="8" t="s">
         <v>919</v>
       </c>
-      <c r="M49" s="10" t="s">
+      <c r="K49" s="8" t="s">
         <v>920</v>
       </c>
-      <c r="N49" s="10"/>
-      <c r="O49" s="10" t="s">
+      <c r="M49" s="8" t="s">
         <v>921</v>
       </c>
-      <c r="Q49" s="10" t="s">
+      <c r="N49" s="8"/>
+      <c r="O49" s="8" t="s">
         <v>922</v>
       </c>
-      <c r="R49" s="10"/>
-      <c r="S49" s="10" t="s">
+      <c r="Q49" s="8" t="s">
         <v>923</v>
       </c>
-      <c r="U49" s="10" t="s">
+      <c r="R49" s="8"/>
+      <c r="S49" s="8" t="s">
         <v>924</v>
       </c>
-      <c r="V49" s="10"/>
-      <c r="W49" s="10" t="s">
+      <c r="U49" s="8" t="s">
         <v>925</v>
       </c>
-      <c r="Y49" s="10" t="s">
+      <c r="V49" s="8"/>
+      <c r="W49" s="8" t="s">
         <v>926</v>
       </c>
-      <c r="Z49" s="10"/>
-      <c r="AA49" s="10" t="s">
+      <c r="Y49" s="8" t="s">
         <v>927</v>
       </c>
-      <c r="AC49" s="10" t="s">
+      <c r="Z49" s="8"/>
+      <c r="AA49" s="8" t="s">
         <v>928</v>
       </c>
-      <c r="AD49" s="10"/>
-      <c r="AE49" s="10" t="s">
+      <c r="AC49" s="8" t="s">
         <v>929</v>
       </c>
+      <c r="AD49" s="8"/>
+      <c r="AE49" s="8" t="s">
+        <v>930</v>
+      </c>
     </row>
     <row r="50" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A50" s="5" t="s">
-        <v>930</v>
-      </c>
-      <c r="B50" s="5" t="s">
+      <c r="A50" s="3" t="s">
         <v>931</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="B50" s="3" t="s">
         <v>932</v>
       </c>
-      <c r="E50" s="10" t="s">
+      <c r="C50" s="3" t="s">
         <v>933</v>
       </c>
-      <c r="F50" s="10" t="s">
+      <c r="E50" s="8" t="s">
         <v>934</v>
       </c>
-      <c r="G50" s="10" t="s">
+      <c r="F50" s="8" t="s">
         <v>935</v>
       </c>
-      <c r="I50" s="10" t="s">
+      <c r="G50" s="8" t="s">
         <v>936</v>
       </c>
-      <c r="J50" s="10" t="s">
+      <c r="I50" s="8" t="s">
         <v>937</v>
       </c>
-      <c r="K50" s="10" t="s">
+      <c r="J50" s="8" t="s">
         <v>938</v>
       </c>
-      <c r="M50" s="10" t="s">
+      <c r="K50" s="8" t="s">
         <v>939</v>
       </c>
-      <c r="N50" s="10" t="s">
+      <c r="M50" s="8" t="s">
         <v>940</v>
       </c>
-      <c r="O50" s="10" t="s">
+      <c r="N50" s="8" t="s">
         <v>941</v>
       </c>
-      <c r="Q50" s="10" t="s">
+      <c r="O50" s="8" t="s">
         <v>942</v>
       </c>
-      <c r="R50" s="10"/>
-      <c r="S50" s="10" t="s">
+      <c r="Q50" s="8" t="s">
         <v>943</v>
       </c>
-      <c r="U50" s="10" t="s">
+      <c r="R50" s="8"/>
+      <c r="S50" s="8" t="s">
         <v>944</v>
       </c>
-      <c r="V50" s="10"/>
-      <c r="W50" s="10" t="s">
+      <c r="U50" s="8" t="s">
         <v>945</v>
       </c>
-      <c r="Y50" s="10" t="s">
+      <c r="V50" s="8"/>
+      <c r="W50" s="8" t="s">
         <v>946</v>
       </c>
-      <c r="Z50" s="10"/>
-      <c r="AA50" s="10" t="s">
+      <c r="Y50" s="8" t="s">
         <v>947</v>
       </c>
-      <c r="AC50" s="10" t="s">
+      <c r="Z50" s="8"/>
+      <c r="AA50" s="8" t="s">
         <v>948</v>
       </c>
-      <c r="AD50" s="10"/>
-      <c r="AE50" s="10" t="s">
+      <c r="AC50" s="8" t="s">
         <v>949</v>
       </c>
+      <c r="AD50" s="8"/>
+      <c r="AE50" s="8" t="s">
+        <v>950</v>
+      </c>
     </row>
     <row r="51" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A51" s="10" t="s">
-        <v>950</v>
-      </c>
-      <c r="B51" s="10" t="s">
+      <c r="A51" s="8" t="s">
         <v>951</v>
       </c>
-      <c r="C51" s="10" t="s">
+      <c r="B51" s="8" t="s">
         <v>952</v>
       </c>
-      <c r="E51" s="10" t="s">
+      <c r="C51" s="8" t="s">
         <v>953</v>
       </c>
-      <c r="F51" s="10" t="s">
+      <c r="E51" s="8" t="s">
         <v>954</v>
       </c>
-      <c r="G51" s="10" t="s">
+      <c r="F51" s="8" t="s">
         <v>955</v>
       </c>
-      <c r="I51" s="10" t="s">
+      <c r="G51" s="8" t="s">
         <v>956</v>
       </c>
-      <c r="J51" s="10" t="s">
+      <c r="I51" s="8" t="s">
         <v>957</v>
       </c>
-      <c r="K51" s="10" t="s">
+      <c r="J51" s="8" t="s">
         <v>958</v>
       </c>
-      <c r="M51" s="10" t="s">
+      <c r="K51" s="8" t="s">
         <v>959</v>
       </c>
-      <c r="N51" s="10"/>
-      <c r="O51" s="10" t="s">
+      <c r="M51" s="8" t="s">
         <v>960</v>
       </c>
-      <c r="Q51" s="10" t="s">
+      <c r="N51" s="8"/>
+      <c r="O51" s="8" t="s">
         <v>961</v>
       </c>
-      <c r="R51" s="10"/>
-      <c r="S51" s="10" t="s">
+      <c r="Q51" s="8" t="s">
         <v>962</v>
       </c>
-      <c r="U51" s="10" t="s">
+      <c r="R51" s="8"/>
+      <c r="S51" s="8" t="s">
         <v>963</v>
       </c>
-      <c r="V51" s="10"/>
-      <c r="W51" s="10" t="s">
+      <c r="U51" s="8" t="s">
         <v>964</v>
       </c>
-      <c r="Y51" s="10" t="s">
+      <c r="V51" s="8"/>
+      <c r="W51" s="8" t="s">
         <v>965</v>
       </c>
-      <c r="Z51" s="10"/>
-      <c r="AA51" s="10" t="s">
+      <c r="Y51" s="8" t="s">
         <v>966</v>
       </c>
-      <c r="AC51" s="10" t="s">
+      <c r="Z51" s="8"/>
+      <c r="AA51" s="8" t="s">
         <v>967</v>
       </c>
-      <c r="AD51" s="10"/>
-      <c r="AE51" s="10" t="s">
+      <c r="AC51" s="8" t="s">
         <v>968</v>
       </c>
+      <c r="AD51" s="8"/>
+      <c r="AE51" s="8" t="s">
+        <v>969</v>
+      </c>
     </row>
     <row r="52" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A52" s="7" t="s">
-        <v>969</v>
-      </c>
-      <c r="B52" s="7" t="s">
+      <c r="A52" s="5" t="s">
         <v>970</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="B52" s="5" t="s">
         <v>971</v>
       </c>
-      <c r="E52" s="10" t="s">
+      <c r="C52" s="5" t="s">
         <v>972</v>
       </c>
-      <c r="F52" s="10" t="s">
+      <c r="E52" s="8" t="s">
         <v>973</v>
       </c>
-      <c r="G52" s="10" t="s">
+      <c r="F52" s="8" t="s">
         <v>974</v>
       </c>
-      <c r="I52" s="10" t="s">
+      <c r="G52" s="8" t="s">
         <v>975</v>
       </c>
-      <c r="J52" s="10" t="s">
+      <c r="I52" s="8" t="s">
         <v>976</v>
       </c>
-      <c r="K52" s="10" t="s">
+      <c r="J52" s="8" t="s">
         <v>977</v>
       </c>
-      <c r="M52" s="10" t="s">
+      <c r="K52" s="8" t="s">
         <v>978</v>
       </c>
-      <c r="N52" s="10"/>
-      <c r="O52" s="10" t="s">
+      <c r="M52" s="8" t="s">
         <v>979</v>
       </c>
-      <c r="Q52" s="10" t="s">
+      <c r="N52" s="8"/>
+      <c r="O52" s="8" t="s">
         <v>980</v>
       </c>
-      <c r="R52" s="10"/>
-      <c r="S52" s="10" t="s">
+      <c r="Q52" s="8" t="s">
         <v>981</v>
       </c>
-      <c r="U52" s="10" t="s">
+      <c r="R52" s="8"/>
+      <c r="S52" s="8" t="s">
         <v>982</v>
       </c>
-      <c r="V52" s="10"/>
-      <c r="W52" s="10" t="s">
+      <c r="U52" s="8" t="s">
         <v>983</v>
       </c>
-      <c r="Y52" s="10" t="s">
+      <c r="V52" s="8"/>
+      <c r="W52" s="8" t="s">
         <v>984</v>
       </c>
-      <c r="Z52" s="10"/>
-      <c r="AA52" s="10" t="s">
+      <c r="Y52" s="8" t="s">
         <v>985</v>
       </c>
-      <c r="AC52" s="10" t="s">
+      <c r="Z52" s="8"/>
+      <c r="AA52" s="8" t="s">
         <v>986</v>
       </c>
-      <c r="AD52" s="10"/>
-      <c r="AE52" s="10" t="s">
+      <c r="AC52" s="8" t="s">
         <v>987</v>
       </c>
+      <c r="AD52" s="8"/>
+      <c r="AE52" s="8" t="s">
+        <v>988</v>
+      </c>
     </row>
     <row r="53" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A53" s="5" t="s">
-        <v>988</v>
-      </c>
-      <c r="B53" s="5" t="s">
+      <c r="A53" s="3" t="s">
         <v>989</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="B53" s="3" t="s">
         <v>990</v>
       </c>
-      <c r="E53" s="10" t="s">
+      <c r="C53" s="3" t="s">
         <v>991</v>
       </c>
-      <c r="F53" s="10" t="s">
+      <c r="E53" s="8" t="s">
         <v>992</v>
       </c>
-      <c r="G53" s="10" t="s">
+      <c r="F53" s="8" t="s">
         <v>993</v>
       </c>
-      <c r="I53" s="7" t="s">
+      <c r="G53" s="8" t="s">
         <v>994</v>
       </c>
-      <c r="J53" s="7" t="s">
+      <c r="I53" s="5" t="s">
         <v>995</v>
       </c>
-      <c r="K53" s="7" t="s">
+      <c r="J53" s="5" t="s">
         <v>996</v>
       </c>
-      <c r="M53" s="10" t="s">
+      <c r="K53" s="5" t="s">
         <v>997</v>
       </c>
-      <c r="N53" s="10"/>
-      <c r="O53" s="10" t="s">
+      <c r="M53" s="8" t="s">
         <v>998</v>
       </c>
-      <c r="Q53" s="10" t="s">
+      <c r="N53" s="8"/>
+      <c r="O53" s="8" t="s">
         <v>999</v>
       </c>
-      <c r="R53" s="10"/>
-      <c r="S53" s="10" t="s">
+      <c r="Q53" s="8" t="s">
         <v>1000</v>
       </c>
-      <c r="U53" s="10" t="s">
+      <c r="R53" s="8"/>
+      <c r="S53" s="8" t="s">
         <v>1001</v>
       </c>
-      <c r="V53" s="10"/>
-      <c r="W53" s="10" t="s">
+      <c r="U53" s="8" t="s">
         <v>1002</v>
       </c>
-      <c r="Y53" s="10" t="s">
+      <c r="V53" s="8"/>
+      <c r="W53" s="8" t="s">
         <v>1003</v>
       </c>
-      <c r="Z53" s="10"/>
-      <c r="AA53" s="10" t="s">
+      <c r="Y53" s="8" t="s">
         <v>1004</v>
       </c>
-      <c r="AC53" s="10" t="s">
+      <c r="Z53" s="8"/>
+      <c r="AA53" s="8" t="s">
         <v>1005</v>
       </c>
-      <c r="AD53" s="10"/>
-      <c r="AE53" s="10" t="s">
+      <c r="AC53" s="8" t="s">
         <v>1006</v>
       </c>
+      <c r="AD53" s="8"/>
+      <c r="AE53" s="8" t="s">
+        <v>1007</v>
+      </c>
     </row>
     <row r="54" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A54" s="5" t="s">
-        <v>1007</v>
-      </c>
-      <c r="B54" s="5" t="s">
+      <c r="A54" s="3" t="s">
         <v>1008</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="B54" s="3" t="s">
         <v>1009</v>
       </c>
-      <c r="E54" s="10" t="s">
+      <c r="C54" s="3" t="s">
         <v>1010</v>
       </c>
-      <c r="F54" s="10" t="s">
+      <c r="E54" s="8" t="s">
         <v>1011</v>
       </c>
-      <c r="G54" s="10" t="s">
+      <c r="F54" s="8" t="s">
         <v>1012</v>
       </c>
-      <c r="I54" s="10" t="s">
+      <c r="G54" s="8" t="s">
         <v>1013</v>
       </c>
-      <c r="J54" s="10" t="s">
+      <c r="I54" s="8" t="s">
         <v>1014</v>
       </c>
-      <c r="K54" s="10" t="s">
+      <c r="J54" s="8" t="s">
         <v>1015</v>
       </c>
-      <c r="M54" s="10" t="s">
+      <c r="K54" s="8" t="s">
         <v>1016</v>
       </c>
-      <c r="N54" s="10"/>
-      <c r="O54" s="10" t="s">
+      <c r="M54" s="8" t="s">
         <v>1017</v>
       </c>
-      <c r="Q54" s="10" t="s">
+      <c r="N54" s="8"/>
+      <c r="O54" s="8" t="s">
         <v>1018</v>
       </c>
-      <c r="R54" s="10"/>
-      <c r="S54" s="10" t="s">
+      <c r="Q54" s="8" t="s">
         <v>1019</v>
       </c>
-      <c r="U54" s="10" t="s">
+      <c r="R54" s="8"/>
+      <c r="S54" s="8" t="s">
         <v>1020</v>
       </c>
-      <c r="V54" s="10"/>
-      <c r="W54" s="10" t="s">
+      <c r="U54" s="8" t="s">
         <v>1021</v>
       </c>
-      <c r="Y54" s="10" t="s">
+      <c r="V54" s="8"/>
+      <c r="W54" s="8" t="s">
         <v>1022</v>
       </c>
-      <c r="Z54" s="10"/>
-      <c r="AA54" s="10" t="s">
+      <c r="Y54" s="8" t="s">
         <v>1023</v>
       </c>
-      <c r="AC54" s="10" t="s">
+      <c r="Z54" s="8"/>
+      <c r="AA54" s="8" t="s">
         <v>1024</v>
       </c>
-      <c r="AD54" s="10"/>
-      <c r="AE54" s="10" t="s">
+      <c r="AC54" s="8" t="s">
         <v>1025</v>
       </c>
+      <c r="AD54" s="8"/>
+      <c r="AE54" s="8" t="s">
+        <v>1026</v>
+      </c>
     </row>
     <row r="55" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A55" s="5" t="s">
-        <v>1026</v>
-      </c>
-      <c r="B55" s="5" t="s">
+      <c r="A55" s="3" t="s">
         <v>1027</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="B55" s="3" t="s">
         <v>1028</v>
       </c>
-      <c r="E55" s="5" t="s">
+      <c r="C55" s="3" t="s">
         <v>1029</v>
       </c>
-      <c r="F55" s="5" t="s">
+      <c r="E55" s="3" t="s">
         <v>1030</v>
       </c>
-      <c r="G55" s="5" t="s">
+      <c r="F55" s="3" t="s">
         <v>1031</v>
       </c>
-      <c r="I55" s="7" t="s">
+      <c r="G55" s="3" t="s">
         <v>1032</v>
       </c>
-      <c r="J55" s="7" t="s">
+      <c r="I55" s="5" t="s">
         <v>1033</v>
       </c>
-      <c r="K55" s="7" t="s">
+      <c r="J55" s="5" t="s">
         <v>1034</v>
       </c>
-      <c r="M55" s="10" t="s">
+      <c r="K55" s="5" t="s">
         <v>1035</v>
       </c>
-      <c r="N55" s="10"/>
-      <c r="O55" s="10" t="s">
+      <c r="M55" s="8" t="s">
         <v>1036</v>
       </c>
-      <c r="Q55" s="10" t="s">
+      <c r="N55" s="8"/>
+      <c r="O55" s="8" t="s">
         <v>1037</v>
       </c>
-      <c r="R55" s="10"/>
-      <c r="S55" s="10" t="s">
+      <c r="Q55" s="8" t="s">
         <v>1038</v>
       </c>
-      <c r="U55" s="10" t="s">
+      <c r="R55" s="8"/>
+      <c r="S55" s="8" t="s">
         <v>1039</v>
       </c>
-      <c r="V55" s="10"/>
-      <c r="W55" s="10" t="s">
+      <c r="U55" s="8" t="s">
         <v>1040</v>
       </c>
-      <c r="Y55" s="10" t="s">
+      <c r="V55" s="8"/>
+      <c r="W55" s="8" t="s">
         <v>1041</v>
       </c>
-      <c r="Z55" s="10"/>
-      <c r="AA55" s="10" t="s">
+      <c r="Y55" s="8" t="s">
         <v>1042</v>
       </c>
-      <c r="AC55" s="10" t="s">
+      <c r="Z55" s="8"/>
+      <c r="AA55" s="8" t="s">
         <v>1043</v>
       </c>
-      <c r="AD55" s="10"/>
-      <c r="AE55" s="10" t="s">
+      <c r="AC55" s="8" t="s">
         <v>1044</v>
       </c>
+      <c r="AD55" s="8"/>
+      <c r="AE55" s="8" t="s">
+        <v>1045</v>
+      </c>
     </row>
     <row r="56" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A56" s="5" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B56" s="5" t="s">
+      <c r="A56" s="3" t="s">
         <v>1046</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="B56" s="3" t="s">
         <v>1047</v>
       </c>
-      <c r="E56" s="10" t="s">
+      <c r="C56" s="3" t="s">
         <v>1048</v>
       </c>
-      <c r="F56" s="10" t="s">
+      <c r="E56" s="8" t="s">
         <v>1049</v>
       </c>
-      <c r="G56" s="10" t="s">
+      <c r="F56" s="8" t="s">
         <v>1050</v>
       </c>
-      <c r="I56" s="5" t="s">
+      <c r="G56" s="8" t="s">
         <v>1051</v>
       </c>
-      <c r="J56" s="5" t="s">
+      <c r="I56" s="3" t="s">
         <v>1052</v>
       </c>
-      <c r="K56" s="5" t="s">
+      <c r="J56" s="3" t="s">
         <v>1053</v>
       </c>
-      <c r="M56" s="10" t="s">
+      <c r="K56" s="3" t="s">
         <v>1054</v>
       </c>
-      <c r="N56" s="10"/>
-      <c r="O56" s="10" t="s">
+      <c r="M56" s="8" t="s">
         <v>1055</v>
       </c>
-      <c r="Q56" s="10" t="s">
+      <c r="N56" s="8"/>
+      <c r="O56" s="8" t="s">
         <v>1056</v>
       </c>
-      <c r="R56" s="10"/>
-      <c r="S56" s="10" t="s">
+      <c r="Q56" s="8" t="s">
         <v>1057</v>
       </c>
-      <c r="U56" s="10" t="s">
+      <c r="R56" s="8"/>
+      <c r="S56" s="8" t="s">
         <v>1058</v>
       </c>
-      <c r="V56" s="10"/>
-      <c r="W56" s="10" t="s">
+      <c r="U56" s="8" t="s">
         <v>1059</v>
       </c>
-      <c r="Y56" s="10" t="s">
+      <c r="V56" s="8"/>
+      <c r="W56" s="8" t="s">
         <v>1060</v>
       </c>
-      <c r="Z56" s="10"/>
-      <c r="AA56" s="10" t="s">
+      <c r="Y56" s="8" t="s">
         <v>1061</v>
       </c>
-      <c r="AC56" s="10" t="s">
+      <c r="Z56" s="8"/>
+      <c r="AA56" s="8" t="s">
         <v>1062</v>
       </c>
-      <c r="AD56" s="10"/>
-      <c r="AE56" s="10" t="s">
+      <c r="AC56" s="8" t="s">
         <v>1063</v>
       </c>
+      <c r="AD56" s="8"/>
+      <c r="AE56" s="8" t="s">
+        <v>1064</v>
+      </c>
     </row>
     <row r="57" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A57" s="5" t="s">
-        <v>1064</v>
-      </c>
-      <c r="B57" s="5" t="s">
+      <c r="A57" s="3" t="s">
         <v>1065</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="B57" s="3" t="s">
         <v>1066</v>
       </c>
-      <c r="E57" s="10" t="s">
+      <c r="C57" s="3" t="s">
         <v>1067</v>
       </c>
-      <c r="F57" s="10" t="s">
+      <c r="E57" s="8" t="s">
         <v>1068</v>
       </c>
-      <c r="G57" s="10" t="s">
+      <c r="F57" s="8" t="s">
         <v>1069</v>
       </c>
+      <c r="G57" s="8" t="s">
+        <v>1070</v>
+      </c>
     </row>
     <row r="58" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A58" s="10" t="s">
-        <v>1070</v>
-      </c>
-      <c r="B58" s="10" t="s">
+      <c r="A58" s="8" t="s">
         <v>1071</v>
       </c>
-      <c r="C58" s="10" t="s">
+      <c r="B58" s="8" t="s">
         <v>1072</v>
       </c>
+      <c r="C58" s="8" t="s">
+        <v>1073</v>
+      </c>
     </row>
     <row r="59" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A59" s="10" t="s">
-        <v>1073</v>
-      </c>
-      <c r="B59" s="10" t="s">
+      <c r="A59" s="8" t="s">
         <v>1074</v>
       </c>
-      <c r="C59" s="10" t="s">
+      <c r="B59" s="8" t="s">
         <v>1075</v>
       </c>
+      <c r="C59" s="8" t="s">
+        <v>1076</v>
+      </c>
     </row>
     <row r="60" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A60" s="10" t="s">
-        <v>1076</v>
-      </c>
-      <c r="B60" s="10" t="s">
+      <c r="A60" s="8" t="s">
         <v>1077</v>
       </c>
-      <c r="C60" s="10" t="s">
+      <c r="B60" s="8" t="s">
         <v>1078</v>
       </c>
-      <c r="E60" s="6"/>
+      <c r="C60" s="8" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E60" s="4"/>
       <c r="F60" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="61" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A61" s="10" t="s">
-        <v>1080</v>
-      </c>
-      <c r="B61" s="10" t="s">
+      <c r="A61" s="8" t="s">
         <v>1081</v>
       </c>
-      <c r="C61" s="10" t="s">
+      <c r="B61" s="8" t="s">
         <v>1082</v>
       </c>
+      <c r="C61" s="8" t="s">
+        <v>1083</v>
+      </c>
     </row>
     <row r="62" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A62" s="10" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B62" s="10" t="s">
+      <c r="A62" s="8" t="s">
         <v>1084</v>
       </c>
-      <c r="C62" s="10" t="s">
+      <c r="B62" s="8" t="s">
         <v>1085</v>
       </c>
-      <c r="E62" s="8"/>
+      <c r="C62" s="8" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E62" s="6"/>
       <c r="F62" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="63" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A63" s="10" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B63" s="10" t="s">
+      <c r="A63" s="8" t="s">
         <v>1088</v>
       </c>
-      <c r="C63" s="10" t="s">
+      <c r="B63" s="8" t="s">
         <v>1089</v>
       </c>
+      <c r="C63" s="8" t="s">
+        <v>1090</v>
+      </c>
     </row>
     <row r="64" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A64" s="10" t="s">
-        <v>1090</v>
-      </c>
-      <c r="B64" s="10" t="s">
+      <c r="A64" s="8" t="s">
         <v>1091</v>
       </c>
-      <c r="C64" s="10" t="s">
+      <c r="B64" s="8" t="s">
         <v>1092</v>
       </c>
+      <c r="C64" s="8" t="s">
+        <v>1093</v>
+      </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A65" s="5" t="s">
-        <v>1093</v>
-      </c>
-      <c r="B65" s="5" t="s">
+      <c r="A65" s="3" t="s">
         <v>1094</v>
       </c>
-      <c r="C65" s="5" t="s">
+      <c r="B65" s="3" t="s">
         <v>1095</v>
       </c>
+      <c r="C65" s="3" t="s">
+        <v>1096</v>
+      </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A66" s="10" t="s">
-        <v>1096</v>
-      </c>
-      <c r="B66" s="10" t="s">
+      <c r="A66" s="8" t="s">
         <v>1097</v>
       </c>
-      <c r="C66" s="10" t="s">
+      <c r="B66" s="8" t="s">
         <v>1098</v>
       </c>
+      <c r="C66" s="8" t="s">
+        <v>1099</v>
+      </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A67" s="10" t="s">
-        <v>1099</v>
-      </c>
-      <c r="B67" s="10"/>
-      <c r="C67" s="10" t="s">
+      <c r="A67" s="8" t="s">
         <v>1100</v>
       </c>
+      <c r="B67" s="8"/>
+      <c r="C67" s="8" t="s">
+        <v>1101</v>
+      </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A68" s="10" t="s">
-        <v>1101</v>
-      </c>
-      <c r="B68" s="10"/>
-      <c r="C68" s="10" t="s">
+      <c r="A68" s="8" t="s">
         <v>1102</v>
       </c>
+      <c r="B68" s="8"/>
+      <c r="C68" s="8" t="s">
+        <v>1103</v>
+      </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A69" s="10" t="s">
-        <v>1103</v>
-      </c>
-      <c r="B69" s="10" t="s">
+      <c r="A69" s="8" t="s">
         <v>1104</v>
       </c>
-      <c r="C69" s="10" t="s">
+      <c r="B69" s="8" t="s">
         <v>1105</v>
       </c>
+      <c r="C69" s="8" t="s">
+        <v>1106</v>
+      </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A70" s="10" t="s">
-        <v>1106</v>
-      </c>
-      <c r="B70" s="10"/>
-      <c r="C70" s="10" t="s">
+      <c r="A70" s="8" t="s">
         <v>1107</v>
       </c>
+      <c r="B70" s="8"/>
+      <c r="C70" s="8" t="s">
+        <v>1108</v>
+      </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A71" s="10" t="s">
-        <v>1108</v>
-      </c>
-      <c r="B71" s="10" t="s">
+      <c r="A71" s="8" t="s">
         <v>1109</v>
       </c>
-      <c r="C71" s="10" t="s">
+      <c r="B71" s="8" t="s">
         <v>1110</v>
       </c>
+      <c r="C71" s="8" t="s">
+        <v>1111</v>
+      </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A72" s="9" t="s">
-        <v>1111</v>
-      </c>
-      <c r="B72" s="9" t="s">
+      <c r="A72" s="7" t="s">
         <v>1112</v>
       </c>
-      <c r="C72" s="9" t="s">
+      <c r="B72" s="7" t="s">
         <v>1113</v>
       </c>
+      <c r="C72" s="7" t="s">
+        <v>1114</v>
+      </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A73" s="7" t="s">
-        <v>1114</v>
-      </c>
-      <c r="B73" s="7" t="s">
+      <c r="A73" s="5" t="s">
         <v>1115</v>
       </c>
-      <c r="C73" s="7" t="s">
+      <c r="B73" s="5" t="s">
         <v>1116</v>
       </c>
+      <c r="C73" s="5" t="s">
+        <v>1117</v>
+      </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A74" s="7" t="s">
-        <v>1117</v>
-      </c>
-      <c r="B74" s="7" t="s">
+      <c r="A74" s="5" t="s">
         <v>1118</v>
       </c>
-      <c r="C74" s="7" t="s">
+      <c r="B74" s="5" t="s">
         <v>1119</v>
       </c>
+      <c r="C74" s="5" t="s">
+        <v>1120</v>
+      </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A75" s="5" t="s">
-        <v>1120</v>
-      </c>
-      <c r="B75" s="5" t="s">
+      <c r="A75" s="3" t="s">
         <v>1121</v>
       </c>
-      <c r="C75" s="5" t="s">
+      <c r="B75" s="3" t="s">
         <v>1122</v>
       </c>
+      <c r="C75" s="3" t="s">
+        <v>1123</v>
+      </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A76" s="10" t="s">
-        <v>1123</v>
-      </c>
-      <c r="B76" s="10" t="s">
+      <c r="A76" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="C76" s="10" t="s">
+      <c r="B76" s="8" t="s">
         <v>1125</v>
       </c>
+      <c r="C76" s="8" t="s">
+        <v>1126</v>
+      </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A77" s="10" t="s">
-        <v>1126</v>
-      </c>
-      <c r="B77" s="10" t="s">
+      <c r="A77" s="8" t="s">
         <v>1127</v>
       </c>
-      <c r="C77" s="10" t="s">
+      <c r="B77" s="8" t="s">
         <v>1128</v>
       </c>
+      <c r="C77" s="8" t="s">
+        <v>1129</v>
+      </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A78" s="10" t="s">
-        <v>1129</v>
-      </c>
-      <c r="B78" s="10"/>
-      <c r="C78" s="10" t="s">
+      <c r="A78" s="8" t="s">
         <v>1130</v>
       </c>
+      <c r="B78" s="8"/>
+      <c r="C78" s="8" t="s">
+        <v>1131</v>
+      </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A79" s="5" t="s">
-        <v>1131</v>
-      </c>
-      <c r="B79" s="5" t="s">
+      <c r="A79" s="3" t="s">
         <v>1132</v>
       </c>
-      <c r="C79" s="5" t="s">
+      <c r="B79" s="3" t="s">
         <v>1133</v>
       </c>
+      <c r="C79" s="3" t="s">
+        <v>1134</v>
+      </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A80" s="10" t="s">
-        <v>1134</v>
-      </c>
-      <c r="B80" s="10" t="s">
+      <c r="A80" s="8" t="s">
         <v>1135</v>
       </c>
-      <c r="C80" s="10" t="s">
+      <c r="B80" s="8" t="s">
         <v>1136</v>
       </c>
+      <c r="C80" s="8" t="s">
+        <v>1137</v>
+      </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A81" s="7" t="s">
-        <v>1137</v>
-      </c>
-      <c r="B81" s="7" t="s">
+      <c r="A81" s="5" t="s">
         <v>1138</v>
       </c>
-      <c r="C81" s="7" t="s">
+      <c r="B81" s="5" t="s">
         <v>1139</v>
       </c>
+      <c r="C81" s="5" t="s">
+        <v>1140</v>
+      </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A82" s="7" t="s">
-        <v>1140</v>
-      </c>
-      <c r="B82" s="7" t="s">
+      <c r="A82" s="5" t="s">
         <v>1141</v>
       </c>
-      <c r="C82" s="7" t="s">
+      <c r="B82" s="5" t="s">
         <v>1142</v>
       </c>
+      <c r="C82" s="5" t="s">
+        <v>1143</v>
+      </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A83" s="5" t="s">
-        <v>1143</v>
-      </c>
-      <c r="B83" s="5" t="s">
+      <c r="A83" s="3" t="s">
         <v>1144</v>
       </c>
-      <c r="C83" s="5" t="s">
+      <c r="B83" s="3" t="s">
         <v>1145</v>
       </c>
+      <c r="C83" s="3" t="s">
+        <v>1146</v>
+      </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A84" s="5" t="s">
-        <v>1146</v>
-      </c>
-      <c r="B84" s="5" t="s">
+      <c r="A84" s="3" t="s">
         <v>1147</v>
       </c>
-      <c r="C84" s="5" t="s">
+      <c r="B84" s="3" t="s">
         <v>1148</v>
       </c>
+      <c r="C84" s="3" t="s">
+        <v>1149</v>
+      </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A85" s="10" t="s">
-        <v>1149</v>
-      </c>
-      <c r="B85" s="10"/>
-      <c r="C85" s="10" t="s">
+      <c r="A85" s="8" t="s">
         <v>1150</v>
       </c>
+      <c r="B85" s="8"/>
+      <c r="C85" s="8" t="s">
+        <v>1151</v>
+      </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A86" s="7" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B86" s="7" t="s">
+      <c r="A86" s="5" t="s">
         <v>1152</v>
       </c>
-      <c r="C86" s="7" t="s">
+      <c r="B86" s="5" t="s">
         <v>1153</v>
       </c>
+      <c r="C86" s="5" t="s">
+        <v>1154</v>
+      </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A87" s="10" t="s">
-        <v>1154</v>
-      </c>
-      <c r="B87" s="10" t="s">
+      <c r="A87" s="8" t="s">
         <v>1155</v>
       </c>
-      <c r="C87" s="10" t="s">
+      <c r="B87" s="8" t="s">
         <v>1156</v>
       </c>
+      <c r="C87" s="8" t="s">
+        <v>1157</v>
+      </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A88" s="10" t="s">
-        <v>1157</v>
-      </c>
-      <c r="B88" s="10"/>
-      <c r="C88" s="10" t="s">
+      <c r="A88" s="8" t="s">
         <v>1158</v>
       </c>
+      <c r="B88" s="8"/>
+      <c r="C88" s="8" t="s">
+        <v>1159</v>
+      </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A89" s="7" t="s">
-        <v>1159</v>
-      </c>
-      <c r="B89" s="7" t="s">
+      <c r="A89" s="5" t="s">
         <v>1160</v>
       </c>
-      <c r="C89" s="7" t="s">
+      <c r="B89" s="5" t="s">
         <v>1161</v>
       </c>
+      <c r="C89" s="5" t="s">
+        <v>1162</v>
+      </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A90" s="7" t="s">
-        <v>1162</v>
-      </c>
-      <c r="B90" s="7" t="s">
+      <c r="A90" s="5" t="s">
         <v>1163</v>
       </c>
-      <c r="C90" s="7" t="s">
+      <c r="B90" s="5" t="s">
         <v>1164</v>
       </c>
+      <c r="C90" s="5" t="s">
+        <v>1165</v>
+      </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A91" s="7" t="s">
-        <v>1165</v>
-      </c>
-      <c r="B91" s="7" t="s">
+      <c r="A91" s="5" t="s">
         <v>1166</v>
       </c>
-      <c r="C91" s="7" t="s">
+      <c r="B91" s="5" t="s">
         <v>1167</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>1168</v>
       </c>
     </row>
   </sheetData>
@@ -8860,1014 +8925,1017 @@
   <dimension ref="A1:C85"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="19.1640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="132.5" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="132.5" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A2" s="10" t="s">
-        <v>1171</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="A2" s="8" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A3" s="8" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A4" s="8" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A5" s="8" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A6" s="8" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="8" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A8" s="8" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A9" s="8" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A10" s="8" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="8" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A12" s="8" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A13" s="8" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A14" s="8" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A15" s="8" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A16" s="8" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A17" s="8" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A18" s="8" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A19" s="8" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A20" s="8" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A21" s="8" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A22" s="8" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A23" s="8" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A24" s="8" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A25" s="8" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A26" s="8" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A27" s="8" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A28" s="8" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A29" s="8" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A30" s="8" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A31" s="8" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A32" s="8" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A33" s="8" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A34" s="8" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A35" s="8" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="8" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A37" s="8" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A38" s="8" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A39" s="8" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A40" s="8" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A41" s="8" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A42" s="8" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A43" s="8" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A44" s="8" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A45" s="8" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A46" s="8" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A47" s="8" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A48" s="8" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A49" s="8" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A50" s="8" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A51" s="8" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A52" s="8" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A53" s="8" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A54" s="8" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A55" s="8" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A56" s="8" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A57" s="8" t="s">
         <v>1172</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="B57" s="8" t="s">
         <v>1173</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A3" s="10" t="s">
+      <c r="C57" s="11" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A58" s="8" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A59" s="8" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A60" s="8" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A61" s="8" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C61" s="11" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A62" s="8" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A63" s="8" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A64" s="8" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A65" s="8" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A66" s="8" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A67" s="8" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A68" s="8" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A69" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A70" s="8" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A71" s="8" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A72" s="8" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A73" s="8" t="s">
         <v>1174</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B73" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>1176</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A4" s="10" t="s">
-        <v>1177</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>1178</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>1179</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A5" s="10" t="s">
-        <v>1180</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>1181</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A6" s="10" t="s">
-        <v>1183</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>1184</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>1185</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="10" t="s">
-        <v>1186</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>1187</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>1188</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A8" s="10" t="s">
-        <v>1189</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>1190</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>1191</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A9" s="10" t="s">
-        <v>1192</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>1193</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>1194</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A10" s="10" t="s">
-        <v>1195</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>1196</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>1197</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="10" t="s">
-        <v>1198</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>1199</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A12" s="10" t="s">
-        <v>1201</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>1202</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>1203</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A13" s="10" t="s">
-        <v>1204</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>1205</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>1206</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A14" s="10" t="s">
-        <v>1207</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>1208</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>1209</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A15" s="10" t="s">
-        <v>1210</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>1211</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>1212</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A16" s="10" t="s">
-        <v>1213</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>1214</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>1215</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A17" s="10" t="s">
-        <v>1216</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>1217</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>1218</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A18" s="10" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>1220</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>1221</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A19" s="10" t="s">
-        <v>1222</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>1223</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>1221</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A20" s="10" t="s">
-        <v>1224</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>1225</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>1226</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A21" s="10" t="s">
+      <c r="C73" s="11" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A74" s="8" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C74" s="11" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A75" s="8" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A76" s="8" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A77" s="8" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C77" s="11" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A78" s="8" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C78" s="11" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A79" s="8" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A80" s="8" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C80" s="11" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A81" s="8" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C81" s="11" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A82" s="8" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C82" s="11" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A83" s="8" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B83" s="8" t="s">
         <v>1227</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>1229</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A22" s="10" t="s">
-        <v>1230</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>1231</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>1232</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A23" s="10" t="s">
-        <v>1233</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>1234</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>1235</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A24" s="10" t="s">
-        <v>1236</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>1237</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>1238</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A25" s="10" t="s">
-        <v>1239</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>1240</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>1241</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A26" s="10" t="s">
-        <v>1242</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>1243</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>1244</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A27" s="10" t="s">
-        <v>1245</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>1246</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>1247</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A28" s="10" t="s">
-        <v>1248</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>1249</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A29" s="10" t="s">
-        <v>1251</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>1252</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>1253</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A30" s="10" t="s">
-        <v>1254</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>1255</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>1256</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A31" s="10" t="s">
-        <v>1257</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>1258</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>1259</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A32" s="10" t="s">
-        <v>1260</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>1261</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>1262</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A33" s="10" t="s">
-        <v>1263</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>1264</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>1265</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A34" s="10" t="s">
-        <v>1266</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>1267</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>1268</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A35" s="10" t="s">
-        <v>1269</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>1270</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>1271</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="10" t="s">
-        <v>1272</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>1273</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>1274</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A37" s="10" t="s">
-        <v>1275</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>1276</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>1277</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A38" s="10" t="s">
-        <v>1278</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>1279</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A39" s="10" t="s">
-        <v>1281</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>1282</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>1283</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A40" s="10" t="s">
-        <v>1284</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>1285</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>1286</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A41" s="10" t="s">
-        <v>1287</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>1288</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>1289</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A42" s="10" t="s">
-        <v>1290</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>1291</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A43" s="10" t="s">
-        <v>1293</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>1294</v>
-      </c>
-      <c r="C43" s="11" t="s">
-        <v>1295</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A44" s="10" t="s">
-        <v>1296</v>
-      </c>
-      <c r="B44" s="10" t="s">
-        <v>1297</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>1298</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A45" s="10" t="s">
-        <v>1299</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>1300</v>
-      </c>
-      <c r="C45" s="11" t="s">
-        <v>1301</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A46" s="10" t="s">
-        <v>1302</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>1303</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>1304</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A47" s="10" t="s">
-        <v>1305</v>
-      </c>
-      <c r="B47" s="10" t="s">
-        <v>1306</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A48" s="10" t="s">
-        <v>1308</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>1309</v>
-      </c>
-      <c r="C48" s="11" t="s">
-        <v>1310</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A49" s="10" t="s">
-        <v>1311</v>
-      </c>
-      <c r="B49" s="10" t="s">
-        <v>1312</v>
-      </c>
-      <c r="C49" s="11" t="s">
-        <v>1313</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A50" s="10" t="s">
-        <v>1314</v>
-      </c>
-      <c r="B50" s="10" t="s">
-        <v>1315</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>1316</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A51" s="10" t="s">
-        <v>1317</v>
-      </c>
-      <c r="B51" s="10" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C51" s="11" t="s">
-        <v>1319</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A52" s="10" t="s">
-        <v>1320</v>
-      </c>
-      <c r="B52" s="10" t="s">
-        <v>1321</v>
-      </c>
-      <c r="C52" s="11" t="s">
-        <v>1322</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A53" s="10" t="s">
-        <v>1323</v>
-      </c>
-      <c r="B53" s="10" t="s">
-        <v>1324</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>1325</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A54" s="10" t="s">
-        <v>1326</v>
-      </c>
-      <c r="B54" s="10" t="s">
-        <v>1327</v>
-      </c>
-      <c r="C54" s="11" t="s">
-        <v>1328</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A55" s="10" t="s">
-        <v>1329</v>
-      </c>
-      <c r="B55" s="10" t="s">
-        <v>1330</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>1331</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A56" s="10" t="s">
-        <v>1332</v>
-      </c>
-      <c r="B56" s="10" t="s">
-        <v>1333</v>
-      </c>
-      <c r="C56" s="11" t="s">
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A57" s="10" t="s">
+      <c r="C83" s="11" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A84" s="8" t="s">
         <v>1335</v>
       </c>
-      <c r="B57" s="10" t="s">
+      <c r="B84" s="8" t="s">
         <v>1336</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C84" s="11" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A85" s="8" t="s">
         <v>1337</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A58" s="10" t="s">
+      <c r="B85" s="8" t="s">
         <v>1338</v>
       </c>
-      <c r="B58" s="10" t="s">
-        <v>1339</v>
-      </c>
-      <c r="C58" s="11" t="s">
-        <v>1340</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A59" s="10" t="s">
-        <v>1341</v>
-      </c>
-      <c r="B59" s="10" t="s">
-        <v>1342</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>1343</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A60" s="10" t="s">
-        <v>1344</v>
-      </c>
-      <c r="B60" s="10" t="s">
-        <v>1345</v>
-      </c>
-      <c r="C60" s="11" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A61" s="10" t="s">
-        <v>1347</v>
-      </c>
-      <c r="B61" s="10" t="s">
-        <v>1348</v>
-      </c>
-      <c r="C61" s="11" t="s">
-        <v>1349</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A62" s="10" t="s">
-        <v>1350</v>
-      </c>
-      <c r="B62" s="10" t="s">
-        <v>1351</v>
-      </c>
-      <c r="C62" s="11" t="s">
-        <v>1352</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A63" s="10" t="s">
-        <v>1353</v>
-      </c>
-      <c r="B63" s="10" t="s">
-        <v>1354</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>1355</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A64" s="10" t="s">
-        <v>1356</v>
-      </c>
-      <c r="B64" s="10" t="s">
-        <v>1357</v>
-      </c>
-      <c r="C64" s="11" t="s">
-        <v>1358</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A65" s="10" t="s">
-        <v>1359</v>
-      </c>
-      <c r="B65" s="10" t="s">
-        <v>1360</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>1361</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A66" s="10" t="s">
-        <v>1362</v>
-      </c>
-      <c r="B66" s="10" t="s">
-        <v>1363</v>
-      </c>
-      <c r="C66" s="11" t="s">
-        <v>1364</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A67" s="10" t="s">
-        <v>1365</v>
-      </c>
-      <c r="B67" s="10" t="s">
-        <v>1366</v>
-      </c>
-      <c r="C67" s="11" t="s">
-        <v>1367</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A68" s="10" t="s">
-        <v>1368</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C68" s="11" t="s">
-        <v>1370</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A69" s="10" t="s">
-        <v>1371</v>
-      </c>
-      <c r="B69" s="10" t="s">
-        <v>1372</v>
-      </c>
-      <c r="C69" s="11" t="s">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A70" s="10" t="s">
-        <v>1374</v>
-      </c>
-      <c r="B70" s="10" t="s">
-        <v>1375</v>
-      </c>
-      <c r="C70" s="11" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A71" s="10" t="s">
-        <v>1377</v>
-      </c>
-      <c r="B71" s="10" t="s">
-        <v>1378</v>
-      </c>
-      <c r="C71" s="11" t="s">
-        <v>1379</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A72" s="10" t="s">
-        <v>1380</v>
-      </c>
-      <c r="B72" s="10" t="s">
-        <v>1381</v>
-      </c>
-      <c r="C72" s="11" t="s">
-        <v>1382</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A73" s="10" t="s">
-        <v>1383</v>
-      </c>
-      <c r="B73" s="10" t="s">
-        <v>1384</v>
-      </c>
-      <c r="C73" s="11" t="s">
-        <v>1385</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A74" s="10" t="s">
-        <v>1386</v>
-      </c>
-      <c r="B74" s="10" t="s">
-        <v>1387</v>
-      </c>
-      <c r="C74" s="11" t="s">
-        <v>1388</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A75" s="10" t="s">
-        <v>1389</v>
-      </c>
-      <c r="B75" s="10" t="s">
-        <v>1390</v>
-      </c>
-      <c r="C75" s="11" t="s">
-        <v>1391</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A76" s="10" t="s">
-        <v>1392</v>
-      </c>
-      <c r="B76" s="10" t="s">
-        <v>1393</v>
-      </c>
-      <c r="C76" s="11" t="s">
-        <v>1394</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A77" s="10" t="s">
-        <v>1395</v>
-      </c>
-      <c r="B77" s="10" t="s">
-        <v>1396</v>
-      </c>
-      <c r="C77" s="11" t="s">
-        <v>1397</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A78" s="10" t="s">
-        <v>1398</v>
-      </c>
-      <c r="B78" s="10" t="s">
-        <v>1399</v>
-      </c>
-      <c r="C78" s="11" t="s">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A79" s="10" t="s">
-        <v>1401</v>
-      </c>
-      <c r="B79" s="10" t="s">
-        <v>1402</v>
-      </c>
-      <c r="C79" s="11" t="s">
-        <v>1179</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A80" s="10" t="s">
-        <v>1403</v>
-      </c>
-      <c r="B80" s="10" t="s">
-        <v>1404</v>
-      </c>
-      <c r="C80" s="11" t="s">
-        <v>1405</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A81" s="10" t="s">
-        <v>1406</v>
-      </c>
-      <c r="B81" s="10" t="s">
-        <v>1407</v>
-      </c>
-      <c r="C81" s="13" t="s">
-        <v>1425</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A82" s="10" t="s">
-        <v>1408</v>
-      </c>
-      <c r="B82" s="10" t="s">
-        <v>1409</v>
-      </c>
-      <c r="C82" s="13" t="s">
-        <v>1426</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A83" s="10" t="s">
-        <v>1410</v>
-      </c>
-      <c r="B83" s="10" t="s">
-        <v>1249</v>
-      </c>
-      <c r="C83" s="13" t="s">
-        <v>1427</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A84" s="10" t="s">
-        <v>1411</v>
-      </c>
-      <c r="B84" s="10" t="s">
-        <v>1412</v>
-      </c>
-      <c r="C84" s="13" t="s">
-        <v>1428</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A85" s="10" t="s">
-        <v>1413</v>
-      </c>
-      <c r="B85" s="10" t="s">
-        <v>1414</v>
-      </c>
-      <c r="C85" s="13" t="s">
+      <c r="C85" s="11" t="s">
         <v>1429</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C85">
+    <sortCondition ref="A2:A85"/>
+  </sortState>
   <phoneticPr fontId="1"/>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="C4" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
-    <hyperlink ref="C5" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
-    <hyperlink ref="C6" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
-    <hyperlink ref="C7" r:id="rId6" display="https://web.archive.org/web/20130114222225/http://www.ric.hi-ho.ne.jp/many/many/calmemo.html" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
-    <hyperlink ref="C8" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
-    <hyperlink ref="C9" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
-    <hyperlink ref="C10" r:id="rId9" location="ct" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
-    <hyperlink ref="C12" r:id="rId10" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
-    <hyperlink ref="C14" r:id="rId11" location="ppxdockshow" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
-    <hyperlink ref="C15" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
-    <hyperlink ref="C16" r:id="rId13" display="https://www.digitalvolcano.co.uk/dcdownload_versions.html" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
-    <hyperlink ref="C17" r:id="rId14" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
-    <hyperlink ref="C19" r:id="rId15" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
-    <hyperlink ref="C20" r:id="rId16" xr:uid="{00000000-0004-0000-0100-00000F000000}"/>
-    <hyperlink ref="C21" r:id="rId17" xr:uid="{00000000-0004-0000-0100-000010000000}"/>
-    <hyperlink ref="C22" r:id="rId18" xr:uid="{00000000-0004-0000-0100-000011000000}"/>
-    <hyperlink ref="C23" r:id="rId19" xr:uid="{00000000-0004-0000-0100-000012000000}"/>
-    <hyperlink ref="C24" r:id="rId20" xr:uid="{00000000-0004-0000-0100-000013000000}"/>
-    <hyperlink ref="C25" r:id="rId21" xr:uid="{00000000-0004-0000-0100-000014000000}"/>
-    <hyperlink ref="C26" r:id="rId22" xr:uid="{00000000-0004-0000-0100-000015000000}"/>
-    <hyperlink ref="C27" r:id="rId23" xr:uid="{00000000-0004-0000-0100-000016000000}"/>
-    <hyperlink ref="C28" r:id="rId24" xr:uid="{00000000-0004-0000-0100-000017000000}"/>
-    <hyperlink ref="C29" r:id="rId25" xr:uid="{00000000-0004-0000-0100-000018000000}"/>
-    <hyperlink ref="C30" r:id="rId26" xr:uid="{00000000-0004-0000-0100-000019000000}"/>
-    <hyperlink ref="C31" r:id="rId27" xr:uid="{00000000-0004-0000-0100-00001A000000}"/>
-    <hyperlink ref="C32" r:id="rId28" xr:uid="{00000000-0004-0000-0100-00001B000000}"/>
-    <hyperlink ref="C34" r:id="rId29" xr:uid="{00000000-0004-0000-0100-00001C000000}"/>
-    <hyperlink ref="C35" r:id="rId30" xr:uid="{00000000-0004-0000-0100-00001D000000}"/>
-    <hyperlink ref="C36" r:id="rId31" location="ppxaux" xr:uid="{00000000-0004-0000-0100-00001E000000}"/>
-    <hyperlink ref="C37" r:id="rId32" xr:uid="{00000000-0004-0000-0100-00001F000000}"/>
-    <hyperlink ref="C38" r:id="rId33" xr:uid="{00000000-0004-0000-0100-000020000000}"/>
-    <hyperlink ref="C39" r:id="rId34" xr:uid="{00000000-0004-0000-0100-000021000000}"/>
-    <hyperlink ref="C40" r:id="rId35" xr:uid="{00000000-0004-0000-0100-000022000000}"/>
-    <hyperlink ref="C41" r:id="rId36" xr:uid="{00000000-0004-0000-0100-000023000000}"/>
-    <hyperlink ref="C42" r:id="rId37" xr:uid="{00000000-0004-0000-0100-000024000000}"/>
-    <hyperlink ref="C43" r:id="rId38" xr:uid="{00000000-0004-0000-0100-000025000000}"/>
-    <hyperlink ref="C44" r:id="rId39" xr:uid="{00000000-0004-0000-0100-000026000000}"/>
-    <hyperlink ref="C45" r:id="rId40" xr:uid="{00000000-0004-0000-0100-000027000000}"/>
-    <hyperlink ref="C46" r:id="rId41" xr:uid="{00000000-0004-0000-0100-000028000000}"/>
-    <hyperlink ref="C47" r:id="rId42" xr:uid="{00000000-0004-0000-0100-000029000000}"/>
-    <hyperlink ref="C48" r:id="rId43" xr:uid="{00000000-0004-0000-0100-00002A000000}"/>
-    <hyperlink ref="C49" r:id="rId44" xr:uid="{00000000-0004-0000-0100-00002B000000}"/>
-    <hyperlink ref="C50" r:id="rId45" xr:uid="{00000000-0004-0000-0100-00002C000000}"/>
-    <hyperlink ref="C51" r:id="rId46" xr:uid="{00000000-0004-0000-0100-00002D000000}"/>
-    <hyperlink ref="C53" r:id="rId47" xr:uid="{00000000-0004-0000-0100-00002E000000}"/>
-    <hyperlink ref="C54" r:id="rId48" display="https://www.adobe.com/jp/products/photoshop.html" xr:uid="{00000000-0004-0000-0100-00002F000000}"/>
-    <hyperlink ref="C56" r:id="rId49" xr:uid="{00000000-0004-0000-0100-000030000000}"/>
-    <hyperlink ref="C57" r:id="rId50" xr:uid="{00000000-0004-0000-0100-000031000000}"/>
-    <hyperlink ref="C58" r:id="rId51" xr:uid="{00000000-0004-0000-0100-000032000000}"/>
-    <hyperlink ref="C60" r:id="rId52" xr:uid="{00000000-0004-0000-0100-000033000000}"/>
-    <hyperlink ref="C61" r:id="rId53" xr:uid="{00000000-0004-0000-0100-000034000000}"/>
-    <hyperlink ref="C62" r:id="rId54" xr:uid="{00000000-0004-0000-0100-000035000000}"/>
-    <hyperlink ref="C63" r:id="rId55" xr:uid="{00000000-0004-0000-0100-000036000000}"/>
-    <hyperlink ref="C64" r:id="rId56" xr:uid="{00000000-0004-0000-0100-000037000000}"/>
-    <hyperlink ref="C65" r:id="rId57" xr:uid="{00000000-0004-0000-0100-000038000000}"/>
-    <hyperlink ref="C66" r:id="rId58" xr:uid="{00000000-0004-0000-0100-000039000000}"/>
-    <hyperlink ref="C67" r:id="rId59" xr:uid="{00000000-0004-0000-0100-00003A000000}"/>
-    <hyperlink ref="C68" r:id="rId60" xr:uid="{00000000-0004-0000-0100-00003B000000}"/>
-    <hyperlink ref="C69" r:id="rId61" xr:uid="{00000000-0004-0000-0100-00003C000000}"/>
-    <hyperlink ref="C70" r:id="rId62" xr:uid="{00000000-0004-0000-0100-00003D000000}"/>
-    <hyperlink ref="C71" r:id="rId63" xr:uid="{00000000-0004-0000-0100-00003E000000}"/>
-    <hyperlink ref="C72" r:id="rId64" xr:uid="{00000000-0004-0000-0100-00003F000000}"/>
-    <hyperlink ref="C73" r:id="rId65" xr:uid="{00000000-0004-0000-0100-000040000000}"/>
+    <hyperlink ref="C57" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="C73" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="C2" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="C3" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
+    <hyperlink ref="C4" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
+    <hyperlink ref="C5" r:id="rId6" display="https://web.archive.org/web/20130114222225/http://www.ric.hi-ho.ne.jp/many/many/calmemo.html" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
+    <hyperlink ref="C6" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
+    <hyperlink ref="C7" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
+    <hyperlink ref="C8" r:id="rId9" location="ct" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
+    <hyperlink ref="C10" r:id="rId10" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
+    <hyperlink ref="C12" r:id="rId11" location="ppxdockshow" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
+    <hyperlink ref="C13" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
+    <hyperlink ref="C14" r:id="rId13" display="https://www.digitalvolcano.co.uk/dcdownload_versions.html" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
+    <hyperlink ref="C15" r:id="rId14" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
+    <hyperlink ref="C17" r:id="rId15" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
+    <hyperlink ref="C18" r:id="rId16" xr:uid="{00000000-0004-0000-0100-00000F000000}"/>
+    <hyperlink ref="C19" r:id="rId17" xr:uid="{00000000-0004-0000-0100-000010000000}"/>
+    <hyperlink ref="C20" r:id="rId18" xr:uid="{00000000-0004-0000-0100-000011000000}"/>
+    <hyperlink ref="C21" r:id="rId19" xr:uid="{00000000-0004-0000-0100-000012000000}"/>
+    <hyperlink ref="C22" r:id="rId20" xr:uid="{00000000-0004-0000-0100-000013000000}"/>
+    <hyperlink ref="C23" r:id="rId21" xr:uid="{00000000-0004-0000-0100-000014000000}"/>
+    <hyperlink ref="C24" r:id="rId22" xr:uid="{00000000-0004-0000-0100-000015000000}"/>
+    <hyperlink ref="C25" r:id="rId23" xr:uid="{00000000-0004-0000-0100-000016000000}"/>
+    <hyperlink ref="C26" r:id="rId24" xr:uid="{00000000-0004-0000-0100-000017000000}"/>
+    <hyperlink ref="C27" r:id="rId25" xr:uid="{00000000-0004-0000-0100-000018000000}"/>
+    <hyperlink ref="C28" r:id="rId26" xr:uid="{00000000-0004-0000-0100-000019000000}"/>
+    <hyperlink ref="C29" r:id="rId27" xr:uid="{00000000-0004-0000-0100-00001A000000}"/>
+    <hyperlink ref="C30" r:id="rId28" xr:uid="{00000000-0004-0000-0100-00001B000000}"/>
+    <hyperlink ref="C32" r:id="rId29" xr:uid="{00000000-0004-0000-0100-00001C000000}"/>
+    <hyperlink ref="C33" r:id="rId30" xr:uid="{00000000-0004-0000-0100-00001D000000}"/>
+    <hyperlink ref="C34" r:id="rId31" location="ppxaux" xr:uid="{00000000-0004-0000-0100-00001E000000}"/>
+    <hyperlink ref="C35" r:id="rId32" xr:uid="{00000000-0004-0000-0100-00001F000000}"/>
+    <hyperlink ref="C36" r:id="rId33" xr:uid="{00000000-0004-0000-0100-000020000000}"/>
+    <hyperlink ref="C37" r:id="rId34" xr:uid="{00000000-0004-0000-0100-000021000000}"/>
+    <hyperlink ref="C38" r:id="rId35" xr:uid="{00000000-0004-0000-0100-000022000000}"/>
+    <hyperlink ref="C39" r:id="rId36" xr:uid="{00000000-0004-0000-0100-000023000000}"/>
+    <hyperlink ref="C40" r:id="rId37" xr:uid="{00000000-0004-0000-0100-000024000000}"/>
+    <hyperlink ref="C41" r:id="rId38" xr:uid="{00000000-0004-0000-0100-000025000000}"/>
+    <hyperlink ref="C42" r:id="rId39" xr:uid="{00000000-0004-0000-0100-000026000000}"/>
+    <hyperlink ref="C43" r:id="rId40" xr:uid="{00000000-0004-0000-0100-000027000000}"/>
+    <hyperlink ref="C44" r:id="rId41" xr:uid="{00000000-0004-0000-0100-000028000000}"/>
+    <hyperlink ref="C45" r:id="rId42" xr:uid="{00000000-0004-0000-0100-000029000000}"/>
+    <hyperlink ref="C46" r:id="rId43" xr:uid="{00000000-0004-0000-0100-00002A000000}"/>
+    <hyperlink ref="C47" r:id="rId44" xr:uid="{00000000-0004-0000-0100-00002B000000}"/>
+    <hyperlink ref="C48" r:id="rId45" xr:uid="{00000000-0004-0000-0100-00002C000000}"/>
+    <hyperlink ref="C49" r:id="rId46" xr:uid="{00000000-0004-0000-0100-00002D000000}"/>
+    <hyperlink ref="C51" r:id="rId47" xr:uid="{00000000-0004-0000-0100-00002E000000}"/>
+    <hyperlink ref="C52" r:id="rId48" display="https://www.adobe.com/jp/products/photoshop.html" xr:uid="{00000000-0004-0000-0100-00002F000000}"/>
+    <hyperlink ref="C54" r:id="rId49" xr:uid="{00000000-0004-0000-0100-000030000000}"/>
+    <hyperlink ref="C55" r:id="rId50" xr:uid="{00000000-0004-0000-0100-000031000000}"/>
+    <hyperlink ref="C56" r:id="rId51" xr:uid="{00000000-0004-0000-0100-000032000000}"/>
+    <hyperlink ref="C59" r:id="rId52" xr:uid="{00000000-0004-0000-0100-000033000000}"/>
+    <hyperlink ref="C60" r:id="rId53" xr:uid="{00000000-0004-0000-0100-000034000000}"/>
+    <hyperlink ref="C61" r:id="rId54" xr:uid="{00000000-0004-0000-0100-000035000000}"/>
+    <hyperlink ref="C62" r:id="rId55" xr:uid="{00000000-0004-0000-0100-000036000000}"/>
+    <hyperlink ref="C63" r:id="rId56" xr:uid="{00000000-0004-0000-0100-000037000000}"/>
+    <hyperlink ref="C64" r:id="rId57" xr:uid="{00000000-0004-0000-0100-000038000000}"/>
+    <hyperlink ref="C65" r:id="rId58" xr:uid="{00000000-0004-0000-0100-000039000000}"/>
+    <hyperlink ref="C66" r:id="rId59" xr:uid="{00000000-0004-0000-0100-00003A000000}"/>
+    <hyperlink ref="C67" r:id="rId60" xr:uid="{00000000-0004-0000-0100-00003B000000}"/>
+    <hyperlink ref="C68" r:id="rId61" xr:uid="{00000000-0004-0000-0100-00003C000000}"/>
+    <hyperlink ref="C69" r:id="rId62" xr:uid="{00000000-0004-0000-0100-00003D000000}"/>
+    <hyperlink ref="C70" r:id="rId63" xr:uid="{00000000-0004-0000-0100-00003E000000}"/>
+    <hyperlink ref="C71" r:id="rId64" xr:uid="{00000000-0004-0000-0100-00003F000000}"/>
+    <hyperlink ref="C72" r:id="rId65" xr:uid="{00000000-0004-0000-0100-000040000000}"/>
     <hyperlink ref="C74" r:id="rId66" xr:uid="{00000000-0004-0000-0100-000041000000}"/>
     <hyperlink ref="C75" r:id="rId67" xr:uid="{00000000-0004-0000-0100-000042000000}"/>
     <hyperlink ref="C76" r:id="rId68" xr:uid="{00000000-0004-0000-0100-000043000000}"/>
@@ -9878,8 +9946,8 @@
     <hyperlink ref="C81" r:id="rId73" xr:uid="{00000000-0004-0000-0100-000048000000}"/>
     <hyperlink ref="C82" r:id="rId74" xr:uid="{00000000-0004-0000-0100-000049000000}"/>
     <hyperlink ref="C83" r:id="rId75" xr:uid="{00000000-0004-0000-0100-00004A000000}"/>
-    <hyperlink ref="C84" r:id="rId76" xr:uid="{45E57D5A-0C69-4EC3-8E3F-9901BFC9A766}"/>
-    <hyperlink ref="C85" r:id="rId77" xr:uid="{8463720D-476B-4256-A085-A9A397E29AD6}"/>
+    <hyperlink ref="C84" r:id="rId76" xr:uid="{00000000-0004-0000-0100-00004B000000}"/>
+    <hyperlink ref="C85" r:id="rId77" xr:uid="{00000000-0004-0000-0100-00004C000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
@@ -9891,53 +9959,53 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="21.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.1640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="76.83203125" style="12" customWidth="1"/>
+    <col min="1" max="1" width="21.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="76.83203125" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
-        <v>1415</v>
+        <v>1339</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A2" s="10" t="s">
-        <v>1416</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>1417</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>1418</v>
+      <c r="A2" s="8" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>1342</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A3" s="10" t="s">
-        <v>1419</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>1420</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>1421</v>
+      <c r="A3" s="8" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>1345</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A4" s="10" t="s">
-        <v>1422</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>1423</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>1424</v>
+      <c r="A4" s="8" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>1348</v>
       </c>
     </row>
   </sheetData>

--- a/key検討用/ppxkey.xlsx
+++ b/key検討用/ppxkey.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gocho\Desktop\ppx_cust20251217(Wed)\ppx_cust\key検討用\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gocho\AppData\Local\Temp\Rar$DIa12644.29093.rartemp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F06A61F-B467-4AAE-9809-9FCBEB5609A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17CED6B2-990C-4DAD-A3CB-5DED8FC7882B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19080" yWindow="5355" windowWidth="24240" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="1430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1461" uniqueCount="1431">
   <si>
     <t>キー</t>
   </si>
@@ -3115,9 +3115,6 @@
   </si>
   <si>
     <t>[SHIFT+F11]</t>
-  </si>
-  <si>
-    <t>タブ付き新規窓(*ppc -combo)</t>
   </si>
   <si>
     <t>%k"\F11"</t>
@@ -4397,6 +4394,14 @@
   </si>
   <si>
     <t>https://github.com/ajeetdsouza/zoxide</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タブ付新規窓(*ppc -combo)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サブディレクトリ以下をインタラクティブサーチ(fzf)</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5035,7 +5040,7 @@
         <v>26</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>27</v>
+        <v>1429</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>28</v>
@@ -6535,9 +6540,7 @@
       <c r="I26" s="8" t="s">
         <v>476</v>
       </c>
-      <c r="J26" s="1" t="s">
-        <v>204</v>
-      </c>
+      <c r="J26" s="1"/>
       <c r="K26" s="8" t="s">
         <v>477</v>
       </c>
@@ -6672,7 +6675,7 @@
         <v>517</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>266</v>
+        <v>1430</v>
       </c>
       <c r="K28" s="8" t="s">
         <v>518</v>
@@ -6735,9 +6738,7 @@
       <c r="I29" s="8" t="s">
         <v>535</v>
       </c>
-      <c r="J29" s="8" t="s">
-        <v>225</v>
-      </c>
+      <c r="J29" s="8"/>
       <c r="K29" s="8" t="s">
         <v>536</v>
       </c>
@@ -6799,9 +6800,7 @@
       <c r="I30" s="8" t="s">
         <v>553</v>
       </c>
-      <c r="J30" s="8" t="s">
-        <v>246</v>
-      </c>
+      <c r="J30" s="8"/>
       <c r="K30" s="8" t="s">
         <v>554</v>
       </c>
@@ -8409,508 +8408,508 @@
         <v>1030</v>
       </c>
       <c r="F55" s="3" t="s">
+        <v>1429</v>
+      </c>
+      <c r="G55" s="3" t="s">
         <v>1031</v>
       </c>
-      <c r="G55" s="3" t="s">
+      <c r="I55" s="5" t="s">
         <v>1032</v>
       </c>
-      <c r="I55" s="5" t="s">
+      <c r="J55" s="5" t="s">
         <v>1033</v>
       </c>
-      <c r="J55" s="5" t="s">
+      <c r="K55" s="5" t="s">
         <v>1034</v>
       </c>
-      <c r="K55" s="5" t="s">
+      <c r="M55" s="8" t="s">
         <v>1035</v>
-      </c>
-      <c r="M55" s="8" t="s">
-        <v>1036</v>
       </c>
       <c r="N55" s="8"/>
       <c r="O55" s="8" t="s">
+        <v>1036</v>
+      </c>
+      <c r="Q55" s="8" t="s">
         <v>1037</v>
-      </c>
-      <c r="Q55" s="8" t="s">
-        <v>1038</v>
       </c>
       <c r="R55" s="8"/>
       <c r="S55" s="8" t="s">
+        <v>1038</v>
+      </c>
+      <c r="U55" s="8" t="s">
         <v>1039</v>
-      </c>
-      <c r="U55" s="8" t="s">
-        <v>1040</v>
       </c>
       <c r="V55" s="8"/>
       <c r="W55" s="8" t="s">
+        <v>1040</v>
+      </c>
+      <c r="Y55" s="8" t="s">
         <v>1041</v>
-      </c>
-      <c r="Y55" s="8" t="s">
-        <v>1042</v>
       </c>
       <c r="Z55" s="8"/>
       <c r="AA55" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="AC55" s="8" t="s">
         <v>1043</v>
-      </c>
-      <c r="AC55" s="8" t="s">
-        <v>1044</v>
       </c>
       <c r="AD55" s="8"/>
       <c r="AE55" s="8" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="56" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A56" s="3" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>1046</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>1047</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="E56" s="8" t="s">
         <v>1048</v>
       </c>
-      <c r="E56" s="8" t="s">
+      <c r="F56" s="8" t="s">
         <v>1049</v>
       </c>
-      <c r="F56" s="8" t="s">
+      <c r="G56" s="8" t="s">
         <v>1050</v>
       </c>
-      <c r="G56" s="8" t="s">
+      <c r="I56" s="3" t="s">
         <v>1051</v>
       </c>
-      <c r="I56" s="3" t="s">
+      <c r="J56" s="3" t="s">
         <v>1052</v>
       </c>
-      <c r="J56" s="3" t="s">
+      <c r="K56" s="3" t="s">
         <v>1053</v>
       </c>
-      <c r="K56" s="3" t="s">
+      <c r="M56" s="8" t="s">
         <v>1054</v>
-      </c>
-      <c r="M56" s="8" t="s">
-        <v>1055</v>
       </c>
       <c r="N56" s="8"/>
       <c r="O56" s="8" t="s">
+        <v>1055</v>
+      </c>
+      <c r="Q56" s="8" t="s">
         <v>1056</v>
-      </c>
-      <c r="Q56" s="8" t="s">
-        <v>1057</v>
       </c>
       <c r="R56" s="8"/>
       <c r="S56" s="8" t="s">
+        <v>1057</v>
+      </c>
+      <c r="U56" s="8" t="s">
         <v>1058</v>
-      </c>
-      <c r="U56" s="8" t="s">
-        <v>1059</v>
       </c>
       <c r="V56" s="8"/>
       <c r="W56" s="8" t="s">
+        <v>1059</v>
+      </c>
+      <c r="Y56" s="8" t="s">
         <v>1060</v>
-      </c>
-      <c r="Y56" s="8" t="s">
-        <v>1061</v>
       </c>
       <c r="Z56" s="8"/>
       <c r="AA56" s="8" t="s">
+        <v>1061</v>
+      </c>
+      <c r="AC56" s="8" t="s">
         <v>1062</v>
-      </c>
-      <c r="AC56" s="8" t="s">
-        <v>1063</v>
       </c>
       <c r="AD56" s="8"/>
       <c r="AE56" s="8" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="57" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A57" s="3" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>1065</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>1066</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="E57" s="8" t="s">
         <v>1067</v>
       </c>
-      <c r="E57" s="8" t="s">
+      <c r="F57" s="8" t="s">
         <v>1068</v>
       </c>
-      <c r="F57" s="8" t="s">
+      <c r="G57" s="8" t="s">
         <v>1069</v>
-      </c>
-      <c r="G57" s="8" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="58" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A58" s="8" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B58" s="8" t="s">
         <v>1071</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="C58" s="8" t="s">
         <v>1072</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>1073</v>
       </c>
     </row>
     <row r="59" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A59" s="8" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B59" s="8" t="s">
         <v>1074</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="C59" s="8" t="s">
         <v>1075</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>1076</v>
       </c>
     </row>
     <row r="60" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A60" s="8" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B60" s="8" t="s">
         <v>1077</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="C60" s="8" t="s">
         <v>1078</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>1079</v>
       </c>
       <c r="E60" s="4"/>
       <c r="F60" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="61" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A61" s="8" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B61" s="8" t="s">
         <v>1081</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="C61" s="8" t="s">
         <v>1082</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="62" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A62" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B62" s="8" t="s">
         <v>1084</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="C62" s="8" t="s">
         <v>1085</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>1086</v>
       </c>
       <c r="E62" s="6"/>
       <c r="F62" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="63" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A63" s="8" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B63" s="8" t="s">
         <v>1088</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="C63" s="8" t="s">
         <v>1089</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>1090</v>
       </c>
     </row>
     <row r="64" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A64" s="8" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B64" s="8" t="s">
         <v>1091</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="C64" s="8" t="s">
         <v>1092</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>1093</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A65" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>1094</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="C65" s="3" t="s">
         <v>1095</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>1096</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A66" s="8" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B66" s="8" t="s">
         <v>1097</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="C66" s="8" t="s">
         <v>1098</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>1099</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A67" s="8" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="B67" s="8"/>
       <c r="C67" s="8" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A68" s="8" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B68" s="8"/>
       <c r="C68" s="8" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A69" s="8" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B69" s="8" t="s">
         <v>1104</v>
       </c>
-      <c r="B69" s="8" t="s">
+      <c r="C69" s="8" t="s">
         <v>1105</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>1106</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A70" s="8" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="B70" s="8"/>
       <c r="C70" s="8" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A71" s="8" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B71" s="8" t="s">
         <v>1109</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="C71" s="8" t="s">
         <v>1110</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>1111</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A72" s="7" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B72" s="7" t="s">
         <v>1112</v>
       </c>
-      <c r="B72" s="7" t="s">
+      <c r="C72" s="7" t="s">
         <v>1113</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>1114</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A73" s="5" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B73" s="5" t="s">
         <v>1115</v>
       </c>
-      <c r="B73" s="5" t="s">
+      <c r="C73" s="5" t="s">
         <v>1116</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>1117</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A74" s="5" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B74" s="5" t="s">
         <v>1118</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="C74" s="5" t="s">
         <v>1119</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>1120</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A75" s="3" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>1121</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="C75" s="3" t="s">
         <v>1122</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>1123</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A76" s="8" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B76" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="B76" s="8" t="s">
+      <c r="C76" s="8" t="s">
         <v>1125</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>1126</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A77" s="8" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B77" s="8" t="s">
         <v>1127</v>
       </c>
-      <c r="B77" s="8" t="s">
+      <c r="C77" s="8" t="s">
         <v>1128</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>1129</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A78" s="8" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B78" s="8"/>
       <c r="C78" s="8" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A79" s="3" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>1132</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="C79" s="3" t="s">
         <v>1133</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>1134</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A80" s="8" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B80" s="8" t="s">
         <v>1135</v>
       </c>
-      <c r="B80" s="8" t="s">
+      <c r="C80" s="8" t="s">
         <v>1136</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>1137</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A81" s="5" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B81" s="5" t="s">
         <v>1138</v>
       </c>
-      <c r="B81" s="5" t="s">
+      <c r="C81" s="5" t="s">
         <v>1139</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A82" s="5" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B82" s="5" t="s">
         <v>1141</v>
       </c>
-      <c r="B82" s="5" t="s">
+      <c r="C82" s="5" t="s">
         <v>1142</v>
-      </c>
-      <c r="C82" s="5" t="s">
-        <v>1143</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A83" s="3" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>1144</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="C83" s="3" t="s">
         <v>1145</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>1146</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A84" s="3" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B84" s="3" t="s">
         <v>1147</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="C84" s="3" t="s">
         <v>1148</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>1149</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A85" s="8" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="B85" s="8"/>
       <c r="C85" s="8" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A86" s="5" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B86" s="5" t="s">
         <v>1152</v>
       </c>
-      <c r="B86" s="5" t="s">
+      <c r="C86" s="5" t="s">
         <v>1153</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>1154</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A87" s="8" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B87" s="8" t="s">
         <v>1155</v>
       </c>
-      <c r="B87" s="8" t="s">
+      <c r="C87" s="8" t="s">
         <v>1156</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>1157</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A88" s="8" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="B88" s="8"/>
       <c r="C88" s="8" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A89" s="5" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B89" s="5" t="s">
         <v>1160</v>
       </c>
-      <c r="B89" s="5" t="s">
+      <c r="C89" s="5" t="s">
         <v>1161</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>1162</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A90" s="5" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B90" s="5" t="s">
         <v>1163</v>
       </c>
-      <c r="B90" s="5" t="s">
+      <c r="C90" s="5" t="s">
         <v>1164</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>1165</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A91" s="5" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B91" s="5" t="s">
         <v>1166</v>
       </c>
-      <c r="B91" s="5" t="s">
+      <c r="C91" s="5" t="s">
         <v>1167</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>1168</v>
       </c>
     </row>
   </sheetData>
@@ -8932,937 +8931,937 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1169</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>1170</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1171</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>1176</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>1177</v>
-      </c>
       <c r="C2" s="11" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>1178</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>1179</v>
-      </c>
       <c r="C3" s="11" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>1180</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>1181</v>
-      </c>
       <c r="C4" s="11" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>1182</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>1183</v>
-      </c>
       <c r="C5" s="11" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>1184</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>1185</v>
-      </c>
       <c r="C6" s="11" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>1186</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>1187</v>
-      </c>
       <c r="C7" s="11" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A8" s="8" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>1188</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>1189</v>
-      </c>
       <c r="C8" s="11" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A9" s="8" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>1190</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>1191</v>
-      </c>
       <c r="C9" s="11" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>1192</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>1193</v>
-      </c>
       <c r="C10" s="11" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>1194</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>1195</v>
-      </c>
       <c r="C11" s="11" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A12" s="8" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>1196</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>1197</v>
-      </c>
       <c r="C12" s="11" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>1198</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>1199</v>
-      </c>
       <c r="C13" s="11" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A14" s="8" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>1200</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>1201</v>
-      </c>
       <c r="C14" s="11" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A15" s="8" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>1202</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>1203</v>
-      </c>
       <c r="C15" s="11" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A16" s="8" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>1204</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>1205</v>
-      </c>
       <c r="C16" s="11" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A17" s="8" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>1206</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>1207</v>
-      </c>
       <c r="C17" s="11" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A18" s="8" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>1208</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>1209</v>
-      </c>
       <c r="C18" s="11" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A19" s="8" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B19" s="8" t="s">
         <v>1210</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>1211</v>
-      </c>
       <c r="C19" s="11" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A20" s="8" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>1212</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>1213</v>
-      </c>
       <c r="C20" s="11" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>1214</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>1215</v>
-      </c>
       <c r="C21" s="11" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A22" s="8" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B22" s="8" t="s">
         <v>1216</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>1217</v>
-      </c>
       <c r="C22" s="11" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A23" s="8" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B23" s="8" t="s">
         <v>1218</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>1219</v>
-      </c>
       <c r="C23" s="11" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A24" s="8" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B24" s="8" t="s">
         <v>1220</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>1221</v>
-      </c>
       <c r="C24" s="11" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A25" s="8" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B25" s="8" t="s">
         <v>1222</v>
       </c>
-      <c r="B25" s="8" t="s">
-        <v>1223</v>
-      </c>
       <c r="C25" s="11" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A26" s="8" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B26" s="8" t="s">
         <v>1224</v>
       </c>
-      <c r="B26" s="8" t="s">
-        <v>1225</v>
-      </c>
       <c r="C26" s="11" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A27" s="8" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B27" s="8" t="s">
         <v>1226</v>
       </c>
-      <c r="B27" s="8" t="s">
-        <v>1227</v>
-      </c>
       <c r="C27" s="11" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A28" s="8" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B28" s="8" t="s">
         <v>1228</v>
       </c>
-      <c r="B28" s="8" t="s">
-        <v>1229</v>
-      </c>
       <c r="C28" s="11" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A29" s="8" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B29" s="8" t="s">
         <v>1230</v>
       </c>
-      <c r="B29" s="8" t="s">
-        <v>1231</v>
-      </c>
       <c r="C29" s="11" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A30" s="8" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B30" s="8" t="s">
         <v>1232</v>
       </c>
-      <c r="B30" s="8" t="s">
-        <v>1233</v>
-      </c>
       <c r="C30" s="11" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A31" s="8" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B31" s="8" t="s">
         <v>1234</v>
       </c>
-      <c r="B31" s="8" t="s">
-        <v>1235</v>
-      </c>
       <c r="C31" s="11" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A32" s="8" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B32" s="8" t="s">
         <v>1236</v>
       </c>
-      <c r="B32" s="8" t="s">
-        <v>1237</v>
-      </c>
       <c r="C32" s="11" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A33" s="8" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B33" s="8" t="s">
         <v>1238</v>
       </c>
-      <c r="B33" s="8" t="s">
-        <v>1239</v>
-      </c>
       <c r="C33" s="11" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A34" s="8" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B34" s="8" t="s">
         <v>1240</v>
       </c>
-      <c r="B34" s="8" t="s">
-        <v>1241</v>
-      </c>
       <c r="C34" s="11" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A35" s="8" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B35" s="8" t="s">
         <v>1242</v>
       </c>
-      <c r="B35" s="8" t="s">
-        <v>1243</v>
-      </c>
       <c r="C35" s="11" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="8" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B36" s="8" t="s">
         <v>1244</v>
       </c>
-      <c r="B36" s="8" t="s">
-        <v>1245</v>
-      </c>
       <c r="C36" s="11" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A37" s="8" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B37" s="8" t="s">
         <v>1246</v>
       </c>
-      <c r="B37" s="8" t="s">
-        <v>1247</v>
-      </c>
       <c r="C37" s="11" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A38" s="8" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B38" s="8" t="s">
         <v>1248</v>
       </c>
-      <c r="B38" s="8" t="s">
-        <v>1249</v>
-      </c>
       <c r="C38" s="11" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A39" s="8" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B39" s="8" t="s">
         <v>1250</v>
       </c>
-      <c r="B39" s="8" t="s">
-        <v>1251</v>
-      </c>
       <c r="C39" s="11" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A40" s="8" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B40" s="8" t="s">
         <v>1252</v>
       </c>
-      <c r="B40" s="8" t="s">
-        <v>1253</v>
-      </c>
       <c r="C40" s="11" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A41" s="8" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B41" s="8" t="s">
         <v>1254</v>
       </c>
-      <c r="B41" s="8" t="s">
-        <v>1255</v>
-      </c>
       <c r="C41" s="11" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A42" s="8" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B42" s="8" t="s">
         <v>1256</v>
       </c>
-      <c r="B42" s="8" t="s">
-        <v>1257</v>
-      </c>
       <c r="C42" s="11" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A43" s="8" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B43" s="8" t="s">
         <v>1258</v>
       </c>
-      <c r="B43" s="8" t="s">
-        <v>1259</v>
-      </c>
       <c r="C43" s="11" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A44" s="8" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B44" s="8" t="s">
         <v>1260</v>
       </c>
-      <c r="B44" s="8" t="s">
-        <v>1261</v>
-      </c>
       <c r="C44" s="11" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A45" s="8" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B45" s="8" t="s">
         <v>1262</v>
       </c>
-      <c r="B45" s="8" t="s">
-        <v>1263</v>
-      </c>
       <c r="C45" s="11" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A46" s="8" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B46" s="8" t="s">
         <v>1264</v>
       </c>
-      <c r="B46" s="8" t="s">
-        <v>1265</v>
-      </c>
       <c r="C46" s="11" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A47" s="8" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B47" s="8" t="s">
         <v>1266</v>
       </c>
-      <c r="B47" s="8" t="s">
-        <v>1267</v>
-      </c>
       <c r="C47" s="11" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A48" s="8" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B48" s="8" t="s">
         <v>1268</v>
       </c>
-      <c r="B48" s="8" t="s">
-        <v>1269</v>
-      </c>
       <c r="C48" s="11" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A49" s="8" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B49" s="8" t="s">
         <v>1270</v>
       </c>
-      <c r="B49" s="8" t="s">
-        <v>1271</v>
-      </c>
       <c r="C49" s="11" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A50" s="8" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B50" s="8" t="s">
         <v>1272</v>
       </c>
-      <c r="B50" s="8" t="s">
-        <v>1273</v>
-      </c>
       <c r="C50" s="11" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A51" s="8" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B51" s="8" t="s">
         <v>1274</v>
       </c>
-      <c r="B51" s="8" t="s">
-        <v>1275</v>
-      </c>
       <c r="C51" s="11" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A52" s="8" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B52" s="8" t="s">
         <v>1276</v>
       </c>
-      <c r="B52" s="8" t="s">
-        <v>1277</v>
-      </c>
       <c r="C52" s="11" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A53" s="8" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B53" s="8" t="s">
         <v>1278</v>
       </c>
-      <c r="B53" s="8" t="s">
-        <v>1279</v>
-      </c>
       <c r="C53" s="11" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A54" s="8" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B54" s="8" t="s">
         <v>1280</v>
       </c>
-      <c r="B54" s="8" t="s">
-        <v>1281</v>
-      </c>
       <c r="C54" s="11" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A55" s="8" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B55" s="8" t="s">
         <v>1282</v>
       </c>
-      <c r="B55" s="8" t="s">
-        <v>1283</v>
-      </c>
       <c r="C55" s="11" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A56" s="8" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B56" s="8" t="s">
         <v>1284</v>
       </c>
-      <c r="B56" s="8" t="s">
-        <v>1285</v>
-      </c>
       <c r="C56" s="11" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A57" s="8" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B57" s="8" t="s">
         <v>1172</v>
       </c>
-      <c r="B57" s="8" t="s">
-        <v>1173</v>
-      </c>
       <c r="C57" s="11" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A58" s="8" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B58" s="8" t="s">
         <v>1286</v>
       </c>
-      <c r="B58" s="8" t="s">
-        <v>1287</v>
-      </c>
       <c r="C58" s="11" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A59" s="8" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B59" s="8" t="s">
         <v>1288</v>
       </c>
-      <c r="B59" s="8" t="s">
-        <v>1289</v>
-      </c>
       <c r="C59" s="11" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A60" s="8" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B60" s="8" t="s">
         <v>1290</v>
       </c>
-      <c r="B60" s="8" t="s">
-        <v>1291</v>
-      </c>
       <c r="C60" s="11" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A61" s="8" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B61" s="8" t="s">
         <v>1292</v>
       </c>
-      <c r="B61" s="8" t="s">
-        <v>1293</v>
-      </c>
       <c r="C61" s="11" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A62" s="8" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B62" s="8" t="s">
         <v>1294</v>
       </c>
-      <c r="B62" s="8" t="s">
-        <v>1295</v>
-      </c>
       <c r="C62" s="11" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A63" s="8" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B63" s="8" t="s">
         <v>1296</v>
       </c>
-      <c r="B63" s="8" t="s">
-        <v>1297</v>
-      </c>
       <c r="C63" s="11" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A64" s="8" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B64" s="8" t="s">
         <v>1298</v>
       </c>
-      <c r="B64" s="8" t="s">
-        <v>1299</v>
-      </c>
       <c r="C64" s="11" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A65" s="8" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B65" s="8" t="s">
         <v>1300</v>
       </c>
-      <c r="B65" s="8" t="s">
-        <v>1301</v>
-      </c>
       <c r="C65" s="11" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A66" s="8" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B66" s="8" t="s">
         <v>1302</v>
       </c>
-      <c r="B66" s="8" t="s">
-        <v>1303</v>
-      </c>
       <c r="C66" s="11" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A67" s="8" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B67" s="8" t="s">
         <v>1304</v>
       </c>
-      <c r="B67" s="8" t="s">
-        <v>1305</v>
-      </c>
       <c r="C67" s="11" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A68" s="8" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B68" s="8" t="s">
         <v>1306</v>
       </c>
-      <c r="B68" s="8" t="s">
-        <v>1307</v>
-      </c>
       <c r="C68" s="11" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A69" s="8" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B69" s="8" t="s">
         <v>1308</v>
       </c>
-      <c r="B69" s="8" t="s">
-        <v>1309</v>
-      </c>
       <c r="C69" s="11" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A70" s="8" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B70" s="8" t="s">
         <v>1310</v>
       </c>
-      <c r="B70" s="8" t="s">
-        <v>1311</v>
-      </c>
       <c r="C70" s="11" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A71" s="8" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B71" s="8" t="s">
         <v>1312</v>
       </c>
-      <c r="B71" s="8" t="s">
-        <v>1313</v>
-      </c>
       <c r="C71" s="11" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A72" s="8" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B72" s="8" t="s">
         <v>1314</v>
       </c>
-      <c r="B72" s="8" t="s">
-        <v>1315</v>
-      </c>
       <c r="C72" s="11" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A73" s="8" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B73" s="8" t="s">
         <v>1174</v>
       </c>
-      <c r="B73" s="8" t="s">
-        <v>1175</v>
-      </c>
       <c r="C73" s="11" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A74" s="8" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B74" s="8" t="s">
         <v>1316</v>
       </c>
-      <c r="B74" s="8" t="s">
-        <v>1317</v>
-      </c>
       <c r="C74" s="11" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A75" s="8" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B75" s="8" t="s">
         <v>1318</v>
       </c>
-      <c r="B75" s="8" t="s">
-        <v>1319</v>
-      </c>
       <c r="C75" s="11" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A76" s="8" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B76" s="8" t="s">
         <v>1320</v>
       </c>
-      <c r="B76" s="8" t="s">
-        <v>1321</v>
-      </c>
       <c r="C76" s="11" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A77" s="8" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B77" s="8" t="s">
         <v>1322</v>
       </c>
-      <c r="B77" s="8" t="s">
-        <v>1323</v>
-      </c>
       <c r="C77" s="11" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A78" s="8" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B78" s="8" t="s">
         <v>1324</v>
       </c>
-      <c r="B78" s="8" t="s">
-        <v>1325</v>
-      </c>
       <c r="C78" s="11" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A79" s="8" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B79" s="8" t="s">
         <v>1326</v>
       </c>
-      <c r="B79" s="8" t="s">
-        <v>1327</v>
-      </c>
       <c r="C79" s="11" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A80" s="8" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B80" s="8" t="s">
         <v>1328</v>
       </c>
-      <c r="B80" s="8" t="s">
-        <v>1329</v>
-      </c>
       <c r="C80" s="11" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A81" s="8" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B81" s="8" t="s">
         <v>1330</v>
       </c>
-      <c r="B81" s="8" t="s">
-        <v>1331</v>
-      </c>
       <c r="C81" s="11" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A82" s="8" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B82" s="8" t="s">
         <v>1332</v>
       </c>
-      <c r="B82" s="8" t="s">
-        <v>1333</v>
-      </c>
       <c r="C82" s="11" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A83" s="8" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A84" s="8" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B84" s="8" t="s">
         <v>1335</v>
       </c>
-      <c r="B84" s="8" t="s">
-        <v>1336</v>
-      </c>
       <c r="C84" s="11" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A85" s="8" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B85" s="8" t="s">
         <v>1337</v>
       </c>
-      <c r="B85" s="8" t="s">
-        <v>1338</v>
-      </c>
       <c r="C85" s="11" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
     </row>
   </sheetData>
@@ -9966,46 +9965,46 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1170</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1171</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>1340</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="C2" s="10" t="s">
         <v>1341</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>1342</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>1343</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="10" t="s">
         <v>1344</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>1345</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>1346</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="10" t="s">
         <v>1347</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>1348</v>
       </c>
     </row>
   </sheetData>

--- a/key検討用/ppxkey.xlsx
+++ b/key検討用/ppxkey.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gocho\AppData\Local\Temp\Rar$DIa12644.29093.rartemp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gocho\Desktop\ppx_cust20251217(Wed)\ppx_cust\key検討用\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17CED6B2-990C-4DAD-A3CB-5DED8FC7882B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37E8A8E2-780D-40C9-9D33-219A0242D5ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19080" yWindow="5355" windowWidth="24240" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1461" uniqueCount="1431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="1430">
   <si>
     <t>キー</t>
   </si>
@@ -2836,9 +2836,6 @@
   </si>
   <si>
     <t>[Ctrl+F6]</t>
-  </si>
-  <si>
-    <t>現在開いている窓・タブ全てから検索</t>
   </si>
   <si>
     <t>%k"^F6"</t>
@@ -4401,7 +4398,13 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>サブディレクトリ以下をインタラクティブサーチ(fzf)</t>
+    <t>窓構成適応・全域検索</t>
+    <rPh sb="0" eb="5">
+      <t>マドコウセイテキオウ</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ゼンイキケンサク</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5040,7 +5043,7 @@
         <v>26</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>28</v>
@@ -6540,7 +6543,9 @@
       <c r="I26" s="8" t="s">
         <v>476</v>
       </c>
-      <c r="J26" s="1"/>
+      <c r="J26" s="1" t="s">
+        <v>204</v>
+      </c>
       <c r="K26" s="8" t="s">
         <v>477</v>
       </c>
@@ -6675,7 +6680,7 @@
         <v>517</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>1430</v>
+        <v>266</v>
       </c>
       <c r="K28" s="8" t="s">
         <v>518</v>
@@ -6738,7 +6743,9 @@
       <c r="I29" s="8" t="s">
         <v>535</v>
       </c>
-      <c r="J29" s="8"/>
+      <c r="J29" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="K29" s="8" t="s">
         <v>536</v>
       </c>
@@ -6800,7 +6807,9 @@
       <c r="I30" s="8" t="s">
         <v>553</v>
       </c>
-      <c r="J30" s="8"/>
+      <c r="J30" s="8" t="s">
+        <v>246</v>
+      </c>
       <c r="K30" s="8" t="s">
         <v>554</v>
       </c>
@@ -8095,821 +8104,821 @@
         <v>937</v>
       </c>
       <c r="J50" s="8" t="s">
+        <v>1429</v>
+      </c>
+      <c r="K50" s="8" t="s">
         <v>938</v>
       </c>
-      <c r="K50" s="8" t="s">
+      <c r="M50" s="8" t="s">
         <v>939</v>
       </c>
-      <c r="M50" s="8" t="s">
+      <c r="N50" s="8" t="s">
         <v>940</v>
       </c>
-      <c r="N50" s="8" t="s">
+      <c r="O50" s="8" t="s">
         <v>941</v>
       </c>
-      <c r="O50" s="8" t="s">
+      <c r="Q50" s="8" t="s">
         <v>942</v>
-      </c>
-      <c r="Q50" s="8" t="s">
-        <v>943</v>
       </c>
       <c r="R50" s="8"/>
       <c r="S50" s="8" t="s">
+        <v>943</v>
+      </c>
+      <c r="U50" s="8" t="s">
         <v>944</v>
-      </c>
-      <c r="U50" s="8" t="s">
-        <v>945</v>
       </c>
       <c r="V50" s="8"/>
       <c r="W50" s="8" t="s">
+        <v>945</v>
+      </c>
+      <c r="Y50" s="8" t="s">
         <v>946</v>
-      </c>
-      <c r="Y50" s="8" t="s">
-        <v>947</v>
       </c>
       <c r="Z50" s="8"/>
       <c r="AA50" s="8" t="s">
+        <v>947</v>
+      </c>
+      <c r="AC50" s="8" t="s">
         <v>948</v>
-      </c>
-      <c r="AC50" s="8" t="s">
-        <v>949</v>
       </c>
       <c r="AD50" s="8"/>
       <c r="AE50" s="8" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="51" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A51" s="8" t="s">
+        <v>950</v>
+      </c>
+      <c r="B51" s="8" t="s">
         <v>951</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="C51" s="8" t="s">
         <v>952</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="E51" s="8" t="s">
         <v>953</v>
       </c>
-      <c r="E51" s="8" t="s">
+      <c r="F51" s="8" t="s">
         <v>954</v>
       </c>
-      <c r="F51" s="8" t="s">
+      <c r="G51" s="8" t="s">
         <v>955</v>
       </c>
-      <c r="G51" s="8" t="s">
+      <c r="I51" s="8" t="s">
         <v>956</v>
       </c>
-      <c r="I51" s="8" t="s">
+      <c r="J51" s="8" t="s">
         <v>957</v>
       </c>
-      <c r="J51" s="8" t="s">
+      <c r="K51" s="8" t="s">
         <v>958</v>
       </c>
-      <c r="K51" s="8" t="s">
+      <c r="M51" s="8" t="s">
         <v>959</v>
-      </c>
-      <c r="M51" s="8" t="s">
-        <v>960</v>
       </c>
       <c r="N51" s="8"/>
       <c r="O51" s="8" t="s">
+        <v>960</v>
+      </c>
+      <c r="Q51" s="8" t="s">
         <v>961</v>
-      </c>
-      <c r="Q51" s="8" t="s">
-        <v>962</v>
       </c>
       <c r="R51" s="8"/>
       <c r="S51" s="8" t="s">
+        <v>962</v>
+      </c>
+      <c r="U51" s="8" t="s">
         <v>963</v>
-      </c>
-      <c r="U51" s="8" t="s">
-        <v>964</v>
       </c>
       <c r="V51" s="8"/>
       <c r="W51" s="8" t="s">
+        <v>964</v>
+      </c>
+      <c r="Y51" s="8" t="s">
         <v>965</v>
-      </c>
-      <c r="Y51" s="8" t="s">
-        <v>966</v>
       </c>
       <c r="Z51" s="8"/>
       <c r="AA51" s="8" t="s">
+        <v>966</v>
+      </c>
+      <c r="AC51" s="8" t="s">
         <v>967</v>
-      </c>
-      <c r="AC51" s="8" t="s">
-        <v>968</v>
       </c>
       <c r="AD51" s="8"/>
       <c r="AE51" s="8" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="52" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A52" s="5" t="s">
+        <v>969</v>
+      </c>
+      <c r="B52" s="5" t="s">
         <v>970</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="C52" s="5" t="s">
         <v>971</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="E52" s="8" t="s">
         <v>972</v>
       </c>
-      <c r="E52" s="8" t="s">
+      <c r="F52" s="8" t="s">
         <v>973</v>
       </c>
-      <c r="F52" s="8" t="s">
+      <c r="G52" s="8" t="s">
         <v>974</v>
       </c>
-      <c r="G52" s="8" t="s">
+      <c r="I52" s="8" t="s">
         <v>975</v>
       </c>
-      <c r="I52" s="8" t="s">
+      <c r="J52" s="8" t="s">
         <v>976</v>
       </c>
-      <c r="J52" s="8" t="s">
+      <c r="K52" s="8" t="s">
         <v>977</v>
       </c>
-      <c r="K52" s="8" t="s">
+      <c r="M52" s="8" t="s">
         <v>978</v>
-      </c>
-      <c r="M52" s="8" t="s">
-        <v>979</v>
       </c>
       <c r="N52" s="8"/>
       <c r="O52" s="8" t="s">
+        <v>979</v>
+      </c>
+      <c r="Q52" s="8" t="s">
         <v>980</v>
-      </c>
-      <c r="Q52" s="8" t="s">
-        <v>981</v>
       </c>
       <c r="R52" s="8"/>
       <c r="S52" s="8" t="s">
+        <v>981</v>
+      </c>
+      <c r="U52" s="8" t="s">
         <v>982</v>
-      </c>
-      <c r="U52" s="8" t="s">
-        <v>983</v>
       </c>
       <c r="V52" s="8"/>
       <c r="W52" s="8" t="s">
+        <v>983</v>
+      </c>
+      <c r="Y52" s="8" t="s">
         <v>984</v>
-      </c>
-      <c r="Y52" s="8" t="s">
-        <v>985</v>
       </c>
       <c r="Z52" s="8"/>
       <c r="AA52" s="8" t="s">
+        <v>985</v>
+      </c>
+      <c r="AC52" s="8" t="s">
         <v>986</v>
-      </c>
-      <c r="AC52" s="8" t="s">
-        <v>987</v>
       </c>
       <c r="AD52" s="8"/>
       <c r="AE52" s="8" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="53" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A53" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>989</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>990</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="E53" s="8" t="s">
         <v>991</v>
       </c>
-      <c r="E53" s="8" t="s">
+      <c r="F53" s="8" t="s">
         <v>992</v>
       </c>
-      <c r="F53" s="8" t="s">
+      <c r="G53" s="8" t="s">
         <v>993</v>
       </c>
-      <c r="G53" s="8" t="s">
+      <c r="I53" s="5" t="s">
         <v>994</v>
       </c>
-      <c r="I53" s="5" t="s">
+      <c r="J53" s="5" t="s">
         <v>995</v>
       </c>
-      <c r="J53" s="5" t="s">
+      <c r="K53" s="5" t="s">
         <v>996</v>
       </c>
-      <c r="K53" s="5" t="s">
+      <c r="M53" s="8" t="s">
         <v>997</v>
-      </c>
-      <c r="M53" s="8" t="s">
-        <v>998</v>
       </c>
       <c r="N53" s="8"/>
       <c r="O53" s="8" t="s">
+        <v>998</v>
+      </c>
+      <c r="Q53" s="8" t="s">
         <v>999</v>
-      </c>
-      <c r="Q53" s="8" t="s">
-        <v>1000</v>
       </c>
       <c r="R53" s="8"/>
       <c r="S53" s="8" t="s">
+        <v>1000</v>
+      </c>
+      <c r="U53" s="8" t="s">
         <v>1001</v>
-      </c>
-      <c r="U53" s="8" t="s">
-        <v>1002</v>
       </c>
       <c r="V53" s="8"/>
       <c r="W53" s="8" t="s">
+        <v>1002</v>
+      </c>
+      <c r="Y53" s="8" t="s">
         <v>1003</v>
-      </c>
-      <c r="Y53" s="8" t="s">
-        <v>1004</v>
       </c>
       <c r="Z53" s="8"/>
       <c r="AA53" s="8" t="s">
+        <v>1004</v>
+      </c>
+      <c r="AC53" s="8" t="s">
         <v>1005</v>
-      </c>
-      <c r="AC53" s="8" t="s">
-        <v>1006</v>
       </c>
       <c r="AD53" s="8"/>
       <c r="AE53" s="8" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="54" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A54" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>1008</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>1009</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="E54" s="8" t="s">
         <v>1010</v>
       </c>
-      <c r="E54" s="8" t="s">
+      <c r="F54" s="8" t="s">
         <v>1011</v>
       </c>
-      <c r="F54" s="8" t="s">
+      <c r="G54" s="8" t="s">
         <v>1012</v>
       </c>
-      <c r="G54" s="8" t="s">
+      <c r="I54" s="8" t="s">
         <v>1013</v>
       </c>
-      <c r="I54" s="8" t="s">
+      <c r="J54" s="8" t="s">
         <v>1014</v>
       </c>
-      <c r="J54" s="8" t="s">
+      <c r="K54" s="8" t="s">
         <v>1015</v>
       </c>
-      <c r="K54" s="8" t="s">
+      <c r="M54" s="8" t="s">
         <v>1016</v>
-      </c>
-      <c r="M54" s="8" t="s">
-        <v>1017</v>
       </c>
       <c r="N54" s="8"/>
       <c r="O54" s="8" t="s">
+        <v>1017</v>
+      </c>
+      <c r="Q54" s="8" t="s">
         <v>1018</v>
-      </c>
-      <c r="Q54" s="8" t="s">
-        <v>1019</v>
       </c>
       <c r="R54" s="8"/>
       <c r="S54" s="8" t="s">
+        <v>1019</v>
+      </c>
+      <c r="U54" s="8" t="s">
         <v>1020</v>
-      </c>
-      <c r="U54" s="8" t="s">
-        <v>1021</v>
       </c>
       <c r="V54" s="8"/>
       <c r="W54" s="8" t="s">
+        <v>1021</v>
+      </c>
+      <c r="Y54" s="8" t="s">
         <v>1022</v>
-      </c>
-      <c r="Y54" s="8" t="s">
-        <v>1023</v>
       </c>
       <c r="Z54" s="8"/>
       <c r="AA54" s="8" t="s">
+        <v>1023</v>
+      </c>
+      <c r="AC54" s="8" t="s">
         <v>1024</v>
-      </c>
-      <c r="AC54" s="8" t="s">
-        <v>1025</v>
       </c>
       <c r="AD54" s="8"/>
       <c r="AE54" s="8" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="55" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A55" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>1027</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="C55" s="3" t="s">
         <v>1028</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="E55" s="3" t="s">
         <v>1029</v>
       </c>
-      <c r="E55" s="3" t="s">
+      <c r="F55" s="3" t="s">
+        <v>1428</v>
+      </c>
+      <c r="G55" s="3" t="s">
         <v>1030</v>
       </c>
-      <c r="F55" s="3" t="s">
-        <v>1429</v>
-      </c>
-      <c r="G55" s="3" t="s">
+      <c r="I55" s="5" t="s">
         <v>1031</v>
       </c>
-      <c r="I55" s="5" t="s">
+      <c r="J55" s="5" t="s">
         <v>1032</v>
       </c>
-      <c r="J55" s="5" t="s">
+      <c r="K55" s="5" t="s">
         <v>1033</v>
       </c>
-      <c r="K55" s="5" t="s">
+      <c r="M55" s="8" t="s">
         <v>1034</v>
-      </c>
-      <c r="M55" s="8" t="s">
-        <v>1035</v>
       </c>
       <c r="N55" s="8"/>
       <c r="O55" s="8" t="s">
+        <v>1035</v>
+      </c>
+      <c r="Q55" s="8" t="s">
         <v>1036</v>
-      </c>
-      <c r="Q55" s="8" t="s">
-        <v>1037</v>
       </c>
       <c r="R55" s="8"/>
       <c r="S55" s="8" t="s">
+        <v>1037</v>
+      </c>
+      <c r="U55" s="8" t="s">
         <v>1038</v>
-      </c>
-      <c r="U55" s="8" t="s">
-        <v>1039</v>
       </c>
       <c r="V55" s="8"/>
       <c r="W55" s="8" t="s">
+        <v>1039</v>
+      </c>
+      <c r="Y55" s="8" t="s">
         <v>1040</v>
-      </c>
-      <c r="Y55" s="8" t="s">
-        <v>1041</v>
       </c>
       <c r="Z55" s="8"/>
       <c r="AA55" s="8" t="s">
+        <v>1041</v>
+      </c>
+      <c r="AC55" s="8" t="s">
         <v>1042</v>
-      </c>
-      <c r="AC55" s="8" t="s">
-        <v>1043</v>
       </c>
       <c r="AD55" s="8"/>
       <c r="AE55" s="8" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="56" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A56" s="3" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>1045</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>1046</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="E56" s="8" t="s">
         <v>1047</v>
       </c>
-      <c r="E56" s="8" t="s">
+      <c r="F56" s="8" t="s">
         <v>1048</v>
       </c>
-      <c r="F56" s="8" t="s">
+      <c r="G56" s="8" t="s">
         <v>1049</v>
       </c>
-      <c r="G56" s="8" t="s">
+      <c r="I56" s="3" t="s">
         <v>1050</v>
       </c>
-      <c r="I56" s="3" t="s">
+      <c r="J56" s="3" t="s">
         <v>1051</v>
       </c>
-      <c r="J56" s="3" t="s">
+      <c r="K56" s="3" t="s">
         <v>1052</v>
       </c>
-      <c r="K56" s="3" t="s">
+      <c r="M56" s="8" t="s">
         <v>1053</v>
-      </c>
-      <c r="M56" s="8" t="s">
-        <v>1054</v>
       </c>
       <c r="N56" s="8"/>
       <c r="O56" s="8" t="s">
+        <v>1054</v>
+      </c>
+      <c r="Q56" s="8" t="s">
         <v>1055</v>
-      </c>
-      <c r="Q56" s="8" t="s">
-        <v>1056</v>
       </c>
       <c r="R56" s="8"/>
       <c r="S56" s="8" t="s">
+        <v>1056</v>
+      </c>
+      <c r="U56" s="8" t="s">
         <v>1057</v>
-      </c>
-      <c r="U56" s="8" t="s">
-        <v>1058</v>
       </c>
       <c r="V56" s="8"/>
       <c r="W56" s="8" t="s">
+        <v>1058</v>
+      </c>
+      <c r="Y56" s="8" t="s">
         <v>1059</v>
-      </c>
-      <c r="Y56" s="8" t="s">
-        <v>1060</v>
       </c>
       <c r="Z56" s="8"/>
       <c r="AA56" s="8" t="s">
+        <v>1060</v>
+      </c>
+      <c r="AC56" s="8" t="s">
         <v>1061</v>
-      </c>
-      <c r="AC56" s="8" t="s">
-        <v>1062</v>
       </c>
       <c r="AD56" s="8"/>
       <c r="AE56" s="8" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="57" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A57" s="3" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>1064</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>1065</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="E57" s="8" t="s">
         <v>1066</v>
       </c>
-      <c r="E57" s="8" t="s">
+      <c r="F57" s="8" t="s">
         <v>1067</v>
       </c>
-      <c r="F57" s="8" t="s">
+      <c r="G57" s="8" t="s">
         <v>1068</v>
-      </c>
-      <c r="G57" s="8" t="s">
-        <v>1069</v>
       </c>
     </row>
     <row r="58" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A58" s="8" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B58" s="8" t="s">
         <v>1070</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="C58" s="8" t="s">
         <v>1071</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="59" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A59" s="8" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B59" s="8" t="s">
         <v>1073</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="C59" s="8" t="s">
         <v>1074</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>1075</v>
       </c>
     </row>
     <row r="60" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A60" s="8" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B60" s="8" t="s">
         <v>1076</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="C60" s="8" t="s">
         <v>1077</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>1078</v>
       </c>
       <c r="E60" s="4"/>
       <c r="F60" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="61" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A61" s="8" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B61" s="8" t="s">
         <v>1080</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="C61" s="8" t="s">
         <v>1081</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>1082</v>
       </c>
     </row>
     <row r="62" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A62" s="8" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B62" s="8" t="s">
         <v>1083</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="C62" s="8" t="s">
         <v>1084</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>1085</v>
       </c>
       <c r="E62" s="6"/>
       <c r="F62" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="63" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A63" s="8" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B63" s="8" t="s">
         <v>1087</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="C63" s="8" t="s">
         <v>1088</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>1089</v>
       </c>
     </row>
     <row r="64" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A64" s="8" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B64" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="C64" s="8" t="s">
         <v>1091</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>1092</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A65" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>1093</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="C65" s="3" t="s">
         <v>1094</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>1095</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A66" s="8" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B66" s="8" t="s">
         <v>1096</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="C66" s="8" t="s">
         <v>1097</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A67" s="8" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="B67" s="8"/>
       <c r="C67" s="8" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A68" s="8" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B68" s="8"/>
       <c r="C68" s="8" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A69" s="8" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B69" s="8" t="s">
         <v>1103</v>
       </c>
-      <c r="B69" s="8" t="s">
+      <c r="C69" s="8" t="s">
         <v>1104</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>1105</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A70" s="8" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="B70" s="8"/>
       <c r="C70" s="8" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A71" s="8" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B71" s="8" t="s">
         <v>1108</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="C71" s="8" t="s">
         <v>1109</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>1110</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A72" s="7" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B72" s="7" t="s">
         <v>1111</v>
       </c>
-      <c r="B72" s="7" t="s">
+      <c r="C72" s="7" t="s">
         <v>1112</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>1113</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A73" s="5" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B73" s="5" t="s">
         <v>1114</v>
       </c>
-      <c r="B73" s="5" t="s">
+      <c r="C73" s="5" t="s">
         <v>1115</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>1116</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A74" s="5" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B74" s="5" t="s">
         <v>1117</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="C74" s="5" t="s">
         <v>1118</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>1119</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A75" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>1120</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="C75" s="3" t="s">
         <v>1121</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>1122</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A76" s="8" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B76" s="8" t="s">
         <v>1123</v>
       </c>
-      <c r="B76" s="8" t="s">
+      <c r="C76" s="8" t="s">
         <v>1124</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>1125</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A77" s="8" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B77" s="8" t="s">
         <v>1126</v>
       </c>
-      <c r="B77" s="8" t="s">
+      <c r="C77" s="8" t="s">
         <v>1127</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>1128</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A78" s="8" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B78" s="8"/>
       <c r="C78" s="8" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A79" s="3" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>1131</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="C79" s="3" t="s">
         <v>1132</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>1133</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A80" s="8" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B80" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="B80" s="8" t="s">
+      <c r="C80" s="8" t="s">
         <v>1135</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>1136</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A81" s="5" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B81" s="5" t="s">
         <v>1137</v>
       </c>
-      <c r="B81" s="5" t="s">
+      <c r="C81" s="5" t="s">
         <v>1138</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>1139</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A82" s="5" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B82" s="5" t="s">
         <v>1140</v>
       </c>
-      <c r="B82" s="5" t="s">
+      <c r="C82" s="5" t="s">
         <v>1141</v>
-      </c>
-      <c r="C82" s="5" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A83" s="3" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>1143</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="C83" s="3" t="s">
         <v>1144</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>1145</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A84" s="3" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B84" s="3" t="s">
         <v>1146</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="C84" s="3" t="s">
         <v>1147</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>1148</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A85" s="8" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="B85" s="8"/>
       <c r="C85" s="8" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A86" s="5" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B86" s="5" t="s">
         <v>1151</v>
       </c>
-      <c r="B86" s="5" t="s">
+      <c r="C86" s="5" t="s">
         <v>1152</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>1153</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A87" s="8" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B87" s="8" t="s">
         <v>1154</v>
       </c>
-      <c r="B87" s="8" t="s">
+      <c r="C87" s="8" t="s">
         <v>1155</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A88" s="8" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B88" s="8"/>
       <c r="C88" s="8" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A89" s="5" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B89" s="5" t="s">
         <v>1159</v>
       </c>
-      <c r="B89" s="5" t="s">
+      <c r="C89" s="5" t="s">
         <v>1160</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>1161</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A90" s="5" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B90" s="5" t="s">
         <v>1162</v>
       </c>
-      <c r="B90" s="5" t="s">
+      <c r="C90" s="5" t="s">
         <v>1163</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>1164</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A91" s="5" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B91" s="5" t="s">
         <v>1165</v>
       </c>
-      <c r="B91" s="5" t="s">
+      <c r="C91" s="5" t="s">
         <v>1166</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>1167</v>
       </c>
     </row>
   </sheetData>
@@ -8931,937 +8940,937 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1168</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>1169</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1170</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>1176</v>
-      </c>
       <c r="C2" s="11" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>1177</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>1178</v>
-      </c>
       <c r="C3" s="11" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>1179</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>1180</v>
-      </c>
       <c r="C4" s="11" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>1181</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>1182</v>
-      </c>
       <c r="C5" s="11" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>1183</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>1184</v>
-      </c>
       <c r="C6" s="11" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>1185</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>1186</v>
-      </c>
       <c r="C7" s="11" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A8" s="8" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>1187</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>1188</v>
-      </c>
       <c r="C8" s="11" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A9" s="8" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>1189</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>1190</v>
-      </c>
       <c r="C9" s="11" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>1191</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>1192</v>
-      </c>
       <c r="C10" s="11" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>1193</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>1194</v>
-      </c>
       <c r="C11" s="11" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A12" s="8" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>1195</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>1196</v>
-      </c>
       <c r="C12" s="11" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>1197</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>1198</v>
-      </c>
       <c r="C13" s="11" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A14" s="8" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>1199</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>1200</v>
-      </c>
       <c r="C14" s="11" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A15" s="8" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>1201</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>1202</v>
-      </c>
       <c r="C15" s="11" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A16" s="8" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>1203</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>1204</v>
-      </c>
       <c r="C16" s="11" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A17" s="8" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>1205</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>1206</v>
-      </c>
       <c r="C17" s="11" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A18" s="8" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>1207</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>1208</v>
-      </c>
       <c r="C18" s="11" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A19" s="8" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B19" s="8" t="s">
         <v>1209</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>1210</v>
-      </c>
       <c r="C19" s="11" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A20" s="8" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>1211</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>1212</v>
-      </c>
       <c r="C20" s="11" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>1213</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>1214</v>
-      </c>
       <c r="C21" s="11" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A22" s="8" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B22" s="8" t="s">
         <v>1215</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>1216</v>
-      </c>
       <c r="C22" s="11" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A23" s="8" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B23" s="8" t="s">
         <v>1217</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>1218</v>
-      </c>
       <c r="C23" s="11" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A24" s="8" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B24" s="8" t="s">
         <v>1219</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>1220</v>
-      </c>
       <c r="C24" s="11" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A25" s="8" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B25" s="8" t="s">
         <v>1221</v>
       </c>
-      <c r="B25" s="8" t="s">
-        <v>1222</v>
-      </c>
       <c r="C25" s="11" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A26" s="8" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B26" s="8" t="s">
         <v>1223</v>
       </c>
-      <c r="B26" s="8" t="s">
-        <v>1224</v>
-      </c>
       <c r="C26" s="11" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A27" s="8" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B27" s="8" t="s">
         <v>1225</v>
       </c>
-      <c r="B27" s="8" t="s">
-        <v>1226</v>
-      </c>
       <c r="C27" s="11" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A28" s="8" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B28" s="8" t="s">
         <v>1227</v>
       </c>
-      <c r="B28" s="8" t="s">
-        <v>1228</v>
-      </c>
       <c r="C28" s="11" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A29" s="8" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B29" s="8" t="s">
         <v>1229</v>
       </c>
-      <c r="B29" s="8" t="s">
-        <v>1230</v>
-      </c>
       <c r="C29" s="11" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A30" s="8" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B30" s="8" t="s">
         <v>1231</v>
       </c>
-      <c r="B30" s="8" t="s">
-        <v>1232</v>
-      </c>
       <c r="C30" s="11" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A31" s="8" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B31" s="8" t="s">
         <v>1233</v>
       </c>
-      <c r="B31" s="8" t="s">
-        <v>1234</v>
-      </c>
       <c r="C31" s="11" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A32" s="8" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B32" s="8" t="s">
         <v>1235</v>
       </c>
-      <c r="B32" s="8" t="s">
-        <v>1236</v>
-      </c>
       <c r="C32" s="11" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A33" s="8" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B33" s="8" t="s">
         <v>1237</v>
       </c>
-      <c r="B33" s="8" t="s">
-        <v>1238</v>
-      </c>
       <c r="C33" s="11" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A34" s="8" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B34" s="8" t="s">
         <v>1239</v>
       </c>
-      <c r="B34" s="8" t="s">
-        <v>1240</v>
-      </c>
       <c r="C34" s="11" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A35" s="8" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B35" s="8" t="s">
         <v>1241</v>
       </c>
-      <c r="B35" s="8" t="s">
-        <v>1242</v>
-      </c>
       <c r="C35" s="11" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="8" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B36" s="8" t="s">
         <v>1243</v>
       </c>
-      <c r="B36" s="8" t="s">
-        <v>1244</v>
-      </c>
       <c r="C36" s="11" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A37" s="8" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B37" s="8" t="s">
         <v>1245</v>
       </c>
-      <c r="B37" s="8" t="s">
-        <v>1246</v>
-      </c>
       <c r="C37" s="11" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A38" s="8" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B38" s="8" t="s">
         <v>1247</v>
       </c>
-      <c r="B38" s="8" t="s">
-        <v>1248</v>
-      </c>
       <c r="C38" s="11" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A39" s="8" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B39" s="8" t="s">
         <v>1249</v>
       </c>
-      <c r="B39" s="8" t="s">
-        <v>1250</v>
-      </c>
       <c r="C39" s="11" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A40" s="8" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B40" s="8" t="s">
         <v>1251</v>
       </c>
-      <c r="B40" s="8" t="s">
-        <v>1252</v>
-      </c>
       <c r="C40" s="11" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A41" s="8" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B41" s="8" t="s">
         <v>1253</v>
       </c>
-      <c r="B41" s="8" t="s">
-        <v>1254</v>
-      </c>
       <c r="C41" s="11" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A42" s="8" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B42" s="8" t="s">
         <v>1255</v>
       </c>
-      <c r="B42" s="8" t="s">
-        <v>1256</v>
-      </c>
       <c r="C42" s="11" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A43" s="8" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B43" s="8" t="s">
         <v>1257</v>
       </c>
-      <c r="B43" s="8" t="s">
-        <v>1258</v>
-      </c>
       <c r="C43" s="11" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A44" s="8" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B44" s="8" t="s">
         <v>1259</v>
       </c>
-      <c r="B44" s="8" t="s">
-        <v>1260</v>
-      </c>
       <c r="C44" s="11" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A45" s="8" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B45" s="8" t="s">
         <v>1261</v>
       </c>
-      <c r="B45" s="8" t="s">
-        <v>1262</v>
-      </c>
       <c r="C45" s="11" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A46" s="8" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B46" s="8" t="s">
         <v>1263</v>
       </c>
-      <c r="B46" s="8" t="s">
-        <v>1264</v>
-      </c>
       <c r="C46" s="11" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A47" s="8" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B47" s="8" t="s">
         <v>1265</v>
       </c>
-      <c r="B47" s="8" t="s">
-        <v>1266</v>
-      </c>
       <c r="C47" s="11" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A48" s="8" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B48" s="8" t="s">
         <v>1267</v>
       </c>
-      <c r="B48" s="8" t="s">
-        <v>1268</v>
-      </c>
       <c r="C48" s="11" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A49" s="8" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B49" s="8" t="s">
         <v>1269</v>
       </c>
-      <c r="B49" s="8" t="s">
-        <v>1270</v>
-      </c>
       <c r="C49" s="11" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A50" s="8" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B50" s="8" t="s">
         <v>1271</v>
       </c>
-      <c r="B50" s="8" t="s">
-        <v>1272</v>
-      </c>
       <c r="C50" s="11" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A51" s="8" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B51" s="8" t="s">
         <v>1273</v>
       </c>
-      <c r="B51" s="8" t="s">
-        <v>1274</v>
-      </c>
       <c r="C51" s="11" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A52" s="8" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B52" s="8" t="s">
         <v>1275</v>
       </c>
-      <c r="B52" s="8" t="s">
-        <v>1276</v>
-      </c>
       <c r="C52" s="11" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A53" s="8" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B53" s="8" t="s">
         <v>1277</v>
       </c>
-      <c r="B53" s="8" t="s">
-        <v>1278</v>
-      </c>
       <c r="C53" s="11" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A54" s="8" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B54" s="8" t="s">
         <v>1279</v>
       </c>
-      <c r="B54" s="8" t="s">
-        <v>1280</v>
-      </c>
       <c r="C54" s="11" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A55" s="8" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B55" s="8" t="s">
         <v>1281</v>
       </c>
-      <c r="B55" s="8" t="s">
-        <v>1282</v>
-      </c>
       <c r="C55" s="11" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A56" s="8" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B56" s="8" t="s">
         <v>1283</v>
       </c>
-      <c r="B56" s="8" t="s">
-        <v>1284</v>
-      </c>
       <c r="C56" s="11" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A57" s="8" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B57" s="8" t="s">
         <v>1171</v>
       </c>
-      <c r="B57" s="8" t="s">
-        <v>1172</v>
-      </c>
       <c r="C57" s="11" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A58" s="8" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B58" s="8" t="s">
         <v>1285</v>
       </c>
-      <c r="B58" s="8" t="s">
-        <v>1286</v>
-      </c>
       <c r="C58" s="11" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A59" s="8" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B59" s="8" t="s">
         <v>1287</v>
       </c>
-      <c r="B59" s="8" t="s">
-        <v>1288</v>
-      </c>
       <c r="C59" s="11" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A60" s="8" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B60" s="8" t="s">
         <v>1289</v>
       </c>
-      <c r="B60" s="8" t="s">
-        <v>1290</v>
-      </c>
       <c r="C60" s="11" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A61" s="8" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B61" s="8" t="s">
         <v>1291</v>
       </c>
-      <c r="B61" s="8" t="s">
-        <v>1292</v>
-      </c>
       <c r="C61" s="11" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A62" s="8" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B62" s="8" t="s">
         <v>1293</v>
       </c>
-      <c r="B62" s="8" t="s">
-        <v>1294</v>
-      </c>
       <c r="C62" s="11" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A63" s="8" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B63" s="8" t="s">
         <v>1295</v>
       </c>
-      <c r="B63" s="8" t="s">
-        <v>1296</v>
-      </c>
       <c r="C63" s="11" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A64" s="8" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B64" s="8" t="s">
         <v>1297</v>
       </c>
-      <c r="B64" s="8" t="s">
-        <v>1298</v>
-      </c>
       <c r="C64" s="11" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A65" s="8" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B65" s="8" t="s">
         <v>1299</v>
       </c>
-      <c r="B65" s="8" t="s">
-        <v>1300</v>
-      </c>
       <c r="C65" s="11" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A66" s="8" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B66" s="8" t="s">
         <v>1301</v>
       </c>
-      <c r="B66" s="8" t="s">
-        <v>1302</v>
-      </c>
       <c r="C66" s="11" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A67" s="8" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B67" s="8" t="s">
         <v>1303</v>
       </c>
-      <c r="B67" s="8" t="s">
-        <v>1304</v>
-      </c>
       <c r="C67" s="11" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A68" s="8" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B68" s="8" t="s">
         <v>1305</v>
       </c>
-      <c r="B68" s="8" t="s">
-        <v>1306</v>
-      </c>
       <c r="C68" s="11" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A69" s="8" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B69" s="8" t="s">
         <v>1307</v>
       </c>
-      <c r="B69" s="8" t="s">
-        <v>1308</v>
-      </c>
       <c r="C69" s="11" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A70" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B70" s="8" t="s">
         <v>1309</v>
       </c>
-      <c r="B70" s="8" t="s">
-        <v>1310</v>
-      </c>
       <c r="C70" s="11" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A71" s="8" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B71" s="8" t="s">
         <v>1311</v>
       </c>
-      <c r="B71" s="8" t="s">
-        <v>1312</v>
-      </c>
       <c r="C71" s="11" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A72" s="8" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B72" s="8" t="s">
         <v>1313</v>
       </c>
-      <c r="B72" s="8" t="s">
-        <v>1314</v>
-      </c>
       <c r="C72" s="11" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A73" s="8" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B73" s="8" t="s">
         <v>1173</v>
       </c>
-      <c r="B73" s="8" t="s">
-        <v>1174</v>
-      </c>
       <c r="C73" s="11" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A74" s="8" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B74" s="8" t="s">
         <v>1315</v>
       </c>
-      <c r="B74" s="8" t="s">
-        <v>1316</v>
-      </c>
       <c r="C74" s="11" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A75" s="8" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B75" s="8" t="s">
         <v>1317</v>
       </c>
-      <c r="B75" s="8" t="s">
-        <v>1318</v>
-      </c>
       <c r="C75" s="11" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A76" s="8" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B76" s="8" t="s">
         <v>1319</v>
       </c>
-      <c r="B76" s="8" t="s">
-        <v>1320</v>
-      </c>
       <c r="C76" s="11" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A77" s="8" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B77" s="8" t="s">
         <v>1321</v>
       </c>
-      <c r="B77" s="8" t="s">
-        <v>1322</v>
-      </c>
       <c r="C77" s="11" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A78" s="8" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B78" s="8" t="s">
         <v>1323</v>
       </c>
-      <c r="B78" s="8" t="s">
-        <v>1324</v>
-      </c>
       <c r="C78" s="11" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A79" s="8" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B79" s="8" t="s">
         <v>1325</v>
       </c>
-      <c r="B79" s="8" t="s">
-        <v>1326</v>
-      </c>
       <c r="C79" s="11" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A80" s="8" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B80" s="8" t="s">
         <v>1327</v>
       </c>
-      <c r="B80" s="8" t="s">
-        <v>1328</v>
-      </c>
       <c r="C80" s="11" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A81" s="8" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B81" s="8" t="s">
         <v>1329</v>
       </c>
-      <c r="B81" s="8" t="s">
-        <v>1330</v>
-      </c>
       <c r="C81" s="11" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A82" s="8" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B82" s="8" t="s">
         <v>1331</v>
       </c>
-      <c r="B82" s="8" t="s">
-        <v>1332</v>
-      </c>
       <c r="C82" s="11" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A83" s="8" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A84" s="8" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B84" s="8" t="s">
         <v>1334</v>
       </c>
-      <c r="B84" s="8" t="s">
-        <v>1335</v>
-      </c>
       <c r="C84" s="11" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A85" s="8" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B85" s="8" t="s">
         <v>1336</v>
       </c>
-      <c r="B85" s="8" t="s">
-        <v>1337</v>
-      </c>
       <c r="C85" s="11" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
     </row>
   </sheetData>
@@ -9965,46 +9974,46 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1169</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1170</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>1339</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="C2" s="10" t="s">
         <v>1340</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>1341</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>1342</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="10" t="s">
         <v>1343</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>1344</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>1345</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="10" t="s">
         <v>1346</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>1347</v>
       </c>
     </row>
   </sheetData>

--- a/key検討用/ppxkey.xlsx
+++ b/key検討用/ppxkey.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gocho\Desktop\ppx_cust20251217(Wed)\ppx_cust\key検討用\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gocho\AppData\Local\Temp\Rar$DIa8044.31842.rartemp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37E8A8E2-780D-40C9-9D33-219A0242D5ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA5118B-96F0-49AA-98FA-301FF44B6B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="5355" windowWidth="24240" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="キー割り当て" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="1430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1463" uniqueCount="1429">
   <si>
     <t>キー</t>
   </si>
@@ -1690,9 +1690,6 @@
   </si>
   <si>
     <t>[Alt+L]</t>
-  </si>
-  <si>
-    <t>パス移動</t>
   </si>
   <si>
     <t>%k"&amp;L"</t>
@@ -5043,7 +5040,7 @@
         <v>26</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>28</v>
@@ -6816,2109 +6813,2107 @@
       <c r="M30" s="8" t="s">
         <v>555</v>
       </c>
-      <c r="N30" s="8" t="s">
+      <c r="N30" s="8"/>
+      <c r="O30" s="8" t="s">
         <v>556</v>
       </c>
-      <c r="O30" s="8" t="s">
+      <c r="Q30" s="8" t="s">
         <v>557</v>
       </c>
-      <c r="Q30" s="8" t="s">
+      <c r="R30" s="8" t="s">
         <v>558</v>
       </c>
-      <c r="R30" s="8" t="s">
+      <c r="S30" s="8" t="s">
         <v>559</v>
       </c>
-      <c r="S30" s="8" t="s">
+      <c r="U30" s="8" t="s">
         <v>560</v>
-      </c>
-      <c r="U30" s="8" t="s">
-        <v>561</v>
       </c>
       <c r="V30" s="8"/>
       <c r="W30" s="8" t="s">
+        <v>561</v>
+      </c>
+      <c r="Y30" s="8" t="s">
         <v>562</v>
-      </c>
-      <c r="Y30" s="8" t="s">
-        <v>563</v>
       </c>
       <c r="Z30" s="8"/>
       <c r="AA30" s="8" t="s">
+        <v>563</v>
+      </c>
+      <c r="AC30" s="8" t="s">
         <v>564</v>
-      </c>
-      <c r="AC30" s="8" t="s">
-        <v>565</v>
       </c>
       <c r="AD30" s="8"/>
       <c r="AE30" s="8" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A31" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="G31" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="I31" s="8" t="s">
         <v>572</v>
       </c>
-      <c r="I31" s="8" t="s">
+      <c r="J31" s="8" t="s">
         <v>573</v>
       </c>
-      <c r="J31" s="8" t="s">
+      <c r="K31" s="8" t="s">
         <v>574</v>
       </c>
-      <c r="K31" s="8" t="s">
+      <c r="M31" s="8" t="s">
         <v>575</v>
       </c>
-      <c r="M31" s="8" t="s">
+      <c r="N31" s="8" t="s">
         <v>576</v>
       </c>
-      <c r="N31" s="8" t="s">
+      <c r="O31" s="8" t="s">
         <v>577</v>
       </c>
-      <c r="O31" s="8" t="s">
+      <c r="Q31" s="8" t="s">
         <v>578</v>
       </c>
-      <c r="Q31" s="8" t="s">
+      <c r="R31" s="8" t="s">
         <v>579</v>
       </c>
-      <c r="R31" s="8" t="s">
+      <c r="S31" s="8" t="s">
         <v>580</v>
       </c>
-      <c r="S31" s="8" t="s">
+      <c r="U31" s="8" t="s">
         <v>581</v>
-      </c>
-      <c r="U31" s="8" t="s">
-        <v>582</v>
       </c>
       <c r="V31" s="8"/>
       <c r="W31" s="8" t="s">
+        <v>582</v>
+      </c>
+      <c r="Y31" s="8" t="s">
         <v>583</v>
-      </c>
-      <c r="Y31" s="8" t="s">
-        <v>584</v>
       </c>
       <c r="Z31" s="8"/>
       <c r="AA31" s="8" t="s">
+        <v>584</v>
+      </c>
+      <c r="AC31" s="8" t="s">
         <v>585</v>
       </c>
-      <c r="AC31" s="8" t="s">
+      <c r="AD31" s="8" t="s">
         <v>586</v>
       </c>
-      <c r="AD31" s="8" t="s">
+      <c r="AE31" s="8" t="s">
         <v>587</v>
-      </c>
-      <c r="AE31" s="8" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A32" s="8" t="s">
+        <v>588</v>
+      </c>
+      <c r="B32" s="8" t="s">
         <v>589</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="C32" s="8" t="s">
         <v>590</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="E32" s="8" t="s">
         <v>591</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="F32" s="8" t="s">
         <v>592</v>
       </c>
-      <c r="F32" s="8" t="s">
+      <c r="G32" s="8" t="s">
         <v>593</v>
       </c>
-      <c r="G32" s="8" t="s">
+      <c r="I32" s="8" t="s">
         <v>594</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>595</v>
       </c>
       <c r="J32" s="8" t="s">
         <v>27</v>
       </c>
       <c r="K32" s="8" t="s">
+        <v>595</v>
+      </c>
+      <c r="M32" s="8" t="s">
         <v>596</v>
-      </c>
-      <c r="M32" s="8" t="s">
-        <v>597</v>
       </c>
       <c r="N32" s="8"/>
       <c r="O32" s="8" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q32" s="8" t="s">
         <v>598</v>
-      </c>
-      <c r="Q32" s="8" t="s">
-        <v>599</v>
       </c>
       <c r="R32" s="8"/>
       <c r="S32" s="8" t="s">
+        <v>599</v>
+      </c>
+      <c r="U32" s="8" t="s">
         <v>600</v>
-      </c>
-      <c r="U32" s="8" t="s">
-        <v>601</v>
       </c>
       <c r="V32" s="8"/>
       <c r="W32" s="8" t="s">
+        <v>601</v>
+      </c>
+      <c r="Y32" s="8" t="s">
         <v>602</v>
-      </c>
-      <c r="Y32" s="8" t="s">
-        <v>603</v>
       </c>
       <c r="Z32" s="8"/>
       <c r="AA32" s="8" t="s">
+        <v>603</v>
+      </c>
+      <c r="AC32" s="8" t="s">
         <v>604</v>
-      </c>
-      <c r="AC32" s="8" t="s">
-        <v>605</v>
       </c>
       <c r="AD32" s="8"/>
       <c r="AE32" s="8" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A33" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>607</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="C33" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="E33" s="8" t="s">
         <v>609</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="F33" s="8" t="s">
         <v>610</v>
       </c>
-      <c r="F33" s="8" t="s">
+      <c r="G33" s="8" t="s">
         <v>611</v>
       </c>
-      <c r="G33" s="8" t="s">
+      <c r="I33" s="8" t="s">
         <v>612</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>613</v>
       </c>
       <c r="J33" s="8"/>
       <c r="K33" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="M33" s="8" t="s">
         <v>614</v>
       </c>
-      <c r="M33" s="8" t="s">
+      <c r="N33" s="8" t="s">
         <v>615</v>
       </c>
-      <c r="N33" s="8" t="s">
+      <c r="O33" s="8" t="s">
         <v>616</v>
       </c>
-      <c r="O33" s="8" t="s">
+      <c r="Q33" s="8" t="s">
         <v>617</v>
-      </c>
-      <c r="Q33" s="8" t="s">
-        <v>618</v>
       </c>
       <c r="R33" s="8"/>
       <c r="S33" s="8" t="s">
+        <v>618</v>
+      </c>
+      <c r="U33" s="8" t="s">
         <v>619</v>
-      </c>
-      <c r="U33" s="8" t="s">
-        <v>620</v>
       </c>
       <c r="V33" s="8"/>
       <c r="W33" s="8" t="s">
+        <v>620</v>
+      </c>
+      <c r="Y33" s="8" t="s">
         <v>621</v>
-      </c>
-      <c r="Y33" s="8" t="s">
-        <v>622</v>
       </c>
       <c r="Z33" s="8"/>
       <c r="AA33" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="AC33" s="8" t="s">
         <v>623</v>
-      </c>
-      <c r="AC33" s="8" t="s">
-        <v>624</v>
       </c>
       <c r="AD33" s="8"/>
       <c r="AE33" s="8" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A34" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>627</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="E34" s="8" t="s">
         <v>628</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="F34" s="8" t="s">
         <v>629</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="G34" s="8" t="s">
         <v>630</v>
       </c>
-      <c r="G34" s="8" t="s">
+      <c r="I34" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="I34" s="8" t="s">
+      <c r="J34" s="8" t="s">
         <v>632</v>
       </c>
-      <c r="J34" s="8" t="s">
+      <c r="K34" s="8" t="s">
         <v>633</v>
       </c>
-      <c r="K34" s="8" t="s">
+      <c r="M34" s="8" t="s">
         <v>634</v>
-      </c>
-      <c r="M34" s="8" t="s">
-        <v>635</v>
       </c>
       <c r="N34" s="8"/>
       <c r="O34" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="Q34" s="8" t="s">
         <v>636</v>
-      </c>
-      <c r="Q34" s="8" t="s">
-        <v>637</v>
       </c>
       <c r="R34" s="8"/>
       <c r="S34" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="U34" s="8" t="s">
         <v>638</v>
-      </c>
-      <c r="U34" s="8" t="s">
-        <v>639</v>
       </c>
       <c r="V34" s="8"/>
       <c r="W34" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="Y34" s="8" t="s">
         <v>640</v>
-      </c>
-      <c r="Y34" s="8" t="s">
-        <v>641</v>
       </c>
       <c r="Z34" s="8"/>
       <c r="AA34" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="AC34" s="8" t="s">
         <v>642</v>
-      </c>
-      <c r="AC34" s="8" t="s">
-        <v>643</v>
       </c>
       <c r="AD34" s="8"/>
       <c r="AE34" s="8" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A35" s="8" t="s">
+        <v>644</v>
+      </c>
+      <c r="B35" s="8" t="s">
         <v>645</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="C35" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="E35" s="8" t="s">
         <v>647</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="F35" s="8" t="s">
         <v>648</v>
       </c>
-      <c r="F35" s="8" t="s">
+      <c r="G35" s="8" t="s">
         <v>649</v>
       </c>
-      <c r="G35" s="8" t="s">
+      <c r="I35" s="8" t="s">
         <v>650</v>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>651</v>
       </c>
       <c r="J35" s="8"/>
       <c r="K35" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="M35" s="3" t="s">
         <v>652</v>
       </c>
-      <c r="M35" s="3" t="s">
+      <c r="N35" s="3" t="s">
         <v>653</v>
       </c>
-      <c r="N35" s="3" t="s">
+      <c r="O35" s="3" t="s">
         <v>654</v>
       </c>
-      <c r="O35" s="3" t="s">
+      <c r="Q35" s="8" t="s">
         <v>655</v>
       </c>
-      <c r="Q35" s="8" t="s">
+      <c r="R35" s="8" t="s">
         <v>656</v>
       </c>
-      <c r="R35" s="8" t="s">
+      <c r="S35" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="S35" s="8" t="s">
+      <c r="U35" s="8" t="s">
         <v>658</v>
-      </c>
-      <c r="U35" s="8" t="s">
-        <v>659</v>
       </c>
       <c r="V35" s="8"/>
       <c r="W35" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="Y35" s="8" t="s">
         <v>660</v>
-      </c>
-      <c r="Y35" s="8" t="s">
-        <v>661</v>
       </c>
       <c r="Z35" s="8"/>
       <c r="AA35" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="AC35" s="8" t="s">
         <v>662</v>
-      </c>
-      <c r="AC35" s="8" t="s">
-        <v>663</v>
       </c>
       <c r="AD35" s="8"/>
       <c r="AE35" s="8" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A36" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>665</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>666</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="E36" s="5" t="s">
         <v>667</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="F36" s="5" t="s">
         <v>668</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="G36" s="5" t="s">
         <v>669</v>
       </c>
-      <c r="G36" s="5" t="s">
+      <c r="I36" s="8" t="s">
         <v>670</v>
-      </c>
-      <c r="I36" s="8" t="s">
-        <v>671</v>
       </c>
       <c r="J36" s="8"/>
       <c r="K36" s="8" t="s">
+        <v>671</v>
+      </c>
+      <c r="M36" s="8" t="s">
         <v>672</v>
       </c>
-      <c r="M36" s="8" t="s">
+      <c r="N36" s="8" t="s">
         <v>673</v>
       </c>
-      <c r="N36" s="8" t="s">
+      <c r="O36" s="8" t="s">
         <v>674</v>
       </c>
-      <c r="O36" s="8" t="s">
+      <c r="Q36" s="8" t="s">
         <v>675</v>
-      </c>
-      <c r="Q36" s="8" t="s">
-        <v>676</v>
       </c>
       <c r="R36" s="8"/>
       <c r="S36" s="8" t="s">
+        <v>676</v>
+      </c>
+      <c r="U36" s="8" t="s">
         <v>677</v>
-      </c>
-      <c r="U36" s="8" t="s">
-        <v>678</v>
       </c>
       <c r="V36" s="8"/>
       <c r="W36" s="8" t="s">
+        <v>678</v>
+      </c>
+      <c r="Y36" s="8" t="s">
         <v>679</v>
-      </c>
-      <c r="Y36" s="8" t="s">
-        <v>680</v>
       </c>
       <c r="Z36" s="8"/>
       <c r="AA36" s="8" t="s">
+        <v>680</v>
+      </c>
+      <c r="AC36" s="8" t="s">
         <v>681</v>
-      </c>
-      <c r="AC36" s="8" t="s">
-        <v>682</v>
       </c>
       <c r="AD36" s="8"/>
       <c r="AE36" s="8" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A37" s="7" t="s">
+        <v>683</v>
+      </c>
+      <c r="B37" s="7" t="s">
         <v>684</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="C37" s="7" t="s">
         <v>685</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="E37" s="8" t="s">
         <v>686</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="F37" s="8" t="s">
         <v>687</v>
       </c>
-      <c r="F37" s="8" t="s">
+      <c r="G37" s="8" t="s">
         <v>688</v>
       </c>
-      <c r="G37" s="8" t="s">
+      <c r="I37" s="8" t="s">
         <v>689</v>
-      </c>
-      <c r="I37" s="8" t="s">
-        <v>690</v>
       </c>
       <c r="J37" s="8"/>
       <c r="K37" s="8" t="s">
+        <v>690</v>
+      </c>
+      <c r="M37" s="8" t="s">
         <v>691</v>
-      </c>
-      <c r="M37" s="8" t="s">
-        <v>692</v>
       </c>
       <c r="N37" s="8"/>
       <c r="O37" s="8" t="s">
+        <v>692</v>
+      </c>
+      <c r="Q37" s="8" t="s">
         <v>693</v>
-      </c>
-      <c r="Q37" s="8" t="s">
-        <v>694</v>
       </c>
       <c r="R37" s="8"/>
       <c r="S37" s="8" t="s">
+        <v>694</v>
+      </c>
+      <c r="U37" s="8" t="s">
         <v>695</v>
-      </c>
-      <c r="U37" s="8" t="s">
-        <v>696</v>
       </c>
       <c r="V37" s="8"/>
       <c r="W37" s="8" t="s">
+        <v>696</v>
+      </c>
+      <c r="Y37" s="5" t="s">
         <v>697</v>
       </c>
-      <c r="Y37" s="5" t="s">
+      <c r="Z37" s="5" t="s">
         <v>698</v>
       </c>
-      <c r="Z37" s="5" t="s">
+      <c r="AA37" s="5" t="s">
         <v>699</v>
       </c>
-      <c r="AA37" s="5" t="s">
+      <c r="AC37" s="8" t="s">
         <v>700</v>
-      </c>
-      <c r="AC37" s="8" t="s">
-        <v>701</v>
       </c>
       <c r="AD37" s="8"/>
       <c r="AE37" s="8" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A38" s="8" t="s">
+        <v>702</v>
+      </c>
+      <c r="B38" s="8" t="s">
         <v>703</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="C38" s="8" t="s">
         <v>704</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="E38" s="8" t="s">
         <v>705</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="F38" s="8" t="s">
         <v>706</v>
       </c>
-      <c r="F38" s="8" t="s">
+      <c r="G38" s="8" t="s">
         <v>707</v>
       </c>
-      <c r="G38" s="8" t="s">
+      <c r="I38" s="8" t="s">
         <v>708</v>
       </c>
-      <c r="I38" s="8" t="s">
+      <c r="J38" s="8" t="s">
         <v>709</v>
       </c>
-      <c r="J38" s="8" t="s">
+      <c r="K38" s="8" t="s">
         <v>710</v>
       </c>
-      <c r="K38" s="8" t="s">
+      <c r="M38" s="8" t="s">
         <v>711</v>
       </c>
-      <c r="M38" s="8" t="s">
+      <c r="N38" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="N38" s="8" t="s">
+      <c r="O38" s="8" t="s">
         <v>713</v>
       </c>
-      <c r="O38" s="8" t="s">
+      <c r="Q38" s="8" t="s">
         <v>714</v>
-      </c>
-      <c r="Q38" s="8" t="s">
-        <v>715</v>
       </c>
       <c r="R38" s="8"/>
       <c r="S38" s="8" t="s">
+        <v>715</v>
+      </c>
+      <c r="U38" s="8" t="s">
         <v>716</v>
-      </c>
-      <c r="U38" s="8" t="s">
-        <v>717</v>
       </c>
       <c r="V38" s="8"/>
       <c r="W38" s="8" t="s">
+        <v>717</v>
+      </c>
+      <c r="Y38" s="8" t="s">
         <v>718</v>
-      </c>
-      <c r="Y38" s="8" t="s">
-        <v>719</v>
       </c>
       <c r="Z38" s="8"/>
       <c r="AA38" s="8" t="s">
+        <v>719</v>
+      </c>
+      <c r="AC38" s="8" t="s">
         <v>720</v>
-      </c>
-      <c r="AC38" s="8" t="s">
-        <v>721</v>
       </c>
       <c r="AD38" s="8"/>
       <c r="AE38" s="8" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A39" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>723</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>724</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="E39" s="5" t="s">
         <v>725</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="F39" s="5" t="s">
         <v>726</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="G39" s="5" t="s">
         <v>727</v>
       </c>
-      <c r="G39" s="5" t="s">
+      <c r="I39" s="8" t="s">
         <v>728</v>
-      </c>
-      <c r="I39" s="8" t="s">
-        <v>729</v>
       </c>
       <c r="J39" s="8"/>
       <c r="K39" s="8" t="s">
+        <v>729</v>
+      </c>
+      <c r="M39" s="8" t="s">
         <v>730</v>
-      </c>
-      <c r="M39" s="8" t="s">
-        <v>731</v>
       </c>
       <c r="N39" s="8"/>
       <c r="O39" s="8" t="s">
+        <v>731</v>
+      </c>
+      <c r="Q39" s="8" t="s">
         <v>732</v>
-      </c>
-      <c r="Q39" s="8" t="s">
-        <v>733</v>
       </c>
       <c r="R39" s="8"/>
       <c r="S39" s="8" t="s">
+        <v>733</v>
+      </c>
+      <c r="U39" s="8" t="s">
         <v>734</v>
-      </c>
-      <c r="U39" s="8" t="s">
-        <v>735</v>
       </c>
       <c r="V39" s="8"/>
       <c r="W39" s="8" t="s">
+        <v>735</v>
+      </c>
+      <c r="Y39" s="8" t="s">
         <v>736</v>
-      </c>
-      <c r="Y39" s="8" t="s">
-        <v>737</v>
       </c>
       <c r="Z39" s="8"/>
       <c r="AA39" s="8" t="s">
+        <v>737</v>
+      </c>
+      <c r="AC39" s="8" t="s">
         <v>738</v>
-      </c>
-      <c r="AC39" s="8" t="s">
-        <v>739</v>
       </c>
       <c r="AD39" s="8"/>
       <c r="AE39" s="8" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A40" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>741</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>742</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="E40" s="8" t="s">
         <v>743</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="F40" s="8" t="s">
         <v>744</v>
       </c>
-      <c r="F40" s="8" t="s">
+      <c r="G40" s="8" t="s">
         <v>745</v>
       </c>
-      <c r="G40" s="8" t="s">
+      <c r="I40" s="3" t="s">
         <v>746</v>
       </c>
-      <c r="I40" s="3" t="s">
+      <c r="J40" s="3" t="s">
         <v>747</v>
       </c>
-      <c r="J40" s="3" t="s">
+      <c r="K40" s="3" t="s">
         <v>748</v>
       </c>
-      <c r="K40" s="3" t="s">
+      <c r="M40" s="8" t="s">
         <v>749</v>
       </c>
-      <c r="M40" s="8" t="s">
+      <c r="N40" s="8" t="s">
         <v>750</v>
       </c>
-      <c r="N40" s="8" t="s">
+      <c r="O40" s="8" t="s">
         <v>751</v>
       </c>
-      <c r="O40" s="8" t="s">
+      <c r="Q40" s="8" t="s">
         <v>752</v>
       </c>
-      <c r="Q40" s="8" t="s">
+      <c r="R40" s="8" t="s">
         <v>753</v>
       </c>
-      <c r="R40" s="8" t="s">
+      <c r="S40" s="8" t="s">
         <v>754</v>
       </c>
-      <c r="S40" s="8" t="s">
+      <c r="U40" s="8" t="s">
         <v>755</v>
-      </c>
-      <c r="U40" s="8" t="s">
-        <v>756</v>
       </c>
       <c r="V40" s="8"/>
       <c r="W40" s="8" t="s">
+        <v>756</v>
+      </c>
+      <c r="Y40" s="8" t="s">
         <v>757</v>
-      </c>
-      <c r="Y40" s="8" t="s">
-        <v>758</v>
       </c>
       <c r="Z40" s="8"/>
       <c r="AA40" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="AC40" s="8" t="s">
         <v>759</v>
-      </c>
-      <c r="AC40" s="8" t="s">
-        <v>760</v>
       </c>
       <c r="AD40" s="8"/>
       <c r="AE40" s="8" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A41" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>762</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>763</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="E41" s="8" t="s">
         <v>764</v>
       </c>
-      <c r="E41" s="8" t="s">
+      <c r="F41" s="8" t="s">
         <v>765</v>
       </c>
-      <c r="F41" s="8" t="s">
+      <c r="G41" s="8" t="s">
         <v>766</v>
       </c>
-      <c r="G41" s="8" t="s">
+      <c r="I41" s="8" t="s">
         <v>767</v>
       </c>
-      <c r="I41" s="8" t="s">
+      <c r="J41" s="8" t="s">
         <v>768</v>
       </c>
-      <c r="J41" s="8" t="s">
+      <c r="K41" s="8" t="s">
         <v>769</v>
       </c>
-      <c r="K41" s="8" t="s">
+      <c r="M41" s="8" t="s">
         <v>770</v>
       </c>
-      <c r="M41" s="8" t="s">
+      <c r="N41" s="8" t="s">
         <v>771</v>
       </c>
-      <c r="N41" s="8" t="s">
+      <c r="O41" s="8" t="s">
         <v>772</v>
       </c>
-      <c r="O41" s="8" t="s">
+      <c r="Q41" s="8" t="s">
         <v>773</v>
       </c>
-      <c r="Q41" s="8" t="s">
+      <c r="R41" s="8" t="s">
         <v>774</v>
       </c>
-      <c r="R41" s="8" t="s">
+      <c r="S41" s="8" t="s">
         <v>775</v>
       </c>
-      <c r="S41" s="8" t="s">
+      <c r="U41" s="8" t="s">
         <v>776</v>
-      </c>
-      <c r="U41" s="8" t="s">
-        <v>777</v>
       </c>
       <c r="V41" s="8"/>
       <c r="W41" s="8" t="s">
+        <v>777</v>
+      </c>
+      <c r="Y41" s="8" t="s">
         <v>778</v>
-      </c>
-      <c r="Y41" s="8" t="s">
-        <v>779</v>
       </c>
       <c r="Z41" s="8"/>
       <c r="AA41" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="AC41" s="8" t="s">
         <v>780</v>
-      </c>
-      <c r="AC41" s="8" t="s">
-        <v>781</v>
       </c>
       <c r="AD41" s="8"/>
       <c r="AE41" s="8" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A42" s="8" t="s">
+        <v>782</v>
+      </c>
+      <c r="B42" s="8" t="s">
         <v>783</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="C42" s="8" t="s">
         <v>784</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="E42" s="3" t="s">
         <v>785</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="F42" s="3" t="s">
         <v>786</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="G42" s="3" t="s">
         <v>787</v>
       </c>
-      <c r="G42" s="3" t="s">
+      <c r="I42" s="3" t="s">
         <v>788</v>
       </c>
-      <c r="I42" s="3" t="s">
+      <c r="J42" s="3" t="s">
         <v>789</v>
       </c>
-      <c r="J42" s="3" t="s">
+      <c r="K42" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="K42" s="3" t="s">
+      <c r="M42" s="8" t="s">
         <v>791</v>
-      </c>
-      <c r="M42" s="8" t="s">
-        <v>792</v>
       </c>
       <c r="N42" s="8"/>
       <c r="O42" s="8" t="s">
+        <v>792</v>
+      </c>
+      <c r="Q42" s="8" t="s">
         <v>793</v>
       </c>
-      <c r="Q42" s="8" t="s">
+      <c r="R42" s="8" t="s">
         <v>794</v>
       </c>
-      <c r="R42" s="8" t="s">
+      <c r="S42" s="8" t="s">
         <v>795</v>
       </c>
-      <c r="S42" s="8" t="s">
+      <c r="U42" s="8" t="s">
         <v>796</v>
-      </c>
-      <c r="U42" s="8" t="s">
-        <v>797</v>
       </c>
       <c r="V42" s="8"/>
       <c r="W42" s="8" t="s">
+        <v>797</v>
+      </c>
+      <c r="Y42" s="8" t="s">
         <v>798</v>
-      </c>
-      <c r="Y42" s="8" t="s">
-        <v>799</v>
       </c>
       <c r="Z42" s="8"/>
       <c r="AA42" s="8" t="s">
+        <v>799</v>
+      </c>
+      <c r="AC42" s="8" t="s">
         <v>800</v>
-      </c>
-      <c r="AC42" s="8" t="s">
-        <v>801</v>
       </c>
       <c r="AD42" s="8"/>
       <c r="AE42" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A43" s="5" t="s">
+        <v>802</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>803</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="C43" s="5" t="s">
         <v>804</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="E43" s="5" t="s">
         <v>805</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="F43" s="5" t="s">
         <v>806</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="G43" s="5" t="s">
         <v>807</v>
       </c>
-      <c r="G43" s="5" t="s">
+      <c r="I43" s="8" t="s">
         <v>808</v>
       </c>
-      <c r="I43" s="8" t="s">
+      <c r="J43" s="8" t="s">
         <v>809</v>
       </c>
-      <c r="J43" s="8" t="s">
+      <c r="K43" s="8" t="s">
         <v>810</v>
       </c>
-      <c r="K43" s="8" t="s">
+      <c r="M43" s="8" t="s">
         <v>811</v>
-      </c>
-      <c r="M43" s="8" t="s">
-        <v>812</v>
       </c>
       <c r="N43" s="8"/>
       <c r="O43" s="8" t="s">
+        <v>812</v>
+      </c>
+      <c r="Q43" s="8" t="s">
         <v>813</v>
-      </c>
-      <c r="Q43" s="8" t="s">
-        <v>814</v>
       </c>
       <c r="R43" s="8"/>
       <c r="S43" s="8" t="s">
+        <v>814</v>
+      </c>
+      <c r="U43" s="8" t="s">
         <v>815</v>
-      </c>
-      <c r="U43" s="8" t="s">
-        <v>816</v>
       </c>
       <c r="V43" s="8"/>
       <c r="W43" s="8" t="s">
+        <v>816</v>
+      </c>
+      <c r="Y43" s="8" t="s">
         <v>817</v>
-      </c>
-      <c r="Y43" s="8" t="s">
-        <v>818</v>
       </c>
       <c r="Z43" s="8"/>
       <c r="AA43" s="8" t="s">
+        <v>818</v>
+      </c>
+      <c r="AC43" s="8" t="s">
         <v>819</v>
-      </c>
-      <c r="AC43" s="8" t="s">
-        <v>820</v>
       </c>
       <c r="AD43" s="8"/>
       <c r="AE43" s="8" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A44" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>822</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>823</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="E44" s="5" t="s">
         <v>824</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="F44" s="5" t="s">
         <v>825</v>
       </c>
-      <c r="F44" s="5" t="s">
+      <c r="G44" s="5" t="s">
         <v>826</v>
       </c>
-      <c r="G44" s="5" t="s">
+      <c r="I44" s="8" t="s">
         <v>827</v>
       </c>
-      <c r="I44" s="8" t="s">
+      <c r="J44" s="8" t="s">
         <v>828</v>
       </c>
-      <c r="J44" s="8" t="s">
+      <c r="K44" s="8" t="s">
         <v>829</v>
       </c>
-      <c r="K44" s="8" t="s">
+      <c r="M44" s="8" t="s">
         <v>830</v>
       </c>
-      <c r="M44" s="8" t="s">
+      <c r="N44" s="8" t="s">
         <v>831</v>
       </c>
-      <c r="N44" s="8" t="s">
+      <c r="O44" s="8" t="s">
         <v>832</v>
       </c>
-      <c r="O44" s="8" t="s">
+      <c r="Q44" s="8" t="s">
         <v>833</v>
-      </c>
-      <c r="Q44" s="8" t="s">
-        <v>834</v>
       </c>
       <c r="R44" s="8"/>
       <c r="S44" s="8" t="s">
+        <v>834</v>
+      </c>
+      <c r="U44" s="8" t="s">
         <v>835</v>
-      </c>
-      <c r="U44" s="8" t="s">
-        <v>836</v>
       </c>
       <c r="V44" s="8"/>
       <c r="W44" s="8" t="s">
+        <v>836</v>
+      </c>
+      <c r="Y44" s="8" t="s">
         <v>837</v>
-      </c>
-      <c r="Y44" s="8" t="s">
-        <v>838</v>
       </c>
       <c r="Z44" s="8"/>
       <c r="AA44" s="8" t="s">
+        <v>838</v>
+      </c>
+      <c r="AC44" s="8" t="s">
         <v>839</v>
-      </c>
-      <c r="AC44" s="8" t="s">
-        <v>840</v>
       </c>
       <c r="AD44" s="8"/>
       <c r="AE44" s="8" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="45" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A45" s="8" t="s">
+        <v>841</v>
+      </c>
+      <c r="B45" s="8" t="s">
         <v>842</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="C45" s="8" t="s">
         <v>843</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="E45" s="5" t="s">
         <v>844</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="F45" s="5" t="s">
         <v>845</v>
       </c>
-      <c r="F45" s="5" t="s">
+      <c r="G45" s="5" t="s">
         <v>846</v>
       </c>
-      <c r="G45" s="5" t="s">
+      <c r="I45" s="8" t="s">
         <v>847</v>
       </c>
-      <c r="I45" s="8" t="s">
+      <c r="J45" s="8" t="s">
         <v>848</v>
       </c>
-      <c r="J45" s="8" t="s">
+      <c r="K45" s="8" t="s">
         <v>849</v>
       </c>
-      <c r="K45" s="8" t="s">
+      <c r="M45" s="8" t="s">
         <v>850</v>
-      </c>
-      <c r="M45" s="8" t="s">
-        <v>851</v>
       </c>
       <c r="N45" s="8"/>
       <c r="O45" s="8" t="s">
+        <v>851</v>
+      </c>
+      <c r="Q45" s="8" t="s">
         <v>852</v>
-      </c>
-      <c r="Q45" s="8" t="s">
-        <v>853</v>
       </c>
       <c r="R45" s="8"/>
       <c r="S45" s="8" t="s">
+        <v>853</v>
+      </c>
+      <c r="U45" s="8" t="s">
         <v>854</v>
-      </c>
-      <c r="U45" s="8" t="s">
-        <v>855</v>
       </c>
       <c r="V45" s="8"/>
       <c r="W45" s="8" t="s">
+        <v>855</v>
+      </c>
+      <c r="Y45" s="8" t="s">
         <v>856</v>
-      </c>
-      <c r="Y45" s="8" t="s">
-        <v>857</v>
       </c>
       <c r="Z45" s="8"/>
       <c r="AA45" s="8" t="s">
+        <v>857</v>
+      </c>
+      <c r="AC45" s="8" t="s">
         <v>858</v>
-      </c>
-      <c r="AC45" s="8" t="s">
-        <v>859</v>
       </c>
       <c r="AD45" s="8"/>
       <c r="AE45" s="8" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A46" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>861</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="C46" s="3" t="s">
         <v>862</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="E46" s="8" t="s">
         <v>863</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="F46" s="8" t="s">
         <v>864</v>
       </c>
-      <c r="F46" s="8" t="s">
+      <c r="G46" s="8" t="s">
         <v>865</v>
       </c>
-      <c r="G46" s="8" t="s">
+      <c r="I46" s="8" t="s">
         <v>866</v>
-      </c>
-      <c r="I46" s="8" t="s">
-        <v>867</v>
       </c>
       <c r="J46" s="8"/>
       <c r="K46" s="8" t="s">
+        <v>867</v>
+      </c>
+      <c r="M46" s="8" t="s">
         <v>868</v>
-      </c>
-      <c r="M46" s="8" t="s">
-        <v>869</v>
       </c>
       <c r="N46" s="8"/>
       <c r="O46" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="Q46" s="8" t="s">
         <v>870</v>
-      </c>
-      <c r="Q46" s="8" t="s">
-        <v>871</v>
       </c>
       <c r="R46" s="8"/>
       <c r="S46" s="8" t="s">
+        <v>871</v>
+      </c>
+      <c r="U46" s="8" t="s">
         <v>872</v>
-      </c>
-      <c r="U46" s="8" t="s">
-        <v>873</v>
       </c>
       <c r="V46" s="8"/>
       <c r="W46" s="8" t="s">
+        <v>873</v>
+      </c>
+      <c r="Y46" s="8" t="s">
         <v>874</v>
-      </c>
-      <c r="Y46" s="8" t="s">
-        <v>875</v>
       </c>
       <c r="Z46" s="8"/>
       <c r="AA46" s="8" t="s">
+        <v>875</v>
+      </c>
+      <c r="AC46" s="8" t="s">
         <v>876</v>
-      </c>
-      <c r="AC46" s="8" t="s">
-        <v>877</v>
       </c>
       <c r="AD46" s="8"/>
       <c r="AE46" s="8" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="47" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A47" s="8" t="s">
+        <v>878</v>
+      </c>
+      <c r="B47" s="8" t="s">
         <v>879</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="C47" s="8" t="s">
         <v>880</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="E47" s="8" t="s">
         <v>881</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>882</v>
       </c>
       <c r="F47" s="8"/>
       <c r="G47" s="8" t="s">
+        <v>882</v>
+      </c>
+      <c r="I47" s="8" t="s">
         <v>883</v>
-      </c>
-      <c r="I47" s="8" t="s">
-        <v>884</v>
       </c>
       <c r="J47" s="8"/>
       <c r="K47" s="8" t="s">
+        <v>884</v>
+      </c>
+      <c r="M47" s="8" t="s">
         <v>885</v>
-      </c>
-      <c r="M47" s="8" t="s">
-        <v>886</v>
       </c>
       <c r="N47" s="8"/>
       <c r="O47" s="8" t="s">
+        <v>886</v>
+      </c>
+      <c r="Q47" s="8" t="s">
         <v>887</v>
-      </c>
-      <c r="Q47" s="8" t="s">
-        <v>888</v>
       </c>
       <c r="R47" s="8"/>
       <c r="S47" s="8" t="s">
+        <v>888</v>
+      </c>
+      <c r="U47" s="8" t="s">
         <v>889</v>
-      </c>
-      <c r="U47" s="8" t="s">
-        <v>890</v>
       </c>
       <c r="V47" s="8"/>
       <c r="W47" s="8" t="s">
+        <v>890</v>
+      </c>
+      <c r="Y47" s="8" t="s">
         <v>891</v>
-      </c>
-      <c r="Y47" s="8" t="s">
-        <v>892</v>
       </c>
       <c r="Z47" s="8"/>
       <c r="AA47" s="8" t="s">
+        <v>892</v>
+      </c>
+      <c r="AC47" s="8" t="s">
         <v>893</v>
-      </c>
-      <c r="AC47" s="8" t="s">
-        <v>894</v>
       </c>
       <c r="AD47" s="8"/>
       <c r="AE47" s="8" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="48" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A48" s="8" t="s">
+        <v>895</v>
+      </c>
+      <c r="B48" s="8" t="s">
         <v>896</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="C48" s="8" t="s">
         <v>897</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="E48" s="5" t="s">
         <v>898</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>899</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>67</v>
       </c>
       <c r="G48" s="5" t="s">
+        <v>899</v>
+      </c>
+      <c r="I48" s="8" t="s">
         <v>900</v>
       </c>
-      <c r="I48" s="8" t="s">
+      <c r="J48" s="8" t="s">
+        <v>768</v>
+      </c>
+      <c r="K48" s="8" t="s">
         <v>901</v>
       </c>
-      <c r="J48" s="8" t="s">
-        <v>769</v>
-      </c>
-      <c r="K48" s="8" t="s">
+      <c r="M48" s="8" t="s">
         <v>902</v>
-      </c>
-      <c r="M48" s="8" t="s">
-        <v>903</v>
       </c>
       <c r="N48" s="8"/>
       <c r="O48" s="8" t="s">
+        <v>903</v>
+      </c>
+      <c r="Q48" s="8" t="s">
         <v>904</v>
-      </c>
-      <c r="Q48" s="8" t="s">
-        <v>905</v>
       </c>
       <c r="R48" s="8"/>
       <c r="S48" s="8" t="s">
+        <v>905</v>
+      </c>
+      <c r="U48" s="8" t="s">
         <v>906</v>
-      </c>
-      <c r="U48" s="8" t="s">
-        <v>907</v>
       </c>
       <c r="V48" s="8"/>
       <c r="W48" s="8" t="s">
+        <v>907</v>
+      </c>
+      <c r="Y48" s="8" t="s">
         <v>908</v>
-      </c>
-      <c r="Y48" s="8" t="s">
-        <v>909</v>
       </c>
       <c r="Z48" s="8"/>
       <c r="AA48" s="8" t="s">
+        <v>909</v>
+      </c>
+      <c r="AC48" s="8" t="s">
         <v>910</v>
-      </c>
-      <c r="AC48" s="8" t="s">
-        <v>911</v>
       </c>
       <c r="AD48" s="8"/>
       <c r="AE48" s="8" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="49" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A49" s="8" t="s">
+        <v>912</v>
+      </c>
+      <c r="B49" s="8" t="s">
         <v>913</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="C49" s="8" t="s">
         <v>914</v>
       </c>
-      <c r="C49" s="8" t="s">
+      <c r="E49" s="8" t="s">
         <v>915</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>916</v>
       </c>
       <c r="F49" s="8"/>
       <c r="G49" s="8" t="s">
+        <v>916</v>
+      </c>
+      <c r="I49" s="8" t="s">
         <v>917</v>
       </c>
-      <c r="I49" s="8" t="s">
+      <c r="J49" s="8" t="s">
         <v>918</v>
       </c>
-      <c r="J49" s="8" t="s">
+      <c r="K49" s="8" t="s">
         <v>919</v>
       </c>
-      <c r="K49" s="8" t="s">
+      <c r="M49" s="8" t="s">
         <v>920</v>
-      </c>
-      <c r="M49" s="8" t="s">
-        <v>921</v>
       </c>
       <c r="N49" s="8"/>
       <c r="O49" s="8" t="s">
+        <v>921</v>
+      </c>
+      <c r="Q49" s="8" t="s">
         <v>922</v>
-      </c>
-      <c r="Q49" s="8" t="s">
-        <v>923</v>
       </c>
       <c r="R49" s="8"/>
       <c r="S49" s="8" t="s">
+        <v>923</v>
+      </c>
+      <c r="U49" s="8" t="s">
         <v>924</v>
-      </c>
-      <c r="U49" s="8" t="s">
-        <v>925</v>
       </c>
       <c r="V49" s="8"/>
       <c r="W49" s="8" t="s">
+        <v>925</v>
+      </c>
+      <c r="Y49" s="8" t="s">
         <v>926</v>
-      </c>
-      <c r="Y49" s="8" t="s">
-        <v>927</v>
       </c>
       <c r="Z49" s="8"/>
       <c r="AA49" s="8" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC49" s="8" t="s">
         <v>928</v>
-      </c>
-      <c r="AC49" s="8" t="s">
-        <v>929</v>
       </c>
       <c r="AD49" s="8"/>
       <c r="AE49" s="8" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="50" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A50" s="3" t="s">
+        <v>930</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>931</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="C50" s="3" t="s">
         <v>932</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="E50" s="8" t="s">
         <v>933</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="F50" s="8" t="s">
         <v>934</v>
       </c>
-      <c r="F50" s="8" t="s">
+      <c r="G50" s="8" t="s">
         <v>935</v>
       </c>
-      <c r="G50" s="8" t="s">
+      <c r="I50" s="8" t="s">
         <v>936</v>
       </c>
-      <c r="I50" s="8" t="s">
+      <c r="J50" s="8" t="s">
+        <v>1428</v>
+      </c>
+      <c r="K50" s="8" t="s">
         <v>937</v>
       </c>
-      <c r="J50" s="8" t="s">
-        <v>1429</v>
-      </c>
-      <c r="K50" s="8" t="s">
+      <c r="M50" s="8" t="s">
         <v>938</v>
       </c>
-      <c r="M50" s="8" t="s">
+      <c r="N50" s="8" t="s">
         <v>939</v>
       </c>
-      <c r="N50" s="8" t="s">
+      <c r="O50" s="8" t="s">
         <v>940</v>
       </c>
-      <c r="O50" s="8" t="s">
+      <c r="Q50" s="8" t="s">
         <v>941</v>
-      </c>
-      <c r="Q50" s="8" t="s">
-        <v>942</v>
       </c>
       <c r="R50" s="8"/>
       <c r="S50" s="8" t="s">
+        <v>942</v>
+      </c>
+      <c r="U50" s="8" t="s">
         <v>943</v>
-      </c>
-      <c r="U50" s="8" t="s">
-        <v>944</v>
       </c>
       <c r="V50" s="8"/>
       <c r="W50" s="8" t="s">
+        <v>944</v>
+      </c>
+      <c r="Y50" s="8" t="s">
         <v>945</v>
-      </c>
-      <c r="Y50" s="8" t="s">
-        <v>946</v>
       </c>
       <c r="Z50" s="8"/>
       <c r="AA50" s="8" t="s">
+        <v>946</v>
+      </c>
+      <c r="AC50" s="8" t="s">
         <v>947</v>
-      </c>
-      <c r="AC50" s="8" t="s">
-        <v>948</v>
       </c>
       <c r="AD50" s="8"/>
       <c r="AE50" s="8" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="51" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A51" s="8" t="s">
+        <v>949</v>
+      </c>
+      <c r="B51" s="8" t="s">
         <v>950</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="C51" s="8" t="s">
         <v>951</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="E51" s="8" t="s">
         <v>952</v>
       </c>
-      <c r="E51" s="8" t="s">
+      <c r="F51" s="8" t="s">
         <v>953</v>
       </c>
-      <c r="F51" s="8" t="s">
+      <c r="G51" s="8" t="s">
         <v>954</v>
       </c>
-      <c r="G51" s="8" t="s">
+      <c r="I51" s="8" t="s">
         <v>955</v>
       </c>
-      <c r="I51" s="8" t="s">
+      <c r="J51" s="8" t="s">
         <v>956</v>
       </c>
-      <c r="J51" s="8" t="s">
+      <c r="K51" s="8" t="s">
         <v>957</v>
       </c>
-      <c r="K51" s="8" t="s">
+      <c r="M51" s="8" t="s">
         <v>958</v>
-      </c>
-      <c r="M51" s="8" t="s">
-        <v>959</v>
       </c>
       <c r="N51" s="8"/>
       <c r="O51" s="8" t="s">
+        <v>959</v>
+      </c>
+      <c r="Q51" s="8" t="s">
         <v>960</v>
-      </c>
-      <c r="Q51" s="8" t="s">
-        <v>961</v>
       </c>
       <c r="R51" s="8"/>
       <c r="S51" s="8" t="s">
+        <v>961</v>
+      </c>
+      <c r="U51" s="8" t="s">
         <v>962</v>
-      </c>
-      <c r="U51" s="8" t="s">
-        <v>963</v>
       </c>
       <c r="V51" s="8"/>
       <c r="W51" s="8" t="s">
+        <v>963</v>
+      </c>
+      <c r="Y51" s="8" t="s">
         <v>964</v>
-      </c>
-      <c r="Y51" s="8" t="s">
-        <v>965</v>
       </c>
       <c r="Z51" s="8"/>
       <c r="AA51" s="8" t="s">
+        <v>965</v>
+      </c>
+      <c r="AC51" s="8" t="s">
         <v>966</v>
-      </c>
-      <c r="AC51" s="8" t="s">
-        <v>967</v>
       </c>
       <c r="AD51" s="8"/>
       <c r="AE51" s="8" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="52" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A52" s="5" t="s">
+        <v>968</v>
+      </c>
+      <c r="B52" s="5" t="s">
         <v>969</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="C52" s="5" t="s">
         <v>970</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="E52" s="8" t="s">
         <v>971</v>
       </c>
-      <c r="E52" s="8" t="s">
+      <c r="F52" s="8" t="s">
         <v>972</v>
       </c>
-      <c r="F52" s="8" t="s">
+      <c r="G52" s="8" t="s">
         <v>973</v>
       </c>
-      <c r="G52" s="8" t="s">
+      <c r="I52" s="8" t="s">
         <v>974</v>
       </c>
-      <c r="I52" s="8" t="s">
+      <c r="J52" s="8" t="s">
         <v>975</v>
       </c>
-      <c r="J52" s="8" t="s">
+      <c r="K52" s="8" t="s">
         <v>976</v>
       </c>
-      <c r="K52" s="8" t="s">
+      <c r="M52" s="8" t="s">
         <v>977</v>
-      </c>
-      <c r="M52" s="8" t="s">
-        <v>978</v>
       </c>
       <c r="N52" s="8"/>
       <c r="O52" s="8" t="s">
+        <v>978</v>
+      </c>
+      <c r="Q52" s="8" t="s">
         <v>979</v>
-      </c>
-      <c r="Q52" s="8" t="s">
-        <v>980</v>
       </c>
       <c r="R52" s="8"/>
       <c r="S52" s="8" t="s">
+        <v>980</v>
+      </c>
+      <c r="U52" s="8" t="s">
         <v>981</v>
-      </c>
-      <c r="U52" s="8" t="s">
-        <v>982</v>
       </c>
       <c r="V52" s="8"/>
       <c r="W52" s="8" t="s">
+        <v>982</v>
+      </c>
+      <c r="Y52" s="8" t="s">
         <v>983</v>
-      </c>
-      <c r="Y52" s="8" t="s">
-        <v>984</v>
       </c>
       <c r="Z52" s="8"/>
       <c r="AA52" s="8" t="s">
+        <v>984</v>
+      </c>
+      <c r="AC52" s="8" t="s">
         <v>985</v>
-      </c>
-      <c r="AC52" s="8" t="s">
-        <v>986</v>
       </c>
       <c r="AD52" s="8"/>
       <c r="AE52" s="8" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="53" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A53" s="3" t="s">
+        <v>987</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>988</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>989</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="E53" s="8" t="s">
         <v>990</v>
       </c>
-      <c r="E53" s="8" t="s">
+      <c r="F53" s="8" t="s">
         <v>991</v>
       </c>
-      <c r="F53" s="8" t="s">
+      <c r="G53" s="8" t="s">
         <v>992</v>
       </c>
-      <c r="G53" s="8" t="s">
+      <c r="I53" s="5" t="s">
         <v>993</v>
       </c>
-      <c r="I53" s="5" t="s">
+      <c r="J53" s="5" t="s">
         <v>994</v>
       </c>
-      <c r="J53" s="5" t="s">
+      <c r="K53" s="5" t="s">
         <v>995</v>
       </c>
-      <c r="K53" s="5" t="s">
+      <c r="M53" s="8" t="s">
         <v>996</v>
-      </c>
-      <c r="M53" s="8" t="s">
-        <v>997</v>
       </c>
       <c r="N53" s="8"/>
       <c r="O53" s="8" t="s">
+        <v>997</v>
+      </c>
+      <c r="Q53" s="8" t="s">
         <v>998</v>
-      </c>
-      <c r="Q53" s="8" t="s">
-        <v>999</v>
       </c>
       <c r="R53" s="8"/>
       <c r="S53" s="8" t="s">
+        <v>999</v>
+      </c>
+      <c r="U53" s="8" t="s">
         <v>1000</v>
-      </c>
-      <c r="U53" s="8" t="s">
-        <v>1001</v>
       </c>
       <c r="V53" s="8"/>
       <c r="W53" s="8" t="s">
+        <v>1001</v>
+      </c>
+      <c r="Y53" s="8" t="s">
         <v>1002</v>
-      </c>
-      <c r="Y53" s="8" t="s">
-        <v>1003</v>
       </c>
       <c r="Z53" s="8"/>
       <c r="AA53" s="8" t="s">
+        <v>1003</v>
+      </c>
+      <c r="AC53" s="8" t="s">
         <v>1004</v>
-      </c>
-      <c r="AC53" s="8" t="s">
-        <v>1005</v>
       </c>
       <c r="AD53" s="8"/>
       <c r="AE53" s="8" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="54" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A54" s="3" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>1007</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>1008</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="E54" s="8" t="s">
         <v>1009</v>
       </c>
-      <c r="E54" s="8" t="s">
+      <c r="F54" s="8" t="s">
         <v>1010</v>
       </c>
-      <c r="F54" s="8" t="s">
+      <c r="G54" s="8" t="s">
         <v>1011</v>
       </c>
-      <c r="G54" s="8" t="s">
+      <c r="I54" s="8" t="s">
         <v>1012</v>
       </c>
-      <c r="I54" s="8" t="s">
+      <c r="J54" s="8" t="s">
         <v>1013</v>
       </c>
-      <c r="J54" s="8" t="s">
+      <c r="K54" s="8" t="s">
         <v>1014</v>
       </c>
-      <c r="K54" s="8" t="s">
+      <c r="M54" s="8" t="s">
         <v>1015</v>
-      </c>
-      <c r="M54" s="8" t="s">
-        <v>1016</v>
       </c>
       <c r="N54" s="8"/>
       <c r="O54" s="8" t="s">
+        <v>1016</v>
+      </c>
+      <c r="Q54" s="8" t="s">
         <v>1017</v>
-      </c>
-      <c r="Q54" s="8" t="s">
-        <v>1018</v>
       </c>
       <c r="R54" s="8"/>
       <c r="S54" s="8" t="s">
+        <v>1018</v>
+      </c>
+      <c r="U54" s="8" t="s">
         <v>1019</v>
-      </c>
-      <c r="U54" s="8" t="s">
-        <v>1020</v>
       </c>
       <c r="V54" s="8"/>
       <c r="W54" s="8" t="s">
+        <v>1020</v>
+      </c>
+      <c r="Y54" s="8" t="s">
         <v>1021</v>
-      </c>
-      <c r="Y54" s="8" t="s">
-        <v>1022</v>
       </c>
       <c r="Z54" s="8"/>
       <c r="AA54" s="8" t="s">
+        <v>1022</v>
+      </c>
+      <c r="AC54" s="8" t="s">
         <v>1023</v>
-      </c>
-      <c r="AC54" s="8" t="s">
-        <v>1024</v>
       </c>
       <c r="AD54" s="8"/>
       <c r="AE54" s="8" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="55" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A55" s="3" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>1026</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="C55" s="3" t="s">
         <v>1027</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="E55" s="3" t="s">
         <v>1028</v>
       </c>
-      <c r="E55" s="3" t="s">
+      <c r="F55" s="3" t="s">
+        <v>1427</v>
+      </c>
+      <c r="G55" s="3" t="s">
         <v>1029</v>
       </c>
-      <c r="F55" s="3" t="s">
-        <v>1428</v>
-      </c>
-      <c r="G55" s="3" t="s">
+      <c r="I55" s="5" t="s">
         <v>1030</v>
       </c>
-      <c r="I55" s="5" t="s">
+      <c r="J55" s="5" t="s">
         <v>1031</v>
       </c>
-      <c r="J55" s="5" t="s">
+      <c r="K55" s="5" t="s">
         <v>1032</v>
       </c>
-      <c r="K55" s="5" t="s">
+      <c r="M55" s="8" t="s">
         <v>1033</v>
-      </c>
-      <c r="M55" s="8" t="s">
-        <v>1034</v>
       </c>
       <c r="N55" s="8"/>
       <c r="O55" s="8" t="s">
+        <v>1034</v>
+      </c>
+      <c r="Q55" s="8" t="s">
         <v>1035</v>
-      </c>
-      <c r="Q55" s="8" t="s">
-        <v>1036</v>
       </c>
       <c r="R55" s="8"/>
       <c r="S55" s="8" t="s">
+        <v>1036</v>
+      </c>
+      <c r="U55" s="8" t="s">
         <v>1037</v>
-      </c>
-      <c r="U55" s="8" t="s">
-        <v>1038</v>
       </c>
       <c r="V55" s="8"/>
       <c r="W55" s="8" t="s">
+        <v>1038</v>
+      </c>
+      <c r="Y55" s="8" t="s">
         <v>1039</v>
-      </c>
-      <c r="Y55" s="8" t="s">
-        <v>1040</v>
       </c>
       <c r="Z55" s="8"/>
       <c r="AA55" s="8" t="s">
+        <v>1040</v>
+      </c>
+      <c r="AC55" s="8" t="s">
         <v>1041</v>
-      </c>
-      <c r="AC55" s="8" t="s">
-        <v>1042</v>
       </c>
       <c r="AD55" s="8"/>
       <c r="AE55" s="8" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="56" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A56" s="3" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>1044</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>1045</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="E56" s="8" t="s">
         <v>1046</v>
       </c>
-      <c r="E56" s="8" t="s">
+      <c r="F56" s="8" t="s">
         <v>1047</v>
       </c>
-      <c r="F56" s="8" t="s">
+      <c r="G56" s="8" t="s">
         <v>1048</v>
       </c>
-      <c r="G56" s="8" t="s">
+      <c r="I56" s="3" t="s">
         <v>1049</v>
       </c>
-      <c r="I56" s="3" t="s">
+      <c r="J56" s="3" t="s">
         <v>1050</v>
       </c>
-      <c r="J56" s="3" t="s">
+      <c r="K56" s="3" t="s">
         <v>1051</v>
       </c>
-      <c r="K56" s="3" t="s">
+      <c r="M56" s="8" t="s">
         <v>1052</v>
-      </c>
-      <c r="M56" s="8" t="s">
-        <v>1053</v>
       </c>
       <c r="N56" s="8"/>
       <c r="O56" s="8" t="s">
+        <v>1053</v>
+      </c>
+      <c r="Q56" s="8" t="s">
         <v>1054</v>
-      </c>
-      <c r="Q56" s="8" t="s">
-        <v>1055</v>
       </c>
       <c r="R56" s="8"/>
       <c r="S56" s="8" t="s">
+        <v>1055</v>
+      </c>
+      <c r="U56" s="8" t="s">
         <v>1056</v>
-      </c>
-      <c r="U56" s="8" t="s">
-        <v>1057</v>
       </c>
       <c r="V56" s="8"/>
       <c r="W56" s="8" t="s">
+        <v>1057</v>
+      </c>
+      <c r="Y56" s="8" t="s">
         <v>1058</v>
-      </c>
-      <c r="Y56" s="8" t="s">
-        <v>1059</v>
       </c>
       <c r="Z56" s="8"/>
       <c r="AA56" s="8" t="s">
+        <v>1059</v>
+      </c>
+      <c r="AC56" s="8" t="s">
         <v>1060</v>
-      </c>
-      <c r="AC56" s="8" t="s">
-        <v>1061</v>
       </c>
       <c r="AD56" s="8"/>
       <c r="AE56" s="8" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="57" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A57" s="3" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>1063</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>1064</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="E57" s="8" t="s">
         <v>1065</v>
       </c>
-      <c r="E57" s="8" t="s">
+      <c r="F57" s="8" t="s">
         <v>1066</v>
       </c>
-      <c r="F57" s="8" t="s">
+      <c r="G57" s="8" t="s">
         <v>1067</v>
-      </c>
-      <c r="G57" s="8" t="s">
-        <v>1068</v>
       </c>
     </row>
     <row r="58" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A58" s="8" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B58" s="8" t="s">
         <v>1069</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="C58" s="8" t="s">
         <v>1070</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="59" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A59" s="8" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B59" s="8" t="s">
         <v>1072</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="C59" s="8" t="s">
         <v>1073</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>1074</v>
       </c>
     </row>
     <row r="60" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A60" s="8" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B60" s="8" t="s">
         <v>1075</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="C60" s="8" t="s">
         <v>1076</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>1077</v>
       </c>
       <c r="E60" s="4"/>
       <c r="F60" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="61" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A61" s="8" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B61" s="8" t="s">
         <v>1079</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="C61" s="8" t="s">
         <v>1080</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>1081</v>
       </c>
     </row>
     <row r="62" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A62" s="8" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B62" s="8" t="s">
         <v>1082</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="C62" s="8" t="s">
         <v>1083</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>1084</v>
       </c>
       <c r="E62" s="6"/>
       <c r="F62" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="63" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A63" s="8" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B63" s="8" t="s">
         <v>1086</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="C63" s="8" t="s">
         <v>1087</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>1088</v>
       </c>
     </row>
     <row r="64" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A64" s="8" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B64" s="8" t="s">
         <v>1089</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="C64" s="8" t="s">
         <v>1090</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>1091</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A65" s="3" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>1092</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="C65" s="3" t="s">
         <v>1093</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>1094</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A66" s="8" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B66" s="8" t="s">
         <v>1095</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="C66" s="8" t="s">
         <v>1096</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>1097</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A67" s="8" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="B67" s="8"/>
       <c r="C67" s="8" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A68" s="8" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="B68" s="8"/>
       <c r="C68" s="8" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A69" s="8" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B69" s="8" t="s">
         <v>1102</v>
       </c>
-      <c r="B69" s="8" t="s">
+      <c r="C69" s="8" t="s">
         <v>1103</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>1104</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A70" s="8" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="B70" s="8"/>
       <c r="C70" s="8" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A71" s="8" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B71" s="8" t="s">
         <v>1107</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="C71" s="8" t="s">
         <v>1108</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>1109</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A72" s="7" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B72" s="7" t="s">
         <v>1110</v>
       </c>
-      <c r="B72" s="7" t="s">
+      <c r="C72" s="7" t="s">
         <v>1111</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>1112</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A73" s="5" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B73" s="5" t="s">
         <v>1113</v>
       </c>
-      <c r="B73" s="5" t="s">
+      <c r="C73" s="5" t="s">
         <v>1114</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>1115</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A74" s="5" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B74" s="5" t="s">
         <v>1116</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="C74" s="5" t="s">
         <v>1117</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A75" s="3" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>1119</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="C75" s="3" t="s">
         <v>1120</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>1121</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A76" s="8" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B76" s="8" t="s">
         <v>1122</v>
       </c>
-      <c r="B76" s="8" t="s">
+      <c r="C76" s="8" t="s">
         <v>1123</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>1124</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A77" s="8" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B77" s="8" t="s">
         <v>1125</v>
       </c>
-      <c r="B77" s="8" t="s">
+      <c r="C77" s="8" t="s">
         <v>1126</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>1127</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A78" s="8" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B78" s="8"/>
       <c r="C78" s="8" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A79" s="3" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>1130</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="C79" s="3" t="s">
         <v>1131</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>1132</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A80" s="8" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B80" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="B80" s="8" t="s">
+      <c r="C80" s="8" t="s">
         <v>1134</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>1135</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A81" s="5" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B81" s="5" t="s">
         <v>1136</v>
       </c>
-      <c r="B81" s="5" t="s">
+      <c r="C81" s="5" t="s">
         <v>1137</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>1138</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A82" s="5" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B82" s="5" t="s">
         <v>1139</v>
       </c>
-      <c r="B82" s="5" t="s">
+      <c r="C82" s="5" t="s">
         <v>1140</v>
-      </c>
-      <c r="C82" s="5" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A83" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>1142</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="C83" s="3" t="s">
         <v>1143</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>1144</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A84" s="3" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B84" s="3" t="s">
         <v>1145</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="C84" s="3" t="s">
         <v>1146</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>1147</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A85" s="8" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="B85" s="8"/>
       <c r="C85" s="8" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A86" s="5" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B86" s="5" t="s">
         <v>1150</v>
       </c>
-      <c r="B86" s="5" t="s">
+      <c r="C86" s="5" t="s">
         <v>1151</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>1152</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A87" s="8" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B87" s="8" t="s">
         <v>1153</v>
       </c>
-      <c r="B87" s="8" t="s">
+      <c r="C87" s="8" t="s">
         <v>1154</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>1155</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A88" s="8" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B88" s="8"/>
       <c r="C88" s="8" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A89" s="5" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B89" s="5" t="s">
         <v>1158</v>
       </c>
-      <c r="B89" s="5" t="s">
+      <c r="C89" s="5" t="s">
         <v>1159</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>1160</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A90" s="5" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B90" s="5" t="s">
         <v>1161</v>
       </c>
-      <c r="B90" s="5" t="s">
+      <c r="C90" s="5" t="s">
         <v>1162</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>1163</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A91" s="5" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B91" s="5" t="s">
         <v>1164</v>
       </c>
-      <c r="B91" s="5" t="s">
+      <c r="C91" s="5" t="s">
         <v>1165</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>1166</v>
       </c>
     </row>
   </sheetData>
@@ -8940,937 +8935,937 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1167</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>1168</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1169</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>1174</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>1175</v>
-      </c>
       <c r="C2" s="11" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>1176</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>1177</v>
-      </c>
       <c r="C3" s="11" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>1178</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>1179</v>
-      </c>
       <c r="C4" s="11" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>1180</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>1181</v>
-      </c>
       <c r="C5" s="11" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>1182</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>1183</v>
-      </c>
       <c r="C6" s="11" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>1184</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>1185</v>
-      </c>
       <c r="C7" s="11" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A8" s="8" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>1186</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>1187</v>
-      </c>
       <c r="C8" s="11" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A9" s="8" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>1188</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>1189</v>
-      </c>
       <c r="C9" s="11" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>1190</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>1191</v>
-      </c>
       <c r="C10" s="11" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>1192</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>1193</v>
-      </c>
       <c r="C11" s="11" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A12" s="8" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>1194</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>1195</v>
-      </c>
       <c r="C12" s="11" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>1196</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>1197</v>
-      </c>
       <c r="C13" s="11" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A14" s="8" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>1198</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>1199</v>
-      </c>
       <c r="C14" s="11" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A15" s="8" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>1200</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>1201</v>
-      </c>
       <c r="C15" s="11" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A16" s="8" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>1202</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>1203</v>
-      </c>
       <c r="C16" s="11" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A17" s="8" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>1204</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>1205</v>
-      </c>
       <c r="C17" s="11" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A18" s="8" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>1206</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>1207</v>
-      </c>
       <c r="C18" s="11" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A19" s="8" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B19" s="8" t="s">
         <v>1208</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>1209</v>
-      </c>
       <c r="C19" s="11" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A20" s="8" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>1210</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>1211</v>
-      </c>
       <c r="C20" s="11" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>1212</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>1213</v>
-      </c>
       <c r="C21" s="11" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A22" s="8" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B22" s="8" t="s">
         <v>1214</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>1215</v>
-      </c>
       <c r="C22" s="11" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A23" s="8" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B23" s="8" t="s">
         <v>1216</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>1217</v>
-      </c>
       <c r="C23" s="11" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A24" s="8" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B24" s="8" t="s">
         <v>1218</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>1219</v>
-      </c>
       <c r="C24" s="11" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A25" s="8" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B25" s="8" t="s">
         <v>1220</v>
       </c>
-      <c r="B25" s="8" t="s">
-        <v>1221</v>
-      </c>
       <c r="C25" s="11" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A26" s="8" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B26" s="8" t="s">
         <v>1222</v>
       </c>
-      <c r="B26" s="8" t="s">
-        <v>1223</v>
-      </c>
       <c r="C26" s="11" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A27" s="8" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B27" s="8" t="s">
         <v>1224</v>
       </c>
-      <c r="B27" s="8" t="s">
-        <v>1225</v>
-      </c>
       <c r="C27" s="11" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A28" s="8" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B28" s="8" t="s">
         <v>1226</v>
       </c>
-      <c r="B28" s="8" t="s">
-        <v>1227</v>
-      </c>
       <c r="C28" s="11" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A29" s="8" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B29" s="8" t="s">
         <v>1228</v>
       </c>
-      <c r="B29" s="8" t="s">
-        <v>1229</v>
-      </c>
       <c r="C29" s="11" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A30" s="8" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B30" s="8" t="s">
         <v>1230</v>
       </c>
-      <c r="B30" s="8" t="s">
-        <v>1231</v>
-      </c>
       <c r="C30" s="11" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A31" s="8" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B31" s="8" t="s">
         <v>1232</v>
       </c>
-      <c r="B31" s="8" t="s">
-        <v>1233</v>
-      </c>
       <c r="C31" s="11" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A32" s="8" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B32" s="8" t="s">
         <v>1234</v>
       </c>
-      <c r="B32" s="8" t="s">
-        <v>1235</v>
-      </c>
       <c r="C32" s="11" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A33" s="8" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B33" s="8" t="s">
         <v>1236</v>
       </c>
-      <c r="B33" s="8" t="s">
-        <v>1237</v>
-      </c>
       <c r="C33" s="11" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A34" s="8" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B34" s="8" t="s">
         <v>1238</v>
       </c>
-      <c r="B34" s="8" t="s">
-        <v>1239</v>
-      </c>
       <c r="C34" s="11" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A35" s="8" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B35" s="8" t="s">
         <v>1240</v>
       </c>
-      <c r="B35" s="8" t="s">
-        <v>1241</v>
-      </c>
       <c r="C35" s="11" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="8" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B36" s="8" t="s">
         <v>1242</v>
       </c>
-      <c r="B36" s="8" t="s">
-        <v>1243</v>
-      </c>
       <c r="C36" s="11" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A37" s="8" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B37" s="8" t="s">
         <v>1244</v>
       </c>
-      <c r="B37" s="8" t="s">
-        <v>1245</v>
-      </c>
       <c r="C37" s="11" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A38" s="8" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B38" s="8" t="s">
         <v>1246</v>
       </c>
-      <c r="B38" s="8" t="s">
-        <v>1247</v>
-      </c>
       <c r="C38" s="11" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A39" s="8" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B39" s="8" t="s">
         <v>1248</v>
       </c>
-      <c r="B39" s="8" t="s">
-        <v>1249</v>
-      </c>
       <c r="C39" s="11" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A40" s="8" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B40" s="8" t="s">
         <v>1250</v>
       </c>
-      <c r="B40" s="8" t="s">
-        <v>1251</v>
-      </c>
       <c r="C40" s="11" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A41" s="8" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B41" s="8" t="s">
         <v>1252</v>
       </c>
-      <c r="B41" s="8" t="s">
-        <v>1253</v>
-      </c>
       <c r="C41" s="11" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A42" s="8" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B42" s="8" t="s">
         <v>1254</v>
       </c>
-      <c r="B42" s="8" t="s">
-        <v>1255</v>
-      </c>
       <c r="C42" s="11" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A43" s="8" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B43" s="8" t="s">
         <v>1256</v>
       </c>
-      <c r="B43" s="8" t="s">
-        <v>1257</v>
-      </c>
       <c r="C43" s="11" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A44" s="8" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B44" s="8" t="s">
         <v>1258</v>
       </c>
-      <c r="B44" s="8" t="s">
-        <v>1259</v>
-      </c>
       <c r="C44" s="11" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A45" s="8" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B45" s="8" t="s">
         <v>1260</v>
       </c>
-      <c r="B45" s="8" t="s">
-        <v>1261</v>
-      </c>
       <c r="C45" s="11" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A46" s="8" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B46" s="8" t="s">
         <v>1262</v>
       </c>
-      <c r="B46" s="8" t="s">
-        <v>1263</v>
-      </c>
       <c r="C46" s="11" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A47" s="8" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B47" s="8" t="s">
         <v>1264</v>
       </c>
-      <c r="B47" s="8" t="s">
-        <v>1265</v>
-      </c>
       <c r="C47" s="11" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A48" s="8" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B48" s="8" t="s">
         <v>1266</v>
       </c>
-      <c r="B48" s="8" t="s">
-        <v>1267</v>
-      </c>
       <c r="C48" s="11" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A49" s="8" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B49" s="8" t="s">
         <v>1268</v>
       </c>
-      <c r="B49" s="8" t="s">
-        <v>1269</v>
-      </c>
       <c r="C49" s="11" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A50" s="8" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B50" s="8" t="s">
         <v>1270</v>
       </c>
-      <c r="B50" s="8" t="s">
-        <v>1271</v>
-      </c>
       <c r="C50" s="11" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A51" s="8" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B51" s="8" t="s">
         <v>1272</v>
       </c>
-      <c r="B51" s="8" t="s">
-        <v>1273</v>
-      </c>
       <c r="C51" s="11" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A52" s="8" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B52" s="8" t="s">
         <v>1274</v>
       </c>
-      <c r="B52" s="8" t="s">
-        <v>1275</v>
-      </c>
       <c r="C52" s="11" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A53" s="8" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B53" s="8" t="s">
         <v>1276</v>
       </c>
-      <c r="B53" s="8" t="s">
-        <v>1277</v>
-      </c>
       <c r="C53" s="11" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A54" s="8" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B54" s="8" t="s">
         <v>1278</v>
       </c>
-      <c r="B54" s="8" t="s">
-        <v>1279</v>
-      </c>
       <c r="C54" s="11" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A55" s="8" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B55" s="8" t="s">
         <v>1280</v>
       </c>
-      <c r="B55" s="8" t="s">
-        <v>1281</v>
-      </c>
       <c r="C55" s="11" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A56" s="8" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B56" s="8" t="s">
         <v>1282</v>
       </c>
-      <c r="B56" s="8" t="s">
-        <v>1283</v>
-      </c>
       <c r="C56" s="11" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A57" s="8" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B57" s="8" t="s">
         <v>1170</v>
       </c>
-      <c r="B57" s="8" t="s">
-        <v>1171</v>
-      </c>
       <c r="C57" s="11" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A58" s="8" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B58" s="8" t="s">
         <v>1284</v>
       </c>
-      <c r="B58" s="8" t="s">
-        <v>1285</v>
-      </c>
       <c r="C58" s="11" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A59" s="8" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B59" s="8" t="s">
         <v>1286</v>
       </c>
-      <c r="B59" s="8" t="s">
-        <v>1287</v>
-      </c>
       <c r="C59" s="11" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A60" s="8" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B60" s="8" t="s">
         <v>1288</v>
       </c>
-      <c r="B60" s="8" t="s">
-        <v>1289</v>
-      </c>
       <c r="C60" s="11" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A61" s="8" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B61" s="8" t="s">
         <v>1290</v>
       </c>
-      <c r="B61" s="8" t="s">
-        <v>1291</v>
-      </c>
       <c r="C61" s="11" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A62" s="8" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B62" s="8" t="s">
         <v>1292</v>
       </c>
-      <c r="B62" s="8" t="s">
-        <v>1293</v>
-      </c>
       <c r="C62" s="11" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A63" s="8" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B63" s="8" t="s">
         <v>1294</v>
       </c>
-      <c r="B63" s="8" t="s">
-        <v>1295</v>
-      </c>
       <c r="C63" s="11" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A64" s="8" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B64" s="8" t="s">
         <v>1296</v>
       </c>
-      <c r="B64" s="8" t="s">
-        <v>1297</v>
-      </c>
       <c r="C64" s="11" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A65" s="8" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B65" s="8" t="s">
         <v>1298</v>
       </c>
-      <c r="B65" s="8" t="s">
-        <v>1299</v>
-      </c>
       <c r="C65" s="11" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A66" s="8" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B66" s="8" t="s">
         <v>1300</v>
       </c>
-      <c r="B66" s="8" t="s">
-        <v>1301</v>
-      </c>
       <c r="C66" s="11" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A67" s="8" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B67" s="8" t="s">
         <v>1302</v>
       </c>
-      <c r="B67" s="8" t="s">
-        <v>1303</v>
-      </c>
       <c r="C67" s="11" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A68" s="8" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B68" s="8" t="s">
         <v>1304</v>
       </c>
-      <c r="B68" s="8" t="s">
-        <v>1305</v>
-      </c>
       <c r="C68" s="11" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A69" s="8" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B69" s="8" t="s">
         <v>1306</v>
       </c>
-      <c r="B69" s="8" t="s">
-        <v>1307</v>
-      </c>
       <c r="C69" s="11" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A70" s="8" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B70" s="8" t="s">
         <v>1308</v>
       </c>
-      <c r="B70" s="8" t="s">
-        <v>1309</v>
-      </c>
       <c r="C70" s="11" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A71" s="8" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B71" s="8" t="s">
         <v>1310</v>
       </c>
-      <c r="B71" s="8" t="s">
-        <v>1311</v>
-      </c>
       <c r="C71" s="11" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A72" s="8" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B72" s="8" t="s">
         <v>1312</v>
       </c>
-      <c r="B72" s="8" t="s">
-        <v>1313</v>
-      </c>
       <c r="C72" s="11" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A73" s="8" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B73" s="8" t="s">
         <v>1172</v>
       </c>
-      <c r="B73" s="8" t="s">
-        <v>1173</v>
-      </c>
       <c r="C73" s="11" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A74" s="8" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B74" s="8" t="s">
         <v>1314</v>
       </c>
-      <c r="B74" s="8" t="s">
-        <v>1315</v>
-      </c>
       <c r="C74" s="11" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A75" s="8" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B75" s="8" t="s">
         <v>1316</v>
       </c>
-      <c r="B75" s="8" t="s">
-        <v>1317</v>
-      </c>
       <c r="C75" s="11" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A76" s="8" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B76" s="8" t="s">
         <v>1318</v>
       </c>
-      <c r="B76" s="8" t="s">
-        <v>1319</v>
-      </c>
       <c r="C76" s="11" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A77" s="8" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B77" s="8" t="s">
         <v>1320</v>
       </c>
-      <c r="B77" s="8" t="s">
-        <v>1321</v>
-      </c>
       <c r="C77" s="11" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A78" s="8" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B78" s="8" t="s">
         <v>1322</v>
       </c>
-      <c r="B78" s="8" t="s">
-        <v>1323</v>
-      </c>
       <c r="C78" s="11" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A79" s="8" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B79" s="8" t="s">
         <v>1324</v>
       </c>
-      <c r="B79" s="8" t="s">
-        <v>1325</v>
-      </c>
       <c r="C79" s="11" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A80" s="8" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B80" s="8" t="s">
         <v>1326</v>
       </c>
-      <c r="B80" s="8" t="s">
-        <v>1327</v>
-      </c>
       <c r="C80" s="11" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A81" s="8" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B81" s="8" t="s">
         <v>1328</v>
       </c>
-      <c r="B81" s="8" t="s">
-        <v>1329</v>
-      </c>
       <c r="C81" s="11" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A82" s="8" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B82" s="8" t="s">
         <v>1330</v>
       </c>
-      <c r="B82" s="8" t="s">
-        <v>1331</v>
-      </c>
       <c r="C82" s="11" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A83" s="8" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A84" s="8" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B84" s="8" t="s">
         <v>1333</v>
       </c>
-      <c r="B84" s="8" t="s">
-        <v>1334</v>
-      </c>
       <c r="C84" s="11" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A85" s="8" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B85" s="8" t="s">
         <v>1335</v>
       </c>
-      <c r="B85" s="8" t="s">
-        <v>1336</v>
-      </c>
       <c r="C85" s="11" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
     </row>
   </sheetData>
@@ -9974,46 +9969,46 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1168</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1169</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>1338</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="C2" s="10" t="s">
         <v>1339</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>1340</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>1341</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="10" t="s">
         <v>1342</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>1343</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>1344</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="10" t="s">
         <v>1345</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>1346</v>
       </c>
     </row>
   </sheetData>

--- a/key検討用/ppxkey.xlsx
+++ b/key検討用/ppxkey.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gocho\AppData\Local\Temp\Rar$DIa8044.31842.rartemp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gocho\AppData\Local\Temp\Rar$DIa7312.11817.rartemp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA5118B-96F0-49AA-98FA-301FF44B6B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D9EA39F-DFA9-4CCF-ABD7-22F9AFBE5C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1463" uniqueCount="1429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1458" uniqueCount="1428">
   <si>
     <t>キー</t>
   </si>
@@ -1290,9 +1290,6 @@
     <t>[Ctrl+Shift+E]</t>
   </si>
   <si>
-    <t>(PPtray)メモ</t>
-  </si>
-  <si>
     <t>%k"^\E"</t>
   </si>
   <si>
@@ -1468,9 +1465,6 @@
   </si>
   <si>
     <t>[Ctrl+Shift+H]</t>
-  </si>
-  <si>
-    <t>ダイアログでエントリのパスを開く(DialogHandler)</t>
   </si>
   <si>
     <t>%k"^\H"</t>
@@ -4403,6 +4397,9 @@
       <t>ゼンイキケンサク</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サブディレクトリ以下をインタラクティブサーチ(fzf)</t>
   </si>
 </sst>
 </file>
@@ -5040,7 +5037,7 @@
         <v>26</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>28</v>
@@ -6358,2562 +6355,2552 @@
       <c r="Q23" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="R23" s="8" t="s">
+      <c r="R23" s="8"/>
+      <c r="S23" s="8" t="s">
         <v>422</v>
       </c>
-      <c r="S23" s="8" t="s">
+      <c r="U23" s="8" t="s">
         <v>423</v>
-      </c>
-      <c r="U23" s="8" t="s">
-        <v>424</v>
       </c>
       <c r="V23" s="8"/>
       <c r="W23" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="Y23" s="8" t="s">
         <v>425</v>
-      </c>
-      <c r="Y23" s="8" t="s">
-        <v>426</v>
       </c>
       <c r="Z23" s="8"/>
       <c r="AA23" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="AC23" s="8" t="s">
         <v>427</v>
-      </c>
-      <c r="AC23" s="8" t="s">
-        <v>428</v>
       </c>
       <c r="AD23" s="8"/>
       <c r="AE23" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A24" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="E24" s="8" t="s">
         <v>432</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="F24" s="8" t="s">
         <v>433</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="G24" s="8" t="s">
         <v>434</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="I24" s="5" t="s">
         <v>435</v>
       </c>
-      <c r="I24" s="5" t="s">
+      <c r="J24" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="J24" s="5" t="s">
+      <c r="K24" s="5" t="s">
         <v>437</v>
       </c>
-      <c r="K24" s="5" t="s">
+      <c r="M24" s="8" t="s">
         <v>438</v>
       </c>
-      <c r="M24" s="8" t="s">
+      <c r="N24" s="8" t="s">
         <v>439</v>
       </c>
-      <c r="N24" s="8" t="s">
+      <c r="O24" s="8" t="s">
         <v>440</v>
       </c>
-      <c r="O24" s="8" t="s">
+      <c r="Q24" s="8" t="s">
         <v>441</v>
       </c>
-      <c r="Q24" s="8" t="s">
+      <c r="R24" s="8" t="s">
         <v>442</v>
       </c>
-      <c r="R24" s="8" t="s">
+      <c r="S24" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="S24" s="8" t="s">
+      <c r="U24" s="8" t="s">
         <v>444</v>
-      </c>
-      <c r="U24" s="8" t="s">
-        <v>445</v>
       </c>
       <c r="V24" s="8"/>
       <c r="W24" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="Y24" s="8" t="s">
         <v>446</v>
-      </c>
-      <c r="Y24" s="8" t="s">
-        <v>447</v>
       </c>
       <c r="Z24" s="8"/>
       <c r="AA24" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="AC24" s="8" t="s">
         <v>448</v>
-      </c>
-      <c r="AC24" s="8" t="s">
-        <v>449</v>
       </c>
       <c r="AD24" s="8"/>
       <c r="AE24" s="8" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A25" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>451</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="C25" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="E25" s="8" t="s">
         <v>453</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="F25" s="8" t="s">
         <v>454</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="G25" s="8" t="s">
         <v>455</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="I25" s="8" t="s">
         <v>456</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>457</v>
       </c>
       <c r="J25" s="8"/>
       <c r="K25" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="M25" s="8" t="s">
         <v>458</v>
-      </c>
-      <c r="M25" s="8" t="s">
-        <v>459</v>
       </c>
       <c r="N25" s="8"/>
       <c r="O25" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="Q25" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="Q25" s="8" t="s">
+      <c r="R25" s="8" t="s">
         <v>461</v>
       </c>
-      <c r="R25" s="8" t="s">
+      <c r="S25" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="S25" s="8" t="s">
+      <c r="U25" s="8" t="s">
         <v>463</v>
-      </c>
-      <c r="U25" s="8" t="s">
-        <v>464</v>
       </c>
       <c r="V25" s="8"/>
       <c r="W25" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="Y25" s="8" t="s">
         <v>465</v>
-      </c>
-      <c r="Y25" s="8" t="s">
-        <v>466</v>
       </c>
       <c r="Z25" s="8"/>
       <c r="AA25" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="AC25" s="8" t="s">
         <v>467</v>
-      </c>
-      <c r="AC25" s="8" t="s">
-        <v>468</v>
       </c>
       <c r="AD25" s="8"/>
       <c r="AE25" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A26" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="C26" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="E26" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="F26" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="G26" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="I26" s="8" t="s">
         <v>475</v>
       </c>
-      <c r="I26" s="8" t="s">
+      <c r="J26" s="1"/>
+      <c r="K26" s="8" t="s">
         <v>476</v>
       </c>
-      <c r="J26" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="K26" s="8" t="s">
+      <c r="M26" s="8" t="s">
         <v>477</v>
       </c>
-      <c r="M26" s="8" t="s">
+      <c r="N26" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="N26" s="8" t="s">
+      <c r="O26" s="8" t="s">
         <v>479</v>
       </c>
-      <c r="O26" s="8" t="s">
+      <c r="Q26" s="8" t="s">
         <v>480</v>
       </c>
-      <c r="Q26" s="8" t="s">
+      <c r="R26" s="8"/>
+      <c r="S26" s="8" t="s">
         <v>481</v>
       </c>
-      <c r="R26" s="8" t="s">
+      <c r="U26" s="8" t="s">
         <v>482</v>
-      </c>
-      <c r="S26" s="8" t="s">
-        <v>483</v>
-      </c>
-      <c r="U26" s="8" t="s">
-        <v>484</v>
       </c>
       <c r="V26" s="8"/>
       <c r="W26" s="8" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="Y26" s="8" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Z26" s="8"/>
       <c r="AA26" s="8" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="AC26" s="8" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="AD26" s="8"/>
       <c r="AE26" s="8" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A27" s="8" t="s">
+        <v>488</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="C27" s="8" t="s">
         <v>490</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="E27" s="8" t="s">
         <v>491</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="F27" s="8" t="s">
         <v>492</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="G27" s="8" t="s">
         <v>493</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="I27" s="8" t="s">
         <v>494</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="J27" s="8" t="s">
         <v>495</v>
       </c>
-      <c r="I27" s="8" t="s">
+      <c r="K27" s="8" t="s">
         <v>496</v>
       </c>
-      <c r="J27" s="8" t="s">
+      <c r="M27" s="8" t="s">
         <v>497</v>
       </c>
-      <c r="K27" s="8" t="s">
+      <c r="N27" s="8" t="s">
         <v>498</v>
       </c>
-      <c r="M27" s="8" t="s">
+      <c r="O27" s="8" t="s">
         <v>499</v>
       </c>
-      <c r="N27" s="8" t="s">
+      <c r="Q27" s="8" t="s">
         <v>500</v>
       </c>
-      <c r="O27" s="8" t="s">
+      <c r="R27" s="8" t="s">
         <v>501</v>
       </c>
-      <c r="Q27" s="8" t="s">
+      <c r="S27" s="8" t="s">
         <v>502</v>
       </c>
-      <c r="R27" s="8" t="s">
+      <c r="U27" s="8" t="s">
         <v>503</v>
-      </c>
-      <c r="S27" s="8" t="s">
-        <v>504</v>
-      </c>
-      <c r="U27" s="8" t="s">
-        <v>505</v>
       </c>
       <c r="V27" s="8"/>
       <c r="W27" s="8" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="Y27" s="8" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="Z27" s="8"/>
       <c r="AA27" s="8" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="AC27" s="8" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="AD27" s="8"/>
       <c r="AE27" s="8" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="28" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A28" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>511</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="E28" s="5" t="s">
         <v>512</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="F28" s="5" t="s">
         <v>513</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="G28" s="5" t="s">
         <v>514</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="I28" s="8" t="s">
         <v>515</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="J28" s="8" t="s">
+        <v>1427</v>
+      </c>
+      <c r="K28" s="8" t="s">
         <v>516</v>
       </c>
-      <c r="I28" s="8" t="s">
+      <c r="M28" s="8" t="s">
         <v>517</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="K28" s="8" t="s">
-        <v>518</v>
-      </c>
-      <c r="M28" s="8" t="s">
-        <v>519</v>
       </c>
       <c r="N28" s="8"/>
       <c r="O28" s="8" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="Q28" s="8" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="R28" s="8"/>
       <c r="S28" s="8" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="U28" s="8" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="V28" s="8"/>
       <c r="W28" s="8" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="Y28" s="8" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="Z28" s="8"/>
       <c r="AA28" s="8" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="AC28" s="8" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="AD28" s="8"/>
       <c r="AE28" s="8" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="29" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A29" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="E29" s="5" t="s">
         <v>530</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="F29" s="5" t="s">
         <v>531</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="G29" s="5" t="s">
         <v>532</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="I29" s="8" t="s">
         <v>533</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="J29" s="8"/>
+      <c r="K29" s="8" t="s">
         <v>534</v>
       </c>
-      <c r="I29" s="8" t="s">
+      <c r="M29" s="8" t="s">
         <v>535</v>
-      </c>
-      <c r="J29" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="K29" s="8" t="s">
-        <v>536</v>
-      </c>
-      <c r="M29" s="8" t="s">
-        <v>537</v>
       </c>
       <c r="N29" s="8"/>
       <c r="O29" s="8" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="Q29" s="8" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="R29" s="8"/>
       <c r="S29" s="8" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="U29" s="8" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="V29" s="8"/>
       <c r="W29" s="8" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="Y29" s="8" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="Z29" s="8"/>
       <c r="AA29" s="8" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="AC29" s="8" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="AD29" s="8"/>
       <c r="AE29" s="8" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A30" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="E30" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="F30" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="G30" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="I30" s="8" t="s">
         <v>551</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="J30" s="8"/>
+      <c r="K30" s="8" t="s">
         <v>552</v>
       </c>
-      <c r="I30" s="8" t="s">
+      <c r="M30" s="8" t="s">
         <v>553</v>
-      </c>
-      <c r="J30" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="K30" s="8" t="s">
-        <v>554</v>
-      </c>
-      <c r="M30" s="8" t="s">
-        <v>555</v>
       </c>
       <c r="N30" s="8"/>
       <c r="O30" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="Q30" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="R30" s="8" t="s">
         <v>556</v>
       </c>
-      <c r="Q30" s="8" t="s">
+      <c r="S30" s="8" t="s">
         <v>557</v>
       </c>
-      <c r="R30" s="8" t="s">
+      <c r="U30" s="8" t="s">
         <v>558</v>
-      </c>
-      <c r="S30" s="8" t="s">
-        <v>559</v>
-      </c>
-      <c r="U30" s="8" t="s">
-        <v>560</v>
       </c>
       <c r="V30" s="8"/>
       <c r="W30" s="8" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="Y30" s="8" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="Z30" s="8"/>
       <c r="AA30" s="8" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="AC30" s="8" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="AD30" s="8"/>
       <c r="AE30" s="8" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A31" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="F31" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="G31" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="I31" s="8" t="s">
         <v>570</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="J31" s="8" t="s">
         <v>571</v>
       </c>
-      <c r="I31" s="8" t="s">
+      <c r="K31" s="8" t="s">
         <v>572</v>
       </c>
-      <c r="J31" s="8" t="s">
+      <c r="M31" s="8" t="s">
         <v>573</v>
       </c>
-      <c r="K31" s="8" t="s">
+      <c r="N31" s="8" t="s">
         <v>574</v>
       </c>
-      <c r="M31" s="8" t="s">
+      <c r="O31" s="8" t="s">
         <v>575</v>
       </c>
-      <c r="N31" s="8" t="s">
+      <c r="Q31" s="8" t="s">
         <v>576</v>
       </c>
-      <c r="O31" s="8" t="s">
+      <c r="R31" s="8" t="s">
         <v>577</v>
       </c>
-      <c r="Q31" s="8" t="s">
+      <c r="S31" s="8" t="s">
         <v>578</v>
       </c>
-      <c r="R31" s="8" t="s">
+      <c r="U31" s="8" t="s">
         <v>579</v>
-      </c>
-      <c r="S31" s="8" t="s">
-        <v>580</v>
-      </c>
-      <c r="U31" s="8" t="s">
-        <v>581</v>
       </c>
       <c r="V31" s="8"/>
       <c r="W31" s="8" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="Y31" s="8" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="Z31" s="8"/>
       <c r="AA31" s="8" t="s">
+        <v>582</v>
+      </c>
+      <c r="AC31" s="8" t="s">
+        <v>583</v>
+      </c>
+      <c r="AD31" s="8" t="s">
         <v>584</v>
       </c>
-      <c r="AC31" s="8" t="s">
+      <c r="AE31" s="8" t="s">
         <v>585</v>
-      </c>
-      <c r="AD31" s="8" t="s">
-        <v>586</v>
-      </c>
-      <c r="AE31" s="8" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A32" s="8" t="s">
+        <v>586</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>587</v>
+      </c>
+      <c r="C32" s="8" t="s">
         <v>588</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="E32" s="8" t="s">
         <v>589</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="F32" s="8" t="s">
         <v>590</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="G32" s="8" t="s">
         <v>591</v>
       </c>
-      <c r="F32" s="8" t="s">
+      <c r="I32" s="8" t="s">
         <v>592</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>593</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>594</v>
       </c>
       <c r="J32" s="8" t="s">
         <v>27</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="M32" s="8" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="N32" s="8"/>
       <c r="O32" s="8" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="Q32" s="8" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="R32" s="8"/>
       <c r="S32" s="8" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="U32" s="8" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="V32" s="8"/>
       <c r="W32" s="8" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="Y32" s="8" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="Z32" s="8"/>
       <c r="AA32" s="8" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AC32" s="8" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AD32" s="8"/>
       <c r="AE32" s="8" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A33" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>606</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="E33" s="8" t="s">
         <v>607</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="F33" s="8" t="s">
         <v>608</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="G33" s="8" t="s">
         <v>609</v>
       </c>
-      <c r="F33" s="8" t="s">
+      <c r="I33" s="8" t="s">
         <v>610</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>611</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>612</v>
       </c>
       <c r="J33" s="8"/>
       <c r="K33" s="8" t="s">
+        <v>611</v>
+      </c>
+      <c r="M33" s="8" t="s">
+        <v>612</v>
+      </c>
+      <c r="N33" s="8" t="s">
         <v>613</v>
       </c>
-      <c r="M33" s="8" t="s">
+      <c r="O33" s="8" t="s">
         <v>614</v>
       </c>
-      <c r="N33" s="8" t="s">
+      <c r="Q33" s="8" t="s">
         <v>615</v>
-      </c>
-      <c r="O33" s="8" t="s">
-        <v>616</v>
-      </c>
-      <c r="Q33" s="8" t="s">
-        <v>617</v>
       </c>
       <c r="R33" s="8"/>
       <c r="S33" s="8" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="U33" s="8" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="V33" s="8"/>
       <c r="W33" s="8" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="Y33" s="8" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="Z33" s="8"/>
       <c r="AA33" s="8" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="AC33" s="8" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="AD33" s="8"/>
       <c r="AE33" s="8" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A34" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="E34" s="8" t="s">
         <v>626</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="F34" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="G34" s="8" t="s">
         <v>628</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="I34" s="8" t="s">
         <v>629</v>
       </c>
-      <c r="G34" s="8" t="s">
+      <c r="J34" s="8" t="s">
         <v>630</v>
       </c>
-      <c r="I34" s="8" t="s">
+      <c r="K34" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="J34" s="8" t="s">
+      <c r="M34" s="8" t="s">
         <v>632</v>
-      </c>
-      <c r="K34" s="8" t="s">
-        <v>633</v>
-      </c>
-      <c r="M34" s="8" t="s">
-        <v>634</v>
       </c>
       <c r="N34" s="8"/>
       <c r="O34" s="8" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="Q34" s="8" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="R34" s="8"/>
       <c r="S34" s="8" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="U34" s="8" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="V34" s="8"/>
       <c r="W34" s="8" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="Y34" s="8" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="Z34" s="8"/>
       <c r="AA34" s="8" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="AC34" s="8" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="AD34" s="8"/>
       <c r="AE34" s="8" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A35" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="C35" s="8" t="s">
         <v>644</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="E35" s="8" t="s">
         <v>645</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="F35" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="G35" s="8" t="s">
         <v>647</v>
       </c>
-      <c r="F35" s="8" t="s">
+      <c r="I35" s="8" t="s">
         <v>648</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>649</v>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>650</v>
       </c>
       <c r="J35" s="8"/>
       <c r="K35" s="8" t="s">
+        <v>649</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="N35" s="3" t="s">
         <v>651</v>
       </c>
-      <c r="M35" s="3" t="s">
+      <c r="O35" s="3" t="s">
         <v>652</v>
       </c>
-      <c r="N35" s="3" t="s">
+      <c r="Q35" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="O35" s="3" t="s">
+      <c r="R35" s="8" t="s">
         <v>654</v>
       </c>
-      <c r="Q35" s="8" t="s">
+      <c r="S35" s="8" t="s">
         <v>655</v>
       </c>
-      <c r="R35" s="8" t="s">
+      <c r="U35" s="8" t="s">
         <v>656</v>
-      </c>
-      <c r="S35" s="8" t="s">
-        <v>657</v>
-      </c>
-      <c r="U35" s="8" t="s">
-        <v>658</v>
       </c>
       <c r="V35" s="8"/>
       <c r="W35" s="8" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="Y35" s="8" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="Z35" s="8"/>
       <c r="AA35" s="8" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="AC35" s="8" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="AD35" s="8"/>
       <c r="AE35" s="8" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A36" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="E36" s="5" t="s">
         <v>665</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="F36" s="5" t="s">
         <v>666</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="G36" s="5" t="s">
         <v>667</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="I36" s="8" t="s">
         <v>668</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>669</v>
-      </c>
-      <c r="I36" s="8" t="s">
-        <v>670</v>
       </c>
       <c r="J36" s="8"/>
       <c r="K36" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="M36" s="8" t="s">
+        <v>670</v>
+      </c>
+      <c r="N36" s="8" t="s">
         <v>671</v>
       </c>
-      <c r="M36" s="8" t="s">
+      <c r="O36" s="8" t="s">
         <v>672</v>
       </c>
-      <c r="N36" s="8" t="s">
+      <c r="Q36" s="8" t="s">
         <v>673</v>
-      </c>
-      <c r="O36" s="8" t="s">
-        <v>674</v>
-      </c>
-      <c r="Q36" s="8" t="s">
-        <v>675</v>
       </c>
       <c r="R36" s="8"/>
       <c r="S36" s="8" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="U36" s="8" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="V36" s="8"/>
       <c r="W36" s="8" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="Y36" s="8" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="Z36" s="8"/>
       <c r="AA36" s="8" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="AC36" s="8" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="AD36" s="8"/>
       <c r="AE36" s="8" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A37" s="7" t="s">
+        <v>681</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="C37" s="7" t="s">
         <v>683</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="E37" s="8" t="s">
         <v>684</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="F37" s="8" t="s">
         <v>685</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="G37" s="8" t="s">
         <v>686</v>
       </c>
-      <c r="F37" s="8" t="s">
+      <c r="I37" s="8" t="s">
         <v>687</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>688</v>
-      </c>
-      <c r="I37" s="8" t="s">
-        <v>689</v>
       </c>
       <c r="J37" s="8"/>
       <c r="K37" s="8" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="M37" s="8" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="N37" s="8"/>
       <c r="O37" s="8" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="Q37" s="8" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="R37" s="8"/>
       <c r="S37" s="8" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="U37" s="8" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="V37" s="8"/>
       <c r="W37" s="8" t="s">
+        <v>694</v>
+      </c>
+      <c r="Y37" s="5" t="s">
+        <v>695</v>
+      </c>
+      <c r="Z37" s="5" t="s">
         <v>696</v>
       </c>
-      <c r="Y37" s="5" t="s">
+      <c r="AA37" s="5" t="s">
         <v>697</v>
       </c>
-      <c r="Z37" s="5" t="s">
+      <c r="AC37" s="8" t="s">
         <v>698</v>
-      </c>
-      <c r="AA37" s="5" t="s">
-        <v>699</v>
-      </c>
-      <c r="AC37" s="8" t="s">
-        <v>700</v>
       </c>
       <c r="AD37" s="8"/>
       <c r="AE37" s="8" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A38" s="8" t="s">
+        <v>700</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>701</v>
+      </c>
+      <c r="C38" s="8" t="s">
         <v>702</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="E38" s="8" t="s">
         <v>703</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="F38" s="8" t="s">
         <v>704</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="G38" s="8" t="s">
         <v>705</v>
       </c>
-      <c r="F38" s="8" t="s">
+      <c r="I38" s="8" t="s">
         <v>706</v>
       </c>
-      <c r="G38" s="8" t="s">
+      <c r="J38" s="8" t="s">
         <v>707</v>
       </c>
-      <c r="I38" s="8" t="s">
+      <c r="K38" s="8" t="s">
         <v>708</v>
       </c>
-      <c r="J38" s="8" t="s">
+      <c r="M38" s="8" t="s">
         <v>709</v>
       </c>
-      <c r="K38" s="8" t="s">
+      <c r="N38" s="8" t="s">
         <v>710</v>
       </c>
-      <c r="M38" s="8" t="s">
+      <c r="O38" s="8" t="s">
         <v>711</v>
       </c>
-      <c r="N38" s="8" t="s">
+      <c r="Q38" s="8" t="s">
         <v>712</v>
-      </c>
-      <c r="O38" s="8" t="s">
-        <v>713</v>
-      </c>
-      <c r="Q38" s="8" t="s">
-        <v>714</v>
       </c>
       <c r="R38" s="8"/>
       <c r="S38" s="8" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="U38" s="8" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="V38" s="8"/>
       <c r="W38" s="8" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="Y38" s="8" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="Z38" s="8"/>
       <c r="AA38" s="8" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="AC38" s="8" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="AD38" s="8"/>
       <c r="AE38" s="8" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A39" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>722</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="E39" s="5" t="s">
         <v>723</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="F39" s="5" t="s">
         <v>724</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="G39" s="5" t="s">
         <v>725</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="I39" s="8" t="s">
         <v>726</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>727</v>
-      </c>
-      <c r="I39" s="8" t="s">
-        <v>728</v>
       </c>
       <c r="J39" s="8"/>
       <c r="K39" s="8" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="N39" s="8"/>
       <c r="O39" s="8" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="Q39" s="8" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="R39" s="8"/>
       <c r="S39" s="8" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="U39" s="8" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="V39" s="8"/>
       <c r="W39" s="8" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="Y39" s="8" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="Z39" s="8"/>
       <c r="AA39" s="8" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="AC39" s="8" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="AD39" s="8"/>
       <c r="AE39" s="8" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A40" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>740</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="E40" s="8" t="s">
         <v>741</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="F40" s="8" t="s">
         <v>742</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="G40" s="8" t="s">
         <v>743</v>
       </c>
-      <c r="F40" s="8" t="s">
+      <c r="I40" s="3" t="s">
         <v>744</v>
       </c>
-      <c r="G40" s="8" t="s">
+      <c r="J40" s="3" t="s">
         <v>745</v>
       </c>
-      <c r="I40" s="3" t="s">
+      <c r="K40" s="3" t="s">
         <v>746</v>
       </c>
-      <c r="J40" s="3" t="s">
+      <c r="M40" s="8" t="s">
         <v>747</v>
       </c>
-      <c r="K40" s="3" t="s">
+      <c r="N40" s="8" t="s">
         <v>748</v>
       </c>
-      <c r="M40" s="8" t="s">
+      <c r="O40" s="8" t="s">
         <v>749</v>
       </c>
-      <c r="N40" s="8" t="s">
+      <c r="Q40" s="8" t="s">
         <v>750</v>
       </c>
-      <c r="O40" s="8" t="s">
+      <c r="R40" s="8" t="s">
         <v>751</v>
       </c>
-      <c r="Q40" s="8" t="s">
+      <c r="S40" s="8" t="s">
         <v>752</v>
       </c>
-      <c r="R40" s="8" t="s">
+      <c r="U40" s="8" t="s">
         <v>753</v>
-      </c>
-      <c r="S40" s="8" t="s">
-        <v>754</v>
-      </c>
-      <c r="U40" s="8" t="s">
-        <v>755</v>
       </c>
       <c r="V40" s="8"/>
       <c r="W40" s="8" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="Y40" s="8" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="Z40" s="8"/>
       <c r="AA40" s="8" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AC40" s="8" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="AD40" s="8"/>
       <c r="AE40" s="8" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A41" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>761</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="E41" s="8" t="s">
         <v>762</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="F41" s="8" t="s">
         <v>763</v>
       </c>
-      <c r="E41" s="8" t="s">
+      <c r="G41" s="8" t="s">
         <v>764</v>
       </c>
-      <c r="F41" s="8" t="s">
+      <c r="I41" s="8" t="s">
         <v>765</v>
       </c>
-      <c r="G41" s="8" t="s">
+      <c r="J41" s="8" t="s">
         <v>766</v>
       </c>
-      <c r="I41" s="8" t="s">
+      <c r="K41" s="8" t="s">
         <v>767</v>
       </c>
-      <c r="J41" s="8" t="s">
+      <c r="M41" s="8" t="s">
         <v>768</v>
       </c>
-      <c r="K41" s="8" t="s">
+      <c r="N41" s="8" t="s">
         <v>769</v>
       </c>
-      <c r="M41" s="8" t="s">
+      <c r="O41" s="8" t="s">
         <v>770</v>
       </c>
-      <c r="N41" s="8" t="s">
+      <c r="Q41" s="8" t="s">
         <v>771</v>
       </c>
-      <c r="O41" s="8" t="s">
+      <c r="R41" s="8" t="s">
         <v>772</v>
       </c>
-      <c r="Q41" s="8" t="s">
+      <c r="S41" s="8" t="s">
         <v>773</v>
       </c>
-      <c r="R41" s="8" t="s">
+      <c r="U41" s="8" t="s">
         <v>774</v>
-      </c>
-      <c r="S41" s="8" t="s">
-        <v>775</v>
-      </c>
-      <c r="U41" s="8" t="s">
-        <v>776</v>
       </c>
       <c r="V41" s="8"/>
       <c r="W41" s="8" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="Y41" s="8" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="Z41" s="8"/>
       <c r="AA41" s="8" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="AC41" s="8" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="AD41" s="8"/>
       <c r="AE41" s="8" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A42" s="8" t="s">
+        <v>780</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>781</v>
+      </c>
+      <c r="C42" s="8" t="s">
         <v>782</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="E42" s="3" t="s">
         <v>783</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="F42" s="3" t="s">
         <v>784</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="G42" s="3" t="s">
         <v>785</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="I42" s="3" t="s">
         <v>786</v>
       </c>
-      <c r="G42" s="3" t="s">
+      <c r="J42" s="3" t="s">
         <v>787</v>
       </c>
-      <c r="I42" s="3" t="s">
+      <c r="K42" s="3" t="s">
         <v>788</v>
       </c>
-      <c r="J42" s="3" t="s">
+      <c r="M42" s="8" t="s">
         <v>789</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>790</v>
-      </c>
-      <c r="M42" s="8" t="s">
-        <v>791</v>
       </c>
       <c r="N42" s="8"/>
       <c r="O42" s="8" t="s">
+        <v>790</v>
+      </c>
+      <c r="Q42" s="8" t="s">
+        <v>791</v>
+      </c>
+      <c r="R42" s="8" t="s">
         <v>792</v>
       </c>
-      <c r="Q42" s="8" t="s">
+      <c r="S42" s="8" t="s">
         <v>793</v>
       </c>
-      <c r="R42" s="8" t="s">
+      <c r="U42" s="8" t="s">
         <v>794</v>
-      </c>
-      <c r="S42" s="8" t="s">
-        <v>795</v>
-      </c>
-      <c r="U42" s="8" t="s">
-        <v>796</v>
       </c>
       <c r="V42" s="8"/>
       <c r="W42" s="8" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="Y42" s="8" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="Z42" s="8"/>
       <c r="AA42" s="8" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="AC42" s="8" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="AD42" s="8"/>
       <c r="AE42" s="8" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A43" s="5" t="s">
+        <v>800</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>801</v>
+      </c>
+      <c r="C43" s="5" t="s">
         <v>802</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="E43" s="5" t="s">
         <v>803</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="F43" s="5" t="s">
         <v>804</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="G43" s="5" t="s">
         <v>805</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="I43" s="8" t="s">
         <v>806</v>
       </c>
-      <c r="G43" s="5" t="s">
+      <c r="J43" s="8" t="s">
         <v>807</v>
       </c>
-      <c r="I43" s="8" t="s">
+      <c r="K43" s="8" t="s">
         <v>808</v>
       </c>
-      <c r="J43" s="8" t="s">
+      <c r="M43" s="8" t="s">
         <v>809</v>
-      </c>
-      <c r="K43" s="8" t="s">
-        <v>810</v>
-      </c>
-      <c r="M43" s="8" t="s">
-        <v>811</v>
       </c>
       <c r="N43" s="8"/>
       <c r="O43" s="8" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="Q43" s="8" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="R43" s="8"/>
       <c r="S43" s="8" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="U43" s="8" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="V43" s="8"/>
       <c r="W43" s="8" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="Y43" s="8" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="Z43" s="8"/>
       <c r="AA43" s="8" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="AC43" s="8" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="AD43" s="8"/>
       <c r="AE43" s="8" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A44" s="3" t="s">
+        <v>819</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>821</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="E44" s="5" t="s">
         <v>822</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="F44" s="5" t="s">
         <v>823</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="G44" s="5" t="s">
         <v>824</v>
       </c>
-      <c r="F44" s="5" t="s">
+      <c r="I44" s="8" t="s">
         <v>825</v>
       </c>
-      <c r="G44" s="5" t="s">
+      <c r="J44" s="8" t="s">
         <v>826</v>
       </c>
-      <c r="I44" s="8" t="s">
+      <c r="K44" s="8" t="s">
         <v>827</v>
       </c>
-      <c r="J44" s="8" t="s">
+      <c r="M44" s="8" t="s">
         <v>828</v>
       </c>
-      <c r="K44" s="8" t="s">
+      <c r="N44" s="8" t="s">
         <v>829</v>
       </c>
-      <c r="M44" s="8" t="s">
+      <c r="O44" s="8" t="s">
         <v>830</v>
       </c>
-      <c r="N44" s="8" t="s">
+      <c r="Q44" s="8" t="s">
         <v>831</v>
-      </c>
-      <c r="O44" s="8" t="s">
-        <v>832</v>
-      </c>
-      <c r="Q44" s="8" t="s">
-        <v>833</v>
       </c>
       <c r="R44" s="8"/>
       <c r="S44" s="8" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="U44" s="8" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="V44" s="8"/>
       <c r="W44" s="8" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="Y44" s="8" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="Z44" s="8"/>
       <c r="AA44" s="8" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="AC44" s="8" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="AD44" s="8"/>
       <c r="AE44" s="8" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="45" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A45" s="8" t="s">
+        <v>839</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>840</v>
+      </c>
+      <c r="C45" s="8" t="s">
         <v>841</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="E45" s="5" t="s">
         <v>842</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="F45" s="5" t="s">
         <v>843</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="G45" s="5" t="s">
         <v>844</v>
       </c>
-      <c r="F45" s="5" t="s">
+      <c r="I45" s="8" t="s">
         <v>845</v>
       </c>
-      <c r="G45" s="5" t="s">
+      <c r="J45" s="8" t="s">
         <v>846</v>
       </c>
-      <c r="I45" s="8" t="s">
+      <c r="K45" s="8" t="s">
         <v>847</v>
       </c>
-      <c r="J45" s="8" t="s">
+      <c r="M45" s="8" t="s">
         <v>848</v>
-      </c>
-      <c r="K45" s="8" t="s">
-        <v>849</v>
-      </c>
-      <c r="M45" s="8" t="s">
-        <v>850</v>
       </c>
       <c r="N45" s="8"/>
       <c r="O45" s="8" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="Q45" s="8" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="R45" s="8"/>
       <c r="S45" s="8" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="U45" s="8" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="V45" s="8"/>
       <c r="W45" s="8" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="Y45" s="8" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="Z45" s="8"/>
       <c r="AA45" s="8" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="AC45" s="8" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="AD45" s="8"/>
       <c r="AE45" s="8" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A46" s="3" t="s">
+        <v>858</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>860</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="E46" s="8" t="s">
         <v>861</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="F46" s="8" t="s">
         <v>862</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="G46" s="8" t="s">
         <v>863</v>
       </c>
-      <c r="F46" s="8" t="s">
+      <c r="I46" s="8" t="s">
         <v>864</v>
-      </c>
-      <c r="G46" s="8" t="s">
-        <v>865</v>
-      </c>
-      <c r="I46" s="8" t="s">
-        <v>866</v>
       </c>
       <c r="J46" s="8"/>
       <c r="K46" s="8" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="M46" s="8" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="N46" s="8"/>
       <c r="O46" s="8" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="Q46" s="8" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="R46" s="8"/>
       <c r="S46" s="8" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="U46" s="8" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="V46" s="8"/>
       <c r="W46" s="8" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="Y46" s="8" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="Z46" s="8"/>
       <c r="AA46" s="8" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="AC46" s="8" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="AD46" s="8"/>
       <c r="AE46" s="8" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
     </row>
     <row r="47" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A47" s="8" t="s">
+        <v>876</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>877</v>
+      </c>
+      <c r="C47" s="8" t="s">
         <v>878</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="E47" s="8" t="s">
         <v>879</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>880</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>881</v>
       </c>
       <c r="F47" s="8"/>
       <c r="G47" s="8" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="J47" s="8"/>
       <c r="K47" s="8" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="M47" s="8" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="N47" s="8"/>
       <c r="O47" s="8" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="Q47" s="8" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="R47" s="8"/>
       <c r="S47" s="8" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="U47" s="8" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="V47" s="8"/>
       <c r="W47" s="8" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="Y47" s="8" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="Z47" s="8"/>
       <c r="AA47" s="8" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="AC47" s="8" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="AD47" s="8"/>
       <c r="AE47" s="8" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="48" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A48" s="8" t="s">
+        <v>893</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>894</v>
+      </c>
+      <c r="C48" s="8" t="s">
         <v>895</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="E48" s="5" t="s">
         <v>896</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>897</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>898</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>67</v>
       </c>
       <c r="G48" s="5" t="s">
+        <v>897</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>898</v>
+      </c>
+      <c r="J48" s="8" t="s">
+        <v>766</v>
+      </c>
+      <c r="K48" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="I48" s="8" t="s">
+      <c r="M48" s="8" t="s">
         <v>900</v>
-      </c>
-      <c r="J48" s="8" t="s">
-        <v>768</v>
-      </c>
-      <c r="K48" s="8" t="s">
-        <v>901</v>
-      </c>
-      <c r="M48" s="8" t="s">
-        <v>902</v>
       </c>
       <c r="N48" s="8"/>
       <c r="O48" s="8" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="Q48" s="8" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="R48" s="8"/>
       <c r="S48" s="8" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="U48" s="8" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="V48" s="8"/>
       <c r="W48" s="8" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="Y48" s="8" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="Z48" s="8"/>
       <c r="AA48" s="8" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="AC48" s="8" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="AD48" s="8"/>
       <c r="AE48" s="8" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
     </row>
     <row r="49" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A49" s="8" t="s">
+        <v>910</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>911</v>
+      </c>
+      <c r="C49" s="8" t="s">
         <v>912</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="E49" s="8" t="s">
         <v>913</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>914</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>915</v>
       </c>
       <c r="F49" s="8"/>
       <c r="G49" s="8" t="s">
+        <v>914</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>915</v>
+      </c>
+      <c r="J49" s="8" t="s">
         <v>916</v>
       </c>
-      <c r="I49" s="8" t="s">
+      <c r="K49" s="8" t="s">
         <v>917</v>
       </c>
-      <c r="J49" s="8" t="s">
+      <c r="M49" s="8" t="s">
         <v>918</v>
-      </c>
-      <c r="K49" s="8" t="s">
-        <v>919</v>
-      </c>
-      <c r="M49" s="8" t="s">
-        <v>920</v>
       </c>
       <c r="N49" s="8"/>
       <c r="O49" s="8" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="Q49" s="8" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="R49" s="8"/>
       <c r="S49" s="8" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="U49" s="8" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="V49" s="8"/>
       <c r="W49" s="8" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="Y49" s="8" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Z49" s="8"/>
       <c r="AA49" s="8" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="AC49" s="8" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="AD49" s="8"/>
       <c r="AE49" s="8" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
     </row>
     <row r="50" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A50" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>929</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>930</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="E50" s="8" t="s">
         <v>931</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="F50" s="8" t="s">
         <v>932</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="G50" s="8" t="s">
         <v>933</v>
       </c>
-      <c r="F50" s="8" t="s">
+      <c r="I50" s="8" t="s">
         <v>934</v>
       </c>
-      <c r="G50" s="8" t="s">
+      <c r="J50" s="8" t="s">
+        <v>1426</v>
+      </c>
+      <c r="K50" s="8" t="s">
         <v>935</v>
       </c>
-      <c r="I50" s="8" t="s">
+      <c r="M50" s="8" t="s">
         <v>936</v>
       </c>
-      <c r="J50" s="8" t="s">
-        <v>1428</v>
-      </c>
-      <c r="K50" s="8" t="s">
+      <c r="N50" s="8" t="s">
         <v>937</v>
       </c>
-      <c r="M50" s="8" t="s">
+      <c r="O50" s="8" t="s">
         <v>938</v>
       </c>
-      <c r="N50" s="8" t="s">
+      <c r="Q50" s="8" t="s">
         <v>939</v>
-      </c>
-      <c r="O50" s="8" t="s">
-        <v>940</v>
-      </c>
-      <c r="Q50" s="8" t="s">
-        <v>941</v>
       </c>
       <c r="R50" s="8"/>
       <c r="S50" s="8" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="U50" s="8" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="V50" s="8"/>
       <c r="W50" s="8" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="Y50" s="8" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="Z50" s="8"/>
       <c r="AA50" s="8" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="AC50" s="8" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="AD50" s="8"/>
       <c r="AE50" s="8" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="51" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A51" s="8" t="s">
+        <v>947</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>948</v>
+      </c>
+      <c r="C51" s="8" t="s">
         <v>949</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="E51" s="8" t="s">
         <v>950</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="F51" s="8" t="s">
         <v>951</v>
       </c>
-      <c r="E51" s="8" t="s">
+      <c r="G51" s="8" t="s">
         <v>952</v>
       </c>
-      <c r="F51" s="8" t="s">
+      <c r="I51" s="8" t="s">
         <v>953</v>
       </c>
-      <c r="G51" s="8" t="s">
+      <c r="J51" s="8" t="s">
         <v>954</v>
       </c>
-      <c r="I51" s="8" t="s">
+      <c r="K51" s="8" t="s">
         <v>955</v>
       </c>
-      <c r="J51" s="8" t="s">
+      <c r="M51" s="8" t="s">
         <v>956</v>
-      </c>
-      <c r="K51" s="8" t="s">
-        <v>957</v>
-      </c>
-      <c r="M51" s="8" t="s">
-        <v>958</v>
       </c>
       <c r="N51" s="8"/>
       <c r="O51" s="8" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="Q51" s="8" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="R51" s="8"/>
       <c r="S51" s="8" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="U51" s="8" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="V51" s="8"/>
       <c r="W51" s="8" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="Y51" s="8" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="Z51" s="8"/>
       <c r="AA51" s="8" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="AC51" s="8" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="AD51" s="8"/>
       <c r="AE51" s="8" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
     </row>
     <row r="52" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A52" s="5" t="s">
+        <v>966</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>967</v>
+      </c>
+      <c r="C52" s="5" t="s">
         <v>968</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="E52" s="8" t="s">
         <v>969</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="F52" s="8" t="s">
         <v>970</v>
       </c>
-      <c r="E52" s="8" t="s">
+      <c r="G52" s="8" t="s">
         <v>971</v>
       </c>
-      <c r="F52" s="8" t="s">
+      <c r="I52" s="8" t="s">
         <v>972</v>
       </c>
-      <c r="G52" s="8" t="s">
+      <c r="J52" s="8" t="s">
         <v>973</v>
       </c>
-      <c r="I52" s="8" t="s">
+      <c r="K52" s="8" t="s">
         <v>974</v>
       </c>
-      <c r="J52" s="8" t="s">
+      <c r="M52" s="8" t="s">
         <v>975</v>
-      </c>
-      <c r="K52" s="8" t="s">
-        <v>976</v>
-      </c>
-      <c r="M52" s="8" t="s">
-        <v>977</v>
       </c>
       <c r="N52" s="8"/>
       <c r="O52" s="8" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="Q52" s="8" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="R52" s="8"/>
       <c r="S52" s="8" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="U52" s="8" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="V52" s="8"/>
       <c r="W52" s="8" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="Y52" s="8" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="Z52" s="8"/>
       <c r="AA52" s="8" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="AC52" s="8" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="AD52" s="8"/>
       <c r="AE52" s="8" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="53" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A53" s="3" t="s">
+        <v>985</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>987</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="E53" s="8" t="s">
         <v>988</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="F53" s="8" t="s">
         <v>989</v>
       </c>
-      <c r="E53" s="8" t="s">
+      <c r="G53" s="8" t="s">
         <v>990</v>
       </c>
-      <c r="F53" s="8" t="s">
+      <c r="I53" s="5" t="s">
         <v>991</v>
       </c>
-      <c r="G53" s="8" t="s">
+      <c r="J53" s="5" t="s">
         <v>992</v>
       </c>
-      <c r="I53" s="5" t="s">
+      <c r="K53" s="5" t="s">
         <v>993</v>
       </c>
-      <c r="J53" s="5" t="s">
+      <c r="M53" s="8" t="s">
         <v>994</v>
-      </c>
-      <c r="K53" s="5" t="s">
-        <v>995</v>
-      </c>
-      <c r="M53" s="8" t="s">
-        <v>996</v>
       </c>
       <c r="N53" s="8"/>
       <c r="O53" s="8" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="Q53" s="8" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="R53" s="8"/>
       <c r="S53" s="8" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="U53" s="8" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="V53" s="8"/>
       <c r="W53" s="8" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="Y53" s="8" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="Z53" s="8"/>
       <c r="AA53" s="8" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="AC53" s="8" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="AD53" s="8"/>
       <c r="AE53" s="8" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="54" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A54" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>1006</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="E54" s="8" t="s">
         <v>1007</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="F54" s="8" t="s">
         <v>1008</v>
       </c>
-      <c r="E54" s="8" t="s">
+      <c r="G54" s="8" t="s">
         <v>1009</v>
       </c>
-      <c r="F54" s="8" t="s">
+      <c r="I54" s="8" t="s">
         <v>1010</v>
       </c>
-      <c r="G54" s="8" t="s">
+      <c r="J54" s="8" t="s">
         <v>1011</v>
       </c>
-      <c r="I54" s="8" t="s">
+      <c r="K54" s="8" t="s">
         <v>1012</v>
       </c>
-      <c r="J54" s="8" t="s">
+      <c r="M54" s="8" t="s">
         <v>1013</v>
-      </c>
-      <c r="K54" s="8" t="s">
-        <v>1014</v>
-      </c>
-      <c r="M54" s="8" t="s">
-        <v>1015</v>
       </c>
       <c r="N54" s="8"/>
       <c r="O54" s="8" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="Q54" s="8" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="R54" s="8"/>
       <c r="S54" s="8" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="U54" s="8" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="V54" s="8"/>
       <c r="W54" s="8" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="Y54" s="8" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="Z54" s="8"/>
       <c r="AA54" s="8" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="AC54" s="8" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="AD54" s="8"/>
       <c r="AE54" s="8" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="55" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A55" s="3" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>1025</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="E55" s="3" t="s">
         <v>1026</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="F55" s="3" t="s">
+        <v>1425</v>
+      </c>
+      <c r="G55" s="3" t="s">
         <v>1027</v>
       </c>
-      <c r="E55" s="3" t="s">
+      <c r="I55" s="5" t="s">
         <v>1028</v>
       </c>
-      <c r="F55" s="3" t="s">
-        <v>1427</v>
-      </c>
-      <c r="G55" s="3" t="s">
+      <c r="J55" s="5" t="s">
         <v>1029</v>
       </c>
-      <c r="I55" s="5" t="s">
+      <c r="K55" s="5" t="s">
         <v>1030</v>
       </c>
-      <c r="J55" s="5" t="s">
+      <c r="M55" s="8" t="s">
         <v>1031</v>
-      </c>
-      <c r="K55" s="5" t="s">
-        <v>1032</v>
-      </c>
-      <c r="M55" s="8" t="s">
-        <v>1033</v>
       </c>
       <c r="N55" s="8"/>
       <c r="O55" s="8" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="Q55" s="8" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="R55" s="8"/>
       <c r="S55" s="8" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="U55" s="8" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="V55" s="8"/>
       <c r="W55" s="8" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="Y55" s="8" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="Z55" s="8"/>
       <c r="AA55" s="8" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="AC55" s="8" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="AD55" s="8"/>
       <c r="AE55" s="8" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="56" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A56" s="3" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>1043</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="E56" s="8" t="s">
         <v>1044</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="F56" s="8" t="s">
         <v>1045</v>
       </c>
-      <c r="E56" s="8" t="s">
+      <c r="G56" s="8" t="s">
         <v>1046</v>
       </c>
-      <c r="F56" s="8" t="s">
+      <c r="I56" s="3" t="s">
         <v>1047</v>
       </c>
-      <c r="G56" s="8" t="s">
+      <c r="J56" s="3" t="s">
         <v>1048</v>
       </c>
-      <c r="I56" s="3" t="s">
+      <c r="K56" s="3" t="s">
         <v>1049</v>
       </c>
-      <c r="J56" s="3" t="s">
+      <c r="M56" s="8" t="s">
         <v>1050</v>
-      </c>
-      <c r="K56" s="3" t="s">
-        <v>1051</v>
-      </c>
-      <c r="M56" s="8" t="s">
-        <v>1052</v>
       </c>
       <c r="N56" s="8"/>
       <c r="O56" s="8" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="Q56" s="8" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="R56" s="8"/>
       <c r="S56" s="8" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="U56" s="8" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="V56" s="8"/>
       <c r="W56" s="8" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="Y56" s="8" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="Z56" s="8"/>
       <c r="AA56" s="8" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="AC56" s="8" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="AD56" s="8"/>
       <c r="AE56" s="8" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="57" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A57" s="3" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>1062</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="E57" s="8" t="s">
         <v>1063</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="F57" s="8" t="s">
         <v>1064</v>
       </c>
-      <c r="E57" s="8" t="s">
+      <c r="G57" s="8" t="s">
         <v>1065</v>
-      </c>
-      <c r="F57" s="8" t="s">
-        <v>1066</v>
-      </c>
-      <c r="G57" s="8" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="58" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A58" s="8" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C58" s="8" t="s">
         <v>1068</v>
-      </c>
-      <c r="B58" s="8" t="s">
-        <v>1069</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="59" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A59" s="8" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C59" s="8" t="s">
         <v>1071</v>
-      </c>
-      <c r="B59" s="8" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>1073</v>
       </c>
     </row>
     <row r="60" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A60" s="8" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C60" s="8" t="s">
         <v>1074</v>
-      </c>
-      <c r="B60" s="8" t="s">
-        <v>1075</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>1076</v>
       </c>
       <c r="E60" s="4"/>
       <c r="F60" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="61" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A61" s="8" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C61" s="8" t="s">
         <v>1078</v>
-      </c>
-      <c r="B61" s="8" t="s">
-        <v>1079</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>1080</v>
       </c>
     </row>
     <row r="62" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A62" s="8" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C62" s="8" t="s">
         <v>1081</v>
-      </c>
-      <c r="B62" s="8" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>1083</v>
       </c>
       <c r="E62" s="6"/>
       <c r="F62" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="63" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A63" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C63" s="8" t="s">
         <v>1085</v>
-      </c>
-      <c r="B63" s="8" t="s">
-        <v>1086</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>1087</v>
       </c>
     </row>
     <row r="64" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A64" s="8" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C64" s="8" t="s">
         <v>1088</v>
-      </c>
-      <c r="B64" s="8" t="s">
-        <v>1089</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>1090</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A65" s="3" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>1091</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>1093</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A66" s="8" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C66" s="8" t="s">
         <v>1094</v>
-      </c>
-      <c r="B66" s="8" t="s">
-        <v>1095</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>1096</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A67" s="8" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="B67" s="8"/>
       <c r="C67" s="8" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A68" s="8" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="B68" s="8"/>
       <c r="C68" s="8" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A69" s="8" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C69" s="8" t="s">
         <v>1101</v>
-      </c>
-      <c r="B69" s="8" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>1103</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A70" s="8" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="B70" s="8"/>
       <c r="C70" s="8" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A71" s="8" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C71" s="8" t="s">
         <v>1106</v>
-      </c>
-      <c r="B71" s="8" t="s">
-        <v>1107</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>1108</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A72" s="7" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C72" s="7" t="s">
         <v>1109</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>1110</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>1111</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A73" s="5" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C73" s="5" t="s">
         <v>1112</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>1113</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>1114</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A74" s="5" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C74" s="5" t="s">
         <v>1115</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>1116</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>1117</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A75" s="3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>1118</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>1119</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>1120</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A76" s="8" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C76" s="8" t="s">
         <v>1121</v>
-      </c>
-      <c r="B76" s="8" t="s">
-        <v>1122</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>1123</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A77" s="8" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C77" s="8" t="s">
         <v>1124</v>
-      </c>
-      <c r="B77" s="8" t="s">
-        <v>1125</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>1126</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A78" s="8" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="B78" s="8"/>
       <c r="C78" s="8" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A79" s="3" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>1129</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>1131</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A80" s="8" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C80" s="8" t="s">
         <v>1132</v>
-      </c>
-      <c r="B80" s="8" t="s">
-        <v>1133</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>1134</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A81" s="5" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C81" s="5" t="s">
         <v>1135</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>1136</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>1137</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A82" s="5" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C82" s="5" t="s">
         <v>1138</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>1139</v>
-      </c>
-      <c r="C82" s="5" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A83" s="3" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>1141</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>1142</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>1143</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A84" s="3" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>1144</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>1145</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>1146</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A85" s="8" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="B85" s="8"/>
       <c r="C85" s="8" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A86" s="5" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C86" s="5" t="s">
         <v>1149</v>
-      </c>
-      <c r="B86" s="5" t="s">
-        <v>1150</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>1151</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A87" s="8" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C87" s="8" t="s">
         <v>1152</v>
-      </c>
-      <c r="B87" s="8" t="s">
-        <v>1153</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>1154</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A88" s="8" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="B88" s="8"/>
       <c r="C88" s="8" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A89" s="5" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C89" s="5" t="s">
         <v>1157</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>1158</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>1159</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A90" s="5" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C90" s="5" t="s">
         <v>1160</v>
-      </c>
-      <c r="B90" s="5" t="s">
-        <v>1161</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>1162</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A91" s="5" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C91" s="5" t="s">
         <v>1163</v>
-      </c>
-      <c r="B91" s="5" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>1165</v>
       </c>
     </row>
   </sheetData>
@@ -8935,937 +8922,937 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1166</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1167</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1168</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A8" s="8" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A9" s="8" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A12" s="8" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A14" s="8" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A15" s="8" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A16" s="8" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A17" s="8" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A18" s="8" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A19" s="8" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A20" s="8" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A22" s="8" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A23" s="8" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A24" s="8" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A25" s="8" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A26" s="8" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A27" s="8" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A28" s="8" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A29" s="8" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A30" s="8" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A31" s="8" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A32" s="8" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A33" s="8" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A34" s="8" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A35" s="8" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="8" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A37" s="8" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A38" s="8" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A39" s="8" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A40" s="8" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A41" s="8" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A42" s="8" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A43" s="8" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A44" s="8" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A45" s="8" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A46" s="8" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A47" s="8" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A48" s="8" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A49" s="8" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A50" s="8" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A51" s="8" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A52" s="8" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A53" s="8" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A54" s="8" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A55" s="8" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A56" s="8" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A57" s="8" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A58" s="8" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A59" s="8" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A60" s="8" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A61" s="8" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A62" s="8" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A63" s="8" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A64" s="8" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A65" s="8" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A66" s="8" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A67" s="8" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A68" s="8" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A69" s="8" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A70" s="8" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A71" s="8" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A72" s="8" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A73" s="8" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A74" s="8" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A75" s="8" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A76" s="8" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A77" s="8" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A78" s="8" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A79" s="8" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A80" s="8" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A81" s="8" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A82" s="8" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A83" s="8" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A84" s="8" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A85" s="8" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
     </row>
   </sheetData>
@@ -9969,46 +9956,46 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>1337</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>1338</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>1339</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>1340</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>1341</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>1342</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>1343</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>1344</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>1345</v>
       </c>
     </row>
   </sheetData>

--- a/key検討用/ppxkey.xlsx
+++ b/key検討用/ppxkey.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gocho\AppData\Local\Temp\Rar$DIa7312.11817.rartemp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gocho\Desktop\ppx_cust20251217(Wed)\ppx_cust\key検討用\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D9EA39F-DFA9-4CCF-ABD7-22F9AFBE5C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84AA83D7-A9CF-459B-9C24-910983763043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1458" uniqueCount="1428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1463" uniqueCount="1429">
   <si>
     <t>キー</t>
   </si>
@@ -1290,6 +1290,9 @@
     <t>[Ctrl+Shift+E]</t>
   </si>
   <si>
+    <t>(PPtray)メモ</t>
+  </si>
+  <si>
     <t>%k"^\E"</t>
   </si>
   <si>
@@ -1467,6 +1470,9 @@
     <t>[Ctrl+Shift+H]</t>
   </si>
   <si>
+    <t>ダイアログでエントリのパスを開く(DialogHandler)</t>
+  </si>
+  <si>
     <t>%k"^\H"</t>
   </si>
   <si>
@@ -2383,9 +2389,6 @@
   </si>
   <si>
     <t>[Ctrl+X]</t>
-  </si>
-  <si>
-    <t>エントリをクリップボードへ切り取り</t>
   </si>
   <si>
     <t>%k"^X"</t>
@@ -4399,7 +4402,17 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>サブディレクトリ以下をインタラクティブサーチ(fzf)</t>
+    <t>エントリをクリップボードへ切り取り/窓操作メニュー（マークなし、タブ付窓のみ）</t>
+    <rPh sb="18" eb="21">
+      <t>マドソウサ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>マド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -5037,7 +5050,7 @@
         <v>26</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>28</v>
@@ -6355,2552 +6368,2562 @@
       <c r="Q23" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="R23" s="8"/>
+      <c r="R23" s="8" t="s">
+        <v>422</v>
+      </c>
       <c r="S23" s="8" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="U23" s="8" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="V23" s="8"/>
       <c r="W23" s="8" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Y23" s="8" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Z23" s="8"/>
       <c r="AA23" s="8" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AC23" s="8" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AD23" s="8"/>
       <c r="AE23" s="8" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A24" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N24" s="8" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="O24" s="8" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q24" s="8" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="R24" s="8" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="S24" s="8" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="U24" s="8" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="V24" s="8"/>
       <c r="W24" s="8" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Y24" s="8" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Z24" s="8"/>
       <c r="AA24" s="8" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AC24" s="8" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AD24" s="8"/>
       <c r="AE24" s="8" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A25" s="5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J25" s="8"/>
       <c r="K25" s="8" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N25" s="8"/>
       <c r="O25" s="8" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Q25" s="8" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="R25" s="8" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="S25" s="8" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="U25" s="8" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="V25" s="8"/>
       <c r="W25" s="8" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Y25" s="8" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Z25" s="8"/>
       <c r="AA25" s="8" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AC25" s="8" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AD25" s="8"/>
       <c r="AE25" s="8" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A26" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>475</v>
-      </c>
-      <c r="J26" s="1"/>
+        <v>476</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>204</v>
+      </c>
       <c r="K26" s="8" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N26" s="8" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Q26" s="8" t="s">
-        <v>480</v>
-      </c>
-      <c r="R26" s="8"/>
+        <v>481</v>
+      </c>
+      <c r="R26" s="8" t="s">
+        <v>482</v>
+      </c>
       <c r="S26" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="U26" s="8" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="V26" s="8"/>
       <c r="W26" s="8" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="Y26" s="8" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="Z26" s="8"/>
       <c r="AA26" s="8" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AC26" s="8" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AD26" s="8"/>
       <c r="AE26" s="8" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A27" s="8" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="N27" s="8" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="O27" s="8" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="Q27" s="8" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="R27" s="8" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="S27" s="8" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="U27" s="8" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="V27" s="8"/>
       <c r="W27" s="8" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="Y27" s="8" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="Z27" s="8"/>
       <c r="AA27" s="8" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AC27" s="8" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AD27" s="8"/>
       <c r="AE27" s="8" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="28" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A28" s="5" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>1427</v>
+        <v>266</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="M28" s="8" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="N28" s="8"/>
       <c r="O28" s="8" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="Q28" s="8" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="R28" s="8"/>
       <c r="S28" s="8" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="U28" s="8" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="V28" s="8"/>
       <c r="W28" s="8" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="Y28" s="8" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="Z28" s="8"/>
       <c r="AA28" s="8" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AC28" s="8" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AD28" s="8"/>
       <c r="AE28" s="8" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="29" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A29" s="3" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>533</v>
-      </c>
-      <c r="J29" s="8"/>
+        <v>535</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="K29" s="8" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="N29" s="8"/>
       <c r="O29" s="8" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="Q29" s="8" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="R29" s="8"/>
       <c r="S29" s="8" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="U29" s="8" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="V29" s="8"/>
       <c r="W29" s="8" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="Y29" s="8" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="Z29" s="8"/>
       <c r="AA29" s="8" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AC29" s="8" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AD29" s="8"/>
       <c r="AE29" s="8" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A30" s="3" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>551</v>
-      </c>
-      <c r="J30" s="8"/>
+        <v>553</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>246</v>
+      </c>
       <c r="K30" s="8" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="M30" s="8" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="N30" s="8"/>
       <c r="O30" s="8" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="Q30" s="8" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="R30" s="8" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="S30" s="8" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="U30" s="8" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="V30" s="8"/>
       <c r="W30" s="8" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="Y30" s="8" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="Z30" s="8"/>
       <c r="AA30" s="8" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AC30" s="8" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AD30" s="8"/>
       <c r="AE30" s="8" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A31" s="3" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="N31" s="8" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="O31" s="8" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="Q31" s="8" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="R31" s="8" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="S31" s="8" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="U31" s="8" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="V31" s="8"/>
       <c r="W31" s="8" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="Y31" s="8" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="Z31" s="8"/>
       <c r="AA31" s="8" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AC31" s="8" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AD31" s="8" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="AE31" s="8" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A32" s="8" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="J32" s="8" t="s">
         <v>27</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="M32" s="8" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="N32" s="8"/>
       <c r="O32" s="8" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="Q32" s="8" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="R32" s="8"/>
       <c r="S32" s="8" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="U32" s="8" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="V32" s="8"/>
       <c r="W32" s="8" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="Y32" s="8" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="Z32" s="8"/>
       <c r="AA32" s="8" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AC32" s="8" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AD32" s="8"/>
       <c r="AE32" s="8" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A33" s="5" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="J33" s="8"/>
       <c r="K33" s="8" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="N33" s="8" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="O33" s="8" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="Q33" s="8" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="R33" s="8"/>
       <c r="S33" s="8" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="U33" s="8" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="V33" s="8"/>
       <c r="W33" s="8" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="Y33" s="8" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="Z33" s="8"/>
       <c r="AA33" s="8" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="AC33" s="8" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="AD33" s="8"/>
       <c r="AE33" s="8" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A34" s="3" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="M34" s="8" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="N34" s="8"/>
       <c r="O34" s="8" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="Q34" s="8" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="R34" s="8"/>
       <c r="S34" s="8" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="U34" s="8" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="V34" s="8"/>
       <c r="W34" s="8" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="Y34" s="8" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="Z34" s="8"/>
       <c r="AA34" s="8" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AC34" s="8" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AD34" s="8"/>
       <c r="AE34" s="8" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A35" s="8" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="J35" s="8"/>
       <c r="K35" s="8" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="Q35" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="R35" s="8" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="S35" s="8" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="U35" s="8" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="V35" s="8"/>
       <c r="W35" s="8" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="Y35" s="8" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="Z35" s="8"/>
       <c r="AA35" s="8" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="AC35" s="8" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="AD35" s="8"/>
       <c r="AE35" s="8" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A36" s="3" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="J36" s="8"/>
       <c r="K36" s="8" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="M36" s="8" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="N36" s="8" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="O36" s="8" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="Q36" s="8" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="R36" s="8"/>
       <c r="S36" s="8" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="U36" s="8" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="V36" s="8"/>
       <c r="W36" s="8" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="Y36" s="8" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="Z36" s="8"/>
       <c r="AA36" s="8" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="AC36" s="8" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="AD36" s="8"/>
       <c r="AE36" s="8" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A37" s="7" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="J37" s="8"/>
       <c r="K37" s="8" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="M37" s="8" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="N37" s="8"/>
       <c r="O37" s="8" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="Q37" s="8" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="R37" s="8"/>
       <c r="S37" s="8" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="U37" s="8" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="V37" s="8"/>
       <c r="W37" s="8" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="Y37" s="5" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="Z37" s="5" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="AA37" s="5" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="AC37" s="8" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="AD37" s="8"/>
       <c r="AE37" s="8" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A38" s="8" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="J38" s="8" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="M38" s="8" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="N38" s="8" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="O38" s="8" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="Q38" s="8" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="R38" s="8"/>
       <c r="S38" s="8" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="U38" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="V38" s="8"/>
       <c r="W38" s="8" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="Y38" s="8" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="Z38" s="8"/>
       <c r="AA38" s="8" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="AC38" s="8" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="AD38" s="8"/>
       <c r="AE38" s="8" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A39" s="3" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="J39" s="8"/>
       <c r="K39" s="8" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="N39" s="8"/>
       <c r="O39" s="8" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="Q39" s="8" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="R39" s="8"/>
       <c r="S39" s="8" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="U39" s="8" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="V39" s="8"/>
       <c r="W39" s="8" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="Y39" s="8" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="Z39" s="8"/>
       <c r="AA39" s="8" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="AC39" s="8" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="AD39" s="8"/>
       <c r="AE39" s="8" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A40" s="3" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="M40" s="8" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="N40" s="8" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="O40" s="8" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="Q40" s="8" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="R40" s="8" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="S40" s="8" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="U40" s="8" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="V40" s="8"/>
       <c r="W40" s="8" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="Y40" s="8" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="Z40" s="8"/>
       <c r="AA40" s="8" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="AC40" s="8" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="AD40" s="8"/>
       <c r="AE40" s="8" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A41" s="3" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="M41" s="8" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="N41" s="8" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="O41" s="8" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="Q41" s="8" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="R41" s="8" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="S41" s="8" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="U41" s="8" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="V41" s="8"/>
       <c r="W41" s="8" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="Y41" s="8" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="Z41" s="8"/>
       <c r="AA41" s="8" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="AC41" s="8" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="AD41" s="8"/>
       <c r="AE41" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A42" s="8" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>787</v>
+        <v>1428</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="M42" s="8" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="N42" s="8"/>
       <c r="O42" s="8" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="Q42" s="8" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="R42" s="8" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="S42" s="8" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="U42" s="8" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="V42" s="8"/>
       <c r="W42" s="8" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="Y42" s="8" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="Z42" s="8"/>
       <c r="AA42" s="8" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="AC42" s="8" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AD42" s="8"/>
       <c r="AE42" s="8" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A43" s="5" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="M43" s="8" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="N43" s="8"/>
       <c r="O43" s="8" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="Q43" s="8" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="R43" s="8"/>
       <c r="S43" s="8" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="U43" s="8" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="V43" s="8"/>
       <c r="W43" s="8" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="Y43" s="8" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="Z43" s="8"/>
       <c r="AA43" s="8" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="AC43" s="8" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AD43" s="8"/>
       <c r="AE43" s="8" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A44" s="3" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="M44" s="8" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="N44" s="8" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="O44" s="8" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="Q44" s="8" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="R44" s="8"/>
       <c r="S44" s="8" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="U44" s="8" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="V44" s="8"/>
       <c r="W44" s="8" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="Y44" s="8" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="Z44" s="8"/>
       <c r="AA44" s="8" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="AC44" s="8" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="AD44" s="8"/>
       <c r="AE44" s="8" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="45" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A45" s="8" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="K45" s="8" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="M45" s="8" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="N45" s="8"/>
       <c r="O45" s="8" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="Q45" s="8" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="R45" s="8"/>
       <c r="S45" s="8" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="U45" s="8" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="V45" s="8"/>
       <c r="W45" s="8" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="Y45" s="8" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="Z45" s="8"/>
       <c r="AA45" s="8" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="AC45" s="8" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="AD45" s="8"/>
       <c r="AE45" s="8" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A46" s="3" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="J46" s="8"/>
       <c r="K46" s="8" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="M46" s="8" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="N46" s="8"/>
       <c r="O46" s="8" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="Q46" s="8" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="R46" s="8"/>
       <c r="S46" s="8" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="U46" s="8" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="V46" s="8"/>
       <c r="W46" s="8" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="Y46" s="8" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="Z46" s="8"/>
       <c r="AA46" s="8" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="AC46" s="8" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="AD46" s="8"/>
       <c r="AE46" s="8" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="47" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A47" s="8" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="F47" s="8"/>
       <c r="G47" s="8" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="J47" s="8"/>
       <c r="K47" s="8" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="M47" s="8" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="N47" s="8"/>
       <c r="O47" s="8" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="Q47" s="8" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="R47" s="8"/>
       <c r="S47" s="8" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="U47" s="8" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="V47" s="8"/>
       <c r="W47" s="8" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="Y47" s="8" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="Z47" s="8"/>
       <c r="AA47" s="8" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="AC47" s="8" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="AD47" s="8"/>
       <c r="AE47" s="8" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="48" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A48" s="8" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>67</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="K48" s="8" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="M48" s="8" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="N48" s="8"/>
       <c r="O48" s="8" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="Q48" s="8" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="R48" s="8"/>
       <c r="S48" s="8" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="U48" s="8" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="V48" s="8"/>
       <c r="W48" s="8" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="Y48" s="8" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="Z48" s="8"/>
       <c r="AA48" s="8" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="AC48" s="8" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="AD48" s="8"/>
       <c r="AE48" s="8" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="49" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A49" s="8" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="F49" s="8"/>
       <c r="G49" s="8" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="M49" s="8" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="N49" s="8"/>
       <c r="O49" s="8" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="Q49" s="8" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="R49" s="8"/>
       <c r="S49" s="8" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="U49" s="8" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="V49" s="8"/>
       <c r="W49" s="8" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="Y49" s="8" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="Z49" s="8"/>
       <c r="AA49" s="8" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="AC49" s="8" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="AD49" s="8"/>
       <c r="AE49" s="8" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
     </row>
     <row r="50" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A50" s="3" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="K50" s="8" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="M50" s="8" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="N50" s="8" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="O50" s="8" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="Q50" s="8" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="R50" s="8"/>
       <c r="S50" s="8" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="U50" s="8" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="V50" s="8"/>
       <c r="W50" s="8" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="Y50" s="8" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="Z50" s="8"/>
       <c r="AA50" s="8" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="AC50" s="8" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="AD50" s="8"/>
       <c r="AE50" s="8" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="51" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A51" s="8" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="K51" s="8" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="M51" s="8" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="N51" s="8"/>
       <c r="O51" s="8" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="Q51" s="8" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="R51" s="8"/>
       <c r="S51" s="8" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="U51" s="8" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="V51" s="8"/>
       <c r="W51" s="8" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="Y51" s="8" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="Z51" s="8"/>
       <c r="AA51" s="8" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="AC51" s="8" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="AD51" s="8"/>
       <c r="AE51" s="8" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="52" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A52" s="5" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="J52" s="8" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="K52" s="8" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="M52" s="8" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="N52" s="8"/>
       <c r="O52" s="8" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="Q52" s="8" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="R52" s="8"/>
       <c r="S52" s="8" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="U52" s="8" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="V52" s="8"/>
       <c r="W52" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="Y52" s="8" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="Z52" s="8"/>
       <c r="AA52" s="8" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="AC52" s="8" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="AD52" s="8"/>
       <c r="AE52" s="8" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
     <row r="53" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A53" s="3" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="N53" s="8"/>
       <c r="O53" s="8" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="Q53" s="8" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="R53" s="8"/>
       <c r="S53" s="8" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="U53" s="8" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="V53" s="8"/>
       <c r="W53" s="8" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="Y53" s="8" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="Z53" s="8"/>
       <c r="AA53" s="8" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="AC53" s="8" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="AD53" s="8"/>
       <c r="AE53" s="8" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="54" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A54" s="3" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="J54" s="8" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="K54" s="8" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="M54" s="8" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="N54" s="8"/>
       <c r="O54" s="8" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="Q54" s="8" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="R54" s="8"/>
       <c r="S54" s="8" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="U54" s="8" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="V54" s="8"/>
       <c r="W54" s="8" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Y54" s="8" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="Z54" s="8"/>
       <c r="AA54" s="8" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="AC54" s="8" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="AD54" s="8"/>
       <c r="AE54" s="8" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="55" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A55" s="3" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="K55" s="5" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="M55" s="8" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="N55" s="8"/>
       <c r="O55" s="8" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="Q55" s="8" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="R55" s="8"/>
       <c r="S55" s="8" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="U55" s="8" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="V55" s="8"/>
       <c r="W55" s="8" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="Y55" s="8" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="Z55" s="8"/>
       <c r="AA55" s="8" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="AC55" s="8" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="AD55" s="8"/>
       <c r="AE55" s="8" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="56" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A56" s="3" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="M56" s="8" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="N56" s="8"/>
       <c r="O56" s="8" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="Q56" s="8" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="R56" s="8"/>
       <c r="S56" s="8" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="U56" s="8" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="V56" s="8"/>
       <c r="W56" s="8" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="Y56" s="8" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="Z56" s="8"/>
       <c r="AA56" s="8" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="AC56" s="8" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="AD56" s="8"/>
       <c r="AE56" s="8" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="57" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A57" s="3" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="58" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A58" s="8" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="59" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A59" s="8" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="60" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A60" s="8" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="E60" s="4"/>
       <c r="F60" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="61" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A61" s="8" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="62" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A62" s="8" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="E62" s="6"/>
       <c r="F62" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="63" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A63" s="8" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="64" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A64" s="8" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A65" s="3" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A66" s="8" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A67" s="8" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B67" s="8"/>
       <c r="C67" s="8" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A68" s="8" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B68" s="8"/>
       <c r="C68" s="8" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A69" s="8" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A70" s="8" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B70" s="8"/>
       <c r="C70" s="8" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A71" s="8" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A72" s="7" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A73" s="5" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A74" s="5" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A75" s="3" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A76" s="8" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A77" s="8" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A78" s="8" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B78" s="8"/>
       <c r="C78" s="8" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A79" s="3" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A80" s="8" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A81" s="5" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A82" s="5" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A83" s="3" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A84" s="3" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A85" s="8" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B85" s="8"/>
       <c r="C85" s="8" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A86" s="5" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A87" s="8" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A88" s="8" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B88" s="8"/>
       <c r="C88" s="8" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A89" s="5" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A90" s="5" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A91" s="5" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
     </row>
   </sheetData>
@@ -8922,937 +8945,937 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A8" s="8" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A9" s="8" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A12" s="8" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A14" s="8" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A15" s="8" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A16" s="8" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A17" s="8" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A18" s="8" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A19" s="8" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A20" s="8" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A22" s="8" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A23" s="8" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A24" s="8" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A25" s="8" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A26" s="8" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A27" s="8" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A28" s="8" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A29" s="8" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A30" s="8" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A31" s="8" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A32" s="8" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A33" s="8" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A34" s="8" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A35" s="8" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="8" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A37" s="8" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A38" s="8" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A39" s="8" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A40" s="8" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A41" s="8" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A42" s="8" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A43" s="8" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A44" s="8" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A45" s="8" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A46" s="8" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A47" s="8" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A48" s="8" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A49" s="8" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A50" s="8" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A51" s="8" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A52" s="8" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A53" s="8" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A54" s="8" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A55" s="8" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A56" s="8" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A57" s="8" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A58" s="8" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A59" s="8" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A60" s="8" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A61" s="8" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A62" s="8" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A63" s="8" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A64" s="8" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A65" s="8" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A66" s="8" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A67" s="8" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A68" s="8" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A69" s="8" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A70" s="8" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A71" s="8" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A72" s="8" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A73" s="8" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A74" s="8" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A75" s="8" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A76" s="8" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A77" s="8" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A78" s="8" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A79" s="8" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A80" s="8" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A81" s="8" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A82" s="8" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A83" s="8" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A84" s="8" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A85" s="8" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
     </row>
   </sheetData>
@@ -9956,46 +9979,46 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
     </row>
   </sheetData>

--- a/key検討用/ppxkey.xlsx
+++ b/key検討用/ppxkey.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gocho\Desktop\ppx_cust20251217(Wed)\ppx_cust\key検討用\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84AA83D7-A9CF-459B-9C24-910983763043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27AF53DC-6122-4C47-9EBA-55DB8D381378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1463" uniqueCount="1429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1469" uniqueCount="1435">
   <si>
     <t>キー</t>
   </si>
@@ -4412,6 +4412,33 @@
     <rPh sb="35" eb="36">
       <t>マド</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>shiba</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Markdownプレビューア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://github.com/rhysd/Shiba</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>lightmark Viewer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IE11を利用したMarkdownプレビューア</t>
+    <rPh sb="5" eb="7">
+      <t>リヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://spr.babyblue.jp/lmread.html</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4517,7 +4544,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -4550,6 +4577,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -8935,7 +8965,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C85"/>
+  <dimension ref="A1:C87"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="19.1640625" style="9" bestFit="1" customWidth="1"/>
@@ -9009,7 +9039,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>1182</v>
       </c>
@@ -9053,7 +9083,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A11" s="8" t="s">
         <v>1190</v>
       </c>
@@ -9328,564 +9358,586 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A36" s="8" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="8" t="s">
         <v>1240</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B37" s="8" t="s">
         <v>1241</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C37" s="11" t="s">
         <v>1379</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A37" s="8" t="s">
-        <v>1242</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>1243</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>1380</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A38" s="8" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A39" s="8" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>1345</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A40" s="8" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>1382</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A41" s="8" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A42" s="8" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A43" s="8" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A44" s="8" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A45" s="8" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A46" s="8" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A47" s="8" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A48" s="8" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A49" s="8" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A50" s="8" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A51" s="8" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A52" s="8" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A53" s="8" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A54" s="8" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A55" s="8" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A56" s="8" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A57" s="8" t="s">
-        <v>1168</v>
+        <v>1280</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>1169</v>
+        <v>1281</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A58" s="8" t="s">
-        <v>1282</v>
+        <v>1168</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>1283</v>
+        <v>1169</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A59" s="8" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A60" s="8" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A61" s="8" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A62" s="8" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A63" s="8" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A64" s="8" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A65" s="8" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A66" s="8" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A67" s="8" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A68" s="8" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A69" s="8" t="s">
-        <v>1304</v>
+        <v>1429</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>1305</v>
-      </c>
-      <c r="C69" s="11" t="s">
-        <v>1411</v>
+        <v>1430</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>1431</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A70" s="8" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>1307</v>
+        <v>1303</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A71" s="8" t="s">
-        <v>1308</v>
+        <v>1304</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>1309</v>
+        <v>1305</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A72" s="8" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>1311</v>
+        <v>1307</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A73" s="8" t="s">
-        <v>1170</v>
+        <v>1308</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>1171</v>
+        <v>1309</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A74" s="8" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A75" s="8" t="s">
-        <v>1314</v>
+        <v>1170</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>1315</v>
+        <v>1171</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A76" s="8" t="s">
-        <v>1316</v>
+        <v>1312</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>1317</v>
+        <v>1313</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A77" s="8" t="s">
-        <v>1318</v>
+        <v>1314</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A78" s="8" t="s">
-        <v>1320</v>
+        <v>1316</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>1321</v>
+        <v>1317</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A79" s="8" t="s">
-        <v>1322</v>
+        <v>1318</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>1323</v>
+        <v>1319</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>1348</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A80" s="8" t="s">
-        <v>1324</v>
+        <v>1320</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>1325</v>
+        <v>1321</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A81" s="8" t="s">
-        <v>1326</v>
+        <v>1322</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>1327</v>
+        <v>1323</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>1422</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A82" s="8" t="s">
-        <v>1328</v>
+        <v>1324</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>1329</v>
+        <v>1325</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>1402</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A83" s="8" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>1223</v>
+        <v>1327</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A84" s="8" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>1424</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A85" s="8" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C85" s="11" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A86" s="8" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C86" s="11" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A87" s="8" t="s">
         <v>1333</v>
       </c>
-      <c r="B85" s="8" t="s">
+      <c r="B87" s="8" t="s">
         <v>1334</v>
       </c>
-      <c r="C85" s="11" t="s">
+      <c r="C87" s="11" t="s">
         <v>1425</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C85">
-    <sortCondition ref="A2:A85"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C87">
+    <sortCondition ref="A2:A87"/>
   </sortState>
   <phoneticPr fontId="1"/>
   <hyperlinks>
-    <hyperlink ref="C57" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="C73" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="C58" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="C75" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
     <hyperlink ref="C2" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
     <hyperlink ref="C3" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
     <hyperlink ref="C4" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
@@ -9916,51 +9968,53 @@
     <hyperlink ref="C33" r:id="rId30" xr:uid="{00000000-0004-0000-0100-00001D000000}"/>
     <hyperlink ref="C34" r:id="rId31" location="ppxaux" xr:uid="{00000000-0004-0000-0100-00001E000000}"/>
     <hyperlink ref="C35" r:id="rId32" xr:uid="{00000000-0004-0000-0100-00001F000000}"/>
-    <hyperlink ref="C36" r:id="rId33" xr:uid="{00000000-0004-0000-0100-000020000000}"/>
-    <hyperlink ref="C37" r:id="rId34" xr:uid="{00000000-0004-0000-0100-000021000000}"/>
-    <hyperlink ref="C38" r:id="rId35" xr:uid="{00000000-0004-0000-0100-000022000000}"/>
-    <hyperlink ref="C39" r:id="rId36" xr:uid="{00000000-0004-0000-0100-000023000000}"/>
-    <hyperlink ref="C40" r:id="rId37" xr:uid="{00000000-0004-0000-0100-000024000000}"/>
-    <hyperlink ref="C41" r:id="rId38" xr:uid="{00000000-0004-0000-0100-000025000000}"/>
-    <hyperlink ref="C42" r:id="rId39" xr:uid="{00000000-0004-0000-0100-000026000000}"/>
-    <hyperlink ref="C43" r:id="rId40" xr:uid="{00000000-0004-0000-0100-000027000000}"/>
-    <hyperlink ref="C44" r:id="rId41" xr:uid="{00000000-0004-0000-0100-000028000000}"/>
-    <hyperlink ref="C45" r:id="rId42" xr:uid="{00000000-0004-0000-0100-000029000000}"/>
-    <hyperlink ref="C46" r:id="rId43" xr:uid="{00000000-0004-0000-0100-00002A000000}"/>
-    <hyperlink ref="C47" r:id="rId44" xr:uid="{00000000-0004-0000-0100-00002B000000}"/>
-    <hyperlink ref="C48" r:id="rId45" xr:uid="{00000000-0004-0000-0100-00002C000000}"/>
-    <hyperlink ref="C49" r:id="rId46" xr:uid="{00000000-0004-0000-0100-00002D000000}"/>
-    <hyperlink ref="C51" r:id="rId47" xr:uid="{00000000-0004-0000-0100-00002E000000}"/>
-    <hyperlink ref="C52" r:id="rId48" display="https://www.adobe.com/jp/products/photoshop.html" xr:uid="{00000000-0004-0000-0100-00002F000000}"/>
-    <hyperlink ref="C54" r:id="rId49" xr:uid="{00000000-0004-0000-0100-000030000000}"/>
-    <hyperlink ref="C55" r:id="rId50" xr:uid="{00000000-0004-0000-0100-000031000000}"/>
-    <hyperlink ref="C56" r:id="rId51" xr:uid="{00000000-0004-0000-0100-000032000000}"/>
-    <hyperlink ref="C59" r:id="rId52" xr:uid="{00000000-0004-0000-0100-000033000000}"/>
-    <hyperlink ref="C60" r:id="rId53" xr:uid="{00000000-0004-0000-0100-000034000000}"/>
-    <hyperlink ref="C61" r:id="rId54" xr:uid="{00000000-0004-0000-0100-000035000000}"/>
-    <hyperlink ref="C62" r:id="rId55" xr:uid="{00000000-0004-0000-0100-000036000000}"/>
-    <hyperlink ref="C63" r:id="rId56" xr:uid="{00000000-0004-0000-0100-000037000000}"/>
-    <hyperlink ref="C64" r:id="rId57" xr:uid="{00000000-0004-0000-0100-000038000000}"/>
-    <hyperlink ref="C65" r:id="rId58" xr:uid="{00000000-0004-0000-0100-000039000000}"/>
-    <hyperlink ref="C66" r:id="rId59" xr:uid="{00000000-0004-0000-0100-00003A000000}"/>
-    <hyperlink ref="C67" r:id="rId60" xr:uid="{00000000-0004-0000-0100-00003B000000}"/>
-    <hyperlink ref="C68" r:id="rId61" xr:uid="{00000000-0004-0000-0100-00003C000000}"/>
-    <hyperlink ref="C69" r:id="rId62" xr:uid="{00000000-0004-0000-0100-00003D000000}"/>
-    <hyperlink ref="C70" r:id="rId63" xr:uid="{00000000-0004-0000-0100-00003E000000}"/>
-    <hyperlink ref="C71" r:id="rId64" xr:uid="{00000000-0004-0000-0100-00003F000000}"/>
-    <hyperlink ref="C72" r:id="rId65" xr:uid="{00000000-0004-0000-0100-000040000000}"/>
-    <hyperlink ref="C74" r:id="rId66" xr:uid="{00000000-0004-0000-0100-000041000000}"/>
-    <hyperlink ref="C75" r:id="rId67" xr:uid="{00000000-0004-0000-0100-000042000000}"/>
-    <hyperlink ref="C76" r:id="rId68" xr:uid="{00000000-0004-0000-0100-000043000000}"/>
-    <hyperlink ref="C77" r:id="rId69" xr:uid="{00000000-0004-0000-0100-000044000000}"/>
-    <hyperlink ref="C78" r:id="rId70" xr:uid="{00000000-0004-0000-0100-000045000000}"/>
-    <hyperlink ref="C79" r:id="rId71" xr:uid="{00000000-0004-0000-0100-000046000000}"/>
-    <hyperlink ref="C80" r:id="rId72" xr:uid="{00000000-0004-0000-0100-000047000000}"/>
-    <hyperlink ref="C81" r:id="rId73" xr:uid="{00000000-0004-0000-0100-000048000000}"/>
-    <hyperlink ref="C82" r:id="rId74" xr:uid="{00000000-0004-0000-0100-000049000000}"/>
-    <hyperlink ref="C83" r:id="rId75" xr:uid="{00000000-0004-0000-0100-00004A000000}"/>
-    <hyperlink ref="C84" r:id="rId76" xr:uid="{00000000-0004-0000-0100-00004B000000}"/>
-    <hyperlink ref="C85" r:id="rId77" xr:uid="{00000000-0004-0000-0100-00004C000000}"/>
+    <hyperlink ref="C37" r:id="rId33" xr:uid="{00000000-0004-0000-0100-000020000000}"/>
+    <hyperlink ref="C38" r:id="rId34" xr:uid="{00000000-0004-0000-0100-000021000000}"/>
+    <hyperlink ref="C39" r:id="rId35" xr:uid="{00000000-0004-0000-0100-000022000000}"/>
+    <hyperlink ref="C40" r:id="rId36" xr:uid="{00000000-0004-0000-0100-000023000000}"/>
+    <hyperlink ref="C41" r:id="rId37" xr:uid="{00000000-0004-0000-0100-000024000000}"/>
+    <hyperlink ref="C42" r:id="rId38" xr:uid="{00000000-0004-0000-0100-000025000000}"/>
+    <hyperlink ref="C43" r:id="rId39" xr:uid="{00000000-0004-0000-0100-000026000000}"/>
+    <hyperlink ref="C44" r:id="rId40" xr:uid="{00000000-0004-0000-0100-000027000000}"/>
+    <hyperlink ref="C45" r:id="rId41" xr:uid="{00000000-0004-0000-0100-000028000000}"/>
+    <hyperlink ref="C46" r:id="rId42" xr:uid="{00000000-0004-0000-0100-000029000000}"/>
+    <hyperlink ref="C47" r:id="rId43" xr:uid="{00000000-0004-0000-0100-00002A000000}"/>
+    <hyperlink ref="C48" r:id="rId44" xr:uid="{00000000-0004-0000-0100-00002B000000}"/>
+    <hyperlink ref="C49" r:id="rId45" xr:uid="{00000000-0004-0000-0100-00002C000000}"/>
+    <hyperlink ref="C50" r:id="rId46" xr:uid="{00000000-0004-0000-0100-00002D000000}"/>
+    <hyperlink ref="C52" r:id="rId47" xr:uid="{00000000-0004-0000-0100-00002E000000}"/>
+    <hyperlink ref="C53" r:id="rId48" display="https://www.adobe.com/jp/products/photoshop.html" xr:uid="{00000000-0004-0000-0100-00002F000000}"/>
+    <hyperlink ref="C55" r:id="rId49" xr:uid="{00000000-0004-0000-0100-000030000000}"/>
+    <hyperlink ref="C56" r:id="rId50" xr:uid="{00000000-0004-0000-0100-000031000000}"/>
+    <hyperlink ref="C57" r:id="rId51" xr:uid="{00000000-0004-0000-0100-000032000000}"/>
+    <hyperlink ref="C60" r:id="rId52" xr:uid="{00000000-0004-0000-0100-000033000000}"/>
+    <hyperlink ref="C61" r:id="rId53" xr:uid="{00000000-0004-0000-0100-000034000000}"/>
+    <hyperlink ref="C62" r:id="rId54" xr:uid="{00000000-0004-0000-0100-000035000000}"/>
+    <hyperlink ref="C63" r:id="rId55" xr:uid="{00000000-0004-0000-0100-000036000000}"/>
+    <hyperlink ref="C64" r:id="rId56" xr:uid="{00000000-0004-0000-0100-000037000000}"/>
+    <hyperlink ref="C65" r:id="rId57" xr:uid="{00000000-0004-0000-0100-000038000000}"/>
+    <hyperlink ref="C66" r:id="rId58" xr:uid="{00000000-0004-0000-0100-000039000000}"/>
+    <hyperlink ref="C67" r:id="rId59" xr:uid="{00000000-0004-0000-0100-00003A000000}"/>
+    <hyperlink ref="C68" r:id="rId60" xr:uid="{00000000-0004-0000-0100-00003B000000}"/>
+    <hyperlink ref="C70" r:id="rId61" xr:uid="{00000000-0004-0000-0100-00003C000000}"/>
+    <hyperlink ref="C71" r:id="rId62" xr:uid="{00000000-0004-0000-0100-00003D000000}"/>
+    <hyperlink ref="C72" r:id="rId63" xr:uid="{00000000-0004-0000-0100-00003E000000}"/>
+    <hyperlink ref="C73" r:id="rId64" xr:uid="{00000000-0004-0000-0100-00003F000000}"/>
+    <hyperlink ref="C74" r:id="rId65" xr:uid="{00000000-0004-0000-0100-000040000000}"/>
+    <hyperlink ref="C76" r:id="rId66" xr:uid="{00000000-0004-0000-0100-000041000000}"/>
+    <hyperlink ref="C77" r:id="rId67" xr:uid="{00000000-0004-0000-0100-000042000000}"/>
+    <hyperlink ref="C78" r:id="rId68" xr:uid="{00000000-0004-0000-0100-000043000000}"/>
+    <hyperlink ref="C79" r:id="rId69" xr:uid="{00000000-0004-0000-0100-000044000000}"/>
+    <hyperlink ref="C80" r:id="rId70" xr:uid="{00000000-0004-0000-0100-000045000000}"/>
+    <hyperlink ref="C81" r:id="rId71" xr:uid="{00000000-0004-0000-0100-000046000000}"/>
+    <hyperlink ref="C82" r:id="rId72" xr:uid="{00000000-0004-0000-0100-000047000000}"/>
+    <hyperlink ref="C83" r:id="rId73" xr:uid="{00000000-0004-0000-0100-000048000000}"/>
+    <hyperlink ref="C84" r:id="rId74" xr:uid="{00000000-0004-0000-0100-000049000000}"/>
+    <hyperlink ref="C85" r:id="rId75" xr:uid="{00000000-0004-0000-0100-00004A000000}"/>
+    <hyperlink ref="C86" r:id="rId76" xr:uid="{00000000-0004-0000-0100-00004B000000}"/>
+    <hyperlink ref="C87" r:id="rId77" xr:uid="{00000000-0004-0000-0100-00004C000000}"/>
+    <hyperlink ref="C69" r:id="rId78" xr:uid="{2A5F41B6-B50F-4470-905C-CEE2880AFAC1}"/>
+    <hyperlink ref="C36" r:id="rId79" xr:uid="{9537A5E8-28D7-4E83-A579-0A9EBD1F2E4C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>

--- a/key検討用/ppxkey.xlsx
+++ b/key検討用/ppxkey.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gocho\Desktop\ppx_cust20251217(Wed)\ppx_cust\key検討用\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gocho\AppData\Local\Temp\Rar$DIa24260.28809.rartemp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27AF53DC-6122-4C47-9EBA-55DB8D381378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6110860A-A5F7-4864-9790-8F190F680CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1469" uniqueCount="1435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="1432">
   <si>
     <t>キー</t>
   </si>
@@ -3982,12 +3982,6 @@
   </si>
   <si>
     <t>VLC：コーデック内蔵動画プレーヤ</t>
-  </si>
-  <si>
-    <t>vscode</t>
-  </si>
-  <si>
-    <t>プログラムエディタ</t>
   </si>
   <si>
     <t>windowspy</t>
@@ -4361,10 +4355,6 @@
   </si>
   <si>
     <t>https://www.videolan.org/</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://code.visualstudio.com/</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -5080,7 +5070,7 @@
         <v>26</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>28</v>
@@ -7631,7 +7621,7 @@
         <v>788</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>789</v>
@@ -8139,7 +8129,7 @@
         <v>935</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="K50" s="8" t="s">
         <v>936</v>
@@ -8452,7 +8442,7 @@
         <v>1027</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>1028</v>
@@ -8965,7 +8955,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C87"/>
+  <dimension ref="A1:C86"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="19.1640625" style="9" bestFit="1" customWidth="1"/>
@@ -8992,7 +8982,7 @@
         <v>1173</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
@@ -9003,7 +8993,7 @@
         <v>1175</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.15">
@@ -9014,7 +9004,7 @@
         <v>1177</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.15">
@@ -9025,7 +9015,7 @@
         <v>1179</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.15">
@@ -9036,7 +9026,7 @@
         <v>1181</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.15">
@@ -9047,7 +9037,7 @@
         <v>1183</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.15">
@@ -9058,7 +9048,7 @@
         <v>1185</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.15">
@@ -9069,7 +9059,7 @@
         <v>1187</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.15">
@@ -9080,7 +9070,7 @@
         <v>1189</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.15">
@@ -9091,7 +9081,7 @@
         <v>1191</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.15">
@@ -9102,7 +9092,7 @@
         <v>1193</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.15">
@@ -9113,7 +9103,7 @@
         <v>1195</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.15">
@@ -9124,7 +9114,7 @@
         <v>1197</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.15">
@@ -9135,7 +9125,7 @@
         <v>1199</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.15">
@@ -9146,7 +9136,7 @@
         <v>1201</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.15">
@@ -9157,7 +9147,7 @@
         <v>1203</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.15">
@@ -9168,7 +9158,7 @@
         <v>1205</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.15">
@@ -9179,7 +9169,7 @@
         <v>1207</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.15">
@@ -9190,7 +9180,7 @@
         <v>1209</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.15">
@@ -9201,7 +9191,7 @@
         <v>1211</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.15">
@@ -9212,7 +9202,7 @@
         <v>1213</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.15">
@@ -9223,7 +9213,7 @@
         <v>1215</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.15">
@@ -9234,7 +9224,7 @@
         <v>1217</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.15">
@@ -9245,7 +9235,7 @@
         <v>1219</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.15">
@@ -9256,7 +9246,7 @@
         <v>1221</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.15">
@@ -9267,7 +9257,7 @@
         <v>1223</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.15">
@@ -9278,7 +9268,7 @@
         <v>1225</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.15">
@@ -9289,7 +9279,7 @@
         <v>1227</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.15">
@@ -9300,7 +9290,7 @@
         <v>1229</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.15">
@@ -9311,7 +9301,7 @@
         <v>1231</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.15">
@@ -9322,7 +9312,7 @@
         <v>1233</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.15">
@@ -9333,7 +9323,7 @@
         <v>1235</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.15">
@@ -9344,7 +9334,7 @@
         <v>1237</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.15">
@@ -9355,18 +9345,18 @@
         <v>1239</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A36" s="8" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>1434</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -9377,7 +9367,7 @@
         <v>1241</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.15">
@@ -9388,7 +9378,7 @@
         <v>1243</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.15">
@@ -9399,7 +9389,7 @@
         <v>1245</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.15">
@@ -9410,7 +9400,7 @@
         <v>1247</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.15">
@@ -9421,7 +9411,7 @@
         <v>1249</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.15">
@@ -9432,7 +9422,7 @@
         <v>1251</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.15">
@@ -9443,7 +9433,7 @@
         <v>1253</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.15">
@@ -9454,7 +9444,7 @@
         <v>1255</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.15">
@@ -9465,7 +9455,7 @@
         <v>1257</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.15">
@@ -9476,7 +9466,7 @@
         <v>1259</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.15">
@@ -9487,7 +9477,7 @@
         <v>1261</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.15">
@@ -9498,7 +9488,7 @@
         <v>1263</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.15">
@@ -9509,7 +9499,7 @@
         <v>1265</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.15">
@@ -9520,7 +9510,7 @@
         <v>1267</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.15">
@@ -9531,7 +9521,7 @@
         <v>1269</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.15">
@@ -9542,7 +9532,7 @@
         <v>1271</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.15">
@@ -9553,7 +9543,7 @@
         <v>1273</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.15">
@@ -9564,7 +9554,7 @@
         <v>1275</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.15">
@@ -9575,7 +9565,7 @@
         <v>1277</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.15">
@@ -9586,7 +9576,7 @@
         <v>1279</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.15">
@@ -9597,7 +9587,7 @@
         <v>1281</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.15">
@@ -9608,7 +9598,7 @@
         <v>1169</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.15">
@@ -9619,7 +9609,7 @@
         <v>1283</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.15">
@@ -9630,7 +9620,7 @@
         <v>1285</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.15">
@@ -9641,7 +9631,7 @@
         <v>1287</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.15">
@@ -9652,7 +9642,7 @@
         <v>1289</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.15">
@@ -9663,7 +9653,7 @@
         <v>1291</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.15">
@@ -9674,7 +9664,7 @@
         <v>1293</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.15">
@@ -9685,7 +9675,7 @@
         <v>1295</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.15">
@@ -9696,7 +9686,7 @@
         <v>1297</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.15">
@@ -9707,7 +9697,7 @@
         <v>1299</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.15">
@@ -9718,18 +9708,18 @@
         <v>1301</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A69" s="8" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.15">
@@ -9740,7 +9730,7 @@
         <v>1303</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.15">
@@ -9751,7 +9741,7 @@
         <v>1305</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.15">
@@ -9762,7 +9752,7 @@
         <v>1307</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.15">
@@ -9773,7 +9763,7 @@
         <v>1309</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.15">
@@ -9784,7 +9774,7 @@
         <v>1311</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.15">
@@ -9795,7 +9785,7 @@
         <v>1171</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.15">
@@ -9806,7 +9796,7 @@
         <v>1313</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.15">
@@ -9817,7 +9807,7 @@
         <v>1315</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.15">
@@ -9828,7 +9818,7 @@
         <v>1317</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.15">
@@ -9839,7 +9829,7 @@
         <v>1319</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.15">
@@ -9850,7 +9840,7 @@
         <v>1321</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>1420</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.15">
@@ -9861,7 +9851,7 @@
         <v>1323</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>1348</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.15">
@@ -9872,7 +9862,7 @@
         <v>1325</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.15">
@@ -9883,7 +9873,7 @@
         <v>1327</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>1422</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.15">
@@ -9891,21 +9881,21 @@
         <v>1328</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>1329</v>
+        <v>1223</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>1402</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A85" s="8" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B85" s="8" t="s">
         <v>1330</v>
       </c>
-      <c r="B85" s="8" t="s">
-        <v>1223</v>
-      </c>
       <c r="C85" s="11" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.15">
@@ -9916,23 +9906,12 @@
         <v>1332</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>1424</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A87" s="8" t="s">
-        <v>1333</v>
-      </c>
-      <c r="B87" s="8" t="s">
-        <v>1334</v>
-      </c>
-      <c r="C87" s="11" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C87">
-    <sortCondition ref="A2:A87"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C86">
+    <sortCondition ref="A2:A86"/>
   </sortState>
   <phoneticPr fontId="1"/>
   <hyperlinks>
@@ -10005,16 +9984,15 @@
     <hyperlink ref="C77" r:id="rId67" xr:uid="{00000000-0004-0000-0100-000042000000}"/>
     <hyperlink ref="C78" r:id="rId68" xr:uid="{00000000-0004-0000-0100-000043000000}"/>
     <hyperlink ref="C79" r:id="rId69" xr:uid="{00000000-0004-0000-0100-000044000000}"/>
-    <hyperlink ref="C80" r:id="rId70" xr:uid="{00000000-0004-0000-0100-000045000000}"/>
-    <hyperlink ref="C81" r:id="rId71" xr:uid="{00000000-0004-0000-0100-000046000000}"/>
-    <hyperlink ref="C82" r:id="rId72" xr:uid="{00000000-0004-0000-0100-000047000000}"/>
-    <hyperlink ref="C83" r:id="rId73" xr:uid="{00000000-0004-0000-0100-000048000000}"/>
-    <hyperlink ref="C84" r:id="rId74" xr:uid="{00000000-0004-0000-0100-000049000000}"/>
-    <hyperlink ref="C85" r:id="rId75" xr:uid="{00000000-0004-0000-0100-00004A000000}"/>
-    <hyperlink ref="C86" r:id="rId76" xr:uid="{00000000-0004-0000-0100-00004B000000}"/>
-    <hyperlink ref="C87" r:id="rId77" xr:uid="{00000000-0004-0000-0100-00004C000000}"/>
-    <hyperlink ref="C69" r:id="rId78" xr:uid="{2A5F41B6-B50F-4470-905C-CEE2880AFAC1}"/>
-    <hyperlink ref="C36" r:id="rId79" xr:uid="{9537A5E8-28D7-4E83-A579-0A9EBD1F2E4C}"/>
+    <hyperlink ref="C80" r:id="rId70" xr:uid="{00000000-0004-0000-0100-000046000000}"/>
+    <hyperlink ref="C81" r:id="rId71" xr:uid="{00000000-0004-0000-0100-000047000000}"/>
+    <hyperlink ref="C82" r:id="rId72" xr:uid="{00000000-0004-0000-0100-000048000000}"/>
+    <hyperlink ref="C83" r:id="rId73" xr:uid="{00000000-0004-0000-0100-000049000000}"/>
+    <hyperlink ref="C84" r:id="rId74" xr:uid="{00000000-0004-0000-0100-00004A000000}"/>
+    <hyperlink ref="C85" r:id="rId75" xr:uid="{00000000-0004-0000-0100-00004B000000}"/>
+    <hyperlink ref="C86" r:id="rId76" xr:uid="{00000000-0004-0000-0100-00004C000000}"/>
+    <hyperlink ref="C69" r:id="rId77" xr:uid="{2A5F41B6-B50F-4470-905C-CEE2880AFAC1}"/>
+    <hyperlink ref="C36" r:id="rId78" xr:uid="{9537A5E8-28D7-4E83-A579-0A9EBD1F2E4C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
@@ -10033,7 +10011,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1166</v>
@@ -10044,35 +10022,35 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>1336</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>1337</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>1338</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>1339</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>1340</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>1341</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>1342</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>1343</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>1344</v>
       </c>
     </row>
   </sheetData>

--- a/key検討用/ppxkey.xlsx
+++ b/key検討用/ppxkey.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gocho\AppData\Local\Temp\Rar$DIa24260.28809.rartemp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gocho\Desktop\ppx_cust20251217(Wed)\ppx_cust\key検討用\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6110860A-A5F7-4864-9790-8F190F680CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD5B440B-0F9C-4AD6-8F2C-6CF8AF532ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3906,12 +3906,6 @@
     <t>バイナリパッチ適用ツール</t>
   </si>
   <si>
-    <t>sakura</t>
-  </si>
-  <si>
-    <t>派生版sakuraVzが高速</t>
-  </si>
-  <si>
     <t>scrdbg</t>
   </si>
   <si>
@@ -3982,6 +3976,12 @@
   </si>
   <si>
     <t>VLC：コーデック内蔵動画プレーヤ</t>
+  </si>
+  <si>
+    <t>vscode</t>
+  </si>
+  <si>
+    <t>プログラムエディタ</t>
   </si>
   <si>
     <t>windowspy</t>
@@ -4302,10 +4302,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>https://github.com/yoshinrt/SakuraVz</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>http://pc-labo.seesaa.net/article/413882845.html</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -4355,6 +4351,10 @@
   </si>
   <si>
     <t>https://www.videolan.org/</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://code.visualstudio.com/</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -9702,24 +9702,24 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A68" s="8" t="s">
-        <v>1300</v>
+        <v>1426</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>1301</v>
-      </c>
-      <c r="C68" s="11" t="s">
-        <v>1407</v>
+        <v>1427</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>1428</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A69" s="8" t="s">
-        <v>1426</v>
+        <v>1300</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>1427</v>
-      </c>
-      <c r="C69" s="12" t="s">
-        <v>1428</v>
+        <v>1301</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>1407</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.15">
@@ -9768,10 +9768,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A74" s="8" t="s">
-        <v>1310</v>
+        <v>1170</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>1311</v>
+        <v>1171</v>
       </c>
       <c r="C74" s="11" t="s">
         <v>1412</v>
@@ -9779,10 +9779,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A75" s="8" t="s">
-        <v>1170</v>
+        <v>1310</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>1171</v>
+        <v>1311</v>
       </c>
       <c r="C75" s="11" t="s">
         <v>1413</v>
@@ -9916,7 +9916,7 @@
   <phoneticPr fontId="1"/>
   <hyperlinks>
     <hyperlink ref="C58" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="C75" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="C74" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
     <hyperlink ref="C2" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
     <hyperlink ref="C3" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
     <hyperlink ref="C4" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
@@ -9971,19 +9971,19 @@
     <hyperlink ref="C62" r:id="rId54" xr:uid="{00000000-0004-0000-0100-000035000000}"/>
     <hyperlink ref="C63" r:id="rId55" xr:uid="{00000000-0004-0000-0100-000036000000}"/>
     <hyperlink ref="C64" r:id="rId56" xr:uid="{00000000-0004-0000-0100-000037000000}"/>
-    <hyperlink ref="C65" r:id="rId57" xr:uid="{00000000-0004-0000-0100-000038000000}"/>
-    <hyperlink ref="C66" r:id="rId58" xr:uid="{00000000-0004-0000-0100-000039000000}"/>
-    <hyperlink ref="C67" r:id="rId59" xr:uid="{00000000-0004-0000-0100-00003A000000}"/>
-    <hyperlink ref="C68" r:id="rId60" xr:uid="{00000000-0004-0000-0100-00003B000000}"/>
-    <hyperlink ref="C70" r:id="rId61" xr:uid="{00000000-0004-0000-0100-00003C000000}"/>
-    <hyperlink ref="C71" r:id="rId62" xr:uid="{00000000-0004-0000-0100-00003D000000}"/>
-    <hyperlink ref="C72" r:id="rId63" xr:uid="{00000000-0004-0000-0100-00003E000000}"/>
-    <hyperlink ref="C73" r:id="rId64" xr:uid="{00000000-0004-0000-0100-00003F000000}"/>
-    <hyperlink ref="C74" r:id="rId65" xr:uid="{00000000-0004-0000-0100-000040000000}"/>
-    <hyperlink ref="C76" r:id="rId66" xr:uid="{00000000-0004-0000-0100-000041000000}"/>
-    <hyperlink ref="C77" r:id="rId67" xr:uid="{00000000-0004-0000-0100-000042000000}"/>
-    <hyperlink ref="C78" r:id="rId68" xr:uid="{00000000-0004-0000-0100-000043000000}"/>
-    <hyperlink ref="C79" r:id="rId69" xr:uid="{00000000-0004-0000-0100-000044000000}"/>
+    <hyperlink ref="C65" r:id="rId57" xr:uid="{00000000-0004-0000-0100-000039000000}"/>
+    <hyperlink ref="C66" r:id="rId58" xr:uid="{00000000-0004-0000-0100-00003A000000}"/>
+    <hyperlink ref="C67" r:id="rId59" xr:uid="{00000000-0004-0000-0100-00003B000000}"/>
+    <hyperlink ref="C69" r:id="rId60" xr:uid="{00000000-0004-0000-0100-00003C000000}"/>
+    <hyperlink ref="C70" r:id="rId61" xr:uid="{00000000-0004-0000-0100-00003D000000}"/>
+    <hyperlink ref="C71" r:id="rId62" xr:uid="{00000000-0004-0000-0100-00003E000000}"/>
+    <hyperlink ref="C72" r:id="rId63" xr:uid="{00000000-0004-0000-0100-00003F000000}"/>
+    <hyperlink ref="C73" r:id="rId64" xr:uid="{00000000-0004-0000-0100-000040000000}"/>
+    <hyperlink ref="C75" r:id="rId65" xr:uid="{00000000-0004-0000-0100-000041000000}"/>
+    <hyperlink ref="C76" r:id="rId66" xr:uid="{00000000-0004-0000-0100-000042000000}"/>
+    <hyperlink ref="C77" r:id="rId67" xr:uid="{00000000-0004-0000-0100-000043000000}"/>
+    <hyperlink ref="C78" r:id="rId68" xr:uid="{00000000-0004-0000-0100-000044000000}"/>
+    <hyperlink ref="C79" r:id="rId69" xr:uid="{00000000-0004-0000-0100-000045000000}"/>
     <hyperlink ref="C80" r:id="rId70" xr:uid="{00000000-0004-0000-0100-000046000000}"/>
     <hyperlink ref="C81" r:id="rId71" xr:uid="{00000000-0004-0000-0100-000047000000}"/>
     <hyperlink ref="C82" r:id="rId72" xr:uid="{00000000-0004-0000-0100-000048000000}"/>
@@ -9991,7 +9991,7 @@
     <hyperlink ref="C84" r:id="rId74" xr:uid="{00000000-0004-0000-0100-00004A000000}"/>
     <hyperlink ref="C85" r:id="rId75" xr:uid="{00000000-0004-0000-0100-00004B000000}"/>
     <hyperlink ref="C86" r:id="rId76" xr:uid="{00000000-0004-0000-0100-00004C000000}"/>
-    <hyperlink ref="C69" r:id="rId77" xr:uid="{2A5F41B6-B50F-4470-905C-CEE2880AFAC1}"/>
+    <hyperlink ref="C68" r:id="rId77" xr:uid="{2A5F41B6-B50F-4470-905C-CEE2880AFAC1}"/>
     <hyperlink ref="C36" r:id="rId78" xr:uid="{9537A5E8-28D7-4E83-A579-0A9EBD1F2E4C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/key検討用/ppxkey.xlsx
+++ b/key検討用/ppxkey.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gocho\Desktop\ppx_cust20251217(Wed)\ppx_cust\key検討用\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD5B440B-0F9C-4AD6-8F2C-6CF8AF532ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E846689C-6049-433A-B6FE-BE9BF4C61CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="1432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1459" uniqueCount="1430">
   <si>
     <t>キー</t>
   </si>
@@ -1470,9 +1470,6 @@
     <t>[Ctrl+Shift+H]</t>
   </si>
   <si>
-    <t>ダイアログでエントリのパスを開く(DialogHandler)</t>
-  </si>
-  <si>
     <t>%k"^\H"</t>
   </si>
   <si>
@@ -3612,12 +3609,6 @@
     <t>画像編集ソフト</t>
   </si>
   <si>
-    <t>dockshow</t>
-  </si>
-  <si>
-    <t>メディアプレーヤー</t>
-  </si>
-  <si>
     <t>dre</t>
   </si>
   <si>
@@ -3976,12 +3967,6 @@
   </si>
   <si>
     <t>VLC：コーデック内蔵動画プレーヤ</t>
-  </si>
-  <si>
-    <t>vscode</t>
-  </si>
-  <si>
-    <t>プログラムエディタ</t>
   </si>
   <si>
     <t>windowspy</t>
@@ -4107,10 +4092,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>http://toro.d.dooo.jp/slppx.html#ppxdockshow</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>http://www.windproject.sakura.ne.jp/thisnor/dre/</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -4351,10 +4332,6 @@
   </si>
   <si>
     <t>https://www.videolan.org/</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://code.visualstudio.com/</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -4429,6 +4406,32 @@
   </si>
   <si>
     <t>https://spr.babyblue.jp/lmread.html</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サブディレクトリ以下をインタラクティブサーチ(fd)</t>
+    <rPh sb="8" eb="10">
+      <t>イカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タブ付き新規窓(*ppc -combo)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>fd(find)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Rust製で高速なfind</t>
+    <rPh sb="4" eb="5">
+      <t>セイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://github.com/sharkdp/fd</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5070,7 +5073,7 @@
         <v>26</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>1423</v>
+        <v>1416</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>28</v>
@@ -6570,9 +6573,7 @@
       <c r="I26" s="8" t="s">
         <v>476</v>
       </c>
-      <c r="J26" s="1" t="s">
-        <v>204</v>
-      </c>
+      <c r="J26" s="1"/>
       <c r="K26" s="8" t="s">
         <v>477</v>
       </c>
@@ -6588,2362 +6589,2356 @@
       <c r="Q26" s="8" t="s">
         <v>481</v>
       </c>
-      <c r="R26" s="8" t="s">
+      <c r="R26" s="8"/>
+      <c r="S26" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="S26" s="8" t="s">
+      <c r="U26" s="8" t="s">
         <v>483</v>
-      </c>
-      <c r="U26" s="8" t="s">
-        <v>484</v>
       </c>
       <c r="V26" s="8"/>
       <c r="W26" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="Y26" s="8" t="s">
         <v>485</v>
-      </c>
-      <c r="Y26" s="8" t="s">
-        <v>486</v>
       </c>
       <c r="Z26" s="8"/>
       <c r="AA26" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="AC26" s="8" t="s">
         <v>487</v>
-      </c>
-      <c r="AC26" s="8" t="s">
-        <v>488</v>
       </c>
       <c r="AD26" s="8"/>
       <c r="AE26" s="8" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A27" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="B27" s="8" t="s">
         <v>490</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="C27" s="8" t="s">
         <v>491</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="E27" s="8" t="s">
         <v>492</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="F27" s="8" t="s">
         <v>493</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="G27" s="8" t="s">
         <v>494</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="I27" s="8" t="s">
         <v>495</v>
       </c>
-      <c r="I27" s="8" t="s">
+      <c r="J27" s="8" t="s">
         <v>496</v>
       </c>
-      <c r="J27" s="8" t="s">
+      <c r="K27" s="8" t="s">
         <v>497</v>
       </c>
-      <c r="K27" s="8" t="s">
+      <c r="M27" s="8" t="s">
         <v>498</v>
       </c>
-      <c r="M27" s="8" t="s">
+      <c r="N27" s="8" t="s">
         <v>499</v>
       </c>
-      <c r="N27" s="8" t="s">
+      <c r="O27" s="8" t="s">
         <v>500</v>
       </c>
-      <c r="O27" s="8" t="s">
+      <c r="Q27" s="8" t="s">
         <v>501</v>
       </c>
-      <c r="Q27" s="8" t="s">
+      <c r="R27" s="8" t="s">
         <v>502</v>
       </c>
-      <c r="R27" s="8" t="s">
+      <c r="S27" s="8" t="s">
         <v>503</v>
       </c>
-      <c r="S27" s="8" t="s">
+      <c r="U27" s="8" t="s">
         <v>504</v>
-      </c>
-      <c r="U27" s="8" t="s">
-        <v>505</v>
       </c>
       <c r="V27" s="8"/>
       <c r="W27" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="Y27" s="8" t="s">
         <v>506</v>
-      </c>
-      <c r="Y27" s="8" t="s">
-        <v>507</v>
       </c>
       <c r="Z27" s="8"/>
       <c r="AA27" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="AC27" s="8" t="s">
         <v>508</v>
-      </c>
-      <c r="AC27" s="8" t="s">
-        <v>509</v>
       </c>
       <c r="AD27" s="8"/>
       <c r="AE27" s="8" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="28" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A28" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>511</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="C28" s="5" t="s">
         <v>512</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="E28" s="5" t="s">
         <v>513</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="F28" s="5" t="s">
         <v>514</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="G28" s="5" t="s">
         <v>515</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="I28" s="8" t="s">
         <v>516</v>
       </c>
-      <c r="I28" s="8" t="s">
+      <c r="J28" s="8" t="s">
+        <v>1425</v>
+      </c>
+      <c r="K28" s="8" t="s">
         <v>517</v>
       </c>
-      <c r="J28" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="K28" s="8" t="s">
+      <c r="M28" s="8" t="s">
         <v>518</v>
-      </c>
-      <c r="M28" s="8" t="s">
-        <v>519</v>
       </c>
       <c r="N28" s="8"/>
       <c r="O28" s="8" t="s">
+        <v>519</v>
+      </c>
+      <c r="Q28" s="8" t="s">
         <v>520</v>
-      </c>
-      <c r="Q28" s="8" t="s">
-        <v>521</v>
       </c>
       <c r="R28" s="8"/>
       <c r="S28" s="8" t="s">
+        <v>521</v>
+      </c>
+      <c r="U28" s="8" t="s">
         <v>522</v>
-      </c>
-      <c r="U28" s="8" t="s">
-        <v>523</v>
       </c>
       <c r="V28" s="8"/>
       <c r="W28" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="Y28" s="8" t="s">
         <v>524</v>
-      </c>
-      <c r="Y28" s="8" t="s">
-        <v>525</v>
       </c>
       <c r="Z28" s="8"/>
       <c r="AA28" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="AC28" s="8" t="s">
         <v>526</v>
-      </c>
-      <c r="AC28" s="8" t="s">
-        <v>527</v>
       </c>
       <c r="AD28" s="8"/>
       <c r="AE28" s="8" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="29" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A29" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="E29" s="5" t="s">
         <v>531</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="F29" s="5" t="s">
         <v>532</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="G29" s="5" t="s">
         <v>533</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="I29" s="8" t="s">
         <v>534</v>
       </c>
-      <c r="I29" s="8" t="s">
+      <c r="J29" s="8"/>
+      <c r="K29" s="8" t="s">
         <v>535</v>
       </c>
-      <c r="J29" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="K29" s="8" t="s">
+      <c r="M29" s="8" t="s">
         <v>536</v>
-      </c>
-      <c r="M29" s="8" t="s">
-        <v>537</v>
       </c>
       <c r="N29" s="8"/>
       <c r="O29" s="8" t="s">
+        <v>537</v>
+      </c>
+      <c r="Q29" s="8" t="s">
         <v>538</v>
-      </c>
-      <c r="Q29" s="8" t="s">
-        <v>539</v>
       </c>
       <c r="R29" s="8"/>
       <c r="S29" s="8" t="s">
+        <v>539</v>
+      </c>
+      <c r="U29" s="8" t="s">
         <v>540</v>
-      </c>
-      <c r="U29" s="8" t="s">
-        <v>541</v>
       </c>
       <c r="V29" s="8"/>
       <c r="W29" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="Y29" s="8" t="s">
         <v>542</v>
-      </c>
-      <c r="Y29" s="8" t="s">
-        <v>543</v>
       </c>
       <c r="Z29" s="8"/>
       <c r="AA29" s="8" t="s">
+        <v>543</v>
+      </c>
+      <c r="AC29" s="8" t="s">
         <v>544</v>
-      </c>
-      <c r="AC29" s="8" t="s">
-        <v>545</v>
       </c>
       <c r="AD29" s="8"/>
       <c r="AE29" s="8" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A30" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="E30" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="F30" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="G30" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="I30" s="8" t="s">
         <v>552</v>
       </c>
-      <c r="I30" s="8" t="s">
+      <c r="J30" s="8"/>
+      <c r="K30" s="8" t="s">
         <v>553</v>
       </c>
-      <c r="J30" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="K30" s="8" t="s">
+      <c r="M30" s="8" t="s">
         <v>554</v>
-      </c>
-      <c r="M30" s="8" t="s">
-        <v>555</v>
       </c>
       <c r="N30" s="8"/>
       <c r="O30" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="Q30" s="8" t="s">
         <v>556</v>
       </c>
-      <c r="Q30" s="8" t="s">
+      <c r="R30" s="8" t="s">
         <v>557</v>
       </c>
-      <c r="R30" s="8" t="s">
+      <c r="S30" s="8" t="s">
         <v>558</v>
       </c>
-      <c r="S30" s="8" t="s">
+      <c r="U30" s="8" t="s">
         <v>559</v>
-      </c>
-      <c r="U30" s="8" t="s">
-        <v>560</v>
       </c>
       <c r="V30" s="8"/>
       <c r="W30" s="8" t="s">
+        <v>560</v>
+      </c>
+      <c r="Y30" s="8" t="s">
         <v>561</v>
-      </c>
-      <c r="Y30" s="8" t="s">
-        <v>562</v>
       </c>
       <c r="Z30" s="8"/>
       <c r="AA30" s="8" t="s">
+        <v>562</v>
+      </c>
+      <c r="AC30" s="8" t="s">
         <v>563</v>
-      </c>
-      <c r="AC30" s="8" t="s">
-        <v>564</v>
       </c>
       <c r="AD30" s="8"/>
       <c r="AE30" s="8" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A31" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="G31" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="I31" s="8" t="s">
         <v>571</v>
       </c>
-      <c r="I31" s="8" t="s">
+      <c r="J31" s="8" t="s">
         <v>572</v>
       </c>
-      <c r="J31" s="8" t="s">
+      <c r="K31" s="8" t="s">
         <v>573</v>
       </c>
-      <c r="K31" s="8" t="s">
+      <c r="M31" s="8" t="s">
         <v>574</v>
       </c>
-      <c r="M31" s="8" t="s">
+      <c r="N31" s="8" t="s">
         <v>575</v>
       </c>
-      <c r="N31" s="8" t="s">
+      <c r="O31" s="8" t="s">
         <v>576</v>
       </c>
-      <c r="O31" s="8" t="s">
+      <c r="Q31" s="8" t="s">
         <v>577</v>
       </c>
-      <c r="Q31" s="8" t="s">
+      <c r="R31" s="8" t="s">
         <v>578</v>
       </c>
-      <c r="R31" s="8" t="s">
+      <c r="S31" s="8" t="s">
         <v>579</v>
       </c>
-      <c r="S31" s="8" t="s">
+      <c r="U31" s="8" t="s">
         <v>580</v>
-      </c>
-      <c r="U31" s="8" t="s">
-        <v>581</v>
       </c>
       <c r="V31" s="8"/>
       <c r="W31" s="8" t="s">
+        <v>581</v>
+      </c>
+      <c r="Y31" s="8" t="s">
         <v>582</v>
-      </c>
-      <c r="Y31" s="8" t="s">
-        <v>583</v>
       </c>
       <c r="Z31" s="8"/>
       <c r="AA31" s="8" t="s">
+        <v>583</v>
+      </c>
+      <c r="AC31" s="8" t="s">
         <v>584</v>
       </c>
-      <c r="AC31" s="8" t="s">
+      <c r="AD31" s="8" t="s">
         <v>585</v>
       </c>
-      <c r="AD31" s="8" t="s">
+      <c r="AE31" s="8" t="s">
         <v>586</v>
-      </c>
-      <c r="AE31" s="8" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A32" s="8" t="s">
+        <v>587</v>
+      </c>
+      <c r="B32" s="8" t="s">
         <v>588</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="C32" s="8" t="s">
         <v>589</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="E32" s="8" t="s">
         <v>590</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="F32" s="8" t="s">
         <v>591</v>
       </c>
-      <c r="F32" s="8" t="s">
+      <c r="G32" s="8" t="s">
         <v>592</v>
       </c>
-      <c r="G32" s="8" t="s">
+      <c r="I32" s="8" t="s">
         <v>593</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>594</v>
       </c>
       <c r="J32" s="8" t="s">
         <v>27</v>
       </c>
       <c r="K32" s="8" t="s">
+        <v>594</v>
+      </c>
+      <c r="M32" s="8" t="s">
         <v>595</v>
-      </c>
-      <c r="M32" s="8" t="s">
-        <v>596</v>
       </c>
       <c r="N32" s="8"/>
       <c r="O32" s="8" t="s">
+        <v>596</v>
+      </c>
+      <c r="Q32" s="8" t="s">
         <v>597</v>
-      </c>
-      <c r="Q32" s="8" t="s">
-        <v>598</v>
       </c>
       <c r="R32" s="8"/>
       <c r="S32" s="8" t="s">
+        <v>598</v>
+      </c>
+      <c r="U32" s="8" t="s">
         <v>599</v>
-      </c>
-      <c r="U32" s="8" t="s">
-        <v>600</v>
       </c>
       <c r="V32" s="8"/>
       <c r="W32" s="8" t="s">
+        <v>600</v>
+      </c>
+      <c r="Y32" s="8" t="s">
         <v>601</v>
-      </c>
-      <c r="Y32" s="8" t="s">
-        <v>602</v>
       </c>
       <c r="Z32" s="8"/>
       <c r="AA32" s="8" t="s">
+        <v>602</v>
+      </c>
+      <c r="AC32" s="8" t="s">
         <v>603</v>
-      </c>
-      <c r="AC32" s="8" t="s">
-        <v>604</v>
       </c>
       <c r="AD32" s="8"/>
       <c r="AE32" s="8" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A33" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>606</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="C33" s="5" t="s">
         <v>607</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="E33" s="8" t="s">
         <v>608</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="F33" s="8" t="s">
         <v>609</v>
       </c>
-      <c r="F33" s="8" t="s">
+      <c r="G33" s="8" t="s">
         <v>610</v>
       </c>
-      <c r="G33" s="8" t="s">
+      <c r="I33" s="8" t="s">
         <v>611</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>612</v>
       </c>
       <c r="J33" s="8"/>
       <c r="K33" s="8" t="s">
+        <v>612</v>
+      </c>
+      <c r="M33" s="8" t="s">
         <v>613</v>
       </c>
-      <c r="M33" s="8" t="s">
+      <c r="N33" s="8" t="s">
         <v>614</v>
       </c>
-      <c r="N33" s="8" t="s">
+      <c r="O33" s="8" t="s">
         <v>615</v>
       </c>
-      <c r="O33" s="8" t="s">
+      <c r="Q33" s="8" t="s">
         <v>616</v>
-      </c>
-      <c r="Q33" s="8" t="s">
-        <v>617</v>
       </c>
       <c r="R33" s="8"/>
       <c r="S33" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="U33" s="8" t="s">
         <v>618</v>
-      </c>
-      <c r="U33" s="8" t="s">
-        <v>619</v>
       </c>
       <c r="V33" s="8"/>
       <c r="W33" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="Y33" s="8" t="s">
         <v>620</v>
-      </c>
-      <c r="Y33" s="8" t="s">
-        <v>621</v>
       </c>
       <c r="Z33" s="8"/>
       <c r="AA33" s="8" t="s">
+        <v>621</v>
+      </c>
+      <c r="AC33" s="8" t="s">
         <v>622</v>
-      </c>
-      <c r="AC33" s="8" t="s">
-        <v>623</v>
       </c>
       <c r="AD33" s="8"/>
       <c r="AE33" s="8" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A34" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="E34" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="F34" s="8" t="s">
         <v>628</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="G34" s="8" t="s">
         <v>629</v>
       </c>
-      <c r="G34" s="8" t="s">
+      <c r="I34" s="8" t="s">
         <v>630</v>
       </c>
-      <c r="I34" s="8" t="s">
+      <c r="J34" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="J34" s="8" t="s">
+      <c r="K34" s="8" t="s">
         <v>632</v>
       </c>
-      <c r="K34" s="8" t="s">
+      <c r="M34" s="8" t="s">
         <v>633</v>
-      </c>
-      <c r="M34" s="8" t="s">
-        <v>634</v>
       </c>
       <c r="N34" s="8"/>
       <c r="O34" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="Q34" s="8" t="s">
         <v>635</v>
-      </c>
-      <c r="Q34" s="8" t="s">
-        <v>636</v>
       </c>
       <c r="R34" s="8"/>
       <c r="S34" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="U34" s="8" t="s">
         <v>637</v>
-      </c>
-      <c r="U34" s="8" t="s">
-        <v>638</v>
       </c>
       <c r="V34" s="8"/>
       <c r="W34" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="Y34" s="8" t="s">
         <v>639</v>
-      </c>
-      <c r="Y34" s="8" t="s">
-        <v>640</v>
       </c>
       <c r="Z34" s="8"/>
       <c r="AA34" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="AC34" s="8" t="s">
         <v>641</v>
-      </c>
-      <c r="AC34" s="8" t="s">
-        <v>642</v>
       </c>
       <c r="AD34" s="8"/>
       <c r="AE34" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A35" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="B35" s="8" t="s">
         <v>644</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="C35" s="8" t="s">
         <v>645</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="E35" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="F35" s="8" t="s">
         <v>647</v>
       </c>
-      <c r="F35" s="8" t="s">
+      <c r="G35" s="8" t="s">
         <v>648</v>
       </c>
-      <c r="G35" s="8" t="s">
+      <c r="I35" s="8" t="s">
         <v>649</v>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>650</v>
       </c>
       <c r="J35" s="8"/>
       <c r="K35" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="M35" s="3" t="s">
         <v>651</v>
       </c>
-      <c r="M35" s="3" t="s">
+      <c r="N35" s="3" t="s">
         <v>652</v>
       </c>
-      <c r="N35" s="3" t="s">
+      <c r="O35" s="3" t="s">
         <v>653</v>
       </c>
-      <c r="O35" s="3" t="s">
+      <c r="Q35" s="8" t="s">
         <v>654</v>
       </c>
-      <c r="Q35" s="8" t="s">
+      <c r="R35" s="8" t="s">
         <v>655</v>
       </c>
-      <c r="R35" s="8" t="s">
+      <c r="S35" s="8" t="s">
         <v>656</v>
       </c>
-      <c r="S35" s="8" t="s">
+      <c r="U35" s="8" t="s">
         <v>657</v>
-      </c>
-      <c r="U35" s="8" t="s">
-        <v>658</v>
       </c>
       <c r="V35" s="8"/>
       <c r="W35" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="Y35" s="8" t="s">
         <v>659</v>
-      </c>
-      <c r="Y35" s="8" t="s">
-        <v>660</v>
       </c>
       <c r="Z35" s="8"/>
       <c r="AA35" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="AC35" s="8" t="s">
         <v>661</v>
-      </c>
-      <c r="AC35" s="8" t="s">
-        <v>662</v>
       </c>
       <c r="AD35" s="8"/>
       <c r="AE35" s="8" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A36" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>665</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="E36" s="5" t="s">
         <v>666</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="F36" s="5" t="s">
         <v>667</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="G36" s="5" t="s">
         <v>668</v>
       </c>
-      <c r="G36" s="5" t="s">
+      <c r="I36" s="8" t="s">
         <v>669</v>
-      </c>
-      <c r="I36" s="8" t="s">
-        <v>670</v>
       </c>
       <c r="J36" s="8"/>
       <c r="K36" s="8" t="s">
+        <v>670</v>
+      </c>
+      <c r="M36" s="8" t="s">
         <v>671</v>
       </c>
-      <c r="M36" s="8" t="s">
+      <c r="N36" s="8" t="s">
         <v>672</v>
       </c>
-      <c r="N36" s="8" t="s">
+      <c r="O36" s="8" t="s">
         <v>673</v>
       </c>
-      <c r="O36" s="8" t="s">
+      <c r="Q36" s="8" t="s">
         <v>674</v>
-      </c>
-      <c r="Q36" s="8" t="s">
-        <v>675</v>
       </c>
       <c r="R36" s="8"/>
       <c r="S36" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="U36" s="8" t="s">
         <v>676</v>
-      </c>
-      <c r="U36" s="8" t="s">
-        <v>677</v>
       </c>
       <c r="V36" s="8"/>
       <c r="W36" s="8" t="s">
+        <v>677</v>
+      </c>
+      <c r="Y36" s="8" t="s">
         <v>678</v>
-      </c>
-      <c r="Y36" s="8" t="s">
-        <v>679</v>
       </c>
       <c r="Z36" s="8"/>
       <c r="AA36" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="AC36" s="8" t="s">
         <v>680</v>
-      </c>
-      <c r="AC36" s="8" t="s">
-        <v>681</v>
       </c>
       <c r="AD36" s="8"/>
       <c r="AE36" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A37" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="B37" s="7" t="s">
         <v>683</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="C37" s="7" t="s">
         <v>684</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="E37" s="8" t="s">
         <v>685</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="F37" s="8" t="s">
         <v>686</v>
       </c>
-      <c r="F37" s="8" t="s">
+      <c r="G37" s="8" t="s">
         <v>687</v>
       </c>
-      <c r="G37" s="8" t="s">
+      <c r="I37" s="8" t="s">
         <v>688</v>
-      </c>
-      <c r="I37" s="8" t="s">
-        <v>689</v>
       </c>
       <c r="J37" s="8"/>
       <c r="K37" s="8" t="s">
+        <v>689</v>
+      </c>
+      <c r="M37" s="8" t="s">
         <v>690</v>
-      </c>
-      <c r="M37" s="8" t="s">
-        <v>691</v>
       </c>
       <c r="N37" s="8"/>
       <c r="O37" s="8" t="s">
+        <v>691</v>
+      </c>
+      <c r="Q37" s="8" t="s">
         <v>692</v>
-      </c>
-      <c r="Q37" s="8" t="s">
-        <v>693</v>
       </c>
       <c r="R37" s="8"/>
       <c r="S37" s="8" t="s">
+        <v>693</v>
+      </c>
+      <c r="U37" s="8" t="s">
         <v>694</v>
-      </c>
-      <c r="U37" s="8" t="s">
-        <v>695</v>
       </c>
       <c r="V37" s="8"/>
       <c r="W37" s="8" t="s">
+        <v>695</v>
+      </c>
+      <c r="Y37" s="5" t="s">
         <v>696</v>
       </c>
-      <c r="Y37" s="5" t="s">
+      <c r="Z37" s="5" t="s">
         <v>697</v>
       </c>
-      <c r="Z37" s="5" t="s">
+      <c r="AA37" s="5" t="s">
         <v>698</v>
       </c>
-      <c r="AA37" s="5" t="s">
+      <c r="AC37" s="8" t="s">
         <v>699</v>
-      </c>
-      <c r="AC37" s="8" t="s">
-        <v>700</v>
       </c>
       <c r="AD37" s="8"/>
       <c r="AE37" s="8" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A38" s="8" t="s">
+        <v>701</v>
+      </c>
+      <c r="B38" s="8" t="s">
         <v>702</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="C38" s="8" t="s">
         <v>703</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="E38" s="8" t="s">
         <v>704</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="F38" s="8" t="s">
         <v>705</v>
       </c>
-      <c r="F38" s="8" t="s">
+      <c r="G38" s="8" t="s">
         <v>706</v>
       </c>
-      <c r="G38" s="8" t="s">
+      <c r="I38" s="8" t="s">
         <v>707</v>
       </c>
-      <c r="I38" s="8" t="s">
+      <c r="J38" s="8" t="s">
         <v>708</v>
       </c>
-      <c r="J38" s="8" t="s">
+      <c r="K38" s="8" t="s">
         <v>709</v>
       </c>
-      <c r="K38" s="8" t="s">
+      <c r="M38" s="8" t="s">
         <v>710</v>
       </c>
-      <c r="M38" s="8" t="s">
+      <c r="N38" s="8" t="s">
         <v>711</v>
       </c>
-      <c r="N38" s="8" t="s">
+      <c r="O38" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="O38" s="8" t="s">
+      <c r="Q38" s="8" t="s">
         <v>713</v>
-      </c>
-      <c r="Q38" s="8" t="s">
-        <v>714</v>
       </c>
       <c r="R38" s="8"/>
       <c r="S38" s="8" t="s">
+        <v>714</v>
+      </c>
+      <c r="U38" s="8" t="s">
         <v>715</v>
-      </c>
-      <c r="U38" s="8" t="s">
-        <v>716</v>
       </c>
       <c r="V38" s="8"/>
       <c r="W38" s="8" t="s">
+        <v>716</v>
+      </c>
+      <c r="Y38" s="8" t="s">
         <v>717</v>
-      </c>
-      <c r="Y38" s="8" t="s">
-        <v>718</v>
       </c>
       <c r="Z38" s="8"/>
       <c r="AA38" s="8" t="s">
+        <v>718</v>
+      </c>
+      <c r="AC38" s="8" t="s">
         <v>719</v>
-      </c>
-      <c r="AC38" s="8" t="s">
-        <v>720</v>
       </c>
       <c r="AD38" s="8"/>
       <c r="AE38" s="8" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A39" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>722</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>723</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="E39" s="5" t="s">
         <v>724</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="F39" s="5" t="s">
         <v>725</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="G39" s="5" t="s">
         <v>726</v>
       </c>
-      <c r="G39" s="5" t="s">
+      <c r="I39" s="8" t="s">
         <v>727</v>
-      </c>
-      <c r="I39" s="8" t="s">
-        <v>728</v>
       </c>
       <c r="J39" s="8"/>
       <c r="K39" s="8" t="s">
+        <v>728</v>
+      </c>
+      <c r="M39" s="8" t="s">
         <v>729</v>
-      </c>
-      <c r="M39" s="8" t="s">
-        <v>730</v>
       </c>
       <c r="N39" s="8"/>
       <c r="O39" s="8" t="s">
+        <v>730</v>
+      </c>
+      <c r="Q39" s="8" t="s">
         <v>731</v>
-      </c>
-      <c r="Q39" s="8" t="s">
-        <v>732</v>
       </c>
       <c r="R39" s="8"/>
       <c r="S39" s="8" t="s">
+        <v>732</v>
+      </c>
+      <c r="U39" s="8" t="s">
         <v>733</v>
-      </c>
-      <c r="U39" s="8" t="s">
-        <v>734</v>
       </c>
       <c r="V39" s="8"/>
       <c r="W39" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="Y39" s="8" t="s">
         <v>735</v>
-      </c>
-      <c r="Y39" s="8" t="s">
-        <v>736</v>
       </c>
       <c r="Z39" s="8"/>
       <c r="AA39" s="8" t="s">
+        <v>736</v>
+      </c>
+      <c r="AC39" s="8" t="s">
         <v>737</v>
-      </c>
-      <c r="AC39" s="8" t="s">
-        <v>738</v>
       </c>
       <c r="AD39" s="8"/>
       <c r="AE39" s="8" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A40" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>740</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>741</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="E40" s="8" t="s">
         <v>742</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="F40" s="8" t="s">
         <v>743</v>
       </c>
-      <c r="F40" s="8" t="s">
+      <c r="G40" s="8" t="s">
         <v>744</v>
       </c>
-      <c r="G40" s="8" t="s">
+      <c r="I40" s="3" t="s">
         <v>745</v>
       </c>
-      <c r="I40" s="3" t="s">
+      <c r="J40" s="3" t="s">
         <v>746</v>
       </c>
-      <c r="J40" s="3" t="s">
+      <c r="K40" s="3" t="s">
         <v>747</v>
       </c>
-      <c r="K40" s="3" t="s">
+      <c r="M40" s="8" t="s">
         <v>748</v>
       </c>
-      <c r="M40" s="8" t="s">
+      <c r="N40" s="8" t="s">
         <v>749</v>
       </c>
-      <c r="N40" s="8" t="s">
+      <c r="O40" s="8" t="s">
         <v>750</v>
       </c>
-      <c r="O40" s="8" t="s">
+      <c r="Q40" s="8" t="s">
         <v>751</v>
       </c>
-      <c r="Q40" s="8" t="s">
+      <c r="R40" s="8" t="s">
         <v>752</v>
       </c>
-      <c r="R40" s="8" t="s">
+      <c r="S40" s="8" t="s">
         <v>753</v>
       </c>
-      <c r="S40" s="8" t="s">
+      <c r="U40" s="8" t="s">
         <v>754</v>
-      </c>
-      <c r="U40" s="8" t="s">
-        <v>755</v>
       </c>
       <c r="V40" s="8"/>
       <c r="W40" s="8" t="s">
+        <v>755</v>
+      </c>
+      <c r="Y40" s="8" t="s">
         <v>756</v>
-      </c>
-      <c r="Y40" s="8" t="s">
-        <v>757</v>
       </c>
       <c r="Z40" s="8"/>
       <c r="AA40" s="8" t="s">
+        <v>757</v>
+      </c>
+      <c r="AC40" s="8" t="s">
         <v>758</v>
-      </c>
-      <c r="AC40" s="8" t="s">
-        <v>759</v>
       </c>
       <c r="AD40" s="8"/>
       <c r="AE40" s="8" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A41" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>761</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>762</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="E41" s="8" t="s">
         <v>763</v>
       </c>
-      <c r="E41" s="8" t="s">
+      <c r="F41" s="8" t="s">
         <v>764</v>
       </c>
-      <c r="F41" s="8" t="s">
+      <c r="G41" s="8" t="s">
         <v>765</v>
       </c>
-      <c r="G41" s="8" t="s">
+      <c r="I41" s="8" t="s">
         <v>766</v>
       </c>
-      <c r="I41" s="8" t="s">
+      <c r="J41" s="8" t="s">
         <v>767</v>
       </c>
-      <c r="J41" s="8" t="s">
+      <c r="K41" s="8" t="s">
         <v>768</v>
       </c>
-      <c r="K41" s="8" t="s">
+      <c r="M41" s="8" t="s">
         <v>769</v>
       </c>
-      <c r="M41" s="8" t="s">
+      <c r="N41" s="8" t="s">
         <v>770</v>
       </c>
-      <c r="N41" s="8" t="s">
+      <c r="O41" s="8" t="s">
         <v>771</v>
       </c>
-      <c r="O41" s="8" t="s">
+      <c r="Q41" s="8" t="s">
         <v>772</v>
       </c>
-      <c r="Q41" s="8" t="s">
+      <c r="R41" s="8" t="s">
         <v>773</v>
       </c>
-      <c r="R41" s="8" t="s">
+      <c r="S41" s="8" t="s">
         <v>774</v>
       </c>
-      <c r="S41" s="8" t="s">
+      <c r="U41" s="8" t="s">
         <v>775</v>
-      </c>
-      <c r="U41" s="8" t="s">
-        <v>776</v>
       </c>
       <c r="V41" s="8"/>
       <c r="W41" s="8" t="s">
+        <v>776</v>
+      </c>
+      <c r="Y41" s="8" t="s">
         <v>777</v>
-      </c>
-      <c r="Y41" s="8" t="s">
-        <v>778</v>
       </c>
       <c r="Z41" s="8"/>
       <c r="AA41" s="8" t="s">
+        <v>778</v>
+      </c>
+      <c r="AC41" s="8" t="s">
         <v>779</v>
-      </c>
-      <c r="AC41" s="8" t="s">
-        <v>780</v>
       </c>
       <c r="AD41" s="8"/>
       <c r="AE41" s="8" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A42" s="8" t="s">
+        <v>781</v>
+      </c>
+      <c r="B42" s="8" t="s">
         <v>782</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="C42" s="8" t="s">
         <v>783</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="E42" s="3" t="s">
         <v>784</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="F42" s="3" t="s">
         <v>785</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="G42" s="3" t="s">
         <v>786</v>
       </c>
-      <c r="G42" s="3" t="s">
+      <c r="I42" s="3" t="s">
         <v>787</v>
       </c>
-      <c r="I42" s="3" t="s">
+      <c r="J42" s="3" t="s">
+        <v>1418</v>
+      </c>
+      <c r="K42" s="3" t="s">
         <v>788</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>1425</v>
-      </c>
-      <c r="K42" s="3" t="s">
+      <c r="M42" s="8" t="s">
         <v>789</v>
-      </c>
-      <c r="M42" s="8" t="s">
-        <v>790</v>
       </c>
       <c r="N42" s="8"/>
       <c r="O42" s="8" t="s">
+        <v>790</v>
+      </c>
+      <c r="Q42" s="8" t="s">
         <v>791</v>
       </c>
-      <c r="Q42" s="8" t="s">
+      <c r="R42" s="8" t="s">
         <v>792</v>
       </c>
-      <c r="R42" s="8" t="s">
+      <c r="S42" s="8" t="s">
         <v>793</v>
       </c>
-      <c r="S42" s="8" t="s">
+      <c r="U42" s="8" t="s">
         <v>794</v>
-      </c>
-      <c r="U42" s="8" t="s">
-        <v>795</v>
       </c>
       <c r="V42" s="8"/>
       <c r="W42" s="8" t="s">
+        <v>795</v>
+      </c>
+      <c r="Y42" s="8" t="s">
         <v>796</v>
-      </c>
-      <c r="Y42" s="8" t="s">
-        <v>797</v>
       </c>
       <c r="Z42" s="8"/>
       <c r="AA42" s="8" t="s">
+        <v>797</v>
+      </c>
+      <c r="AC42" s="8" t="s">
         <v>798</v>
-      </c>
-      <c r="AC42" s="8" t="s">
-        <v>799</v>
       </c>
       <c r="AD42" s="8"/>
       <c r="AE42" s="8" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A43" s="5" t="s">
+        <v>800</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>801</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="C43" s="5" t="s">
         <v>802</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="E43" s="5" t="s">
         <v>803</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="F43" s="5" t="s">
         <v>804</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="G43" s="5" t="s">
         <v>805</v>
       </c>
-      <c r="G43" s="5" t="s">
+      <c r="I43" s="8" t="s">
         <v>806</v>
       </c>
-      <c r="I43" s="8" t="s">
+      <c r="J43" s="8" t="s">
         <v>807</v>
       </c>
-      <c r="J43" s="8" t="s">
+      <c r="K43" s="8" t="s">
         <v>808</v>
       </c>
-      <c r="K43" s="8" t="s">
+      <c r="M43" s="8" t="s">
         <v>809</v>
-      </c>
-      <c r="M43" s="8" t="s">
-        <v>810</v>
       </c>
       <c r="N43" s="8"/>
       <c r="O43" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="Q43" s="8" t="s">
         <v>811</v>
-      </c>
-      <c r="Q43" s="8" t="s">
-        <v>812</v>
       </c>
       <c r="R43" s="8"/>
       <c r="S43" s="8" t="s">
+        <v>812</v>
+      </c>
+      <c r="U43" s="8" t="s">
         <v>813</v>
-      </c>
-      <c r="U43" s="8" t="s">
-        <v>814</v>
       </c>
       <c r="V43" s="8"/>
       <c r="W43" s="8" t="s">
+        <v>814</v>
+      </c>
+      <c r="Y43" s="8" t="s">
         <v>815</v>
-      </c>
-      <c r="Y43" s="8" t="s">
-        <v>816</v>
       </c>
       <c r="Z43" s="8"/>
       <c r="AA43" s="8" t="s">
+        <v>816</v>
+      </c>
+      <c r="AC43" s="8" t="s">
         <v>817</v>
-      </c>
-      <c r="AC43" s="8" t="s">
-        <v>818</v>
       </c>
       <c r="AD43" s="8"/>
       <c r="AE43" s="8" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A44" s="3" t="s">
+        <v>819</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>820</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>821</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="E44" s="5" t="s">
         <v>822</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="F44" s="5" t="s">
         <v>823</v>
       </c>
-      <c r="F44" s="5" t="s">
+      <c r="G44" s="5" t="s">
         <v>824</v>
       </c>
-      <c r="G44" s="5" t="s">
+      <c r="I44" s="8" t="s">
         <v>825</v>
       </c>
-      <c r="I44" s="8" t="s">
+      <c r="J44" s="8" t="s">
         <v>826</v>
       </c>
-      <c r="J44" s="8" t="s">
+      <c r="K44" s="8" t="s">
         <v>827</v>
       </c>
-      <c r="K44" s="8" t="s">
+      <c r="M44" s="8" t="s">
         <v>828</v>
       </c>
-      <c r="M44" s="8" t="s">
+      <c r="N44" s="8" t="s">
         <v>829</v>
       </c>
-      <c r="N44" s="8" t="s">
+      <c r="O44" s="8" t="s">
         <v>830</v>
       </c>
-      <c r="O44" s="8" t="s">
+      <c r="Q44" s="8" t="s">
         <v>831</v>
-      </c>
-      <c r="Q44" s="8" t="s">
-        <v>832</v>
       </c>
       <c r="R44" s="8"/>
       <c r="S44" s="8" t="s">
+        <v>832</v>
+      </c>
+      <c r="U44" s="8" t="s">
         <v>833</v>
-      </c>
-      <c r="U44" s="8" t="s">
-        <v>834</v>
       </c>
       <c r="V44" s="8"/>
       <c r="W44" s="8" t="s">
+        <v>834</v>
+      </c>
+      <c r="Y44" s="8" t="s">
         <v>835</v>
-      </c>
-      <c r="Y44" s="8" t="s">
-        <v>836</v>
       </c>
       <c r="Z44" s="8"/>
       <c r="AA44" s="8" t="s">
+        <v>836</v>
+      </c>
+      <c r="AC44" s="8" t="s">
         <v>837</v>
-      </c>
-      <c r="AC44" s="8" t="s">
-        <v>838</v>
       </c>
       <c r="AD44" s="8"/>
       <c r="AE44" s="8" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="45" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A45" s="8" t="s">
+        <v>839</v>
+      </c>
+      <c r="B45" s="8" t="s">
         <v>840</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="C45" s="8" t="s">
         <v>841</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="E45" s="5" t="s">
         <v>842</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="F45" s="5" t="s">
         <v>843</v>
       </c>
-      <c r="F45" s="5" t="s">
+      <c r="G45" s="5" t="s">
         <v>844</v>
       </c>
-      <c r="G45" s="5" t="s">
+      <c r="I45" s="8" t="s">
         <v>845</v>
       </c>
-      <c r="I45" s="8" t="s">
+      <c r="J45" s="8" t="s">
         <v>846</v>
       </c>
-      <c r="J45" s="8" t="s">
+      <c r="K45" s="8" t="s">
         <v>847</v>
       </c>
-      <c r="K45" s="8" t="s">
+      <c r="M45" s="8" t="s">
         <v>848</v>
-      </c>
-      <c r="M45" s="8" t="s">
-        <v>849</v>
       </c>
       <c r="N45" s="8"/>
       <c r="O45" s="8" t="s">
+        <v>849</v>
+      </c>
+      <c r="Q45" s="8" t="s">
         <v>850</v>
-      </c>
-      <c r="Q45" s="8" t="s">
-        <v>851</v>
       </c>
       <c r="R45" s="8"/>
       <c r="S45" s="8" t="s">
+        <v>851</v>
+      </c>
+      <c r="U45" s="8" t="s">
         <v>852</v>
-      </c>
-      <c r="U45" s="8" t="s">
-        <v>853</v>
       </c>
       <c r="V45" s="8"/>
       <c r="W45" s="8" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y45" s="8" t="s">
         <v>854</v>
-      </c>
-      <c r="Y45" s="8" t="s">
-        <v>855</v>
       </c>
       <c r="Z45" s="8"/>
       <c r="AA45" s="8" t="s">
+        <v>855</v>
+      </c>
+      <c r="AC45" s="8" t="s">
         <v>856</v>
-      </c>
-      <c r="AC45" s="8" t="s">
-        <v>857</v>
       </c>
       <c r="AD45" s="8"/>
       <c r="AE45" s="8" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A46" s="3" t="s">
+        <v>858</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>859</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="C46" s="3" t="s">
         <v>860</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="E46" s="8" t="s">
         <v>861</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="F46" s="8" t="s">
         <v>862</v>
       </c>
-      <c r="F46" s="8" t="s">
+      <c r="G46" s="8" t="s">
         <v>863</v>
       </c>
-      <c r="G46" s="8" t="s">
+      <c r="I46" s="8" t="s">
         <v>864</v>
-      </c>
-      <c r="I46" s="8" t="s">
-        <v>865</v>
       </c>
       <c r="J46" s="8"/>
       <c r="K46" s="8" t="s">
+        <v>865</v>
+      </c>
+      <c r="M46" s="8" t="s">
         <v>866</v>
-      </c>
-      <c r="M46" s="8" t="s">
-        <v>867</v>
       </c>
       <c r="N46" s="8"/>
       <c r="O46" s="8" t="s">
+        <v>867</v>
+      </c>
+      <c r="Q46" s="8" t="s">
         <v>868</v>
-      </c>
-      <c r="Q46" s="8" t="s">
-        <v>869</v>
       </c>
       <c r="R46" s="8"/>
       <c r="S46" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="U46" s="8" t="s">
         <v>870</v>
-      </c>
-      <c r="U46" s="8" t="s">
-        <v>871</v>
       </c>
       <c r="V46" s="8"/>
       <c r="W46" s="8" t="s">
+        <v>871</v>
+      </c>
+      <c r="Y46" s="8" t="s">
         <v>872</v>
-      </c>
-      <c r="Y46" s="8" t="s">
-        <v>873</v>
       </c>
       <c r="Z46" s="8"/>
       <c r="AA46" s="8" t="s">
+        <v>873</v>
+      </c>
+      <c r="AC46" s="8" t="s">
         <v>874</v>
-      </c>
-      <c r="AC46" s="8" t="s">
-        <v>875</v>
       </c>
       <c r="AD46" s="8"/>
       <c r="AE46" s="8" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="47" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A47" s="8" t="s">
+        <v>876</v>
+      </c>
+      <c r="B47" s="8" t="s">
         <v>877</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="C47" s="8" t="s">
         <v>878</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="E47" s="8" t="s">
         <v>879</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>880</v>
       </c>
       <c r="F47" s="8"/>
       <c r="G47" s="8" t="s">
+        <v>880</v>
+      </c>
+      <c r="I47" s="8" t="s">
         <v>881</v>
-      </c>
-      <c r="I47" s="8" t="s">
-        <v>882</v>
       </c>
       <c r="J47" s="8"/>
       <c r="K47" s="8" t="s">
+        <v>882</v>
+      </c>
+      <c r="M47" s="8" t="s">
         <v>883</v>
-      </c>
-      <c r="M47" s="8" t="s">
-        <v>884</v>
       </c>
       <c r="N47" s="8"/>
       <c r="O47" s="8" t="s">
+        <v>884</v>
+      </c>
+      <c r="Q47" s="8" t="s">
         <v>885</v>
-      </c>
-      <c r="Q47" s="8" t="s">
-        <v>886</v>
       </c>
       <c r="R47" s="8"/>
       <c r="S47" s="8" t="s">
+        <v>886</v>
+      </c>
+      <c r="U47" s="8" t="s">
         <v>887</v>
-      </c>
-      <c r="U47" s="8" t="s">
-        <v>888</v>
       </c>
       <c r="V47" s="8"/>
       <c r="W47" s="8" t="s">
+        <v>888</v>
+      </c>
+      <c r="Y47" s="8" t="s">
         <v>889</v>
-      </c>
-      <c r="Y47" s="8" t="s">
-        <v>890</v>
       </c>
       <c r="Z47" s="8"/>
       <c r="AA47" s="8" t="s">
+        <v>890</v>
+      </c>
+      <c r="AC47" s="8" t="s">
         <v>891</v>
-      </c>
-      <c r="AC47" s="8" t="s">
-        <v>892</v>
       </c>
       <c r="AD47" s="8"/>
       <c r="AE47" s="8" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="48" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A48" s="8" t="s">
+        <v>893</v>
+      </c>
+      <c r="B48" s="8" t="s">
         <v>894</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="C48" s="8" t="s">
         <v>895</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="E48" s="5" t="s">
         <v>896</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>897</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>67</v>
       </c>
       <c r="G48" s="5" t="s">
+        <v>897</v>
+      </c>
+      <c r="I48" s="8" t="s">
         <v>898</v>
       </c>
-      <c r="I48" s="8" t="s">
+      <c r="J48" s="8" t="s">
+        <v>767</v>
+      </c>
+      <c r="K48" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="J48" s="8" t="s">
-        <v>768</v>
-      </c>
-      <c r="K48" s="8" t="s">
+      <c r="M48" s="8" t="s">
         <v>900</v>
-      </c>
-      <c r="M48" s="8" t="s">
-        <v>901</v>
       </c>
       <c r="N48" s="8"/>
       <c r="O48" s="8" t="s">
+        <v>901</v>
+      </c>
+      <c r="Q48" s="8" t="s">
         <v>902</v>
-      </c>
-      <c r="Q48" s="8" t="s">
-        <v>903</v>
       </c>
       <c r="R48" s="8"/>
       <c r="S48" s="8" t="s">
+        <v>903</v>
+      </c>
+      <c r="U48" s="8" t="s">
         <v>904</v>
-      </c>
-      <c r="U48" s="8" t="s">
-        <v>905</v>
       </c>
       <c r="V48" s="8"/>
       <c r="W48" s="8" t="s">
+        <v>905</v>
+      </c>
+      <c r="Y48" s="8" t="s">
         <v>906</v>
-      </c>
-      <c r="Y48" s="8" t="s">
-        <v>907</v>
       </c>
       <c r="Z48" s="8"/>
       <c r="AA48" s="8" t="s">
+        <v>907</v>
+      </c>
+      <c r="AC48" s="8" t="s">
         <v>908</v>
-      </c>
-      <c r="AC48" s="8" t="s">
-        <v>909</v>
       </c>
       <c r="AD48" s="8"/>
       <c r="AE48" s="8" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="49" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A49" s="8" t="s">
+        <v>910</v>
+      </c>
+      <c r="B49" s="8" t="s">
         <v>911</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="C49" s="8" t="s">
         <v>912</v>
       </c>
-      <c r="C49" s="8" t="s">
+      <c r="E49" s="8" t="s">
         <v>913</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>914</v>
       </c>
       <c r="F49" s="8"/>
       <c r="G49" s="8" t="s">
+        <v>914</v>
+      </c>
+      <c r="I49" s="8" t="s">
         <v>915</v>
       </c>
-      <c r="I49" s="8" t="s">
+      <c r="J49" s="8" t="s">
         <v>916</v>
       </c>
-      <c r="J49" s="8" t="s">
+      <c r="K49" s="8" t="s">
         <v>917</v>
       </c>
-      <c r="K49" s="8" t="s">
+      <c r="M49" s="8" t="s">
         <v>918</v>
-      </c>
-      <c r="M49" s="8" t="s">
-        <v>919</v>
       </c>
       <c r="N49" s="8"/>
       <c r="O49" s="8" t="s">
+        <v>919</v>
+      </c>
+      <c r="Q49" s="8" t="s">
         <v>920</v>
-      </c>
-      <c r="Q49" s="8" t="s">
-        <v>921</v>
       </c>
       <c r="R49" s="8"/>
       <c r="S49" s="8" t="s">
+        <v>921</v>
+      </c>
+      <c r="U49" s="8" t="s">
         <v>922</v>
-      </c>
-      <c r="U49" s="8" t="s">
-        <v>923</v>
       </c>
       <c r="V49" s="8"/>
       <c r="W49" s="8" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y49" s="8" t="s">
         <v>924</v>
-      </c>
-      <c r="Y49" s="8" t="s">
-        <v>925</v>
       </c>
       <c r="Z49" s="8"/>
       <c r="AA49" s="8" t="s">
+        <v>925</v>
+      </c>
+      <c r="AC49" s="8" t="s">
         <v>926</v>
-      </c>
-      <c r="AC49" s="8" t="s">
-        <v>927</v>
       </c>
       <c r="AD49" s="8"/>
       <c r="AE49" s="8" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="50" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A50" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>929</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="C50" s="3" t="s">
         <v>930</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="E50" s="8" t="s">
         <v>931</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="F50" s="8" t="s">
         <v>932</v>
       </c>
-      <c r="F50" s="8" t="s">
+      <c r="G50" s="8" t="s">
         <v>933</v>
       </c>
-      <c r="G50" s="8" t="s">
+      <c r="I50" s="8" t="s">
         <v>934</v>
       </c>
-      <c r="I50" s="8" t="s">
+      <c r="J50" s="8" t="s">
+        <v>1417</v>
+      </c>
+      <c r="K50" s="8" t="s">
         <v>935</v>
       </c>
-      <c r="J50" s="8" t="s">
-        <v>1424</v>
-      </c>
-      <c r="K50" s="8" t="s">
+      <c r="M50" s="8" t="s">
         <v>936</v>
       </c>
-      <c r="M50" s="8" t="s">
+      <c r="N50" s="8" t="s">
         <v>937</v>
       </c>
-      <c r="N50" s="8" t="s">
+      <c r="O50" s="8" t="s">
         <v>938</v>
       </c>
-      <c r="O50" s="8" t="s">
+      <c r="Q50" s="8" t="s">
         <v>939</v>
-      </c>
-      <c r="Q50" s="8" t="s">
-        <v>940</v>
       </c>
       <c r="R50" s="8"/>
       <c r="S50" s="8" t="s">
+        <v>940</v>
+      </c>
+      <c r="U50" s="8" t="s">
         <v>941</v>
-      </c>
-      <c r="U50" s="8" t="s">
-        <v>942</v>
       </c>
       <c r="V50" s="8"/>
       <c r="W50" s="8" t="s">
+        <v>942</v>
+      </c>
+      <c r="Y50" s="8" t="s">
         <v>943</v>
-      </c>
-      <c r="Y50" s="8" t="s">
-        <v>944</v>
       </c>
       <c r="Z50" s="8"/>
       <c r="AA50" s="8" t="s">
+        <v>944</v>
+      </c>
+      <c r="AC50" s="8" t="s">
         <v>945</v>
-      </c>
-      <c r="AC50" s="8" t="s">
-        <v>946</v>
       </c>
       <c r="AD50" s="8"/>
       <c r="AE50" s="8" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="51" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A51" s="8" t="s">
+        <v>947</v>
+      </c>
+      <c r="B51" s="8" t="s">
         <v>948</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="C51" s="8" t="s">
         <v>949</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="E51" s="8" t="s">
         <v>950</v>
       </c>
-      <c r="E51" s="8" t="s">
+      <c r="F51" s="8" t="s">
         <v>951</v>
       </c>
-      <c r="F51" s="8" t="s">
+      <c r="G51" s="8" t="s">
         <v>952</v>
       </c>
-      <c r="G51" s="8" t="s">
+      <c r="I51" s="8" t="s">
         <v>953</v>
       </c>
-      <c r="I51" s="8" t="s">
+      <c r="J51" s="8" t="s">
         <v>954</v>
       </c>
-      <c r="J51" s="8" t="s">
+      <c r="K51" s="8" t="s">
         <v>955</v>
       </c>
-      <c r="K51" s="8" t="s">
+      <c r="M51" s="8" t="s">
         <v>956</v>
-      </c>
-      <c r="M51" s="8" t="s">
-        <v>957</v>
       </c>
       <c r="N51" s="8"/>
       <c r="O51" s="8" t="s">
+        <v>957</v>
+      </c>
+      <c r="Q51" s="8" t="s">
         <v>958</v>
-      </c>
-      <c r="Q51" s="8" t="s">
-        <v>959</v>
       </c>
       <c r="R51" s="8"/>
       <c r="S51" s="8" t="s">
+        <v>959</v>
+      </c>
+      <c r="U51" s="8" t="s">
         <v>960</v>
-      </c>
-      <c r="U51" s="8" t="s">
-        <v>961</v>
       </c>
       <c r="V51" s="8"/>
       <c r="W51" s="8" t="s">
+        <v>961</v>
+      </c>
+      <c r="Y51" s="8" t="s">
         <v>962</v>
-      </c>
-      <c r="Y51" s="8" t="s">
-        <v>963</v>
       </c>
       <c r="Z51" s="8"/>
       <c r="AA51" s="8" t="s">
+        <v>963</v>
+      </c>
+      <c r="AC51" s="8" t="s">
         <v>964</v>
-      </c>
-      <c r="AC51" s="8" t="s">
-        <v>965</v>
       </c>
       <c r="AD51" s="8"/>
       <c r="AE51" s="8" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="52" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A52" s="5" t="s">
+        <v>966</v>
+      </c>
+      <c r="B52" s="5" t="s">
         <v>967</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="C52" s="5" t="s">
         <v>968</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="E52" s="8" t="s">
         <v>969</v>
       </c>
-      <c r="E52" s="8" t="s">
+      <c r="F52" s="8" t="s">
         <v>970</v>
       </c>
-      <c r="F52" s="8" t="s">
+      <c r="G52" s="8" t="s">
         <v>971</v>
       </c>
-      <c r="G52" s="8" t="s">
+      <c r="I52" s="8" t="s">
         <v>972</v>
       </c>
-      <c r="I52" s="8" t="s">
+      <c r="J52" s="8" t="s">
         <v>973</v>
       </c>
-      <c r="J52" s="8" t="s">
+      <c r="K52" s="8" t="s">
         <v>974</v>
       </c>
-      <c r="K52" s="8" t="s">
+      <c r="M52" s="8" t="s">
         <v>975</v>
-      </c>
-      <c r="M52" s="8" t="s">
-        <v>976</v>
       </c>
       <c r="N52" s="8"/>
       <c r="O52" s="8" t="s">
+        <v>976</v>
+      </c>
+      <c r="Q52" s="8" t="s">
         <v>977</v>
-      </c>
-      <c r="Q52" s="8" t="s">
-        <v>978</v>
       </c>
       <c r="R52" s="8"/>
       <c r="S52" s="8" t="s">
+        <v>978</v>
+      </c>
+      <c r="U52" s="8" t="s">
         <v>979</v>
-      </c>
-      <c r="U52" s="8" t="s">
-        <v>980</v>
       </c>
       <c r="V52" s="8"/>
       <c r="W52" s="8" t="s">
+        <v>980</v>
+      </c>
+      <c r="Y52" s="8" t="s">
         <v>981</v>
-      </c>
-      <c r="Y52" s="8" t="s">
-        <v>982</v>
       </c>
       <c r="Z52" s="8"/>
       <c r="AA52" s="8" t="s">
+        <v>982</v>
+      </c>
+      <c r="AC52" s="8" t="s">
         <v>983</v>
-      </c>
-      <c r="AC52" s="8" t="s">
-        <v>984</v>
       </c>
       <c r="AD52" s="8"/>
       <c r="AE52" s="8" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="53" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A53" s="3" t="s">
+        <v>985</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>986</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>987</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="E53" s="8" t="s">
         <v>988</v>
       </c>
-      <c r="E53" s="8" t="s">
+      <c r="F53" s="8" t="s">
         <v>989</v>
       </c>
-      <c r="F53" s="8" t="s">
+      <c r="G53" s="8" t="s">
         <v>990</v>
       </c>
-      <c r="G53" s="8" t="s">
+      <c r="I53" s="5" t="s">
         <v>991</v>
       </c>
-      <c r="I53" s="5" t="s">
+      <c r="J53" s="5" t="s">
         <v>992</v>
       </c>
-      <c r="J53" s="5" t="s">
+      <c r="K53" s="5" t="s">
         <v>993</v>
       </c>
-      <c r="K53" s="5" t="s">
+      <c r="M53" s="8" t="s">
         <v>994</v>
-      </c>
-      <c r="M53" s="8" t="s">
-        <v>995</v>
       </c>
       <c r="N53" s="8"/>
       <c r="O53" s="8" t="s">
+        <v>995</v>
+      </c>
+      <c r="Q53" s="8" t="s">
         <v>996</v>
-      </c>
-      <c r="Q53" s="8" t="s">
-        <v>997</v>
       </c>
       <c r="R53" s="8"/>
       <c r="S53" s="8" t="s">
+        <v>997</v>
+      </c>
+      <c r="U53" s="8" t="s">
         <v>998</v>
-      </c>
-      <c r="U53" s="8" t="s">
-        <v>999</v>
       </c>
       <c r="V53" s="8"/>
       <c r="W53" s="8" t="s">
+        <v>999</v>
+      </c>
+      <c r="Y53" s="8" t="s">
         <v>1000</v>
-      </c>
-      <c r="Y53" s="8" t="s">
-        <v>1001</v>
       </c>
       <c r="Z53" s="8"/>
       <c r="AA53" s="8" t="s">
+        <v>1001</v>
+      </c>
+      <c r="AC53" s="8" t="s">
         <v>1002</v>
-      </c>
-      <c r="AC53" s="8" t="s">
-        <v>1003</v>
       </c>
       <c r="AD53" s="8"/>
       <c r="AE53" s="8" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="54" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A54" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>1005</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>1006</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="E54" s="8" t="s">
         <v>1007</v>
       </c>
-      <c r="E54" s="8" t="s">
+      <c r="F54" s="8" t="s">
         <v>1008</v>
       </c>
-      <c r="F54" s="8" t="s">
+      <c r="G54" s="8" t="s">
         <v>1009</v>
       </c>
-      <c r="G54" s="8" t="s">
+      <c r="I54" s="8" t="s">
         <v>1010</v>
       </c>
-      <c r="I54" s="8" t="s">
+      <c r="J54" s="8" t="s">
         <v>1011</v>
       </c>
-      <c r="J54" s="8" t="s">
+      <c r="K54" s="8" t="s">
         <v>1012</v>
       </c>
-      <c r="K54" s="8" t="s">
+      <c r="M54" s="8" t="s">
         <v>1013</v>
-      </c>
-      <c r="M54" s="8" t="s">
-        <v>1014</v>
       </c>
       <c r="N54" s="8"/>
       <c r="O54" s="8" t="s">
+        <v>1014</v>
+      </c>
+      <c r="Q54" s="8" t="s">
         <v>1015</v>
-      </c>
-      <c r="Q54" s="8" t="s">
-        <v>1016</v>
       </c>
       <c r="R54" s="8"/>
       <c r="S54" s="8" t="s">
+        <v>1016</v>
+      </c>
+      <c r="U54" s="8" t="s">
         <v>1017</v>
-      </c>
-      <c r="U54" s="8" t="s">
-        <v>1018</v>
       </c>
       <c r="V54" s="8"/>
       <c r="W54" s="8" t="s">
+        <v>1018</v>
+      </c>
+      <c r="Y54" s="8" t="s">
         <v>1019</v>
-      </c>
-      <c r="Y54" s="8" t="s">
-        <v>1020</v>
       </c>
       <c r="Z54" s="8"/>
       <c r="AA54" s="8" t="s">
+        <v>1020</v>
+      </c>
+      <c r="AC54" s="8" t="s">
         <v>1021</v>
-      </c>
-      <c r="AC54" s="8" t="s">
-        <v>1022</v>
       </c>
       <c r="AD54" s="8"/>
       <c r="AE54" s="8" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="55" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A55" s="3" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>1024</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="C55" s="3" t="s">
         <v>1025</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="E55" s="3" t="s">
         <v>1026</v>
       </c>
-      <c r="E55" s="3" t="s">
+      <c r="F55" s="3" t="s">
+        <v>1426</v>
+      </c>
+      <c r="G55" s="3" t="s">
         <v>1027</v>
       </c>
-      <c r="F55" s="3" t="s">
-        <v>1423</v>
-      </c>
-      <c r="G55" s="3" t="s">
+      <c r="I55" s="5" t="s">
         <v>1028</v>
       </c>
-      <c r="I55" s="5" t="s">
+      <c r="J55" s="5" t="s">
         <v>1029</v>
       </c>
-      <c r="J55" s="5" t="s">
+      <c r="K55" s="5" t="s">
         <v>1030</v>
       </c>
-      <c r="K55" s="5" t="s">
+      <c r="M55" s="8" t="s">
         <v>1031</v>
-      </c>
-      <c r="M55" s="8" t="s">
-        <v>1032</v>
       </c>
       <c r="N55" s="8"/>
       <c r="O55" s="8" t="s">
+        <v>1032</v>
+      </c>
+      <c r="Q55" s="8" t="s">
         <v>1033</v>
-      </c>
-      <c r="Q55" s="8" t="s">
-        <v>1034</v>
       </c>
       <c r="R55" s="8"/>
       <c r="S55" s="8" t="s">
+        <v>1034</v>
+      </c>
+      <c r="U55" s="8" t="s">
         <v>1035</v>
-      </c>
-      <c r="U55" s="8" t="s">
-        <v>1036</v>
       </c>
       <c r="V55" s="8"/>
       <c r="W55" s="8" t="s">
+        <v>1036</v>
+      </c>
+      <c r="Y55" s="8" t="s">
         <v>1037</v>
-      </c>
-      <c r="Y55" s="8" t="s">
-        <v>1038</v>
       </c>
       <c r="Z55" s="8"/>
       <c r="AA55" s="8" t="s">
+        <v>1038</v>
+      </c>
+      <c r="AC55" s="8" t="s">
         <v>1039</v>
-      </c>
-      <c r="AC55" s="8" t="s">
-        <v>1040</v>
       </c>
       <c r="AD55" s="8"/>
       <c r="AE55" s="8" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="56" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A56" s="3" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>1042</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>1043</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="E56" s="8" t="s">
         <v>1044</v>
       </c>
-      <c r="E56" s="8" t="s">
+      <c r="F56" s="8" t="s">
         <v>1045</v>
       </c>
-      <c r="F56" s="8" t="s">
+      <c r="G56" s="8" t="s">
         <v>1046</v>
       </c>
-      <c r="G56" s="8" t="s">
+      <c r="I56" s="3" t="s">
         <v>1047</v>
       </c>
-      <c r="I56" s="3" t="s">
+      <c r="J56" s="3" t="s">
         <v>1048</v>
       </c>
-      <c r="J56" s="3" t="s">
+      <c r="K56" s="3" t="s">
         <v>1049</v>
       </c>
-      <c r="K56" s="3" t="s">
+      <c r="M56" s="8" t="s">
         <v>1050</v>
-      </c>
-      <c r="M56" s="8" t="s">
-        <v>1051</v>
       </c>
       <c r="N56" s="8"/>
       <c r="O56" s="8" t="s">
+        <v>1051</v>
+      </c>
+      <c r="Q56" s="8" t="s">
         <v>1052</v>
-      </c>
-      <c r="Q56" s="8" t="s">
-        <v>1053</v>
       </c>
       <c r="R56" s="8"/>
       <c r="S56" s="8" t="s">
+        <v>1053</v>
+      </c>
+      <c r="U56" s="8" t="s">
         <v>1054</v>
-      </c>
-      <c r="U56" s="8" t="s">
-        <v>1055</v>
       </c>
       <c r="V56" s="8"/>
       <c r="W56" s="8" t="s">
+        <v>1055</v>
+      </c>
+      <c r="Y56" s="8" t="s">
         <v>1056</v>
-      </c>
-      <c r="Y56" s="8" t="s">
-        <v>1057</v>
       </c>
       <c r="Z56" s="8"/>
       <c r="AA56" s="8" t="s">
+        <v>1057</v>
+      </c>
+      <c r="AC56" s="8" t="s">
         <v>1058</v>
-      </c>
-      <c r="AC56" s="8" t="s">
-        <v>1059</v>
       </c>
       <c r="AD56" s="8"/>
       <c r="AE56" s="8" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="57" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A57" s="3" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>1061</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>1062</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="E57" s="8" t="s">
         <v>1063</v>
       </c>
-      <c r="E57" s="8" t="s">
+      <c r="F57" s="8" t="s">
         <v>1064</v>
       </c>
-      <c r="F57" s="8" t="s">
+      <c r="G57" s="8" t="s">
         <v>1065</v>
-      </c>
-      <c r="G57" s="8" t="s">
-        <v>1066</v>
       </c>
     </row>
     <row r="58" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A58" s="8" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B58" s="8" t="s">
         <v>1067</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="C58" s="8" t="s">
         <v>1068</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>1069</v>
       </c>
     </row>
     <row r="59" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A59" s="8" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B59" s="8" t="s">
         <v>1070</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="C59" s="8" t="s">
         <v>1071</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="60" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A60" s="8" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B60" s="8" t="s">
         <v>1073</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="C60" s="8" t="s">
         <v>1074</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>1075</v>
       </c>
       <c r="E60" s="4"/>
       <c r="F60" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="61" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A61" s="8" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B61" s="8" t="s">
         <v>1077</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="C61" s="8" t="s">
         <v>1078</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>1079</v>
       </c>
     </row>
     <row r="62" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A62" s="8" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B62" s="8" t="s">
         <v>1080</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="C62" s="8" t="s">
         <v>1081</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>1082</v>
       </c>
       <c r="E62" s="6"/>
       <c r="F62" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="63" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A63" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B63" s="8" t="s">
         <v>1084</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="C63" s="8" t="s">
         <v>1085</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="64" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A64" s="8" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B64" s="8" t="s">
         <v>1087</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="C64" s="8" t="s">
         <v>1088</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>1089</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A65" s="3" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>1090</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="C65" s="3" t="s">
         <v>1091</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>1092</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A66" s="8" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B66" s="8" t="s">
         <v>1093</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="C66" s="8" t="s">
         <v>1094</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>1095</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A67" s="8" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B67" s="8"/>
       <c r="C67" s="8" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A68" s="8" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="B68" s="8"/>
       <c r="C68" s="8" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A69" s="8" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B69" s="8" t="s">
         <v>1100</v>
       </c>
-      <c r="B69" s="8" t="s">
+      <c r="C69" s="8" t="s">
         <v>1101</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A70" s="8" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="B70" s="8"/>
       <c r="C70" s="8" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A71" s="8" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B71" s="8" t="s">
         <v>1105</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="C71" s="8" t="s">
         <v>1106</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>1107</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A72" s="7" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B72" s="7" t="s">
         <v>1108</v>
       </c>
-      <c r="B72" s="7" t="s">
+      <c r="C72" s="7" t="s">
         <v>1109</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>1110</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A73" s="5" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B73" s="5" t="s">
         <v>1111</v>
       </c>
-      <c r="B73" s="5" t="s">
+      <c r="C73" s="5" t="s">
         <v>1112</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>1113</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A74" s="5" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B74" s="5" t="s">
         <v>1114</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="C74" s="5" t="s">
         <v>1115</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>1116</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A75" s="3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>1117</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="C75" s="3" t="s">
         <v>1118</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>1119</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A76" s="8" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B76" s="8" t="s">
         <v>1120</v>
       </c>
-      <c r="B76" s="8" t="s">
+      <c r="C76" s="8" t="s">
         <v>1121</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>1122</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A77" s="8" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B77" s="8" t="s">
         <v>1123</v>
       </c>
-      <c r="B77" s="8" t="s">
+      <c r="C77" s="8" t="s">
         <v>1124</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>1125</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A78" s="8" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B78" s="8"/>
       <c r="C78" s="8" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A79" s="3" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>1128</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="C79" s="3" t="s">
         <v>1129</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>1130</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A80" s="8" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B80" s="8" t="s">
         <v>1131</v>
       </c>
-      <c r="B80" s="8" t="s">
+      <c r="C80" s="8" t="s">
         <v>1132</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>1133</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A81" s="5" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B81" s="5" t="s">
         <v>1134</v>
       </c>
-      <c r="B81" s="5" t="s">
+      <c r="C81" s="5" t="s">
         <v>1135</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>1136</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A82" s="5" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B82" s="5" t="s">
         <v>1137</v>
       </c>
-      <c r="B82" s="5" t="s">
+      <c r="C82" s="5" t="s">
         <v>1138</v>
-      </c>
-      <c r="C82" s="5" t="s">
-        <v>1139</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A83" s="3" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>1140</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="C83" s="3" t="s">
         <v>1141</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A84" s="3" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B84" s="3" t="s">
         <v>1143</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="C84" s="3" t="s">
         <v>1144</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>1145</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A85" s="8" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B85" s="8"/>
       <c r="C85" s="8" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A86" s="5" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B86" s="5" t="s">
         <v>1148</v>
       </c>
-      <c r="B86" s="5" t="s">
+      <c r="C86" s="5" t="s">
         <v>1149</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A87" s="8" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B87" s="8" t="s">
         <v>1151</v>
       </c>
-      <c r="B87" s="8" t="s">
+      <c r="C87" s="8" t="s">
         <v>1152</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>1153</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A88" s="8" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B88" s="8"/>
       <c r="C88" s="8" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A89" s="5" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B89" s="5" t="s">
         <v>1156</v>
       </c>
-      <c r="B89" s="5" t="s">
+      <c r="C89" s="5" t="s">
         <v>1157</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>1158</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A90" s="5" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B90" s="5" t="s">
         <v>1159</v>
       </c>
-      <c r="B90" s="5" t="s">
+      <c r="C90" s="5" t="s">
         <v>1160</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>1161</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A91" s="5" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B91" s="5" t="s">
         <v>1162</v>
       </c>
-      <c r="B91" s="5" t="s">
+      <c r="C91" s="5" t="s">
         <v>1163</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>1164</v>
       </c>
     </row>
   </sheetData>
@@ -8955,7 +8950,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C86"/>
+  <dimension ref="A1:C85"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="19.1640625" style="9" bestFit="1" customWidth="1"/>
@@ -8965,953 +8960,942 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1165</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>1166</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1167</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>1172</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>1173</v>
-      </c>
       <c r="C2" s="11" t="s">
-        <v>1344</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>1174</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>1175</v>
-      </c>
       <c r="C3" s="11" t="s">
-        <v>1345</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>1176</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>1177</v>
-      </c>
       <c r="C4" s="11" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>1178</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>1179</v>
-      </c>
       <c r="C5" s="11" t="s">
-        <v>1347</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>1180</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>1181</v>
-      </c>
       <c r="C6" s="11" t="s">
-        <v>1348</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>1182</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>1183</v>
-      </c>
       <c r="C7" s="11" t="s">
-        <v>1349</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A8" s="8" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>1184</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>1185</v>
-      </c>
       <c r="C8" s="11" t="s">
-        <v>1350</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A9" s="8" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>1186</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>1187</v>
-      </c>
       <c r="C9" s="11" t="s">
-        <v>1351</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>1188</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>1189</v>
-      </c>
       <c r="C10" s="11" t="s">
-        <v>1352</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A11" s="8" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>1190</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>1191</v>
-      </c>
       <c r="C11" s="11" t="s">
-        <v>1353</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A12" s="8" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>1192</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>1193</v>
-      </c>
       <c r="C12" s="11" t="s">
-        <v>1354</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>1194</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>1195</v>
-      </c>
       <c r="C13" s="11" t="s">
-        <v>1355</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A14" s="8" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>1196</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>1197</v>
-      </c>
       <c r="C14" s="11" t="s">
-        <v>1356</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A15" s="8" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>1198</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>1199</v>
-      </c>
       <c r="C15" s="11" t="s">
-        <v>1357</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A16" s="8" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>1200</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>1201</v>
-      </c>
       <c r="C16" s="11" t="s">
-        <v>1358</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A17" s="8" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>1202</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>1203</v>
-      </c>
       <c r="C17" s="11" t="s">
-        <v>1359</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A18" s="8" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>1204</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>1205</v>
-      </c>
       <c r="C18" s="11" t="s">
-        <v>1359</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A19" s="8" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B19" s="8" t="s">
         <v>1206</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>1207</v>
-      </c>
       <c r="C19" s="11" t="s">
-        <v>1360</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A20" s="8" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>1208</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>1209</v>
-      </c>
       <c r="C20" s="11" t="s">
-        <v>1361</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>1210</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>1211</v>
-      </c>
       <c r="C21" s="11" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A22" s="8" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B22" s="8" t="s">
         <v>1212</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>1213</v>
-      </c>
       <c r="C22" s="11" t="s">
-        <v>1363</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A23" s="8" t="s">
-        <v>1214</v>
+        <v>1427</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>1215</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>1364</v>
+        <v>1428</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>1429</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A24" s="8" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>1365</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A25" s="8" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>1366</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A26" s="8" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>1367</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A27" s="8" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>1368</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A28" s="8" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>1369</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A29" s="8" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>1370</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A30" s="8" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>1371</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A31" s="8" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>1372</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A32" s="8" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>1373</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A33" s="8" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>1374</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A34" s="8" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>1375</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A35" s="8" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>1376</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A36" s="8" t="s">
-        <v>1429</v>
+        <v>1422</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>1430</v>
+        <v>1423</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>1431</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="8" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>1377</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A38" s="8" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>1378</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A39" s="8" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>1379</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A40" s="8" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>1343</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A41" s="8" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>1380</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A42" s="8" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>1381</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A43" s="8" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>1382</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A44" s="8" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>1383</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A45" s="8" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>1384</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A46" s="8" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>1385</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A47" s="8" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A48" s="8" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>1387</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A49" s="8" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>1388</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A50" s="8" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>1389</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A51" s="8" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>1390</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A52" s="8" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>1391</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A53" s="8" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>1392</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A54" s="8" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>1393</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A55" s="8" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>1394</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A56" s="8" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>1395</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A57" s="8" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>1396</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A58" s="8" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B58" s="8" t="s">
         <v>1168</v>
       </c>
-      <c r="B58" s="8" t="s">
-        <v>1169</v>
-      </c>
       <c r="C58" s="11" t="s">
-        <v>1397</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A59" s="8" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>1398</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A60" s="8" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>1399</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A61" s="8" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>1400</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A62" s="8" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>1401</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A63" s="8" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>1402</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A64" s="8" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>1403</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A65" s="8" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>1404</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A66" s="8" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>1405</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A67" s="8" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>1299</v>
+        <v>1296</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>1406</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A68" s="8" t="s">
-        <v>1426</v>
+        <v>1419</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>1427</v>
+        <v>1420</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>1428</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A69" s="8" t="s">
-        <v>1300</v>
+        <v>1297</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>1407</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A70" s="8" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>1408</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A71" s="8" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>1305</v>
+        <v>1302</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>1409</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A72" s="8" t="s">
-        <v>1306</v>
+        <v>1303</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>1410</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A73" s="8" t="s">
-        <v>1308</v>
+        <v>1305</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>1411</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A74" s="8" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B74" s="8" t="s">
         <v>1170</v>
       </c>
-      <c r="B74" s="8" t="s">
-        <v>1171</v>
-      </c>
       <c r="C74" s="11" t="s">
-        <v>1412</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A75" s="8" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>1413</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A76" s="8" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>1414</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A77" s="8" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>1415</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A78" s="8" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>1416</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A79" s="8" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>1417</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A80" s="8" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>1346</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A81" s="8" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>1418</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A82" s="8" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>1419</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A83" s="8" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>1327</v>
+        <v>1220</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>1400</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A84" s="8" t="s">
-        <v>1328</v>
+        <v>1324</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>1223</v>
+        <v>1325</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>1420</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A85" s="8" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>1330</v>
+        <v>1327</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>1421</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A86" s="8" t="s">
-        <v>1331</v>
-      </c>
-      <c r="B86" s="8" t="s">
-        <v>1332</v>
-      </c>
-      <c r="C86" s="11" t="s">
-        <v>1422</v>
+        <v>1415</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C86">
-    <sortCondition ref="A2:A86"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C85">
+    <sortCondition ref="A2:A85"/>
   </sortState>
   <phoneticPr fontId="1"/>
   <hyperlinks>
@@ -9927,72 +9911,71 @@
     <hyperlink ref="C10" r:id="rId10" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
     <hyperlink ref="C12" r:id="rId11" location="ppxdockshow" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
     <hyperlink ref="C13" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
-    <hyperlink ref="C14" r:id="rId13" display="https://www.digitalvolcano.co.uk/dcdownload_versions.html" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
-    <hyperlink ref="C15" r:id="rId14" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
-    <hyperlink ref="C17" r:id="rId15" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
-    <hyperlink ref="C18" r:id="rId16" xr:uid="{00000000-0004-0000-0100-00000F000000}"/>
-    <hyperlink ref="C19" r:id="rId17" xr:uid="{00000000-0004-0000-0100-000010000000}"/>
-    <hyperlink ref="C20" r:id="rId18" xr:uid="{00000000-0004-0000-0100-000011000000}"/>
-    <hyperlink ref="C21" r:id="rId19" xr:uid="{00000000-0004-0000-0100-000012000000}"/>
-    <hyperlink ref="C22" r:id="rId20" xr:uid="{00000000-0004-0000-0100-000013000000}"/>
-    <hyperlink ref="C23" r:id="rId21" xr:uid="{00000000-0004-0000-0100-000014000000}"/>
-    <hyperlink ref="C24" r:id="rId22" xr:uid="{00000000-0004-0000-0100-000015000000}"/>
-    <hyperlink ref="C25" r:id="rId23" xr:uid="{00000000-0004-0000-0100-000016000000}"/>
-    <hyperlink ref="C26" r:id="rId24" xr:uid="{00000000-0004-0000-0100-000017000000}"/>
-    <hyperlink ref="C27" r:id="rId25" xr:uid="{00000000-0004-0000-0100-000018000000}"/>
-    <hyperlink ref="C28" r:id="rId26" xr:uid="{00000000-0004-0000-0100-000019000000}"/>
-    <hyperlink ref="C29" r:id="rId27" xr:uid="{00000000-0004-0000-0100-00001A000000}"/>
-    <hyperlink ref="C30" r:id="rId28" xr:uid="{00000000-0004-0000-0100-00001B000000}"/>
-    <hyperlink ref="C32" r:id="rId29" xr:uid="{00000000-0004-0000-0100-00001C000000}"/>
-    <hyperlink ref="C33" r:id="rId30" xr:uid="{00000000-0004-0000-0100-00001D000000}"/>
-    <hyperlink ref="C34" r:id="rId31" location="ppxaux" xr:uid="{00000000-0004-0000-0100-00001E000000}"/>
-    <hyperlink ref="C35" r:id="rId32" xr:uid="{00000000-0004-0000-0100-00001F000000}"/>
-    <hyperlink ref="C37" r:id="rId33" xr:uid="{00000000-0004-0000-0100-000020000000}"/>
-    <hyperlink ref="C38" r:id="rId34" xr:uid="{00000000-0004-0000-0100-000021000000}"/>
-    <hyperlink ref="C39" r:id="rId35" xr:uid="{00000000-0004-0000-0100-000022000000}"/>
-    <hyperlink ref="C40" r:id="rId36" xr:uid="{00000000-0004-0000-0100-000023000000}"/>
-    <hyperlink ref="C41" r:id="rId37" xr:uid="{00000000-0004-0000-0100-000024000000}"/>
-    <hyperlink ref="C42" r:id="rId38" xr:uid="{00000000-0004-0000-0100-000025000000}"/>
-    <hyperlink ref="C43" r:id="rId39" xr:uid="{00000000-0004-0000-0100-000026000000}"/>
-    <hyperlink ref="C44" r:id="rId40" xr:uid="{00000000-0004-0000-0100-000027000000}"/>
-    <hyperlink ref="C45" r:id="rId41" xr:uid="{00000000-0004-0000-0100-000028000000}"/>
-    <hyperlink ref="C46" r:id="rId42" xr:uid="{00000000-0004-0000-0100-000029000000}"/>
-    <hyperlink ref="C47" r:id="rId43" xr:uid="{00000000-0004-0000-0100-00002A000000}"/>
-    <hyperlink ref="C48" r:id="rId44" xr:uid="{00000000-0004-0000-0100-00002B000000}"/>
-    <hyperlink ref="C49" r:id="rId45" xr:uid="{00000000-0004-0000-0100-00002C000000}"/>
-    <hyperlink ref="C50" r:id="rId46" xr:uid="{00000000-0004-0000-0100-00002D000000}"/>
-    <hyperlink ref="C52" r:id="rId47" xr:uid="{00000000-0004-0000-0100-00002E000000}"/>
-    <hyperlink ref="C53" r:id="rId48" display="https://www.adobe.com/jp/products/photoshop.html" xr:uid="{00000000-0004-0000-0100-00002F000000}"/>
-    <hyperlink ref="C55" r:id="rId49" xr:uid="{00000000-0004-0000-0100-000030000000}"/>
-    <hyperlink ref="C56" r:id="rId50" xr:uid="{00000000-0004-0000-0100-000031000000}"/>
-    <hyperlink ref="C57" r:id="rId51" xr:uid="{00000000-0004-0000-0100-000032000000}"/>
-    <hyperlink ref="C60" r:id="rId52" xr:uid="{00000000-0004-0000-0100-000033000000}"/>
-    <hyperlink ref="C61" r:id="rId53" xr:uid="{00000000-0004-0000-0100-000034000000}"/>
-    <hyperlink ref="C62" r:id="rId54" xr:uid="{00000000-0004-0000-0100-000035000000}"/>
-    <hyperlink ref="C63" r:id="rId55" xr:uid="{00000000-0004-0000-0100-000036000000}"/>
-    <hyperlink ref="C64" r:id="rId56" xr:uid="{00000000-0004-0000-0100-000037000000}"/>
-    <hyperlink ref="C65" r:id="rId57" xr:uid="{00000000-0004-0000-0100-000039000000}"/>
-    <hyperlink ref="C66" r:id="rId58" xr:uid="{00000000-0004-0000-0100-00003A000000}"/>
-    <hyperlink ref="C67" r:id="rId59" xr:uid="{00000000-0004-0000-0100-00003B000000}"/>
-    <hyperlink ref="C69" r:id="rId60" xr:uid="{00000000-0004-0000-0100-00003C000000}"/>
-    <hyperlink ref="C70" r:id="rId61" xr:uid="{00000000-0004-0000-0100-00003D000000}"/>
-    <hyperlink ref="C71" r:id="rId62" xr:uid="{00000000-0004-0000-0100-00003E000000}"/>
-    <hyperlink ref="C72" r:id="rId63" xr:uid="{00000000-0004-0000-0100-00003F000000}"/>
-    <hyperlink ref="C73" r:id="rId64" xr:uid="{00000000-0004-0000-0100-000040000000}"/>
-    <hyperlink ref="C75" r:id="rId65" xr:uid="{00000000-0004-0000-0100-000041000000}"/>
-    <hyperlink ref="C76" r:id="rId66" xr:uid="{00000000-0004-0000-0100-000042000000}"/>
-    <hyperlink ref="C77" r:id="rId67" xr:uid="{00000000-0004-0000-0100-000043000000}"/>
-    <hyperlink ref="C78" r:id="rId68" xr:uid="{00000000-0004-0000-0100-000044000000}"/>
-    <hyperlink ref="C79" r:id="rId69" xr:uid="{00000000-0004-0000-0100-000045000000}"/>
-    <hyperlink ref="C80" r:id="rId70" xr:uid="{00000000-0004-0000-0100-000046000000}"/>
-    <hyperlink ref="C81" r:id="rId71" xr:uid="{00000000-0004-0000-0100-000047000000}"/>
-    <hyperlink ref="C82" r:id="rId72" xr:uid="{00000000-0004-0000-0100-000048000000}"/>
-    <hyperlink ref="C83" r:id="rId73" xr:uid="{00000000-0004-0000-0100-000049000000}"/>
-    <hyperlink ref="C84" r:id="rId74" xr:uid="{00000000-0004-0000-0100-00004A000000}"/>
-    <hyperlink ref="C85" r:id="rId75" xr:uid="{00000000-0004-0000-0100-00004B000000}"/>
-    <hyperlink ref="C86" r:id="rId76" xr:uid="{00000000-0004-0000-0100-00004C000000}"/>
-    <hyperlink ref="C68" r:id="rId77" xr:uid="{2A5F41B6-B50F-4470-905C-CEE2880AFAC1}"/>
-    <hyperlink ref="C36" r:id="rId78" xr:uid="{9537A5E8-28D7-4E83-A579-0A9EBD1F2E4C}"/>
+    <hyperlink ref="C14" r:id="rId13" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
+    <hyperlink ref="C16" r:id="rId14" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
+    <hyperlink ref="C17" r:id="rId15" xr:uid="{00000000-0004-0000-0100-00000F000000}"/>
+    <hyperlink ref="C18" r:id="rId16" xr:uid="{00000000-0004-0000-0100-000010000000}"/>
+    <hyperlink ref="C19" r:id="rId17" xr:uid="{00000000-0004-0000-0100-000011000000}"/>
+    <hyperlink ref="C20" r:id="rId18" xr:uid="{00000000-0004-0000-0100-000012000000}"/>
+    <hyperlink ref="C21" r:id="rId19" xr:uid="{00000000-0004-0000-0100-000013000000}"/>
+    <hyperlink ref="C22" r:id="rId20" xr:uid="{00000000-0004-0000-0100-000014000000}"/>
+    <hyperlink ref="C24" r:id="rId21" xr:uid="{00000000-0004-0000-0100-000015000000}"/>
+    <hyperlink ref="C25" r:id="rId22" xr:uid="{00000000-0004-0000-0100-000016000000}"/>
+    <hyperlink ref="C26" r:id="rId23" xr:uid="{00000000-0004-0000-0100-000017000000}"/>
+    <hyperlink ref="C27" r:id="rId24" xr:uid="{00000000-0004-0000-0100-000018000000}"/>
+    <hyperlink ref="C28" r:id="rId25" xr:uid="{00000000-0004-0000-0100-000019000000}"/>
+    <hyperlink ref="C29" r:id="rId26" xr:uid="{00000000-0004-0000-0100-00001A000000}"/>
+    <hyperlink ref="C30" r:id="rId27" xr:uid="{00000000-0004-0000-0100-00001B000000}"/>
+    <hyperlink ref="C32" r:id="rId28" xr:uid="{00000000-0004-0000-0100-00001C000000}"/>
+    <hyperlink ref="C33" r:id="rId29" xr:uid="{00000000-0004-0000-0100-00001D000000}"/>
+    <hyperlink ref="C34" r:id="rId30" location="ppxaux" xr:uid="{00000000-0004-0000-0100-00001E000000}"/>
+    <hyperlink ref="C35" r:id="rId31" xr:uid="{00000000-0004-0000-0100-00001F000000}"/>
+    <hyperlink ref="C37" r:id="rId32" xr:uid="{00000000-0004-0000-0100-000020000000}"/>
+    <hyperlink ref="C38" r:id="rId33" xr:uid="{00000000-0004-0000-0100-000021000000}"/>
+    <hyperlink ref="C39" r:id="rId34" xr:uid="{00000000-0004-0000-0100-000022000000}"/>
+    <hyperlink ref="C40" r:id="rId35" xr:uid="{00000000-0004-0000-0100-000023000000}"/>
+    <hyperlink ref="C41" r:id="rId36" xr:uid="{00000000-0004-0000-0100-000024000000}"/>
+    <hyperlink ref="C42" r:id="rId37" xr:uid="{00000000-0004-0000-0100-000025000000}"/>
+    <hyperlink ref="C43" r:id="rId38" xr:uid="{00000000-0004-0000-0100-000026000000}"/>
+    <hyperlink ref="C44" r:id="rId39" xr:uid="{00000000-0004-0000-0100-000027000000}"/>
+    <hyperlink ref="C45" r:id="rId40" xr:uid="{00000000-0004-0000-0100-000028000000}"/>
+    <hyperlink ref="C46" r:id="rId41" xr:uid="{00000000-0004-0000-0100-000029000000}"/>
+    <hyperlink ref="C47" r:id="rId42" xr:uid="{00000000-0004-0000-0100-00002A000000}"/>
+    <hyperlink ref="C48" r:id="rId43" xr:uid="{00000000-0004-0000-0100-00002B000000}"/>
+    <hyperlink ref="C49" r:id="rId44" xr:uid="{00000000-0004-0000-0100-00002C000000}"/>
+    <hyperlink ref="C50" r:id="rId45" xr:uid="{00000000-0004-0000-0100-00002D000000}"/>
+    <hyperlink ref="C52" r:id="rId46" xr:uid="{00000000-0004-0000-0100-00002E000000}"/>
+    <hyperlink ref="C53" r:id="rId47" display="https://www.adobe.com/jp/products/photoshop.html" xr:uid="{00000000-0004-0000-0100-00002F000000}"/>
+    <hyperlink ref="C55" r:id="rId48" xr:uid="{00000000-0004-0000-0100-000030000000}"/>
+    <hyperlink ref="C56" r:id="rId49" xr:uid="{00000000-0004-0000-0100-000031000000}"/>
+    <hyperlink ref="C57" r:id="rId50" xr:uid="{00000000-0004-0000-0100-000032000000}"/>
+    <hyperlink ref="C60" r:id="rId51" xr:uid="{00000000-0004-0000-0100-000033000000}"/>
+    <hyperlink ref="C61" r:id="rId52" xr:uid="{00000000-0004-0000-0100-000034000000}"/>
+    <hyperlink ref="C62" r:id="rId53" xr:uid="{00000000-0004-0000-0100-000035000000}"/>
+    <hyperlink ref="C63" r:id="rId54" xr:uid="{00000000-0004-0000-0100-000036000000}"/>
+    <hyperlink ref="C64" r:id="rId55" xr:uid="{00000000-0004-0000-0100-000037000000}"/>
+    <hyperlink ref="C65" r:id="rId56" xr:uid="{00000000-0004-0000-0100-000039000000}"/>
+    <hyperlink ref="C66" r:id="rId57" xr:uid="{00000000-0004-0000-0100-00003A000000}"/>
+    <hyperlink ref="C67" r:id="rId58" xr:uid="{00000000-0004-0000-0100-00003B000000}"/>
+    <hyperlink ref="C69" r:id="rId59" xr:uid="{00000000-0004-0000-0100-00003C000000}"/>
+    <hyperlink ref="C70" r:id="rId60" xr:uid="{00000000-0004-0000-0100-00003D000000}"/>
+    <hyperlink ref="C71" r:id="rId61" xr:uid="{00000000-0004-0000-0100-00003E000000}"/>
+    <hyperlink ref="C72" r:id="rId62" xr:uid="{00000000-0004-0000-0100-00003F000000}"/>
+    <hyperlink ref="C73" r:id="rId63" xr:uid="{00000000-0004-0000-0100-000040000000}"/>
+    <hyperlink ref="C75" r:id="rId64" xr:uid="{00000000-0004-0000-0100-000041000000}"/>
+    <hyperlink ref="C76" r:id="rId65" xr:uid="{00000000-0004-0000-0100-000042000000}"/>
+    <hyperlink ref="C77" r:id="rId66" xr:uid="{00000000-0004-0000-0100-000043000000}"/>
+    <hyperlink ref="C78" r:id="rId67" xr:uid="{00000000-0004-0000-0100-000044000000}"/>
+    <hyperlink ref="C79" r:id="rId68" xr:uid="{00000000-0004-0000-0100-000046000000}"/>
+    <hyperlink ref="C80" r:id="rId69" xr:uid="{00000000-0004-0000-0100-000047000000}"/>
+    <hyperlink ref="C81" r:id="rId70" xr:uid="{00000000-0004-0000-0100-000048000000}"/>
+    <hyperlink ref="C82" r:id="rId71" xr:uid="{00000000-0004-0000-0100-000049000000}"/>
+    <hyperlink ref="C83" r:id="rId72" xr:uid="{00000000-0004-0000-0100-00004A000000}"/>
+    <hyperlink ref="C84" r:id="rId73" xr:uid="{00000000-0004-0000-0100-00004B000000}"/>
+    <hyperlink ref="C85" r:id="rId74" xr:uid="{00000000-0004-0000-0100-00004C000000}"/>
+    <hyperlink ref="C68" r:id="rId75" xr:uid="{2A5F41B6-B50F-4470-905C-CEE2880AFAC1}"/>
+    <hyperlink ref="C36" r:id="rId76" xr:uid="{9537A5E8-28D7-4E83-A579-0A9EBD1F2E4C}"/>
+    <hyperlink ref="C23" r:id="rId77" xr:uid="{CE3C87E8-1595-4C10-A771-26A85F43B0BB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
@@ -10011,46 +9994,46 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
-        <v>1333</v>
+        <v>1328</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1166</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1167</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
-        <v>1334</v>
+        <v>1329</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1335</v>
+        <v>1330</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1336</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
-        <v>1337</v>
+        <v>1332</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1338</v>
+        <v>1333</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>1339</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
-        <v>1340</v>
+        <v>1335</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1341</v>
+        <v>1336</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1342</v>
+        <v>1337</v>
       </c>
     </row>
   </sheetData>
